--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.09166</v>
+        <v>3.18648</v>
       </c>
       <c r="C2" t="n">
-        <v>3.02829</v>
+        <v>3.89968</v>
       </c>
       <c r="D2" t="n">
-        <v>8.429209999999999</v>
+        <v>8.095470000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.56033</v>
+        <v>2.54098</v>
       </c>
       <c r="F2" t="n">
-        <v>2.75279</v>
+        <v>2.57124</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.19064</v>
+        <v>3.28563</v>
       </c>
       <c r="C3" t="n">
-        <v>3.17106</v>
+        <v>4.0788</v>
       </c>
       <c r="D3" t="n">
-        <v>8.63617</v>
+        <v>8.435320000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2.60242</v>
+        <v>2.59016</v>
       </c>
       <c r="F3" t="n">
-        <v>2.78491</v>
+        <v>2.61995</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.3419</v>
+        <v>3.44089</v>
       </c>
       <c r="C4" t="n">
-        <v>3.36659</v>
+        <v>4.37172</v>
       </c>
       <c r="D4" t="n">
-        <v>9.055730000000001</v>
+        <v>8.68529</v>
       </c>
       <c r="E4" t="n">
-        <v>2.69715</v>
+        <v>2.67606</v>
       </c>
       <c r="F4" t="n">
-        <v>2.87868</v>
+        <v>2.72776</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.63434</v>
+        <v>3.69568</v>
       </c>
       <c r="C5" t="n">
-        <v>3.70317</v>
+        <v>4.71365</v>
       </c>
       <c r="D5" t="n">
-        <v>9.50262</v>
+        <v>9.20435</v>
       </c>
       <c r="E5" t="n">
-        <v>2.81358</v>
+        <v>2.80126</v>
       </c>
       <c r="F5" t="n">
-        <v>2.99418</v>
+        <v>2.85774</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.38628</v>
+        <v>4.42947</v>
       </c>
       <c r="C6" t="n">
-        <v>4.51167</v>
+        <v>5.44357</v>
       </c>
       <c r="D6" t="n">
-        <v>9.95106</v>
+        <v>9.5044</v>
       </c>
       <c r="E6" t="n">
-        <v>3.01452</v>
+        <v>2.99914</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2273</v>
+        <v>3.10445</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>5.71346</v>
+        <v>6.08509</v>
       </c>
       <c r="C7" t="n">
-        <v>6.02251</v>
+        <v>6.57045</v>
       </c>
       <c r="D7" t="n">
-        <v>7.13238</v>
+        <v>6.93207</v>
       </c>
       <c r="E7" t="n">
-        <v>3.47834</v>
+        <v>3.47941</v>
       </c>
       <c r="F7" t="n">
-        <v>3.62555</v>
+        <v>3.4996</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>7.99355</v>
+        <v>8.369820000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>8.050459999999999</v>
+        <v>3.48875</v>
       </c>
       <c r="D8" t="n">
-        <v>7.50918</v>
+        <v>7.26995</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4146</v>
+        <v>4.44528</v>
       </c>
       <c r="F8" t="n">
-        <v>4.60269</v>
+        <v>4.48087</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>11.3665</v>
+        <v>11.8241</v>
       </c>
       <c r="C9" t="n">
-        <v>11.0238</v>
+        <v>3.50315</v>
       </c>
       <c r="D9" t="n">
-        <v>7.82113</v>
+        <v>7.61047</v>
       </c>
       <c r="E9" t="n">
-        <v>2.37931</v>
+        <v>2.38303</v>
       </c>
       <c r="F9" t="n">
-        <v>2.55471</v>
+        <v>2.38992</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.9181</v>
+        <v>2.95073</v>
       </c>
       <c r="C10" t="n">
-        <v>2.83009</v>
+        <v>3.53653</v>
       </c>
       <c r="D10" t="n">
-        <v>8.13949</v>
+        <v>7.92044</v>
       </c>
       <c r="E10" t="n">
-        <v>2.39322</v>
+        <v>2.3999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.57506</v>
+        <v>2.41211</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.94658</v>
+        <v>3.00061</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8434</v>
+        <v>3.54649</v>
       </c>
       <c r="D11" t="n">
-        <v>8.472759999999999</v>
+        <v>8.24835</v>
       </c>
       <c r="E11" t="n">
-        <v>2.41458</v>
+        <v>2.40622</v>
       </c>
       <c r="F11" t="n">
-        <v>2.59061</v>
+        <v>2.42601</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.97537</v>
+        <v>3.03733</v>
       </c>
       <c r="C12" t="n">
-        <v>2.89423</v>
+        <v>3.6021</v>
       </c>
       <c r="D12" t="n">
-        <v>8.86173</v>
+        <v>8.58352</v>
       </c>
       <c r="E12" t="n">
-        <v>2.45688</v>
+        <v>2.45306</v>
       </c>
       <c r="F12" t="n">
-        <v>2.62772</v>
+        <v>2.46338</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.02671</v>
+        <v>3.0559</v>
       </c>
       <c r="C13" t="n">
-        <v>2.94857</v>
+        <v>3.62457</v>
       </c>
       <c r="D13" t="n">
-        <v>9.08306</v>
+        <v>8.852980000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.47142</v>
+        <v>2.4782</v>
       </c>
       <c r="F13" t="n">
-        <v>2.65239</v>
+        <v>2.47981</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.0997</v>
+        <v>3.10711</v>
       </c>
       <c r="C14" t="n">
-        <v>3.01986</v>
+        <v>3.68121</v>
       </c>
       <c r="D14" t="n">
-        <v>9.39499</v>
+        <v>9.178610000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.49982</v>
+        <v>2.49465</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6839</v>
+        <v>2.53289</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.14731</v>
+        <v>3.15751</v>
       </c>
       <c r="C15" t="n">
-        <v>3.13167</v>
+        <v>3.77806</v>
       </c>
       <c r="D15" t="n">
-        <v>9.686629999999999</v>
+        <v>9.48086</v>
       </c>
       <c r="E15" t="n">
-        <v>2.55495</v>
+        <v>2.54947</v>
       </c>
       <c r="F15" t="n">
-        <v>2.73256</v>
+        <v>2.58078</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.286</v>
+        <v>3.25305</v>
       </c>
       <c r="C16" t="n">
-        <v>3.2319</v>
+        <v>3.89873</v>
       </c>
       <c r="D16" t="n">
-        <v>10.0119</v>
+        <v>9.778079999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.62419</v>
+        <v>2.61317</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7965</v>
+        <v>2.63847</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.439</v>
+        <v>3.42946</v>
       </c>
       <c r="C17" t="n">
-        <v>3.42203</v>
+        <v>4.06091</v>
       </c>
       <c r="D17" t="n">
-        <v>10.3058</v>
+        <v>10.0877</v>
       </c>
       <c r="E17" t="n">
-        <v>2.70071</v>
+        <v>2.68788</v>
       </c>
       <c r="F17" t="n">
-        <v>2.87683</v>
+        <v>2.73446</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.74857</v>
+        <v>3.64313</v>
       </c>
       <c r="C18" t="n">
-        <v>3.68963</v>
+        <v>4.31572</v>
       </c>
       <c r="D18" t="n">
-        <v>10.5761</v>
+        <v>10.3961</v>
       </c>
       <c r="E18" t="n">
-        <v>2.78079</v>
+        <v>2.75886</v>
       </c>
       <c r="F18" t="n">
-        <v>2.96562</v>
+        <v>2.82093</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.2103</v>
+        <v>4.11165</v>
       </c>
       <c r="C19" t="n">
-        <v>4.18412</v>
+        <v>4.72944</v>
       </c>
       <c r="D19" t="n">
-        <v>10.9608</v>
+        <v>10.7232</v>
       </c>
       <c r="E19" t="n">
-        <v>2.91179</v>
+        <v>2.90496</v>
       </c>
       <c r="F19" t="n">
-        <v>3.10534</v>
+        <v>2.98193</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.94951</v>
+        <v>4.92975</v>
       </c>
       <c r="C20" t="n">
-        <v>4.9142</v>
+        <v>5.35635</v>
       </c>
       <c r="D20" t="n">
-        <v>11.2792</v>
+        <v>11.0231</v>
       </c>
       <c r="E20" t="n">
-        <v>3.16917</v>
+        <v>3.14402</v>
       </c>
       <c r="F20" t="n">
-        <v>3.37282</v>
+        <v>3.24826</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.10996</v>
+        <v>6.24936</v>
       </c>
       <c r="C21" t="n">
-        <v>6.26294</v>
+        <v>6.50235</v>
       </c>
       <c r="D21" t="n">
-        <v>8.30109</v>
+        <v>8.068049999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>3.64559</v>
+        <v>3.6374</v>
       </c>
       <c r="F21" t="n">
-        <v>3.84013</v>
+        <v>3.74503</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>8.221299999999999</v>
+        <v>8.15361</v>
       </c>
       <c r="C22" t="n">
-        <v>8.127269999999999</v>
+        <v>3.53798</v>
       </c>
       <c r="D22" t="n">
-        <v>8.60014</v>
+        <v>8.33433</v>
       </c>
       <c r="E22" t="n">
-        <v>4.78178</v>
+        <v>4.77558</v>
       </c>
       <c r="F22" t="n">
-        <v>4.96652</v>
+        <v>4.84967</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>10.9127</v>
+        <v>10.9975</v>
       </c>
       <c r="C23" t="n">
-        <v>10.8554</v>
+        <v>3.53948</v>
       </c>
       <c r="D23" t="n">
-        <v>8.883660000000001</v>
+        <v>8.613770000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4185</v>
+        <v>2.4239</v>
       </c>
       <c r="F23" t="n">
-        <v>2.61845</v>
+        <v>2.49831</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.99258</v>
+        <v>2.99095</v>
       </c>
       <c r="C24" t="n">
-        <v>3.03545</v>
+        <v>3.56594</v>
       </c>
       <c r="D24" t="n">
-        <v>9.220879999999999</v>
+        <v>8.94589</v>
       </c>
       <c r="E24" t="n">
-        <v>2.44426</v>
+        <v>2.43766</v>
       </c>
       <c r="F24" t="n">
-        <v>2.65063</v>
+        <v>2.53614</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.04958</v>
+        <v>3.052</v>
       </c>
       <c r="C25" t="n">
-        <v>3.10641</v>
+        <v>3.6446</v>
       </c>
       <c r="D25" t="n">
-        <v>9.513170000000001</v>
+        <v>9.26239</v>
       </c>
       <c r="E25" t="n">
-        <v>2.45905</v>
+        <v>2.46045</v>
       </c>
       <c r="F25" t="n">
-        <v>2.69599</v>
+        <v>2.57452</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.12669</v>
+        <v>3.12433</v>
       </c>
       <c r="C26" t="n">
-        <v>3.19945</v>
+        <v>3.6334</v>
       </c>
       <c r="D26" t="n">
-        <v>9.781840000000001</v>
+        <v>9.528119999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.49148</v>
+        <v>2.48907</v>
       </c>
       <c r="F26" t="n">
-        <v>2.74539</v>
+        <v>2.63938</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.15445</v>
+        <v>3.14605</v>
       </c>
       <c r="C27" t="n">
-        <v>3.29324</v>
+        <v>3.69886</v>
       </c>
       <c r="D27" t="n">
-        <v>10.1005</v>
+        <v>9.858449999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>2.53048</v>
+        <v>2.52012</v>
       </c>
       <c r="F27" t="n">
-        <v>2.81423</v>
+        <v>2.70166</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.21746</v>
+        <v>3.20416</v>
       </c>
       <c r="C28" t="n">
-        <v>3.381</v>
+        <v>3.73932</v>
       </c>
       <c r="D28" t="n">
-        <v>10.361</v>
+        <v>10.136</v>
       </c>
       <c r="E28" t="n">
-        <v>2.57212</v>
+        <v>2.56364</v>
       </c>
       <c r="F28" t="n">
-        <v>2.88426</v>
+        <v>2.78613</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.31451</v>
+        <v>3.32775</v>
       </c>
       <c r="C29" t="n">
-        <v>3.49717</v>
+        <v>3.85849</v>
       </c>
       <c r="D29" t="n">
-        <v>10.6872</v>
+        <v>10.421</v>
       </c>
       <c r="E29" t="n">
-        <v>2.62851</v>
+        <v>2.63398</v>
       </c>
       <c r="F29" t="n">
-        <v>2.97889</v>
+        <v>2.88469</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.47775</v>
+        <v>3.45204</v>
       </c>
       <c r="C30" t="n">
-        <v>3.63826</v>
+        <v>3.95452</v>
       </c>
       <c r="D30" t="n">
-        <v>10.9766</v>
+        <v>10.7574</v>
       </c>
       <c r="E30" t="n">
-        <v>2.69827</v>
+        <v>2.68463</v>
       </c>
       <c r="F30" t="n">
-        <v>3.03938</v>
+        <v>2.94245</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.6895</v>
+        <v>3.61782</v>
       </c>
       <c r="C31" t="n">
-        <v>3.83303</v>
+        <v>4.08934</v>
       </c>
       <c r="D31" t="n">
-        <v>11.2745</v>
+        <v>10.9891</v>
       </c>
       <c r="E31" t="n">
-        <v>2.77436</v>
+        <v>2.77039</v>
       </c>
       <c r="F31" t="n">
-        <v>3.14583</v>
+        <v>3.06043</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.9517</v>
+        <v>3.98443</v>
       </c>
       <c r="C32" t="n">
-        <v>4.10579</v>
+        <v>4.3836</v>
       </c>
       <c r="D32" t="n">
-        <v>11.4936</v>
+        <v>11.2329</v>
       </c>
       <c r="E32" t="n">
-        <v>2.86109</v>
+        <v>2.85436</v>
       </c>
       <c r="F32" t="n">
-        <v>3.22875</v>
+        <v>3.1357</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.47943</v>
+        <v>4.47963</v>
       </c>
       <c r="C33" t="n">
-        <v>4.50772</v>
+        <v>4.67767</v>
       </c>
       <c r="D33" t="n">
-        <v>11.85</v>
+        <v>11.5575</v>
       </c>
       <c r="E33" t="n">
-        <v>3.00439</v>
+        <v>2.97049</v>
       </c>
       <c r="F33" t="n">
-        <v>3.36988</v>
+        <v>3.2846</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.08572</v>
+        <v>5.15243</v>
       </c>
       <c r="C34" t="n">
-        <v>5.27083</v>
+        <v>5.34801</v>
       </c>
       <c r="D34" t="n">
-        <v>12.0975</v>
+        <v>11.8391</v>
       </c>
       <c r="E34" t="n">
-        <v>3.23867</v>
+        <v>3.23963</v>
       </c>
       <c r="F34" t="n">
-        <v>3.62111</v>
+        <v>3.53025</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>6.16078</v>
+        <v>6.2606</v>
       </c>
       <c r="C35" t="n">
-        <v>6.28418</v>
+        <v>6.39624</v>
       </c>
       <c r="D35" t="n">
-        <v>8.68943</v>
+        <v>8.47939</v>
       </c>
       <c r="E35" t="n">
-        <v>3.70482</v>
+        <v>3.71952</v>
       </c>
       <c r="F35" t="n">
-        <v>4.06867</v>
+        <v>3.97359</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.75892</v>
+        <v>7.99228</v>
       </c>
       <c r="C36" t="n">
-        <v>7.83999</v>
+        <v>8.05199</v>
       </c>
       <c r="D36" t="n">
-        <v>8.99624</v>
+        <v>8.683059999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>4.52206</v>
+        <v>4.55002</v>
       </c>
       <c r="F36" t="n">
-        <v>4.8292</v>
+        <v>4.75406</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>10.4897</v>
+        <v>10.5864</v>
       </c>
       <c r="C37" t="n">
-        <v>10.3882</v>
+        <v>3.5888</v>
       </c>
       <c r="D37" t="n">
-        <v>9.29866</v>
+        <v>8.996829999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>2.47992</v>
+        <v>2.47394</v>
       </c>
       <c r="F37" t="n">
-        <v>2.80649</v>
+        <v>2.68978</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>3.0497</v>
+        <v>3.05217</v>
       </c>
       <c r="C38" t="n">
-        <v>3.24851</v>
+        <v>3.62686</v>
       </c>
       <c r="D38" t="n">
-        <v>9.60995</v>
+        <v>9.40493</v>
       </c>
       <c r="E38" t="n">
-        <v>2.51061</v>
+        <v>2.50123</v>
       </c>
       <c r="F38" t="n">
-        <v>2.84596</v>
+        <v>2.72784</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.08418</v>
+        <v>3.10884</v>
       </c>
       <c r="C39" t="n">
-        <v>3.30773</v>
+        <v>3.66048</v>
       </c>
       <c r="D39" t="n">
-        <v>9.93539</v>
+        <v>9.659369999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>2.53635</v>
+        <v>2.52225</v>
       </c>
       <c r="F39" t="n">
-        <v>2.88398</v>
+        <v>2.77399</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.15047</v>
+        <v>3.14686</v>
       </c>
       <c r="C40" t="n">
-        <v>3.37799</v>
+        <v>3.69819</v>
       </c>
       <c r="D40" t="n">
-        <v>10.2621</v>
+        <v>9.97176</v>
       </c>
       <c r="E40" t="n">
-        <v>2.56279</v>
+        <v>2.55662</v>
       </c>
       <c r="F40" t="n">
-        <v>2.91164</v>
+        <v>2.7983</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.22569</v>
+        <v>3.21213</v>
       </c>
       <c r="C41" t="n">
-        <v>3.46571</v>
+        <v>3.72784</v>
       </c>
       <c r="D41" t="n">
-        <v>10.5235</v>
+        <v>10.2442</v>
       </c>
       <c r="E41" t="n">
-        <v>2.59129</v>
+        <v>2.58322</v>
       </c>
       <c r="F41" t="n">
-        <v>2.95297</v>
+        <v>2.85138</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.28534</v>
+        <v>3.29809</v>
       </c>
       <c r="C42" t="n">
-        <v>3.54148</v>
+        <v>3.75103</v>
       </c>
       <c r="D42" t="n">
-        <v>10.8697</v>
+        <v>10.5407</v>
       </c>
       <c r="E42" t="n">
-        <v>2.63713</v>
+        <v>2.62675</v>
       </c>
       <c r="F42" t="n">
-        <v>2.99946</v>
+        <v>2.89505</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.42657</v>
+        <v>3.4193</v>
       </c>
       <c r="C43" t="n">
-        <v>3.65678</v>
+        <v>3.89511</v>
       </c>
       <c r="D43" t="n">
-        <v>11.1611</v>
+        <v>10.8225</v>
       </c>
       <c r="E43" t="n">
-        <v>2.67362</v>
+        <v>2.66867</v>
       </c>
       <c r="F43" t="n">
-        <v>3.06157</v>
+        <v>2.96407</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.54839</v>
+        <v>3.5658</v>
       </c>
       <c r="C44" t="n">
-        <v>3.83359</v>
+        <v>4.02037</v>
       </c>
       <c r="D44" t="n">
-        <v>11.4378</v>
+        <v>11.1015</v>
       </c>
       <c r="E44" t="n">
-        <v>2.75364</v>
+        <v>2.74032</v>
       </c>
       <c r="F44" t="n">
-        <v>3.12659</v>
+        <v>3.04407</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.78546</v>
+        <v>3.75946</v>
       </c>
       <c r="C45" t="n">
-        <v>3.99647</v>
+        <v>4.13223</v>
       </c>
       <c r="D45" t="n">
-        <v>11.7231</v>
+        <v>11.3876</v>
       </c>
       <c r="E45" t="n">
-        <v>2.81412</v>
+        <v>2.81369</v>
       </c>
       <c r="F45" t="n">
-        <v>3.19989</v>
+        <v>3.11577</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.10342</v>
+        <v>4.10492</v>
       </c>
       <c r="C46" t="n">
-        <v>4.3503</v>
+        <v>4.34205</v>
       </c>
       <c r="D46" t="n">
-        <v>12.0454</v>
+        <v>11.6497</v>
       </c>
       <c r="E46" t="n">
-        <v>2.92004</v>
+        <v>2.91593</v>
       </c>
       <c r="F46" t="n">
-        <v>3.32128</v>
+        <v>3.23961</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.57911</v>
+        <v>4.45626</v>
       </c>
       <c r="C47" t="n">
-        <v>4.74967</v>
+        <v>4.68692</v>
       </c>
       <c r="D47" t="n">
-        <v>12.2523</v>
+        <v>11.909</v>
       </c>
       <c r="E47" t="n">
-        <v>3.08025</v>
+        <v>3.05803</v>
       </c>
       <c r="F47" t="n">
-        <v>3.48294</v>
+        <v>3.38599</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.2219</v>
+        <v>5.11526</v>
       </c>
       <c r="C48" t="n">
-        <v>5.40381</v>
+        <v>5.28284</v>
       </c>
       <c r="D48" t="n">
-        <v>12.6381</v>
+        <v>12.2282</v>
       </c>
       <c r="E48" t="n">
-        <v>3.32909</v>
+        <v>3.32911</v>
       </c>
       <c r="F48" t="n">
-        <v>3.71395</v>
+        <v>3.6477</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.17705</v>
+        <v>6.05104</v>
       </c>
       <c r="C49" t="n">
-        <v>6.26867</v>
+        <v>6.11846</v>
       </c>
       <c r="D49" t="n">
-        <v>12.8718</v>
+        <v>12.4841</v>
       </c>
       <c r="E49" t="n">
-        <v>3.73831</v>
+        <v>3.74204</v>
       </c>
       <c r="F49" t="n">
-        <v>4.11902</v>
+        <v>4.01974</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>7.60404</v>
+        <v>7.48574</v>
       </c>
       <c r="C50" t="n">
-        <v>7.80236</v>
+        <v>7.41536</v>
       </c>
       <c r="D50" t="n">
-        <v>9.115410000000001</v>
+        <v>8.78195</v>
       </c>
       <c r="E50" t="n">
-        <v>4.36676</v>
+        <v>4.37411</v>
       </c>
       <c r="F50" t="n">
-        <v>4.6827</v>
+        <v>4.61566</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>9.96654</v>
+        <v>9.700480000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>9.92422</v>
+        <v>3.59919</v>
       </c>
       <c r="D51" t="n">
-        <v>9.440289999999999</v>
+        <v>9.110659999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>2.53255</v>
+        <v>2.52349</v>
       </c>
       <c r="F51" t="n">
-        <v>2.89868</v>
+        <v>2.7786</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>13.2199</v>
+        <v>13.1</v>
       </c>
       <c r="C52" t="n">
-        <v>13.1605</v>
+        <v>3.61925</v>
       </c>
       <c r="D52" t="n">
-        <v>9.778930000000001</v>
+        <v>9.456580000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>2.54993</v>
+        <v>2.55356</v>
       </c>
       <c r="F52" t="n">
-        <v>2.93219</v>
+        <v>2.82397</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.10577</v>
+        <v>3.12214</v>
       </c>
       <c r="C53" t="n">
-        <v>3.40716</v>
+        <v>3.66026</v>
       </c>
       <c r="D53" t="n">
-        <v>10.0792</v>
+        <v>9.754530000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>2.57117</v>
+        <v>2.57809</v>
       </c>
       <c r="F53" t="n">
-        <v>2.96486</v>
+        <v>2.85327</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.16368</v>
+        <v>3.18617</v>
       </c>
       <c r="C54" t="n">
-        <v>3.50247</v>
+        <v>3.7129</v>
       </c>
       <c r="D54" t="n">
-        <v>10.3945</v>
+        <v>10.0736</v>
       </c>
       <c r="E54" t="n">
-        <v>2.61808</v>
+        <v>2.60571</v>
       </c>
       <c r="F54" t="n">
-        <v>3.01968</v>
+        <v>2.89568</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.23684</v>
+        <v>3.24967</v>
       </c>
       <c r="C55" t="n">
-        <v>3.61284</v>
+        <v>3.75022</v>
       </c>
       <c r="D55" t="n">
-        <v>10.7216</v>
+        <v>10.4142</v>
       </c>
       <c r="E55" t="n">
-        <v>2.65034</v>
+        <v>2.63809</v>
       </c>
       <c r="F55" t="n">
-        <v>3.06139</v>
+        <v>2.95029</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.3303</v>
+        <v>3.34007</v>
       </c>
       <c r="C56" t="n">
-        <v>3.64726</v>
+        <v>3.8326</v>
       </c>
       <c r="D56" t="n">
-        <v>10.9962</v>
+        <v>10.7023</v>
       </c>
       <c r="E56" t="n">
-        <v>2.70266</v>
+        <v>2.68172</v>
       </c>
       <c r="F56" t="n">
-        <v>3.11844</v>
+        <v>2.99911</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.41012</v>
+        <v>3.44038</v>
       </c>
       <c r="C57" t="n">
-        <v>3.79006</v>
+        <v>3.90581</v>
       </c>
       <c r="D57" t="n">
-        <v>11.3014</v>
+        <v>10.9816</v>
       </c>
       <c r="E57" t="n">
-        <v>2.74957</v>
+        <v>2.73197</v>
       </c>
       <c r="F57" t="n">
-        <v>3.1523</v>
+        <v>3.06865</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.5595</v>
+        <v>3.60207</v>
       </c>
       <c r="C58" t="n">
-        <v>3.91702</v>
+        <v>4.02277</v>
       </c>
       <c r="D58" t="n">
-        <v>11.5888</v>
+        <v>11.2544</v>
       </c>
       <c r="E58" t="n">
-        <v>2.81214</v>
+        <v>2.78691</v>
       </c>
       <c r="F58" t="n">
-        <v>3.24099</v>
+        <v>3.14739</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.74503</v>
+        <v>3.81563</v>
       </c>
       <c r="C59" t="n">
-        <v>4.13139</v>
+        <v>4.17186</v>
       </c>
       <c r="D59" t="n">
-        <v>11.8239</v>
+        <v>11.5133</v>
       </c>
       <c r="E59" t="n">
-        <v>2.88225</v>
+        <v>2.86702</v>
       </c>
       <c r="F59" t="n">
-        <v>3.30845</v>
+        <v>3.22578</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.02145</v>
+        <v>4.04194</v>
       </c>
       <c r="C60" t="n">
-        <v>4.36358</v>
+        <v>4.42906</v>
       </c>
       <c r="D60" t="n">
-        <v>12.1283</v>
+        <v>11.7572</v>
       </c>
       <c r="E60" t="n">
-        <v>2.99978</v>
+        <v>2.97463</v>
       </c>
       <c r="F60" t="n">
-        <v>3.43649</v>
+        <v>3.35578</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.40999</v>
+        <v>4.48061</v>
       </c>
       <c r="C61" t="n">
-        <v>4.76475</v>
+        <v>4.76343</v>
       </c>
       <c r="D61" t="n">
-        <v>12.4002</v>
+        <v>12.0097</v>
       </c>
       <c r="E61" t="n">
-        <v>3.14844</v>
+        <v>3.14575</v>
       </c>
       <c r="F61" t="n">
-        <v>3.59612</v>
+        <v>3.52426</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.87559</v>
+        <v>5.03692</v>
       </c>
       <c r="C62" t="n">
-        <v>5.28655</v>
+        <v>5.28087</v>
       </c>
       <c r="D62" t="n">
-        <v>12.7047</v>
+        <v>12.3481</v>
       </c>
       <c r="E62" t="n">
-        <v>3.39648</v>
+        <v>3.38332</v>
       </c>
       <c r="F62" t="n">
-        <v>3.85039</v>
+        <v>3.78405</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.80821</v>
+        <v>5.90261</v>
       </c>
       <c r="C63" t="n">
-        <v>6.07348</v>
+        <v>6.03292</v>
       </c>
       <c r="D63" t="n">
-        <v>13.0787</v>
+        <v>12.7432</v>
       </c>
       <c r="E63" t="n">
-        <v>3.75069</v>
+        <v>3.77491</v>
       </c>
       <c r="F63" t="n">
-        <v>4.20751</v>
+        <v>4.16145</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.99804</v>
+        <v>7.20095</v>
       </c>
       <c r="C64" t="n">
-        <v>7.30327</v>
+        <v>7.20723</v>
       </c>
       <c r="D64" t="n">
-        <v>9.352069999999999</v>
+        <v>8.9991</v>
       </c>
       <c r="E64" t="n">
-        <v>4.34727</v>
+        <v>4.35124</v>
       </c>
       <c r="F64" t="n">
-        <v>4.78584</v>
+        <v>4.7092</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>9.04278</v>
+        <v>9.21105</v>
       </c>
       <c r="C65" t="n">
-        <v>9.137029999999999</v>
+        <v>4.16829</v>
       </c>
       <c r="D65" t="n">
-        <v>9.7034</v>
+        <v>9.400880000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>5.3707</v>
+        <v>5.38616</v>
       </c>
       <c r="F65" t="n">
-        <v>5.74123</v>
+        <v>5.71334</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>12.2079</v>
+        <v>12.2045</v>
       </c>
       <c r="C66" t="n">
-        <v>12.2342</v>
+        <v>4.18174</v>
       </c>
       <c r="D66" t="n">
-        <v>10.1067</v>
+        <v>9.73883</v>
       </c>
       <c r="E66" t="n">
-        <v>3.01834</v>
+        <v>3.03065</v>
       </c>
       <c r="F66" t="n">
-        <v>3.40485</v>
+        <v>3.3723</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.4901</v>
+        <v>3.50721</v>
       </c>
       <c r="C67" t="n">
-        <v>4.28804</v>
+        <v>4.21167</v>
       </c>
       <c r="D67" t="n">
-        <v>10.4969</v>
+        <v>10.1159</v>
       </c>
       <c r="E67" t="n">
-        <v>3.04008</v>
+        <v>3.04854</v>
       </c>
       <c r="F67" t="n">
-        <v>3.44548</v>
+        <v>3.41232</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.5782</v>
+        <v>3.54801</v>
       </c>
       <c r="C68" t="n">
-        <v>4.36678</v>
+        <v>4.25454</v>
       </c>
       <c r="D68" t="n">
-        <v>10.9689</v>
+        <v>10.5411</v>
       </c>
       <c r="E68" t="n">
-        <v>3.06768</v>
+        <v>3.07552</v>
       </c>
       <c r="F68" t="n">
-        <v>3.51774</v>
+        <v>3.44708</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.64324</v>
+        <v>3.58928</v>
       </c>
       <c r="C69" t="n">
-        <v>4.47376</v>
+        <v>4.3002</v>
       </c>
       <c r="D69" t="n">
-        <v>11.6072</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="n">
-        <v>3.09092</v>
+        <v>3.10376</v>
       </c>
       <c r="F69" t="n">
-        <v>3.57453</v>
+        <v>3.51054</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.68362</v>
+        <v>3.68883</v>
       </c>
       <c r="C70" t="n">
-        <v>4.5959</v>
+        <v>4.3472</v>
       </c>
       <c r="D70" t="n">
-        <v>11.9124</v>
+        <v>11.3807</v>
       </c>
       <c r="E70" t="n">
-        <v>3.13959</v>
+        <v>3.13985</v>
       </c>
       <c r="F70" t="n">
-        <v>3.64207</v>
+        <v>3.59074</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.78111</v>
+        <v>3.76228</v>
       </c>
       <c r="C71" t="n">
-        <v>4.74504</v>
+        <v>4.42088</v>
       </c>
       <c r="D71" t="n">
-        <v>12.4872</v>
+        <v>11.9044</v>
       </c>
       <c r="E71" t="n">
-        <v>3.18461</v>
+        <v>3.16866</v>
       </c>
       <c r="F71" t="n">
-        <v>3.71226</v>
+        <v>3.66281</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.93297</v>
+        <v>3.93084</v>
       </c>
       <c r="C72" t="n">
-        <v>4.90914</v>
+        <v>4.52371</v>
       </c>
       <c r="D72" t="n">
-        <v>12.9706</v>
+        <v>12.8951</v>
       </c>
       <c r="E72" t="n">
-        <v>3.23664</v>
+        <v>3.23535</v>
       </c>
       <c r="F72" t="n">
-        <v>3.79804</v>
+        <v>3.71943</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.11128</v>
+        <v>4.10688</v>
       </c>
       <c r="C73" t="n">
-        <v>5.09244</v>
+        <v>4.66508</v>
       </c>
       <c r="D73" t="n">
-        <v>13.57</v>
+        <v>13.7335</v>
       </c>
       <c r="E73" t="n">
-        <v>3.30059</v>
+        <v>3.30733</v>
       </c>
       <c r="F73" t="n">
-        <v>3.90787</v>
+        <v>3.829</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.32416</v>
+        <v>4.35155</v>
       </c>
       <c r="C74" t="n">
-        <v>5.38444</v>
+        <v>4.83523</v>
       </c>
       <c r="D74" t="n">
-        <v>14.596</v>
+        <v>14.7325</v>
       </c>
       <c r="E74" t="n">
-        <v>3.41076</v>
+        <v>3.40197</v>
       </c>
       <c r="F74" t="n">
-        <v>4.02505</v>
+        <v>3.96809</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.65805</v>
+        <v>4.72015</v>
       </c>
       <c r="C75" t="n">
-        <v>5.6955</v>
+        <v>5.16912</v>
       </c>
       <c r="D75" t="n">
-        <v>15.476</v>
+        <v>15.4703</v>
       </c>
       <c r="E75" t="n">
-        <v>3.53013</v>
+        <v>3.54654</v>
       </c>
       <c r="F75" t="n">
-        <v>4.21169</v>
+        <v>4.10987</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.20349</v>
+        <v>5.23627</v>
       </c>
       <c r="C76" t="n">
-        <v>6.20457</v>
+        <v>5.63428</v>
       </c>
       <c r="D76" t="n">
-        <v>16.2247</v>
+        <v>16.4256</v>
       </c>
       <c r="E76" t="n">
-        <v>3.73074</v>
+        <v>3.75312</v>
       </c>
       <c r="F76" t="n">
-        <v>4.43649</v>
+        <v>4.35149</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.93137</v>
+        <v>6.00651</v>
       </c>
       <c r="C77" t="n">
-        <v>6.91001</v>
+        <v>6.35324</v>
       </c>
       <c r="D77" t="n">
-        <v>17.5874</v>
+        <v>17.5746</v>
       </c>
       <c r="E77" t="n">
-        <v>4.07254</v>
+        <v>4.07401</v>
       </c>
       <c r="F77" t="n">
-        <v>4.76907</v>
+        <v>4.69287</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>7.06781</v>
+        <v>7.19026</v>
       </c>
       <c r="C78" t="n">
-        <v>8.0288</v>
+        <v>7.39067</v>
       </c>
       <c r="D78" t="n">
-        <v>15.6414</v>
+        <v>15.3064</v>
       </c>
       <c r="E78" t="n">
-        <v>4.56746</v>
+        <v>4.56987</v>
       </c>
       <c r="F78" t="n">
-        <v>5.27022</v>
+        <v>5.18284</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>8.829190000000001</v>
+        <v>9.007210000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>9.81325</v>
+        <v>4.57794</v>
       </c>
       <c r="D79" t="n">
-        <v>16.6806</v>
+        <v>16.474</v>
       </c>
       <c r="E79" t="n">
-        <v>5.42265</v>
+        <v>5.42582</v>
       </c>
       <c r="F79" t="n">
-        <v>6.11136</v>
+        <v>6.04799</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>11.6449</v>
+        <v>11.7503</v>
       </c>
       <c r="C80" t="n">
-        <v>13.0476</v>
+        <v>4.60292</v>
       </c>
       <c r="D80" t="n">
-        <v>17.6797</v>
+        <v>17.4981</v>
       </c>
       <c r="E80" t="n">
-        <v>3.32957</v>
+        <v>3.30842</v>
       </c>
       <c r="F80" t="n">
-        <v>3.87181</v>
+        <v>3.81511</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.10513</v>
+        <v>4.07439</v>
       </c>
       <c r="C81" t="n">
-        <v>5.06391</v>
+        <v>4.62247</v>
       </c>
       <c r="D81" t="n">
-        <v>18.8502</v>
+        <v>18.6146</v>
       </c>
       <c r="E81" t="n">
-        <v>3.33752</v>
+        <v>3.3199</v>
       </c>
       <c r="F81" t="n">
-        <v>3.93466</v>
+        <v>3.87929</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.15184</v>
+        <v>4.12185</v>
       </c>
       <c r="C82" t="n">
-        <v>5.16625</v>
+        <v>4.65804</v>
       </c>
       <c r="D82" t="n">
-        <v>19.7962</v>
+        <v>19.6673</v>
       </c>
       <c r="E82" t="n">
-        <v>3.38095</v>
+        <v>3.36067</v>
       </c>
       <c r="F82" t="n">
-        <v>3.99129</v>
+        <v>3.93674</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.21943</v>
+        <v>4.19368</v>
       </c>
       <c r="C83" t="n">
-        <v>5.35225</v>
+        <v>4.6955</v>
       </c>
       <c r="D83" t="n">
-        <v>21.0298</v>
+        <v>20.8134</v>
       </c>
       <c r="E83" t="n">
-        <v>3.41281</v>
+        <v>3.39648</v>
       </c>
       <c r="F83" t="n">
-        <v>4.05049</v>
+        <v>4.00353</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.30183</v>
+        <v>4.2815</v>
       </c>
       <c r="C84" t="n">
-        <v>5.61028</v>
+        <v>4.76101</v>
       </c>
       <c r="D84" t="n">
-        <v>22.0823</v>
+        <v>21.8141</v>
       </c>
       <c r="E84" t="n">
-        <v>3.43865</v>
+        <v>3.43171</v>
       </c>
       <c r="F84" t="n">
-        <v>4.11206</v>
+        <v>4.07444</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.39605</v>
+        <v>4.37841</v>
       </c>
       <c r="C85" t="n">
-        <v>5.83887</v>
+        <v>4.83979</v>
       </c>
       <c r="D85" t="n">
-        <v>23.1676</v>
+        <v>22.8729</v>
       </c>
       <c r="E85" t="n">
-        <v>3.48226</v>
+        <v>3.48282</v>
       </c>
       <c r="F85" t="n">
-        <v>4.20188</v>
+        <v>4.15152</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>4.5282</v>
+        <v>4.52684</v>
       </c>
       <c r="C86" t="n">
-        <v>6.32617</v>
+        <v>4.95757</v>
       </c>
       <c r="D86" t="n">
-        <v>24.2874</v>
+        <v>24.0739</v>
       </c>
       <c r="E86" t="n">
-        <v>3.54613</v>
+        <v>3.5352</v>
       </c>
       <c r="F86" t="n">
-        <v>4.3002</v>
+        <v>4.27309</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.70087</v>
+        <v>4.71199</v>
       </c>
       <c r="C87" t="n">
-        <v>7.07123</v>
+        <v>5.11988</v>
       </c>
       <c r="D87" t="n">
-        <v>25.4222</v>
+        <v>25.223</v>
       </c>
       <c r="E87" t="n">
-        <v>3.62323</v>
+        <v>3.59273</v>
       </c>
       <c r="F87" t="n">
-        <v>4.45901</v>
+        <v>4.41454</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.9628</v>
+        <v>4.95864</v>
       </c>
       <c r="C88" t="n">
-        <v>7.92219</v>
+        <v>5.37623</v>
       </c>
       <c r="D88" t="n">
-        <v>26.6317</v>
+        <v>26.3122</v>
       </c>
       <c r="E88" t="n">
-        <v>3.73005</v>
+        <v>3.70899</v>
       </c>
       <c r="F88" t="n">
-        <v>4.68758</v>
+        <v>4.61476</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>5.25475</v>
+        <v>5.27862</v>
       </c>
       <c r="C89" t="n">
-        <v>9.188980000000001</v>
+        <v>5.79039</v>
       </c>
       <c r="D89" t="n">
-        <v>27.7781</v>
+        <v>27.5722</v>
       </c>
       <c r="E89" t="n">
-        <v>3.91222</v>
+        <v>3.88256</v>
       </c>
       <c r="F89" t="n">
-        <v>4.99919</v>
+        <v>4.9507</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>5.81346</v>
+        <v>5.86859</v>
       </c>
       <c r="C90" t="n">
-        <v>10.566</v>
+        <v>6.40145</v>
       </c>
       <c r="D90" t="n">
-        <v>29.0774</v>
+        <v>28.8005</v>
       </c>
       <c r="E90" t="n">
-        <v>4.14924</v>
+        <v>4.19213</v>
       </c>
       <c r="F90" t="n">
-        <v>5.57186</v>
+        <v>5.48625</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>6.61686</v>
+        <v>6.65453</v>
       </c>
       <c r="C91" t="n">
-        <v>12.3215</v>
+        <v>7.27967</v>
       </c>
       <c r="D91" t="n">
-        <v>30.386</v>
+        <v>30.2682</v>
       </c>
       <c r="E91" t="n">
-        <v>4.63684</v>
+        <v>4.58305</v>
       </c>
       <c r="F91" t="n">
-        <v>6.37987</v>
+        <v>6.40262</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>7.88801</v>
+        <v>7.9374</v>
       </c>
       <c r="C92" t="n">
-        <v>14.3473</v>
+        <v>8.50413</v>
       </c>
       <c r="D92" t="n">
-        <v>24.7809</v>
+        <v>24.4973</v>
       </c>
       <c r="E92" t="n">
-        <v>5.2531</v>
+        <v>5.27263</v>
       </c>
       <c r="F92" t="n">
-        <v>7.62657</v>
+        <v>7.46259</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>10.0618</v>
+        <v>9.98203</v>
       </c>
       <c r="C93" t="n">
-        <v>16.8092</v>
+        <v>10.3498</v>
       </c>
       <c r="D93" t="n">
-        <v>25.6809</v>
+        <v>25.385</v>
       </c>
       <c r="E93" t="n">
-        <v>6.32207</v>
+        <v>6.41242</v>
       </c>
       <c r="F93" t="n">
-        <v>9.27464</v>
+        <v>9.24859</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>12.979</v>
+        <v>13.0278</v>
       </c>
       <c r="C94" t="n">
-        <v>20.4687</v>
+        <v>5.26464</v>
       </c>
       <c r="D94" t="n">
-        <v>26.6129</v>
+        <v>26.2617</v>
       </c>
       <c r="E94" t="n">
-        <v>3.69125</v>
+        <v>3.65741</v>
       </c>
       <c r="F94" t="n">
-        <v>4.78326</v>
+        <v>4.70837</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.91415</v>
+        <v>4.84549</v>
       </c>
       <c r="C95" t="n">
-        <v>9.172639999999999</v>
+        <v>5.47137</v>
       </c>
       <c r="D95" t="n">
-        <v>27.509</v>
+        <v>27.2173</v>
       </c>
       <c r="E95" t="n">
-        <v>3.75892</v>
+        <v>3.81426</v>
       </c>
       <c r="F95" t="n">
-        <v>5.13854</v>
+        <v>5.08457</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>5.16739</v>
+        <v>5.16747</v>
       </c>
       <c r="C96" t="n">
-        <v>9.9597</v>
+        <v>5.70777</v>
       </c>
       <c r="D96" t="n">
-        <v>28.4291</v>
+        <v>28.0967</v>
       </c>
       <c r="E96" t="n">
-        <v>3.97171</v>
+        <v>3.99751</v>
       </c>
       <c r="F96" t="n">
-        <v>5.66055</v>
+        <v>5.57159</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>5.61992</v>
+        <v>5.61694</v>
       </c>
       <c r="C97" t="n">
-        <v>10.6914</v>
+        <v>5.99601</v>
       </c>
       <c r="D97" t="n">
-        <v>29.3825</v>
+        <v>29.1484</v>
       </c>
       <c r="E97" t="n">
-        <v>4.21842</v>
+        <v>4.20192</v>
       </c>
       <c r="F97" t="n">
-        <v>6.13653</v>
+        <v>6.12472</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.03453</v>
+        <v>6.09287</v>
       </c>
       <c r="C98" t="n">
-        <v>11.4122</v>
+        <v>6.24347</v>
       </c>
       <c r="D98" t="n">
-        <v>30.3672</v>
+        <v>30.1346</v>
       </c>
       <c r="E98" t="n">
-        <v>4.47532</v>
+        <v>4.49263</v>
       </c>
       <c r="F98" t="n">
-        <v>6.69196</v>
+        <v>6.68656</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>6.55194</v>
+        <v>6.59538</v>
       </c>
       <c r="C99" t="n">
-        <v>11.9217</v>
+        <v>6.50611</v>
       </c>
       <c r="D99" t="n">
-        <v>31.4374</v>
+        <v>31.15</v>
       </c>
       <c r="E99" t="n">
-        <v>4.83263</v>
+        <v>4.816</v>
       </c>
       <c r="F99" t="n">
-        <v>7.29908</v>
+        <v>7.26518</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.10695</v>
+        <v>7.08524</v>
       </c>
       <c r="C100" t="n">
-        <v>12.5437</v>
+        <v>6.79978</v>
       </c>
       <c r="D100" t="n">
-        <v>32.5312</v>
+        <v>32.2139</v>
       </c>
       <c r="E100" t="n">
-        <v>5.09844</v>
+        <v>5.11707</v>
       </c>
       <c r="F100" t="n">
-        <v>7.7991</v>
+        <v>7.79641</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.65451</v>
+        <v>7.62302</v>
       </c>
       <c r="C101" t="n">
-        <v>13.1454</v>
+        <v>7.0512</v>
       </c>
       <c r="D101" t="n">
-        <v>33.6143</v>
+        <v>33.3232</v>
       </c>
       <c r="E101" t="n">
-        <v>5.38953</v>
+        <v>5.37726</v>
       </c>
       <c r="F101" t="n">
-        <v>8.27782</v>
+        <v>8.29679</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.21932</v>
+        <v>8.21195</v>
       </c>
       <c r="C102" t="n">
-        <v>13.8687</v>
+        <v>7.40778</v>
       </c>
       <c r="D102" t="n">
-        <v>34.7989</v>
+        <v>34.406</v>
       </c>
       <c r="E102" t="n">
-        <v>5.67352</v>
+        <v>5.65269</v>
       </c>
       <c r="F102" t="n">
-        <v>8.78496</v>
+        <v>8.82869</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.81457</v>
+        <v>8.808870000000001</v>
       </c>
       <c r="C103" t="n">
-        <v>14.5797</v>
+        <v>7.83995</v>
       </c>
       <c r="D103" t="n">
-        <v>35.9495</v>
+        <v>35.5798</v>
       </c>
       <c r="E103" t="n">
-        <v>5.94869</v>
+        <v>5.92144</v>
       </c>
       <c r="F103" t="n">
-        <v>9.30284</v>
+        <v>9.28185</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.449870000000001</v>
+        <v>9.477449999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>15.5318</v>
+        <v>8.42428</v>
       </c>
       <c r="D104" t="n">
-        <v>37.3149</v>
+        <v>36.8831</v>
       </c>
       <c r="E104" t="n">
-        <v>6.27095</v>
+        <v>6.2735</v>
       </c>
       <c r="F104" t="n">
-        <v>9.81306</v>
+        <v>9.83047</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.3258</v>
+        <v>10.327</v>
       </c>
       <c r="C105" t="n">
-        <v>16.7797</v>
+        <v>9.22884</v>
       </c>
       <c r="D105" t="n">
-        <v>38.6321</v>
+        <v>38.2957</v>
       </c>
       <c r="E105" t="n">
-        <v>6.69072</v>
+        <v>6.7184</v>
       </c>
       <c r="F105" t="n">
-        <v>10.5206</v>
+        <v>10.478</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>11.4952</v>
+        <v>11.3865</v>
       </c>
       <c r="C106" t="n">
-        <v>18.2949</v>
+        <v>10.3609</v>
       </c>
       <c r="D106" t="n">
-        <v>39.9923</v>
+        <v>39.6408</v>
       </c>
       <c r="E106" t="n">
-        <v>7.30816</v>
+        <v>7.24979</v>
       </c>
       <c r="F106" t="n">
-        <v>11.4131</v>
+        <v>11.3595</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.0824</v>
+        <v>13.0096</v>
       </c>
       <c r="C107" t="n">
-        <v>20.5293</v>
+        <v>11.9565</v>
       </c>
       <c r="D107" t="n">
-        <v>30.4832</v>
+        <v>30.102</v>
       </c>
       <c r="E107" t="n">
-        <v>8.212529999999999</v>
+        <v>8.197900000000001</v>
       </c>
       <c r="F107" t="n">
-        <v>12.6616</v>
+        <v>12.5924</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>15.3909</v>
+        <v>15.3982</v>
       </c>
       <c r="C108" t="n">
-        <v>23.8511</v>
+        <v>6.77549</v>
       </c>
       <c r="D108" t="n">
-        <v>31.3869</v>
+        <v>31.0041</v>
       </c>
       <c r="E108" t="n">
-        <v>5.4058</v>
+        <v>5.41708</v>
       </c>
       <c r="F108" t="n">
-        <v>7.81453</v>
+        <v>7.79716</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>19.2201</v>
+        <v>19.2023</v>
       </c>
       <c r="C109" t="n">
-        <v>29.3419</v>
+        <v>6.91096</v>
       </c>
       <c r="D109" t="n">
-        <v>32.2928</v>
+        <v>31.9667</v>
       </c>
       <c r="E109" t="n">
-        <v>5.54637</v>
+        <v>5.54074</v>
       </c>
       <c r="F109" t="n">
-        <v>8.05142</v>
+        <v>8.0213</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.85119</v>
+        <v>7.82588</v>
       </c>
       <c r="C110" t="n">
-        <v>12.3438</v>
+        <v>7.06409</v>
       </c>
       <c r="D110" t="n">
-        <v>33.2417</v>
+        <v>32.8497</v>
       </c>
       <c r="E110" t="n">
-        <v>5.68755</v>
+        <v>5.67583</v>
       </c>
       <c r="F110" t="n">
-        <v>8.30509</v>
+        <v>8.251519999999999</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.106120000000001</v>
+        <v>8.0717</v>
       </c>
       <c r="C111" t="n">
-        <v>12.7252</v>
+        <v>7.20658</v>
       </c>
       <c r="D111" t="n">
-        <v>34.1604</v>
+        <v>33.7019</v>
       </c>
       <c r="E111" t="n">
-        <v>5.80985</v>
+        <v>5.80874</v>
       </c>
       <c r="F111" t="n">
-        <v>8.567970000000001</v>
+        <v>8.51633</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.311719999999999</v>
+        <v>8.28572</v>
       </c>
       <c r="C112" t="n">
-        <v>13.1587</v>
+        <v>7.36203</v>
       </c>
       <c r="D112" t="n">
-        <v>35.0926</v>
+        <v>34.6518</v>
       </c>
       <c r="E112" t="n">
-        <v>5.97668</v>
+        <v>5.93259</v>
       </c>
       <c r="F112" t="n">
-        <v>8.8048</v>
+        <v>8.753069999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.58479</v>
+        <v>8.51586</v>
       </c>
       <c r="C113" t="n">
-        <v>13.5707</v>
+        <v>7.55285</v>
       </c>
       <c r="D113" t="n">
-        <v>35.9756</v>
+        <v>35.7686</v>
       </c>
       <c r="E113" t="n">
-        <v>6.1182</v>
+        <v>6.1002</v>
       </c>
       <c r="F113" t="n">
-        <v>9.09479</v>
+        <v>9.017200000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.881779999999999</v>
+        <v>8.79542</v>
       </c>
       <c r="C114" t="n">
-        <v>14.0772</v>
+        <v>7.77441</v>
       </c>
       <c r="D114" t="n">
-        <v>37.0462</v>
+        <v>36.7985</v>
       </c>
       <c r="E114" t="n">
-        <v>6.29092</v>
+        <v>6.25241</v>
       </c>
       <c r="F114" t="n">
-        <v>9.37682</v>
+        <v>9.33039</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.17807</v>
+        <v>9.168620000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>14.6191</v>
+        <v>8.03387</v>
       </c>
       <c r="D115" t="n">
-        <v>38.1927</v>
+        <v>37.7396</v>
       </c>
       <c r="E115" t="n">
-        <v>6.48213</v>
+        <v>6.4529</v>
       </c>
       <c r="F115" t="n">
-        <v>9.70415</v>
+        <v>9.68085</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>9.56748</v>
+        <v>9.524470000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>15.2385</v>
+        <v>8.347580000000001</v>
       </c>
       <c r="D116" t="n">
-        <v>39.3242</v>
+        <v>38.9943</v>
       </c>
       <c r="E116" t="n">
-        <v>6.6908</v>
+        <v>6.6581</v>
       </c>
       <c r="F116" t="n">
-        <v>10.0778</v>
+        <v>10.022</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.0297</v>
+        <v>9.99067</v>
       </c>
       <c r="C117" t="n">
-        <v>16.0121</v>
+        <v>8.78205</v>
       </c>
       <c r="D117" t="n">
-        <v>40.4633</v>
+        <v>40.1046</v>
       </c>
       <c r="E117" t="n">
-        <v>6.94413</v>
+        <v>6.90346</v>
       </c>
       <c r="F117" t="n">
-        <v>10.4813</v>
+        <v>10.4336</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>10.6357</v>
+        <v>10.5768</v>
       </c>
       <c r="C118" t="n">
-        <v>16.8917</v>
+        <v>9.374129999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>41.6241</v>
+        <v>41.1414</v>
       </c>
       <c r="E118" t="n">
-        <v>7.24303</v>
+        <v>7.21919</v>
       </c>
       <c r="F118" t="n">
-        <v>10.9901</v>
+        <v>10.9546</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>11.4236</v>
+        <v>11.3377</v>
       </c>
       <c r="C119" t="n">
-        <v>18.0587</v>
+        <v>10.1427</v>
       </c>
       <c r="D119" t="n">
-        <v>42.8247</v>
+        <v>42.6866</v>
       </c>
       <c r="E119" t="n">
-        <v>7.66825</v>
+        <v>7.62983</v>
       </c>
       <c r="F119" t="n">
-        <v>11.6014</v>
+        <v>11.5743</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>12.4664</v>
+        <v>12.4187</v>
       </c>
       <c r="C120" t="n">
-        <v>19.6897</v>
+        <v>11.2264</v>
       </c>
       <c r="D120" t="n">
-        <v>44.3821</v>
+        <v>43.9791</v>
       </c>
       <c r="E120" t="n">
-        <v>8.228859999999999</v>
+        <v>8.201650000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>12.5248</v>
+        <v>12.4601</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.931</v>
+        <v>13.8943</v>
       </c>
       <c r="C121" t="n">
-        <v>21.9097</v>
+        <v>12.8265</v>
       </c>
       <c r="D121" t="n">
-        <v>33.1131</v>
+        <v>32.9394</v>
       </c>
       <c r="E121" t="n">
-        <v>9.105090000000001</v>
+        <v>9.06808</v>
       </c>
       <c r="F121" t="n">
-        <v>13.7304</v>
+        <v>13.6493</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>16.1447</v>
+        <v>16.1354</v>
       </c>
       <c r="C122" t="n">
-        <v>25.2229</v>
+        <v>7.11518</v>
       </c>
       <c r="D122" t="n">
-        <v>34.1299</v>
+        <v>33.8939</v>
       </c>
       <c r="E122" t="n">
-        <v>10.5176</v>
+        <v>10.4783</v>
       </c>
       <c r="F122" t="n">
-        <v>15.6772</v>
+        <v>15.5274</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>19.6728</v>
+        <v>19.7202</v>
       </c>
       <c r="C123" t="n">
-        <v>30.5192</v>
+        <v>7.27358</v>
       </c>
       <c r="D123" t="n">
-        <v>34.9501</v>
+        <v>34.6706</v>
       </c>
       <c r="E123" t="n">
-        <v>5.90945</v>
+        <v>5.89541</v>
       </c>
       <c r="F123" t="n">
-        <v>8.54222</v>
+        <v>8.49823</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>8.25769</v>
+        <v>8.27309</v>
       </c>
       <c r="C124" t="n">
-        <v>13.1221</v>
+        <v>7.3802</v>
       </c>
       <c r="D124" t="n">
-        <v>35.9846</v>
+        <v>35.6219</v>
       </c>
       <c r="E124" t="n">
-        <v>6.04169</v>
+        <v>6.03595</v>
       </c>
       <c r="F124" t="n">
-        <v>8.81874</v>
+        <v>8.75958</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>8.502509999999999</v>
+        <v>8.47353</v>
       </c>
       <c r="C125" t="n">
-        <v>13.4846</v>
+        <v>7.54262</v>
       </c>
       <c r="D125" t="n">
-        <v>36.8959</v>
+        <v>36.4247</v>
       </c>
       <c r="E125" t="n">
-        <v>6.19809</v>
+        <v>6.17212</v>
       </c>
       <c r="F125" t="n">
-        <v>9.06686</v>
+        <v>9.016450000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>8.745699999999999</v>
+        <v>8.720510000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>13.9449</v>
+        <v>7.70297</v>
       </c>
       <c r="D126" t="n">
-        <v>37.7318</v>
+        <v>37.5066</v>
       </c>
       <c r="E126" t="n">
-        <v>6.32745</v>
+        <v>6.31083</v>
       </c>
       <c r="F126" t="n">
-        <v>9.362209999999999</v>
+        <v>9.30523</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>9.00156</v>
+        <v>8.94909</v>
       </c>
       <c r="C127" t="n">
-        <v>14.4584</v>
+        <v>7.88346</v>
       </c>
       <c r="D127" t="n">
-        <v>38.7067</v>
+        <v>38.4126</v>
       </c>
       <c r="E127" t="n">
-        <v>6.48826</v>
+        <v>6.4433</v>
       </c>
       <c r="F127" t="n">
-        <v>9.658939999999999</v>
+        <v>9.614940000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>9.27183</v>
+        <v>9.22129</v>
       </c>
       <c r="C128" t="n">
-        <v>14.8815</v>
+        <v>8.09469</v>
       </c>
       <c r="D128" t="n">
-        <v>39.8864</v>
+        <v>39.3684</v>
       </c>
       <c r="E128" t="n">
-        <v>6.67658</v>
+        <v>6.63868</v>
       </c>
       <c r="F128" t="n">
-        <v>9.953849999999999</v>
+        <v>9.882709999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>9.59488</v>
+        <v>9.57324</v>
       </c>
       <c r="C129" t="n">
-        <v>15.5087</v>
+        <v>8.36401</v>
       </c>
       <c r="D129" t="n">
-        <v>41.0123</v>
+        <v>40.5014</v>
       </c>
       <c r="E129" t="n">
-        <v>6.85678</v>
+        <v>6.8185</v>
       </c>
       <c r="F129" t="n">
-        <v>10.3041</v>
+        <v>10.2701</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>9.986520000000001</v>
+        <v>9.93271</v>
       </c>
       <c r="C130" t="n">
-        <v>16.1449</v>
+        <v>8.714880000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>41.9634</v>
+        <v>41.6453</v>
       </c>
       <c r="E130" t="n">
-        <v>7.08015</v>
+        <v>7.03003</v>
       </c>
       <c r="F130" t="n">
-        <v>10.7088</v>
+        <v>10.6204</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>10.4015</v>
+        <v>10.4056</v>
       </c>
       <c r="C131" t="n">
-        <v>16.8925</v>
+        <v>9.134779999999999</v>
       </c>
       <c r="D131" t="n">
-        <v>43.061</v>
+        <v>42.6156</v>
       </c>
       <c r="E131" t="n">
-        <v>7.37414</v>
+        <v>7.32901</v>
       </c>
       <c r="F131" t="n">
-        <v>11.1802</v>
+        <v>11.145</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>10.9842</v>
+        <v>10.9526</v>
       </c>
       <c r="C132" t="n">
-        <v>17.8179</v>
+        <v>9.71557</v>
       </c>
       <c r="D132" t="n">
-        <v>44.3958</v>
+        <v>44.0096</v>
       </c>
       <c r="E132" t="n">
-        <v>7.67333</v>
+        <v>7.66871</v>
       </c>
       <c r="F132" t="n">
-        <v>11.7201</v>
+        <v>11.6445</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>11.7617</v>
+        <v>11.7223</v>
       </c>
       <c r="C133" t="n">
-        <v>18.9766</v>
+        <v>10.495</v>
       </c>
       <c r="D133" t="n">
-        <v>45.5145</v>
+        <v>45.2231</v>
       </c>
       <c r="E133" t="n">
-        <v>8.10689</v>
+        <v>8.07729</v>
       </c>
       <c r="F133" t="n">
-        <v>12.3555</v>
+        <v>12.2798</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>12.7984</v>
+        <v>12.7457</v>
       </c>
       <c r="C134" t="n">
-        <v>20.5143</v>
+        <v>11.5585</v>
       </c>
       <c r="D134" t="n">
-        <v>46.9125</v>
+        <v>46.4807</v>
       </c>
       <c r="E134" t="n">
-        <v>8.634869999999999</v>
+        <v>8.64324</v>
       </c>
       <c r="F134" t="n">
-        <v>13.1815</v>
+        <v>13.1744</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>14.1932</v>
+        <v>14.165</v>
       </c>
       <c r="C135" t="n">
-        <v>22.6108</v>
+        <v>13.0804</v>
       </c>
       <c r="D135" t="n">
-        <v>34.7129</v>
+        <v>34.3063</v>
       </c>
       <c r="E135" t="n">
-        <v>9.46114</v>
+        <v>9.470980000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>14.4419</v>
+        <v>14.3586</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>16.3205</v>
+        <v>16.2387</v>
       </c>
       <c r="C136" t="n">
-        <v>25.7879</v>
+        <v>16.8681</v>
       </c>
       <c r="D136" t="n">
-        <v>35.4143</v>
+        <v>35.1354</v>
       </c>
       <c r="E136" t="n">
-        <v>10.7333</v>
+        <v>10.7524</v>
       </c>
       <c r="F136" t="n">
-        <v>16.1899</v>
+        <v>16.1294</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>19.5223</v>
+        <v>19.463</v>
       </c>
       <c r="C137" t="n">
-        <v>30.774</v>
+        <v>16.9558</v>
       </c>
       <c r="D137" t="n">
-        <v>36.5204</v>
+        <v>36.0625</v>
       </c>
       <c r="E137" t="n">
-        <v>13.1</v>
+        <v>12.9837</v>
       </c>
       <c r="F137" t="n">
-        <v>16.1461</v>
+        <v>16.052</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>14.8757</v>
+        <v>14.7753</v>
       </c>
       <c r="C138" t="n">
-        <v>20.4085</v>
+        <v>17.0182</v>
       </c>
       <c r="D138" t="n">
-        <v>37.3648</v>
+        <v>37.107</v>
       </c>
       <c r="E138" t="n">
-        <v>13.1483</v>
+        <v>13.1076</v>
       </c>
       <c r="F138" t="n">
-        <v>16.3441</v>
+        <v>16.4424</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>15.0396</v>
+        <v>14.9289</v>
       </c>
       <c r="C139" t="n">
-        <v>20.8379</v>
+        <v>17.2024</v>
       </c>
       <c r="D139" t="n">
-        <v>38.4457</v>
+        <v>37.8581</v>
       </c>
       <c r="E139" t="n">
-        <v>13.3188</v>
+        <v>13.2832</v>
       </c>
       <c r="F139" t="n">
-        <v>16.7246</v>
+        <v>16.6032</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>15.1501</v>
+        <v>15.0377</v>
       </c>
       <c r="C140" t="n">
-        <v>21.226</v>
+        <v>17.3903</v>
       </c>
       <c r="D140" t="n">
-        <v>39.2354</v>
+        <v>38.8571</v>
       </c>
       <c r="E140" t="n">
-        <v>13.4674</v>
+        <v>13.4564</v>
       </c>
       <c r="F140" t="n">
-        <v>16.9591</v>
+        <v>16.9042</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>15.3644</v>
+        <v>15.4022</v>
       </c>
       <c r="C141" t="n">
-        <v>21.6647</v>
+        <v>17.6159</v>
       </c>
       <c r="D141" t="n">
-        <v>40.2647</v>
+        <v>39.9292</v>
       </c>
       <c r="E141" t="n">
-        <v>13.5364</v>
+        <v>13.5477</v>
       </c>
       <c r="F141" t="n">
-        <v>17.305</v>
+        <v>17.222</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>15.5003</v>
+        <v>15.5193</v>
       </c>
       <c r="C142" t="n">
-        <v>22.1256</v>
+        <v>17.8882</v>
       </c>
       <c r="D142" t="n">
-        <v>41.3167</v>
+        <v>40.8518</v>
       </c>
       <c r="E142" t="n">
-        <v>13.8031</v>
+        <v>13.6968</v>
       </c>
       <c r="F142" t="n">
-        <v>17.6167</v>
+        <v>17.5968</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.6981</v>
+        <v>15.7468</v>
       </c>
       <c r="C143" t="n">
-        <v>22.6969</v>
+        <v>18.1192</v>
       </c>
       <c r="D143" t="n">
-        <v>42.2298</v>
+        <v>42.0113</v>
       </c>
       <c r="E143" t="n">
-        <v>13.9819</v>
+        <v>13.9042</v>
       </c>
       <c r="F143" t="n">
-        <v>17.9192</v>
+        <v>17.9461</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.56687</v>
+        <v>2.55689</v>
       </c>
       <c r="C2" t="n">
-        <v>3.42982</v>
+        <v>3.41986</v>
       </c>
       <c r="D2" t="n">
-        <v>8.40889</v>
+        <v>8.668900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.21928</v>
+        <v>2.21914</v>
       </c>
       <c r="F2" t="n">
-        <v>2.23721</v>
+        <v>2.2354</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.70555</v>
+        <v>2.61384</v>
       </c>
       <c r="C3" t="n">
-        <v>3.57182</v>
+        <v>3.57768</v>
       </c>
       <c r="D3" t="n">
-        <v>8.588559999999999</v>
+        <v>8.81244</v>
       </c>
       <c r="E3" t="n">
-        <v>2.29453</v>
+        <v>2.3072</v>
       </c>
       <c r="F3" t="n">
-        <v>2.31197</v>
+        <v>2.32395</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.88613</v>
+        <v>2.75842</v>
       </c>
       <c r="C4" t="n">
-        <v>3.82499</v>
+        <v>3.83562</v>
       </c>
       <c r="D4" t="n">
-        <v>9.02885</v>
+        <v>9.05756</v>
       </c>
       <c r="E4" t="n">
-        <v>2.41278</v>
+        <v>2.41347</v>
       </c>
       <c r="F4" t="n">
-        <v>2.39915</v>
+        <v>2.40077</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.08711</v>
+        <v>3.03953</v>
       </c>
       <c r="C5" t="n">
-        <v>4.28499</v>
+        <v>4.2662</v>
       </c>
       <c r="D5" t="n">
-        <v>9.40781</v>
+        <v>9.51989</v>
       </c>
       <c r="E5" t="n">
-        <v>2.51992</v>
+        <v>2.52498</v>
       </c>
       <c r="F5" t="n">
-        <v>2.49576</v>
+        <v>2.50422</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.65765</v>
+        <v>3.83448</v>
       </c>
       <c r="C6" t="n">
-        <v>4.92487</v>
+        <v>4.93479</v>
       </c>
       <c r="D6" t="n">
-        <v>9.77261</v>
+        <v>9.903650000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.70849</v>
+        <v>2.73924</v>
       </c>
       <c r="F6" t="n">
-        <v>2.68875</v>
+        <v>2.69628</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>5.08494</v>
+        <v>5.11216</v>
       </c>
       <c r="C7" t="n">
-        <v>6.07739</v>
+        <v>6.08217</v>
       </c>
       <c r="D7" t="n">
-        <v>7.1363</v>
+        <v>7.18577</v>
       </c>
       <c r="E7" t="n">
-        <v>3.09886</v>
+        <v>1.99893</v>
       </c>
       <c r="F7" t="n">
-        <v>3.00652</v>
+        <v>2.00205</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>7.46848</v>
+        <v>7.15584</v>
       </c>
       <c r="C8" t="n">
-        <v>3.05014</v>
+        <v>3.05698</v>
       </c>
       <c r="D8" t="n">
-        <v>7.45192</v>
+        <v>7.52296</v>
       </c>
       <c r="E8" t="n">
-        <v>3.87112</v>
+        <v>2.015</v>
       </c>
       <c r="F8" t="n">
-        <v>3.77211</v>
+        <v>2.0166</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>9.926920000000001</v>
+        <v>10.2743</v>
       </c>
       <c r="C9" t="n">
-        <v>3.07663</v>
+        <v>3.09111</v>
       </c>
       <c r="D9" t="n">
-        <v>7.74375</v>
+        <v>7.8376</v>
       </c>
       <c r="E9" t="n">
-        <v>2.01645</v>
+        <v>2.02275</v>
       </c>
       <c r="F9" t="n">
-        <v>2.03416</v>
+        <v>2.0283</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.36274</v>
+        <v>2.33643</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11636</v>
+        <v>3.11562</v>
       </c>
       <c r="D10" t="n">
-        <v>8.12133</v>
+        <v>8.22987</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0362</v>
+        <v>2.04145</v>
       </c>
       <c r="F10" t="n">
-        <v>2.06033</v>
+        <v>2.06357</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.4148</v>
+        <v>2.37912</v>
       </c>
       <c r="C11" t="n">
-        <v>3.14847</v>
+        <v>3.16331</v>
       </c>
       <c r="D11" t="n">
-        <v>8.47058</v>
+        <v>8.56277</v>
       </c>
       <c r="E11" t="n">
-        <v>2.05697</v>
+        <v>2.06328</v>
       </c>
       <c r="F11" t="n">
-        <v>2.07041</v>
+        <v>2.07922</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.45969</v>
+        <v>2.44845</v>
       </c>
       <c r="C12" t="n">
-        <v>3.18192</v>
+        <v>3.20145</v>
       </c>
       <c r="D12" t="n">
-        <v>8.80805</v>
+        <v>8.88837</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0805</v>
+        <v>2.08321</v>
       </c>
       <c r="F12" t="n">
-        <v>2.09256</v>
+        <v>2.10675</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.48429</v>
+        <v>2.49388</v>
       </c>
       <c r="C13" t="n">
-        <v>3.2231</v>
+        <v>3.24175</v>
       </c>
       <c r="D13" t="n">
-        <v>9.040929999999999</v>
+        <v>9.17794</v>
       </c>
       <c r="E13" t="n">
-        <v>2.10521</v>
+        <v>2.0991</v>
       </c>
       <c r="F13" t="n">
-        <v>2.12478</v>
+        <v>2.12592</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.52136</v>
+        <v>2.54447</v>
       </c>
       <c r="C14" t="n">
-        <v>3.32255</v>
+        <v>3.33593</v>
       </c>
       <c r="D14" t="n">
-        <v>9.3878</v>
+        <v>9.430389999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.14267</v>
+        <v>2.13877</v>
       </c>
       <c r="F14" t="n">
-        <v>2.16419</v>
+        <v>2.15793</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.62098</v>
+        <v>2.60513</v>
       </c>
       <c r="C15" t="n">
-        <v>3.41919</v>
+        <v>3.42009</v>
       </c>
       <c r="D15" t="n">
-        <v>9.64967</v>
+        <v>9.73221</v>
       </c>
       <c r="E15" t="n">
-        <v>2.18595</v>
+        <v>2.18137</v>
       </c>
       <c r="F15" t="n">
-        <v>2.21576</v>
+        <v>2.21779</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.69987</v>
+        <v>2.69899</v>
       </c>
       <c r="C16" t="n">
-        <v>3.57477</v>
+        <v>3.58921</v>
       </c>
       <c r="D16" t="n">
-        <v>9.989409999999999</v>
+        <v>10.1294</v>
       </c>
       <c r="E16" t="n">
-        <v>2.24058</v>
+        <v>2.23367</v>
       </c>
       <c r="F16" t="n">
-        <v>2.25304</v>
+        <v>2.26608</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>2.81696</v>
+        <v>2.80369</v>
       </c>
       <c r="C17" t="n">
-        <v>3.76255</v>
+        <v>3.77122</v>
       </c>
       <c r="D17" t="n">
-        <v>10.2899</v>
+        <v>10.3968</v>
       </c>
       <c r="E17" t="n">
-        <v>2.31541</v>
+        <v>2.30286</v>
       </c>
       <c r="F17" t="n">
-        <v>2.32913</v>
+        <v>2.34004</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.06572</v>
+        <v>3.0652</v>
       </c>
       <c r="C18" t="n">
-        <v>4.01445</v>
+        <v>4.00964</v>
       </c>
       <c r="D18" t="n">
-        <v>10.5619</v>
+        <v>10.686</v>
       </c>
       <c r="E18" t="n">
-        <v>2.42379</v>
+        <v>2.40976</v>
       </c>
       <c r="F18" t="n">
-        <v>2.44906</v>
+        <v>2.4724</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.41417</v>
+        <v>3.42062</v>
       </c>
       <c r="C19" t="n">
-        <v>4.51772</v>
+        <v>4.56828</v>
       </c>
       <c r="D19" t="n">
-        <v>10.9424</v>
+        <v>11.0718</v>
       </c>
       <c r="E19" t="n">
-        <v>2.57426</v>
+        <v>2.58929</v>
       </c>
       <c r="F19" t="n">
-        <v>2.62676</v>
+        <v>2.63108</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.22816</v>
+        <v>4.21813</v>
       </c>
       <c r="C20" t="n">
-        <v>5.22305</v>
+        <v>5.24446</v>
       </c>
       <c r="D20" t="n">
-        <v>11.244</v>
+        <v>11.381</v>
       </c>
       <c r="E20" t="n">
-        <v>2.86006</v>
+        <v>2.85174</v>
       </c>
       <c r="F20" t="n">
-        <v>2.89128</v>
+        <v>2.88117</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.31676</v>
+        <v>5.37267</v>
       </c>
       <c r="C21" t="n">
-        <v>6.15162</v>
+        <v>6.26358</v>
       </c>
       <c r="D21" t="n">
-        <v>8.28186</v>
+        <v>8.39012</v>
       </c>
       <c r="E21" t="n">
-        <v>3.29965</v>
+        <v>2.02446</v>
       </c>
       <c r="F21" t="n">
-        <v>3.31312</v>
+        <v>2.0738</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>6.9907</v>
+        <v>7.01943</v>
       </c>
       <c r="C22" t="n">
-        <v>3.17532</v>
+        <v>3.20443</v>
       </c>
       <c r="D22" t="n">
-        <v>8.59221</v>
+        <v>8.681290000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>4.06824</v>
+        <v>2.03982</v>
       </c>
       <c r="F22" t="n">
-        <v>4.09795</v>
+        <v>2.1068</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>9.519780000000001</v>
+        <v>9.61243</v>
       </c>
       <c r="C23" t="n">
-        <v>3.23819</v>
+        <v>3.22931</v>
       </c>
       <c r="D23" t="n">
-        <v>8.869429999999999</v>
+        <v>8.93413</v>
       </c>
       <c r="E23" t="n">
-        <v>2.06021</v>
+        <v>2.06655</v>
       </c>
       <c r="F23" t="n">
-        <v>2.13793</v>
+        <v>2.13355</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.46121</v>
+        <v>2.45608</v>
       </c>
       <c r="C24" t="n">
-        <v>3.28852</v>
+        <v>3.25453</v>
       </c>
       <c r="D24" t="n">
-        <v>9.19862</v>
+        <v>9.303430000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.08251</v>
+        <v>2.09124</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1836</v>
+        <v>2.17184</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.52893</v>
+        <v>2.50327</v>
       </c>
       <c r="C25" t="n">
-        <v>3.26073</v>
+        <v>3.30587</v>
       </c>
       <c r="D25" t="n">
-        <v>9.525930000000001</v>
+        <v>9.62655</v>
       </c>
       <c r="E25" t="n">
-        <v>2.11282</v>
+        <v>2.11631</v>
       </c>
       <c r="F25" t="n">
-        <v>2.22624</v>
+        <v>2.22345</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.55653</v>
+        <v>2.55597</v>
       </c>
       <c r="C26" t="n">
-        <v>3.33788</v>
+        <v>3.34459</v>
       </c>
       <c r="D26" t="n">
-        <v>9.785310000000001</v>
+        <v>9.88026</v>
       </c>
       <c r="E26" t="n">
-        <v>2.14592</v>
+        <v>2.14591</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2783</v>
+        <v>2.29111</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.62982</v>
+        <v>2.63236</v>
       </c>
       <c r="C27" t="n">
-        <v>3.34367</v>
+        <v>3.38656</v>
       </c>
       <c r="D27" t="n">
-        <v>10.1015</v>
+        <v>10.2185</v>
       </c>
       <c r="E27" t="n">
-        <v>2.16799</v>
+        <v>2.17206</v>
       </c>
       <c r="F27" t="n">
-        <v>2.3453</v>
+        <v>2.34231</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>2.71919</v>
+        <v>2.67704</v>
       </c>
       <c r="C28" t="n">
-        <v>3.44979</v>
+        <v>3.44303</v>
       </c>
       <c r="D28" t="n">
-        <v>10.3554</v>
+        <v>10.4514</v>
       </c>
       <c r="E28" t="n">
-        <v>2.21151</v>
+        <v>2.20742</v>
       </c>
       <c r="F28" t="n">
-        <v>2.39898</v>
+        <v>2.39949</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>2.76095</v>
+        <v>2.80414</v>
       </c>
       <c r="C29" t="n">
-        <v>3.57031</v>
+        <v>3.56189</v>
       </c>
       <c r="D29" t="n">
-        <v>10.6798</v>
+        <v>10.811</v>
       </c>
       <c r="E29" t="n">
-        <v>2.26868</v>
+        <v>2.27224</v>
       </c>
       <c r="F29" t="n">
-        <v>2.48639</v>
+        <v>2.47811</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>2.92765</v>
+        <v>2.91226</v>
       </c>
       <c r="C30" t="n">
-        <v>3.71566</v>
+        <v>3.70356</v>
       </c>
       <c r="D30" t="n">
-        <v>10.974</v>
+        <v>11.0923</v>
       </c>
       <c r="E30" t="n">
-        <v>2.31697</v>
+        <v>2.32117</v>
       </c>
       <c r="F30" t="n">
-        <v>2.54363</v>
+        <v>2.54934</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.11225</v>
+        <v>3.13591</v>
       </c>
       <c r="C31" t="n">
-        <v>3.87455</v>
+        <v>3.85696</v>
       </c>
       <c r="D31" t="n">
-        <v>11.2533</v>
+        <v>11.3636</v>
       </c>
       <c r="E31" t="n">
-        <v>2.37327</v>
+        <v>2.3818</v>
       </c>
       <c r="F31" t="n">
-        <v>2.62495</v>
+        <v>2.61938</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.40236</v>
+        <v>3.38177</v>
       </c>
       <c r="C32" t="n">
-        <v>4.10619</v>
+        <v>4.07947</v>
       </c>
       <c r="D32" t="n">
-        <v>11.5065</v>
+        <v>11.6444</v>
       </c>
       <c r="E32" t="n">
-        <v>2.47142</v>
+        <v>2.48847</v>
       </c>
       <c r="F32" t="n">
-        <v>2.72449</v>
+        <v>2.72532</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>3.88385</v>
+        <v>3.86728</v>
       </c>
       <c r="C33" t="n">
-        <v>4.53813</v>
+        <v>4.51565</v>
       </c>
       <c r="D33" t="n">
-        <v>11.8248</v>
+        <v>11.9551</v>
       </c>
       <c r="E33" t="n">
-        <v>2.63657</v>
+        <v>2.62626</v>
       </c>
       <c r="F33" t="n">
-        <v>2.88635</v>
+        <v>2.90029</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.49338</v>
+        <v>4.65561</v>
       </c>
       <c r="C34" t="n">
-        <v>5.12022</v>
+        <v>5.14502</v>
       </c>
       <c r="D34" t="n">
-        <v>12.1119</v>
+        <v>12.2318</v>
       </c>
       <c r="E34" t="n">
-        <v>2.89218</v>
+        <v>2.88981</v>
       </c>
       <c r="F34" t="n">
-        <v>3.13296</v>
+        <v>3.14181</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.53445</v>
+        <v>5.66962</v>
       </c>
       <c r="C35" t="n">
-        <v>6.09945</v>
+        <v>6.06951</v>
       </c>
       <c r="D35" t="n">
-        <v>8.6791</v>
+        <v>8.739190000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>3.30951</v>
+        <v>2.07305</v>
       </c>
       <c r="F35" t="n">
-        <v>3.54095</v>
+        <v>2.27492</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.14083</v>
+        <v>7.44555</v>
       </c>
       <c r="C36" t="n">
-        <v>7.47578</v>
+        <v>7.45185</v>
       </c>
       <c r="D36" t="n">
-        <v>8.997450000000001</v>
+        <v>9.07931</v>
       </c>
       <c r="E36" t="n">
-        <v>4.00864</v>
+        <v>2.08494</v>
       </c>
       <c r="F36" t="n">
-        <v>4.18965</v>
+        <v>2.30714</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>9.506320000000001</v>
+        <v>9.658950000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>3.25848</v>
+        <v>3.25583</v>
       </c>
       <c r="D37" t="n">
-        <v>9.28692</v>
+        <v>9.36734</v>
       </c>
       <c r="E37" t="n">
-        <v>2.11445</v>
+        <v>2.11175</v>
       </c>
       <c r="F37" t="n">
-        <v>2.32613</v>
+        <v>2.34626</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.49799</v>
+        <v>2.50448</v>
       </c>
       <c r="C38" t="n">
-        <v>3.29303</v>
+        <v>3.28214</v>
       </c>
       <c r="D38" t="n">
-        <v>9.59125</v>
+        <v>9.683540000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>2.13618</v>
+        <v>2.1337</v>
       </c>
       <c r="F38" t="n">
-        <v>2.36977</v>
+        <v>2.3748</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.55111</v>
+        <v>2.54909</v>
       </c>
       <c r="C39" t="n">
-        <v>3.29383</v>
+        <v>3.33293</v>
       </c>
       <c r="D39" t="n">
-        <v>9.92043</v>
+        <v>10.0277</v>
       </c>
       <c r="E39" t="n">
-        <v>2.1618</v>
+        <v>2.1665</v>
       </c>
       <c r="F39" t="n">
-        <v>2.40799</v>
+        <v>2.41168</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.61123</v>
+        <v>2.59173</v>
       </c>
       <c r="C40" t="n">
-        <v>3.35293</v>
+        <v>3.35272</v>
       </c>
       <c r="D40" t="n">
-        <v>10.2428</v>
+        <v>10.3248</v>
       </c>
       <c r="E40" t="n">
-        <v>2.18458</v>
+        <v>2.1938</v>
       </c>
       <c r="F40" t="n">
-        <v>2.4364</v>
+        <v>2.42851</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>2.63721</v>
+        <v>2.6356</v>
       </c>
       <c r="C41" t="n">
-        <v>3.36185</v>
+        <v>3.41617</v>
       </c>
       <c r="D41" t="n">
-        <v>10.5128</v>
+        <v>10.5928</v>
       </c>
       <c r="E41" t="n">
-        <v>2.21736</v>
+        <v>2.21087</v>
       </c>
       <c r="F41" t="n">
-        <v>2.46188</v>
+        <v>2.46607</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>2.70769</v>
+        <v>2.72487</v>
       </c>
       <c r="C42" t="n">
-        <v>3.4814</v>
+        <v>3.4781</v>
       </c>
       <c r="D42" t="n">
-        <v>10.7975</v>
+        <v>10.8908</v>
       </c>
       <c r="E42" t="n">
-        <v>2.24748</v>
+        <v>2.25269</v>
       </c>
       <c r="F42" t="n">
-        <v>2.50985</v>
+        <v>2.51621</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>2.81753</v>
+        <v>2.8244</v>
       </c>
       <c r="C43" t="n">
-        <v>3.51785</v>
+        <v>3.56524</v>
       </c>
       <c r="D43" t="n">
-        <v>11.0961</v>
+        <v>11.2297</v>
       </c>
       <c r="E43" t="n">
-        <v>2.29292</v>
+        <v>2.29604</v>
       </c>
       <c r="F43" t="n">
-        <v>2.55756</v>
+        <v>2.5573</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>2.93917</v>
+        <v>2.95508</v>
       </c>
       <c r="C44" t="n">
-        <v>3.67345</v>
+        <v>3.68628</v>
       </c>
       <c r="D44" t="n">
-        <v>11.3782</v>
+        <v>11.5011</v>
       </c>
       <c r="E44" t="n">
-        <v>2.34517</v>
+        <v>2.35179</v>
       </c>
       <c r="F44" t="n">
-        <v>2.63005</v>
+        <v>2.64516</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.12499</v>
+        <v>3.1103</v>
       </c>
       <c r="C45" t="n">
-        <v>3.86496</v>
+        <v>3.89741</v>
       </c>
       <c r="D45" t="n">
-        <v>11.6539</v>
+        <v>11.7677</v>
       </c>
       <c r="E45" t="n">
-        <v>2.42048</v>
+        <v>2.42109</v>
       </c>
       <c r="F45" t="n">
-        <v>2.70897</v>
+        <v>2.72126</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>3.4185</v>
+        <v>3.37955</v>
       </c>
       <c r="C46" t="n">
-        <v>4.12653</v>
+        <v>4.11961</v>
       </c>
       <c r="D46" t="n">
-        <v>11.935</v>
+        <v>12.0531</v>
       </c>
       <c r="E46" t="n">
-        <v>2.50766</v>
+        <v>2.52878</v>
       </c>
       <c r="F46" t="n">
-        <v>2.80577</v>
+        <v>2.82273</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>3.82843</v>
+        <v>3.80611</v>
       </c>
       <c r="C47" t="n">
-        <v>4.44283</v>
+        <v>4.49584</v>
       </c>
       <c r="D47" t="n">
-        <v>12.1896</v>
+        <v>12.2959</v>
       </c>
       <c r="E47" t="n">
-        <v>2.66565</v>
+        <v>2.67075</v>
       </c>
       <c r="F47" t="n">
-        <v>2.97158</v>
+        <v>2.97273</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.37338</v>
+        <v>4.34642</v>
       </c>
       <c r="C48" t="n">
-        <v>5.10093</v>
+        <v>5.08516</v>
       </c>
       <c r="D48" t="n">
-        <v>12.4783</v>
+        <v>12.6244</v>
       </c>
       <c r="E48" t="n">
-        <v>2.91526</v>
+        <v>2.92486</v>
       </c>
       <c r="F48" t="n">
-        <v>3.21129</v>
+        <v>3.21886</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.26617</v>
+        <v>5.21517</v>
       </c>
       <c r="C49" t="n">
-        <v>5.83551</v>
+        <v>5.87728</v>
       </c>
       <c r="D49" t="n">
-        <v>12.7517</v>
+        <v>12.9032</v>
       </c>
       <c r="E49" t="n">
-        <v>3.28898</v>
+        <v>3.27834</v>
       </c>
       <c r="F49" t="n">
-        <v>3.56418</v>
+        <v>3.55542</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>6.50502</v>
+        <v>6.40675</v>
       </c>
       <c r="C50" t="n">
-        <v>7.1403</v>
+        <v>7.14111</v>
       </c>
       <c r="D50" t="n">
-        <v>9.103289999999999</v>
+        <v>9.180429999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>3.92056</v>
+        <v>2.12262</v>
       </c>
       <c r="F50" t="n">
-        <v>4.13377</v>
+        <v>2.34835</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>8.567170000000001</v>
+        <v>8.455920000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>3.28952</v>
+        <v>3.27923</v>
       </c>
       <c r="D51" t="n">
-        <v>9.43088</v>
+        <v>9.49865</v>
       </c>
       <c r="E51" t="n">
-        <v>2.13651</v>
+        <v>2.13382</v>
       </c>
       <c r="F51" t="n">
-        <v>2.35389</v>
+        <v>2.37907</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>11.5472</v>
+        <v>11.5636</v>
       </c>
       <c r="C52" t="n">
-        <v>3.32169</v>
+        <v>3.31436</v>
       </c>
       <c r="D52" t="n">
-        <v>9.74696</v>
+        <v>9.826549999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>2.15302</v>
+        <v>2.16088</v>
       </c>
       <c r="F52" t="n">
-        <v>2.40689</v>
+        <v>2.40302</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>2.58401</v>
+        <v>2.57116</v>
       </c>
       <c r="C53" t="n">
-        <v>3.3286</v>
+        <v>3.34091</v>
       </c>
       <c r="D53" t="n">
-        <v>10.0566</v>
+        <v>10.1318</v>
       </c>
       <c r="E53" t="n">
-        <v>2.18647</v>
+        <v>2.18666</v>
       </c>
       <c r="F53" t="n">
-        <v>2.44928</v>
+        <v>2.43425</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>2.59311</v>
+        <v>2.59244</v>
       </c>
       <c r="C54" t="n">
-        <v>3.39658</v>
+        <v>3.37784</v>
       </c>
       <c r="D54" t="n">
-        <v>10.3929</v>
+        <v>10.4808</v>
       </c>
       <c r="E54" t="n">
-        <v>2.20893</v>
+        <v>2.20792</v>
       </c>
       <c r="F54" t="n">
-        <v>2.49386</v>
+        <v>2.4835</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>2.68102</v>
+        <v>2.68433</v>
       </c>
       <c r="C55" t="n">
-        <v>3.42877</v>
+        <v>3.43168</v>
       </c>
       <c r="D55" t="n">
-        <v>10.6929</v>
+        <v>10.7993</v>
       </c>
       <c r="E55" t="n">
-        <v>2.24427</v>
+        <v>2.24153</v>
       </c>
       <c r="F55" t="n">
-        <v>2.52802</v>
+        <v>2.51032</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>2.74534</v>
+        <v>2.7255</v>
       </c>
       <c r="C56" t="n">
-        <v>3.46374</v>
+        <v>3.48116</v>
       </c>
       <c r="D56" t="n">
-        <v>11.0133</v>
+        <v>11.0968</v>
       </c>
       <c r="E56" t="n">
-        <v>2.27758</v>
+        <v>2.2774</v>
       </c>
       <c r="F56" t="n">
-        <v>2.5745</v>
+        <v>2.56973</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>2.85748</v>
+        <v>2.83221</v>
       </c>
       <c r="C57" t="n">
-        <v>3.58761</v>
+        <v>3.55676</v>
       </c>
       <c r="D57" t="n">
-        <v>11.2731</v>
+        <v>11.3829</v>
       </c>
       <c r="E57" t="n">
-        <v>2.33379</v>
+        <v>2.32648</v>
       </c>
       <c r="F57" t="n">
-        <v>2.65092</v>
+        <v>2.6339</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>2.95739</v>
+        <v>2.96943</v>
       </c>
       <c r="C58" t="n">
-        <v>3.69032</v>
+        <v>3.68605</v>
       </c>
       <c r="D58" t="n">
-        <v>11.5794</v>
+        <v>11.6953</v>
       </c>
       <c r="E58" t="n">
-        <v>2.37464</v>
+        <v>2.3795</v>
       </c>
       <c r="F58" t="n">
-        <v>2.71021</v>
+        <v>2.68588</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.13624</v>
+        <v>3.11923</v>
       </c>
       <c r="C59" t="n">
-        <v>3.83533</v>
+        <v>3.83756</v>
       </c>
       <c r="D59" t="n">
-        <v>11.8314</v>
+        <v>11.9415</v>
       </c>
       <c r="E59" t="n">
-        <v>2.45249</v>
+        <v>2.44848</v>
       </c>
       <c r="F59" t="n">
-        <v>2.77908</v>
+        <v>2.79207</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>3.34884</v>
+        <v>3.36143</v>
       </c>
       <c r="C60" t="n">
-        <v>4.06739</v>
+        <v>4.09607</v>
       </c>
       <c r="D60" t="n">
-        <v>12.1179</v>
+        <v>12.2136</v>
       </c>
       <c r="E60" t="n">
-        <v>2.53537</v>
+        <v>2.53184</v>
       </c>
       <c r="F60" t="n">
-        <v>2.89367</v>
+        <v>2.88556</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>3.71031</v>
+        <v>3.70215</v>
       </c>
       <c r="C61" t="n">
-        <v>4.44368</v>
+        <v>4.39923</v>
       </c>
       <c r="D61" t="n">
-        <v>12.3869</v>
+        <v>12.5325</v>
       </c>
       <c r="E61" t="n">
-        <v>2.68935</v>
+        <v>2.66863</v>
       </c>
       <c r="F61" t="n">
-        <v>3.03739</v>
+        <v>3.00987</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.23563</v>
+        <v>4.20247</v>
       </c>
       <c r="C62" t="n">
-        <v>4.90412</v>
+        <v>4.91166</v>
       </c>
       <c r="D62" t="n">
-        <v>12.7248</v>
+        <v>12.8216</v>
       </c>
       <c r="E62" t="n">
-        <v>2.89358</v>
+        <v>2.89747</v>
       </c>
       <c r="F62" t="n">
-        <v>3.22848</v>
+        <v>3.2589</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.95794</v>
+        <v>4.98132</v>
       </c>
       <c r="C63" t="n">
-        <v>5.72753</v>
+        <v>5.70879</v>
       </c>
       <c r="D63" t="n">
-        <v>13.0972</v>
+        <v>13.2456</v>
       </c>
       <c r="E63" t="n">
-        <v>3.22696</v>
+        <v>3.23815</v>
       </c>
       <c r="F63" t="n">
-        <v>3.59351</v>
+        <v>3.59962</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.2143</v>
+        <v>6.09163</v>
       </c>
       <c r="C64" t="n">
-        <v>6.91389</v>
+        <v>6.81453</v>
       </c>
       <c r="D64" t="n">
-        <v>9.300459999999999</v>
+        <v>9.35768</v>
       </c>
       <c r="E64" t="n">
-        <v>3.75758</v>
+        <v>2.45439</v>
       </c>
       <c r="F64" t="n">
-        <v>4.07396</v>
+        <v>2.73936</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>7.94213</v>
+        <v>7.89345</v>
       </c>
       <c r="C65" t="n">
-        <v>3.76864</v>
+        <v>3.8108</v>
       </c>
       <c r="D65" t="n">
-        <v>9.65274</v>
+        <v>9.685930000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>4.66978</v>
+        <v>2.48843</v>
       </c>
       <c r="F65" t="n">
-        <v>4.93229</v>
+        <v>2.7741</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>10.8362</v>
+        <v>10.8815</v>
       </c>
       <c r="C66" t="n">
-        <v>3.86079</v>
+        <v>3.85163</v>
       </c>
       <c r="D66" t="n">
-        <v>10.0607</v>
+        <v>10.1011</v>
       </c>
       <c r="E66" t="n">
-        <v>2.48985</v>
+        <v>2.50585</v>
       </c>
       <c r="F66" t="n">
-        <v>2.8197</v>
+        <v>2.82163</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>2.87516</v>
+        <v>2.8851</v>
       </c>
       <c r="C67" t="n">
-        <v>3.84607</v>
+        <v>3.88704</v>
       </c>
       <c r="D67" t="n">
-        <v>10.4039</v>
+        <v>10.5926</v>
       </c>
       <c r="E67" t="n">
-        <v>2.51402</v>
+        <v>2.51324</v>
       </c>
       <c r="F67" t="n">
-        <v>2.88239</v>
+        <v>2.8725</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>2.92446</v>
+        <v>2.93471</v>
       </c>
       <c r="C68" t="n">
-        <v>3.90518</v>
+        <v>3.92449</v>
       </c>
       <c r="D68" t="n">
-        <v>10.9179</v>
+        <v>11.1341</v>
       </c>
       <c r="E68" t="n">
-        <v>2.54797</v>
+        <v>2.53291</v>
       </c>
       <c r="F68" t="n">
-        <v>2.93365</v>
+        <v>2.8976</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>2.98721</v>
+        <v>2.98593</v>
       </c>
       <c r="C69" t="n">
-        <v>3.95146</v>
+        <v>3.9478</v>
       </c>
       <c r="D69" t="n">
-        <v>11.3257</v>
+        <v>11.6277</v>
       </c>
       <c r="E69" t="n">
-        <v>2.57833</v>
+        <v>2.56436</v>
       </c>
       <c r="F69" t="n">
-        <v>2.97544</v>
+        <v>2.9837</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.06214</v>
+        <v>3.07201</v>
       </c>
       <c r="C70" t="n">
-        <v>4.03128</v>
+        <v>3.99639</v>
       </c>
       <c r="D70" t="n">
-        <v>11.8477</v>
+        <v>12.1749</v>
       </c>
       <c r="E70" t="n">
-        <v>2.60314</v>
+        <v>2.58741</v>
       </c>
       <c r="F70" t="n">
-        <v>3.04491</v>
+        <v>3.04351</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.14407</v>
+        <v>3.14595</v>
       </c>
       <c r="C71" t="n">
-        <v>4.11676</v>
+        <v>4.08627</v>
       </c>
       <c r="D71" t="n">
-        <v>12.6538</v>
+        <v>13.086</v>
       </c>
       <c r="E71" t="n">
-        <v>2.64388</v>
+        <v>2.64299</v>
       </c>
       <c r="F71" t="n">
-        <v>3.11558</v>
+        <v>3.10715</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.25625</v>
+        <v>3.28005</v>
       </c>
       <c r="C72" t="n">
-        <v>4.16481</v>
+        <v>4.17834</v>
       </c>
       <c r="D72" t="n">
-        <v>12.928</v>
+        <v>14.0454</v>
       </c>
       <c r="E72" t="n">
-        <v>2.71551</v>
+        <v>2.70401</v>
       </c>
       <c r="F72" t="n">
-        <v>3.20692</v>
+        <v>3.21337</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>3.428</v>
+        <v>3.42631</v>
       </c>
       <c r="C73" t="n">
-        <v>4.31568</v>
+        <v>4.30069</v>
       </c>
       <c r="D73" t="n">
-        <v>13.7605</v>
+        <v>14.7208</v>
       </c>
       <c r="E73" t="n">
-        <v>2.76556</v>
+        <v>2.77289</v>
       </c>
       <c r="F73" t="n">
-        <v>3.29797</v>
+        <v>3.29042</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>3.6251</v>
+        <v>3.64312</v>
       </c>
       <c r="C74" t="n">
-        <v>4.51316</v>
+        <v>4.52403</v>
       </c>
       <c r="D74" t="n">
-        <v>14.5149</v>
+        <v>15.9369</v>
       </c>
       <c r="E74" t="n">
-        <v>2.87305</v>
+        <v>2.87707</v>
       </c>
       <c r="F74" t="n">
-        <v>3.39482</v>
+        <v>3.43966</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>3.93421</v>
+        <v>3.96018</v>
       </c>
       <c r="C75" t="n">
-        <v>4.83636</v>
+        <v>4.81202</v>
       </c>
       <c r="D75" t="n">
-        <v>15.2498</v>
+        <v>16.9455</v>
       </c>
       <c r="E75" t="n">
-        <v>3.01305</v>
+        <v>3.01029</v>
       </c>
       <c r="F75" t="n">
-        <v>3.57198</v>
+        <v>3.60682</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>4.38247</v>
+        <v>4.43314</v>
       </c>
       <c r="C76" t="n">
-        <v>5.30013</v>
+        <v>5.27144</v>
       </c>
       <c r="D76" t="n">
-        <v>16.2724</v>
+        <v>17.8101</v>
       </c>
       <c r="E76" t="n">
-        <v>3.2079</v>
+        <v>3.21045</v>
       </c>
       <c r="F76" t="n">
-        <v>3.79632</v>
+        <v>3.82642</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.07345</v>
+        <v>5.08169</v>
       </c>
       <c r="C77" t="n">
-        <v>5.93559</v>
+        <v>5.94381</v>
       </c>
       <c r="D77" t="n">
-        <v>17.6544</v>
+        <v>19.463</v>
       </c>
       <c r="E77" t="n">
-        <v>3.51305</v>
+        <v>3.52201</v>
       </c>
       <c r="F77" t="n">
-        <v>4.11672</v>
+        <v>4.16053</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.1057</v>
+        <v>6.13602</v>
       </c>
       <c r="C78" t="n">
-        <v>7.02872</v>
+        <v>7.0011</v>
       </c>
       <c r="D78" t="n">
-        <v>15.3806</v>
+        <v>16.1126</v>
       </c>
       <c r="E78" t="n">
-        <v>3.9791</v>
+        <v>2.70881</v>
       </c>
       <c r="F78" t="n">
-        <v>4.58732</v>
+        <v>3.20516</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.71086</v>
+        <v>7.73949</v>
       </c>
       <c r="C79" t="n">
-        <v>4.1664</v>
+        <v>4.18125</v>
       </c>
       <c r="D79" t="n">
-        <v>16.5006</v>
+        <v>17.1212</v>
       </c>
       <c r="E79" t="n">
-        <v>4.83683</v>
+        <v>2.7215</v>
       </c>
       <c r="F79" t="n">
-        <v>5.39297</v>
+        <v>3.23585</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>10.2985</v>
+        <v>10.384</v>
       </c>
       <c r="C80" t="n">
-        <v>4.24238</v>
+        <v>4.20458</v>
       </c>
       <c r="D80" t="n">
-        <v>17.5173</v>
+        <v>17.9837</v>
       </c>
       <c r="E80" t="n">
-        <v>2.73775</v>
+        <v>2.73854</v>
       </c>
       <c r="F80" t="n">
-        <v>3.24961</v>
+        <v>3.28525</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>3.44026</v>
+        <v>3.44849</v>
       </c>
       <c r="C81" t="n">
-        <v>4.23809</v>
+        <v>4.21363</v>
       </c>
       <c r="D81" t="n">
-        <v>18.6502</v>
+        <v>18.9709</v>
       </c>
       <c r="E81" t="n">
-        <v>2.76597</v>
+        <v>2.76379</v>
       </c>
       <c r="F81" t="n">
-        <v>3.2962</v>
+        <v>3.32622</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>3.50816</v>
+        <v>3.50109</v>
       </c>
       <c r="C82" t="n">
-        <v>4.27337</v>
+        <v>4.24963</v>
       </c>
       <c r="D82" t="n">
-        <v>19.7075</v>
+        <v>19.9715</v>
       </c>
       <c r="E82" t="n">
-        <v>2.78873</v>
+        <v>2.79154</v>
       </c>
       <c r="F82" t="n">
-        <v>3.34676</v>
+        <v>3.38748</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>3.53292</v>
+        <v>3.56411</v>
       </c>
       <c r="C83" t="n">
-        <v>4.29649</v>
+        <v>4.32971</v>
       </c>
       <c r="D83" t="n">
-        <v>20.7804</v>
+        <v>21.0676</v>
       </c>
       <c r="E83" t="n">
-        <v>2.81965</v>
+        <v>2.79739</v>
       </c>
       <c r="F83" t="n">
-        <v>3.39979</v>
+        <v>3.44517</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>3.64626</v>
+        <v>3.62726</v>
       </c>
       <c r="C84" t="n">
-        <v>4.39179</v>
+        <v>4.36464</v>
       </c>
       <c r="D84" t="n">
-        <v>21.9549</v>
+        <v>22.0684</v>
       </c>
       <c r="E84" t="n">
-        <v>2.84481</v>
+        <v>2.83822</v>
       </c>
       <c r="F84" t="n">
-        <v>3.4685</v>
+        <v>3.52118</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>3.72168</v>
+        <v>3.75903</v>
       </c>
       <c r="C85" t="n">
-        <v>4.43961</v>
+        <v>4.44259</v>
       </c>
       <c r="D85" t="n">
-        <v>23.0269</v>
+        <v>23.2455</v>
       </c>
       <c r="E85" t="n">
-        <v>2.90338</v>
+        <v>2.89127</v>
       </c>
       <c r="F85" t="n">
-        <v>3.55378</v>
+        <v>3.62703</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>3.85613</v>
+        <v>3.86073</v>
       </c>
       <c r="C86" t="n">
-        <v>4.60643</v>
+        <v>4.56645</v>
       </c>
       <c r="D86" t="n">
-        <v>24.1262</v>
+        <v>24.3604</v>
       </c>
       <c r="E86" t="n">
-        <v>2.97609</v>
+        <v>2.95247</v>
       </c>
       <c r="F86" t="n">
-        <v>3.66238</v>
+        <v>3.74134</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.00696</v>
+        <v>4.00821</v>
       </c>
       <c r="C87" t="n">
-        <v>4.75513</v>
+        <v>4.68512</v>
       </c>
       <c r="D87" t="n">
-        <v>25.2446</v>
+        <v>25.491</v>
       </c>
       <c r="E87" t="n">
-        <v>3.042</v>
+        <v>3.01274</v>
       </c>
       <c r="F87" t="n">
-        <v>3.7906</v>
+        <v>3.86999</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.18834</v>
+        <v>4.22264</v>
       </c>
       <c r="C88" t="n">
-        <v>5.0979</v>
+        <v>4.92422</v>
       </c>
       <c r="D88" t="n">
-        <v>26.484</v>
+        <v>26.6635</v>
       </c>
       <c r="E88" t="n">
-        <v>3.21222</v>
+        <v>3.13998</v>
       </c>
       <c r="F88" t="n">
-        <v>4.01513</v>
+        <v>4.07261</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>4.56609</v>
+        <v>4.5601</v>
       </c>
       <c r="C89" t="n">
-        <v>5.40543</v>
+        <v>5.34028</v>
       </c>
       <c r="D89" t="n">
-        <v>27.6911</v>
+        <v>27.9413</v>
       </c>
       <c r="E89" t="n">
-        <v>3.32571</v>
+        <v>3.3032</v>
       </c>
       <c r="F89" t="n">
-        <v>4.38171</v>
+        <v>4.46166</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>4.98172</v>
+        <v>5.06155</v>
       </c>
       <c r="C90" t="n">
-        <v>6.0877</v>
+        <v>5.88649</v>
       </c>
       <c r="D90" t="n">
-        <v>28.9424</v>
+        <v>29.1777</v>
       </c>
       <c r="E90" t="n">
-        <v>3.75001</v>
+        <v>3.58667</v>
       </c>
       <c r="F90" t="n">
-        <v>4.80917</v>
+        <v>4.93904</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>5.77937</v>
+        <v>5.76095</v>
       </c>
       <c r="C91" t="n">
-        <v>6.91739</v>
+        <v>6.71323</v>
       </c>
       <c r="D91" t="n">
-        <v>30.225</v>
+        <v>30.548</v>
       </c>
       <c r="E91" t="n">
-        <v>4.20729</v>
+        <v>3.99658</v>
       </c>
       <c r="F91" t="n">
-        <v>5.58027</v>
+        <v>5.66693</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>6.96701</v>
+        <v>6.92282</v>
       </c>
       <c r="C92" t="n">
-        <v>8.05035</v>
+        <v>7.98574</v>
       </c>
       <c r="D92" t="n">
-        <v>24.9224</v>
+        <v>24.7116</v>
       </c>
       <c r="E92" t="n">
-        <v>4.86339</v>
+        <v>2.91013</v>
       </c>
       <c r="F92" t="n">
-        <v>6.65866</v>
+        <v>3.63995</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>8.838229999999999</v>
+        <v>8.81617</v>
       </c>
       <c r="C93" t="n">
-        <v>9.68571</v>
+        <v>9.69131</v>
       </c>
       <c r="D93" t="n">
-        <v>25.4065</v>
+        <v>25.5943</v>
       </c>
       <c r="E93" t="n">
-        <v>6.07546</v>
+        <v>2.97136</v>
       </c>
       <c r="F93" t="n">
-        <v>8.246740000000001</v>
+        <v>3.84102</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>11.569</v>
+        <v>11.6135</v>
       </c>
       <c r="C94" t="n">
-        <v>4.89641</v>
+        <v>4.84993</v>
       </c>
       <c r="D94" t="n">
-        <v>26.5056</v>
+        <v>26.4752</v>
       </c>
       <c r="E94" t="n">
-        <v>3.02709</v>
+        <v>3.05835</v>
       </c>
       <c r="F94" t="n">
-        <v>4.19073</v>
+        <v>4.08002</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.19256</v>
+        <v>4.13138</v>
       </c>
       <c r="C95" t="n">
-        <v>5.13407</v>
+        <v>5.06245</v>
       </c>
       <c r="D95" t="n">
-        <v>27.4657</v>
+        <v>27.5292</v>
       </c>
       <c r="E95" t="n">
-        <v>3.23682</v>
+        <v>3.1695</v>
       </c>
       <c r="F95" t="n">
-        <v>4.57102</v>
+        <v>4.4261</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>4.47188</v>
+        <v>4.44897</v>
       </c>
       <c r="C96" t="n">
-        <v>5.27236</v>
+        <v>5.24843</v>
       </c>
       <c r="D96" t="n">
-        <v>28.3747</v>
+        <v>28.4133</v>
       </c>
       <c r="E96" t="n">
-        <v>3.43621</v>
+        <v>3.35218</v>
       </c>
       <c r="F96" t="n">
-        <v>4.83561</v>
+        <v>4.91819</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>4.88224</v>
+        <v>4.80712</v>
       </c>
       <c r="C97" t="n">
-        <v>5.52196</v>
+        <v>5.54502</v>
       </c>
       <c r="D97" t="n">
-        <v>29.2576</v>
+        <v>29.4984</v>
       </c>
       <c r="E97" t="n">
-        <v>3.61107</v>
+        <v>3.59654</v>
       </c>
       <c r="F97" t="n">
-        <v>5.27697</v>
+        <v>5.42063</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>5.20879</v>
+        <v>5.32585</v>
       </c>
       <c r="C98" t="n">
-        <v>5.78434</v>
+        <v>5.81268</v>
       </c>
       <c r="D98" t="n">
-        <v>30.1805</v>
+        <v>30.3904</v>
       </c>
       <c r="E98" t="n">
-        <v>3.85989</v>
+        <v>3.87801</v>
       </c>
       <c r="F98" t="n">
-        <v>5.79163</v>
+        <v>5.92485</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>5.69886</v>
+        <v>5.81483</v>
       </c>
       <c r="C99" t="n">
-        <v>5.92133</v>
+        <v>6.06558</v>
       </c>
       <c r="D99" t="n">
-        <v>31.2947</v>
+        <v>31.3713</v>
       </c>
       <c r="E99" t="n">
-        <v>4.1527</v>
+        <v>4.20824</v>
       </c>
       <c r="F99" t="n">
-        <v>6.43127</v>
+        <v>6.541</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>6.09276</v>
+        <v>6.25914</v>
       </c>
       <c r="C100" t="n">
-        <v>6.29712</v>
+        <v>6.3852</v>
       </c>
       <c r="D100" t="n">
-        <v>32.3032</v>
+        <v>32.4777</v>
       </c>
       <c r="E100" t="n">
-        <v>4.43949</v>
+        <v>4.52167</v>
       </c>
       <c r="F100" t="n">
-        <v>6.71726</v>
+        <v>7.12708</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>6.72051</v>
+        <v>6.81015</v>
       </c>
       <c r="C101" t="n">
-        <v>6.57587</v>
+        <v>6.655</v>
       </c>
       <c r="D101" t="n">
-        <v>33.528</v>
+        <v>33.6137</v>
       </c>
       <c r="E101" t="n">
-        <v>4.73174</v>
+        <v>4.78947</v>
       </c>
       <c r="F101" t="n">
-        <v>7.33544</v>
+        <v>7.60495</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.28547</v>
+        <v>7.38198</v>
       </c>
       <c r="C102" t="n">
-        <v>6.89335</v>
+        <v>7.0342</v>
       </c>
       <c r="D102" t="n">
-        <v>34.591</v>
+        <v>34.828</v>
       </c>
       <c r="E102" t="n">
-        <v>4.99468</v>
+        <v>5.10395</v>
       </c>
       <c r="F102" t="n">
-        <v>7.83695</v>
+        <v>8.08611</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>7.82482</v>
+        <v>7.91375</v>
       </c>
       <c r="C103" t="n">
-        <v>7.36944</v>
+        <v>7.4589</v>
       </c>
       <c r="D103" t="n">
-        <v>35.7576</v>
+        <v>36.0679</v>
       </c>
       <c r="E103" t="n">
-        <v>5.24938</v>
+        <v>5.35459</v>
       </c>
       <c r="F103" t="n">
-        <v>8.385809999999999</v>
+        <v>8.55156</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>8.463279999999999</v>
+        <v>8.555070000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>7.97237</v>
+        <v>8.04261</v>
       </c>
       <c r="D104" t="n">
-        <v>36.9715</v>
+        <v>37.2476</v>
       </c>
       <c r="E104" t="n">
-        <v>5.59728</v>
+        <v>5.65307</v>
       </c>
       <c r="F104" t="n">
-        <v>8.92464</v>
+        <v>9.08038</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>9.26314</v>
+        <v>9.34615</v>
       </c>
       <c r="C105" t="n">
-        <v>8.722860000000001</v>
+        <v>8.836650000000001</v>
       </c>
       <c r="D105" t="n">
-        <v>38.2689</v>
+        <v>38.585</v>
       </c>
       <c r="E105" t="n">
-        <v>5.98262</v>
+        <v>6.05021</v>
       </c>
       <c r="F105" t="n">
-        <v>9.579829999999999</v>
+        <v>9.67934</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>10.3267</v>
+        <v>10.3764</v>
       </c>
       <c r="C106" t="n">
-        <v>9.840949999999999</v>
+        <v>9.992509999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>39.597</v>
+        <v>39.7928</v>
       </c>
       <c r="E106" t="n">
-        <v>6.58482</v>
+        <v>6.63848</v>
       </c>
       <c r="F106" t="n">
-        <v>10.3764</v>
+        <v>10.5269</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>11.7866</v>
+        <v>11.8302</v>
       </c>
       <c r="C107" t="n">
-        <v>11.4059</v>
+        <v>11.5109</v>
       </c>
       <c r="D107" t="n">
-        <v>30.2649</v>
+        <v>30.4864</v>
       </c>
       <c r="E107" t="n">
-        <v>7.40963</v>
+        <v>4.67677</v>
       </c>
       <c r="F107" t="n">
-        <v>11.5475</v>
+        <v>6.88002</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.9766</v>
+        <v>14.012</v>
       </c>
       <c r="C108" t="n">
-        <v>6.3613</v>
+        <v>6.43585</v>
       </c>
       <c r="D108" t="n">
-        <v>31.1555</v>
+        <v>31.5222</v>
       </c>
       <c r="E108" t="n">
-        <v>4.70492</v>
+        <v>4.7904</v>
       </c>
       <c r="F108" t="n">
-        <v>7.01021</v>
+        <v>7.11294</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>17.5786</v>
+        <v>17.5422</v>
       </c>
       <c r="C109" t="n">
-        <v>6.48137</v>
+        <v>6.58028</v>
       </c>
       <c r="D109" t="n">
-        <v>32.0776</v>
+        <v>32.3978</v>
       </c>
       <c r="E109" t="n">
-        <v>4.8463</v>
+        <v>4.93524</v>
       </c>
       <c r="F109" t="n">
-        <v>7.25284</v>
+        <v>7.32273</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.00977</v>
+        <v>7.05217</v>
       </c>
       <c r="C110" t="n">
-        <v>6.62451</v>
+        <v>6.71469</v>
       </c>
       <c r="D110" t="n">
-        <v>32.9083</v>
+        <v>33.1248</v>
       </c>
       <c r="E110" t="n">
-        <v>4.97181</v>
+        <v>5.0548</v>
       </c>
       <c r="F110" t="n">
-        <v>7.47739</v>
+        <v>7.5425</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.20494</v>
+        <v>7.28746</v>
       </c>
       <c r="C111" t="n">
-        <v>6.76334</v>
+        <v>6.86078</v>
       </c>
       <c r="D111" t="n">
-        <v>33.7275</v>
+        <v>34.2435</v>
       </c>
       <c r="E111" t="n">
-        <v>5.11778</v>
+        <v>5.18259</v>
       </c>
       <c r="F111" t="n">
-        <v>7.70955</v>
+        <v>7.82108</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.45426</v>
+        <v>7.48679</v>
       </c>
       <c r="C112" t="n">
-        <v>6.95048</v>
+        <v>7.02284</v>
       </c>
       <c r="D112" t="n">
-        <v>34.8537</v>
+        <v>35.203</v>
       </c>
       <c r="E112" t="n">
-        <v>5.24843</v>
+        <v>5.33828</v>
       </c>
       <c r="F112" t="n">
-        <v>7.94822</v>
+        <v>8.040100000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>7.70772</v>
+        <v>7.70739</v>
       </c>
       <c r="C113" t="n">
-        <v>7.11818</v>
+        <v>7.20343</v>
       </c>
       <c r="D113" t="n">
-        <v>35.7168</v>
+        <v>36.1293</v>
       </c>
       <c r="E113" t="n">
-        <v>5.39053</v>
+        <v>5.47471</v>
       </c>
       <c r="F113" t="n">
-        <v>8.22395</v>
+        <v>8.307930000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>7.9647</v>
+        <v>8.008609999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>7.33</v>
+        <v>7.44333</v>
       </c>
       <c r="D114" t="n">
-        <v>36.702</v>
+        <v>37.0391</v>
       </c>
       <c r="E114" t="n">
-        <v>5.5502</v>
+        <v>5.62961</v>
       </c>
       <c r="F114" t="n">
-        <v>8.515829999999999</v>
+        <v>8.608890000000001</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>8.2369</v>
+        <v>8.27847</v>
       </c>
       <c r="C115" t="n">
-        <v>7.59081</v>
+        <v>7.69126</v>
       </c>
       <c r="D115" t="n">
-        <v>37.9803</v>
+        <v>38.1584</v>
       </c>
       <c r="E115" t="n">
-        <v>5.74497</v>
+        <v>5.80419</v>
       </c>
       <c r="F115" t="n">
-        <v>8.81061</v>
+        <v>8.92506</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>8.60783</v>
+        <v>8.611980000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>7.90533</v>
+        <v>8.014889999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>38.9558</v>
+        <v>39.4888</v>
       </c>
       <c r="E116" t="n">
-        <v>5.94034</v>
+        <v>5.99634</v>
       </c>
       <c r="F116" t="n">
-        <v>9.16267</v>
+        <v>9.220789999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>9.017110000000001</v>
+        <v>9.02361</v>
       </c>
       <c r="C117" t="n">
-        <v>8.34704</v>
+        <v>8.45499</v>
       </c>
       <c r="D117" t="n">
-        <v>40.2185</v>
+        <v>40.3975</v>
       </c>
       <c r="E117" t="n">
-        <v>6.17303</v>
+        <v>6.27723</v>
       </c>
       <c r="F117" t="n">
-        <v>9.546860000000001</v>
+        <v>9.665179999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>9.533569999999999</v>
+        <v>9.58695</v>
       </c>
       <c r="C118" t="n">
-        <v>8.875769999999999</v>
+        <v>9.01666</v>
       </c>
       <c r="D118" t="n">
-        <v>41.2935</v>
+        <v>41.9454</v>
       </c>
       <c r="E118" t="n">
-        <v>6.47396</v>
+        <v>6.58952</v>
       </c>
       <c r="F118" t="n">
-        <v>10.004</v>
+        <v>10.1484</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>10.2537</v>
+        <v>10.2764</v>
       </c>
       <c r="C119" t="n">
-        <v>9.700979999999999</v>
+        <v>9.77872</v>
       </c>
       <c r="D119" t="n">
-        <v>42.7052</v>
+        <v>43.0319</v>
       </c>
       <c r="E119" t="n">
-        <v>6.86352</v>
+        <v>6.95255</v>
       </c>
       <c r="F119" t="n">
-        <v>10.6032</v>
+        <v>10.7105</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>11.1986</v>
+        <v>11.2641</v>
       </c>
       <c r="C120" t="n">
-        <v>10.6971</v>
+        <v>10.8842</v>
       </c>
       <c r="D120" t="n">
-        <v>44.0794</v>
+        <v>44.2761</v>
       </c>
       <c r="E120" t="n">
-        <v>7.40352</v>
+        <v>7.50497</v>
       </c>
       <c r="F120" t="n">
-        <v>11.4575</v>
+        <v>11.5665</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>12.5841</v>
+        <v>12.6232</v>
       </c>
       <c r="C121" t="n">
-        <v>12.2979</v>
+        <v>12.4639</v>
       </c>
       <c r="D121" t="n">
-        <v>33.0637</v>
+        <v>33.2879</v>
       </c>
       <c r="E121" t="n">
-        <v>8.192629999999999</v>
+        <v>5.0304</v>
       </c>
       <c r="F121" t="n">
-        <v>12.5753</v>
+        <v>7.41159</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>14.5306</v>
+        <v>14.6165</v>
       </c>
       <c r="C122" t="n">
-        <v>6.73031</v>
+        <v>6.81715</v>
       </c>
       <c r="D122" t="n">
-        <v>33.952</v>
+        <v>34.32</v>
       </c>
       <c r="E122" t="n">
-        <v>9.508470000000001</v>
+        <v>5.15759</v>
       </c>
       <c r="F122" t="n">
-        <v>14.3498</v>
+        <v>7.6278</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>17.7141</v>
+        <v>17.844</v>
       </c>
       <c r="C123" t="n">
-        <v>6.89507</v>
+        <v>6.92494</v>
       </c>
       <c r="D123" t="n">
-        <v>34.7089</v>
+        <v>35.1104</v>
       </c>
       <c r="E123" t="n">
-        <v>5.25514</v>
+        <v>5.27713</v>
       </c>
       <c r="F123" t="n">
-        <v>7.78867</v>
+        <v>7.84306</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>7.43328</v>
+        <v>7.46987</v>
       </c>
       <c r="C124" t="n">
-        <v>7.02418</v>
+        <v>7.0998</v>
       </c>
       <c r="D124" t="n">
-        <v>35.645</v>
+        <v>36.0874</v>
       </c>
       <c r="E124" t="n">
-        <v>5.37459</v>
+        <v>5.41599</v>
       </c>
       <c r="F124" t="n">
-        <v>8.038029999999999</v>
+        <v>8.1187</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>7.58633</v>
+        <v>7.67051</v>
       </c>
       <c r="C125" t="n">
-        <v>7.19802</v>
+        <v>7.23049</v>
       </c>
       <c r="D125" t="n">
-        <v>36.6759</v>
+        <v>36.9911</v>
       </c>
       <c r="E125" t="n">
-        <v>5.52795</v>
+        <v>5.54918</v>
       </c>
       <c r="F125" t="n">
-        <v>8.288880000000001</v>
+        <v>8.33014</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>7.81194</v>
+        <v>7.87417</v>
       </c>
       <c r="C126" t="n">
-        <v>7.31109</v>
+        <v>7.40444</v>
       </c>
       <c r="D126" t="n">
-        <v>37.6709</v>
+        <v>38.0258</v>
       </c>
       <c r="E126" t="n">
-        <v>5.6795</v>
+        <v>5.69132</v>
       </c>
       <c r="F126" t="n">
-        <v>8.552</v>
+        <v>8.628489999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>8.2226</v>
+        <v>8.05828</v>
       </c>
       <c r="C127" t="n">
-        <v>7.75366</v>
+        <v>7.59188</v>
       </c>
       <c r="D127" t="n">
-        <v>38.5789</v>
+        <v>39.0059</v>
       </c>
       <c r="E127" t="n">
-        <v>5.84578</v>
+        <v>5.84278</v>
       </c>
       <c r="F127" t="n">
-        <v>8.856260000000001</v>
+        <v>8.893269999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>8.27312</v>
+        <v>8.372820000000001</v>
       </c>
       <c r="C128" t="n">
-        <v>7.73264</v>
+        <v>7.84117</v>
       </c>
       <c r="D128" t="n">
-        <v>39.5974</v>
+        <v>39.8644</v>
       </c>
       <c r="E128" t="n">
-        <v>5.9895</v>
+        <v>5.98512</v>
       </c>
       <c r="F128" t="n">
-        <v>9.131130000000001</v>
+        <v>9.22166</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>8.590070000000001</v>
+        <v>8.64058</v>
       </c>
       <c r="C129" t="n">
-        <v>8.01017</v>
+        <v>8.10642</v>
       </c>
       <c r="D129" t="n">
-        <v>40.5941</v>
+        <v>40.9883</v>
       </c>
       <c r="E129" t="n">
-        <v>6.16004</v>
+        <v>6.1936</v>
       </c>
       <c r="F129" t="n">
-        <v>9.46644</v>
+        <v>9.5595</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>10.6484</v>
+        <v>9.0252</v>
       </c>
       <c r="C130" t="n">
-        <v>8.320349999999999</v>
+        <v>8.423410000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>41.5434</v>
+        <v>41.9628</v>
       </c>
       <c r="E130" t="n">
-        <v>6.50623</v>
+        <v>6.3861</v>
       </c>
       <c r="F130" t="n">
-        <v>9.8209</v>
+        <v>9.925280000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>9.363479999999999</v>
+        <v>9.43956</v>
       </c>
       <c r="C131" t="n">
-        <v>8.81053</v>
+        <v>8.842639999999999</v>
       </c>
       <c r="D131" t="n">
-        <v>42.7604</v>
+        <v>43.1042</v>
       </c>
       <c r="E131" t="n">
-        <v>6.63675</v>
+        <v>6.68288</v>
       </c>
       <c r="F131" t="n">
-        <v>10.2667</v>
+        <v>10.4085</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>11.9145</v>
+        <v>9.951309999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>9.322800000000001</v>
+        <v>9.445130000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>44.1445</v>
+        <v>44.5559</v>
       </c>
       <c r="E132" t="n">
-        <v>6.93982</v>
+        <v>6.96817</v>
       </c>
       <c r="F132" t="n">
-        <v>10.7951</v>
+        <v>10.8742</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>11.2526</v>
+        <v>10.6305</v>
       </c>
       <c r="C133" t="n">
-        <v>10.5736</v>
+        <v>10.1607</v>
       </c>
       <c r="D133" t="n">
-        <v>45.1412</v>
+        <v>45.7218</v>
       </c>
       <c r="E133" t="n">
-        <v>8.12899</v>
+        <v>7.37907</v>
       </c>
       <c r="F133" t="n">
-        <v>11.4031</v>
+        <v>11.5693</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>12.5272</v>
+        <v>11.5936</v>
       </c>
       <c r="C134" t="n">
-        <v>11.1137</v>
+        <v>11.2512</v>
       </c>
       <c r="D134" t="n">
-        <v>46.5569</v>
+        <v>46.9746</v>
       </c>
       <c r="E134" t="n">
-        <v>7.91974</v>
+        <v>7.9213</v>
       </c>
       <c r="F134" t="n">
-        <v>12.1796</v>
+        <v>12.3561</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.2099</v>
+        <v>12.8906</v>
       </c>
       <c r="C135" t="n">
-        <v>12.6859</v>
+        <v>12.7907</v>
       </c>
       <c r="D135" t="n">
-        <v>34.5243</v>
+        <v>34.7596</v>
       </c>
       <c r="E135" t="n">
-        <v>8.804589999999999</v>
+        <v>11.6198</v>
       </c>
       <c r="F135" t="n">
-        <v>13.3047</v>
+        <v>14.2789</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>14.7705</v>
+        <v>14.7955</v>
       </c>
       <c r="C136" t="n">
-        <v>16.875</v>
+        <v>15.5126</v>
       </c>
       <c r="D136" t="n">
-        <v>35.228</v>
+        <v>35.7053</v>
       </c>
       <c r="E136" t="n">
-        <v>9.851739999999999</v>
+        <v>11.7376</v>
       </c>
       <c r="F136" t="n">
-        <v>14.902</v>
+        <v>14.5176</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.6304</v>
+        <v>17.7412</v>
       </c>
       <c r="C137" t="n">
-        <v>17.0121</v>
+        <v>15.6982</v>
       </c>
       <c r="D137" t="n">
-        <v>36.2128</v>
+        <v>36.7302</v>
       </c>
       <c r="E137" t="n">
-        <v>11.936</v>
+        <v>11.829</v>
       </c>
       <c r="F137" t="n">
-        <v>14.4638</v>
+        <v>14.6678</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>13.4411</v>
+        <v>13.3117</v>
       </c>
       <c r="C138" t="n">
-        <v>15.4833</v>
+        <v>15.8214</v>
       </c>
       <c r="D138" t="n">
-        <v>37.016</v>
+        <v>37.4791</v>
       </c>
       <c r="E138" t="n">
-        <v>11.6964</v>
+        <v>11.9034</v>
       </c>
       <c r="F138" t="n">
-        <v>15.1417</v>
+        <v>14.9281</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>13.1024</v>
+        <v>13.345</v>
       </c>
       <c r="C139" t="n">
-        <v>16.2107</v>
+        <v>15.9525</v>
       </c>
       <c r="D139" t="n">
-        <v>38.1324</v>
+        <v>38.4097</v>
       </c>
       <c r="E139" t="n">
-        <v>11.9157</v>
+        <v>12.0122</v>
       </c>
       <c r="F139" t="n">
-        <v>15.2472</v>
+        <v>15.1665</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.3154</v>
+        <v>13.4941</v>
       </c>
       <c r="C140" t="n">
-        <v>15.9763</v>
+        <v>16.1421</v>
       </c>
       <c r="D140" t="n">
-        <v>38.8804</v>
+        <v>39.4052</v>
       </c>
       <c r="E140" t="n">
-        <v>11.8864</v>
+        <v>12.1738</v>
       </c>
       <c r="F140" t="n">
-        <v>15.3939</v>
+        <v>15.4683</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>13.8774</v>
+        <v>13.6899</v>
       </c>
       <c r="C141" t="n">
-        <v>17.6307</v>
+        <v>16.2626</v>
       </c>
       <c r="D141" t="n">
-        <v>39.9856</v>
+        <v>40.5023</v>
       </c>
       <c r="E141" t="n">
-        <v>12.0529</v>
+        <v>12.2246</v>
       </c>
       <c r="F141" t="n">
-        <v>15.5815</v>
+        <v>15.7133</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>14.7181</v>
+        <v>13.8462</v>
       </c>
       <c r="C142" t="n">
-        <v>18.8762</v>
+        <v>16.4483</v>
       </c>
       <c r="D142" t="n">
-        <v>41.0046</v>
+        <v>41.5283</v>
       </c>
       <c r="E142" t="n">
-        <v>13.0967</v>
+        <v>12.4478</v>
       </c>
       <c r="F142" t="n">
-        <v>15.8733</v>
+        <v>16.0468</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.7</v>
+        <v>14.1914</v>
       </c>
       <c r="C143" t="n">
-        <v>18.3924</v>
+        <v>16.6716</v>
       </c>
       <c r="D143" t="n">
-        <v>42.0976</v>
+        <v>42.5433</v>
       </c>
       <c r="E143" t="n">
-        <v>12.8039</v>
+        <v>12.6162</v>
       </c>
       <c r="F143" t="n">
-        <v>16.09</v>
+        <v>16.3944</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.55689</v>
+        <v>2.58003</v>
       </c>
       <c r="C2" t="n">
-        <v>3.41986</v>
+        <v>3.57639</v>
       </c>
       <c r="D2" t="n">
-        <v>8.668900000000001</v>
+        <v>8.18013</v>
       </c>
       <c r="E2" t="n">
-        <v>2.21914</v>
+        <v>2.15548</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2354</v>
+        <v>2.15039</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.61384</v>
+        <v>2.64692</v>
       </c>
       <c r="C3" t="n">
-        <v>3.57768</v>
+        <v>3.69991</v>
       </c>
       <c r="D3" t="n">
-        <v>8.81244</v>
+        <v>8.478199999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3072</v>
+        <v>2.25463</v>
       </c>
       <c r="F3" t="n">
-        <v>2.32395</v>
+        <v>2.2647</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.75842</v>
+        <v>2.76653</v>
       </c>
       <c r="C4" t="n">
-        <v>3.83562</v>
+        <v>3.95729</v>
       </c>
       <c r="D4" t="n">
-        <v>9.05756</v>
+        <v>8.743830000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.41347</v>
+        <v>2.3366</v>
       </c>
       <c r="F4" t="n">
-        <v>2.40077</v>
+        <v>2.35595</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.03953</v>
+        <v>3.1561</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2662</v>
+        <v>4.386</v>
       </c>
       <c r="D5" t="n">
-        <v>9.51989</v>
+        <v>9.18031</v>
       </c>
       <c r="E5" t="n">
-        <v>2.52498</v>
+        <v>2.45972</v>
       </c>
       <c r="F5" t="n">
-        <v>2.50422</v>
+        <v>2.48484</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.83448</v>
+        <v>3.75016</v>
       </c>
       <c r="C6" t="n">
-        <v>4.93479</v>
+        <v>4.9474</v>
       </c>
       <c r="D6" t="n">
-        <v>9.903650000000001</v>
+        <v>9.50009</v>
       </c>
       <c r="E6" t="n">
-        <v>2.73924</v>
+        <v>2.65004</v>
       </c>
       <c r="F6" t="n">
-        <v>2.69628</v>
+        <v>2.71792</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>5.11216</v>
+        <v>5.13836</v>
       </c>
       <c r="C7" t="n">
-        <v>6.08217</v>
+        <v>6.07208</v>
       </c>
       <c r="D7" t="n">
-        <v>7.18577</v>
+        <v>6.97386</v>
       </c>
       <c r="E7" t="n">
-        <v>1.99893</v>
+        <v>1.91985</v>
       </c>
       <c r="F7" t="n">
-        <v>2.00205</v>
+        <v>1.90859</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>7.15584</v>
+        <v>7.38722</v>
       </c>
       <c r="C8" t="n">
-        <v>3.05698</v>
+        <v>3.20868</v>
       </c>
       <c r="D8" t="n">
-        <v>7.52296</v>
+        <v>7.31945</v>
       </c>
       <c r="E8" t="n">
-        <v>2.015</v>
+        <v>1.93434</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0166</v>
+        <v>1.92106</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>10.2743</v>
+        <v>10.3572</v>
       </c>
       <c r="C9" t="n">
-        <v>3.09111</v>
+        <v>3.23378</v>
       </c>
       <c r="D9" t="n">
-        <v>7.8376</v>
+        <v>7.62132</v>
       </c>
       <c r="E9" t="n">
-        <v>2.02275</v>
+        <v>1.94906</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0283</v>
+        <v>1.93975</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.33643</v>
+        <v>2.34244</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11562</v>
+        <v>3.26322</v>
       </c>
       <c r="D10" t="n">
-        <v>8.22987</v>
+        <v>7.8764</v>
       </c>
       <c r="E10" t="n">
-        <v>2.04145</v>
+        <v>1.97753</v>
       </c>
       <c r="F10" t="n">
-        <v>2.06357</v>
+        <v>1.96686</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.37912</v>
+        <v>2.37377</v>
       </c>
       <c r="C11" t="n">
-        <v>3.16331</v>
+        <v>3.28846</v>
       </c>
       <c r="D11" t="n">
-        <v>8.56277</v>
+        <v>8.21115</v>
       </c>
       <c r="E11" t="n">
-        <v>2.06328</v>
+        <v>2.00096</v>
       </c>
       <c r="F11" t="n">
-        <v>2.07922</v>
+        <v>1.98913</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.44845</v>
+        <v>2.42395</v>
       </c>
       <c r="C12" t="n">
-        <v>3.20145</v>
+        <v>3.32773</v>
       </c>
       <c r="D12" t="n">
-        <v>8.88837</v>
+        <v>8.552809999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.08321</v>
+        <v>2.02626</v>
       </c>
       <c r="F12" t="n">
-        <v>2.10675</v>
+        <v>2.015</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.49388</v>
+        <v>2.46576</v>
       </c>
       <c r="C13" t="n">
-        <v>3.24175</v>
+        <v>3.3537</v>
       </c>
       <c r="D13" t="n">
-        <v>9.17794</v>
+        <v>8.848750000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0991</v>
+        <v>2.0401</v>
       </c>
       <c r="F13" t="n">
-        <v>2.12592</v>
+        <v>2.03665</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.54447</v>
+        <v>2.52019</v>
       </c>
       <c r="C14" t="n">
-        <v>3.33593</v>
+        <v>3.44511</v>
       </c>
       <c r="D14" t="n">
-        <v>9.430389999999999</v>
+        <v>9.14528</v>
       </c>
       <c r="E14" t="n">
-        <v>2.13877</v>
+        <v>2.08973</v>
       </c>
       <c r="F14" t="n">
-        <v>2.15793</v>
+        <v>2.0792</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.60513</v>
+        <v>2.60998</v>
       </c>
       <c r="C15" t="n">
-        <v>3.42009</v>
+        <v>3.51803</v>
       </c>
       <c r="D15" t="n">
-        <v>9.73221</v>
+        <v>9.405519999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.18137</v>
+        <v>2.13005</v>
       </c>
       <c r="F15" t="n">
-        <v>2.21779</v>
+        <v>2.13555</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.69899</v>
+        <v>2.71517</v>
       </c>
       <c r="C16" t="n">
-        <v>3.58921</v>
+        <v>3.67816</v>
       </c>
       <c r="D16" t="n">
-        <v>10.1294</v>
+        <v>9.75953</v>
       </c>
       <c r="E16" t="n">
-        <v>2.23367</v>
+        <v>2.19197</v>
       </c>
       <c r="F16" t="n">
-        <v>2.26608</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>2.80369</v>
+        <v>2.8876</v>
       </c>
       <c r="C17" t="n">
-        <v>3.77122</v>
+        <v>3.8576</v>
       </c>
       <c r="D17" t="n">
-        <v>10.3968</v>
+        <v>10.0459</v>
       </c>
       <c r="E17" t="n">
-        <v>2.30286</v>
+        <v>2.26453</v>
       </c>
       <c r="F17" t="n">
-        <v>2.34004</v>
+        <v>2.27003</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.0652</v>
+        <v>3.14995</v>
       </c>
       <c r="C18" t="n">
-        <v>4.00964</v>
+        <v>4.05925</v>
       </c>
       <c r="D18" t="n">
-        <v>10.686</v>
+        <v>10.4017</v>
       </c>
       <c r="E18" t="n">
-        <v>2.40976</v>
+        <v>2.38255</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4724</v>
+        <v>2.39458</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.42062</v>
+        <v>3.53958</v>
       </c>
       <c r="C19" t="n">
-        <v>4.56828</v>
+        <v>4.56919</v>
       </c>
       <c r="D19" t="n">
-        <v>11.0718</v>
+        <v>10.7048</v>
       </c>
       <c r="E19" t="n">
-        <v>2.58929</v>
+        <v>2.53206</v>
       </c>
       <c r="F19" t="n">
-        <v>2.63108</v>
+        <v>2.58137</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.21813</v>
+        <v>4.28591</v>
       </c>
       <c r="C20" t="n">
-        <v>5.24446</v>
+        <v>5.21428</v>
       </c>
       <c r="D20" t="n">
-        <v>11.381</v>
+        <v>10.9963</v>
       </c>
       <c r="E20" t="n">
-        <v>2.85174</v>
+        <v>2.79336</v>
       </c>
       <c r="F20" t="n">
-        <v>2.88117</v>
+        <v>2.86042</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.37267</v>
+        <v>5.40478</v>
       </c>
       <c r="C21" t="n">
-        <v>6.26358</v>
+        <v>6.13769</v>
       </c>
       <c r="D21" t="n">
-        <v>8.39012</v>
+        <v>8.04541</v>
       </c>
       <c r="E21" t="n">
-        <v>2.02446</v>
+        <v>1.96294</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0738</v>
+        <v>1.98345</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>7.01943</v>
+        <v>7.17769</v>
       </c>
       <c r="C22" t="n">
-        <v>3.20443</v>
+        <v>3.27947</v>
       </c>
       <c r="D22" t="n">
-        <v>8.681290000000001</v>
+        <v>8.33675</v>
       </c>
       <c r="E22" t="n">
-        <v>2.03982</v>
+        <v>1.97033</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1068</v>
+        <v>2.013</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>9.61243</v>
+        <v>9.60375</v>
       </c>
       <c r="C23" t="n">
-        <v>3.22931</v>
+        <v>3.27856</v>
       </c>
       <c r="D23" t="n">
-        <v>8.93413</v>
+        <v>8.62594</v>
       </c>
       <c r="E23" t="n">
-        <v>2.06655</v>
+        <v>2.0037</v>
       </c>
       <c r="F23" t="n">
-        <v>2.13355</v>
+        <v>2.03616</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.45608</v>
+        <v>2.47819</v>
       </c>
       <c r="C24" t="n">
-        <v>3.25453</v>
+        <v>3.34289</v>
       </c>
       <c r="D24" t="n">
-        <v>9.303430000000001</v>
+        <v>8.95735</v>
       </c>
       <c r="E24" t="n">
-        <v>2.09124</v>
+        <v>2.01324</v>
       </c>
       <c r="F24" t="n">
-        <v>2.17184</v>
+        <v>2.08003</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.50327</v>
+        <v>2.51078</v>
       </c>
       <c r="C25" t="n">
-        <v>3.30587</v>
+        <v>3.33435</v>
       </c>
       <c r="D25" t="n">
-        <v>9.62655</v>
+        <v>9.26765</v>
       </c>
       <c r="E25" t="n">
-        <v>2.11631</v>
+        <v>2.04933</v>
       </c>
       <c r="F25" t="n">
-        <v>2.22345</v>
+        <v>2.13275</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.55597</v>
+        <v>2.58328</v>
       </c>
       <c r="C26" t="n">
-        <v>3.34459</v>
+        <v>3.42354</v>
       </c>
       <c r="D26" t="n">
-        <v>9.88026</v>
+        <v>9.57161</v>
       </c>
       <c r="E26" t="n">
-        <v>2.14591</v>
+        <v>2.08714</v>
       </c>
       <c r="F26" t="n">
-        <v>2.29111</v>
+        <v>2.19202</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.63236</v>
+        <v>2.61581</v>
       </c>
       <c r="C27" t="n">
-        <v>3.38656</v>
+        <v>3.43787</v>
       </c>
       <c r="D27" t="n">
-        <v>10.2185</v>
+        <v>9.884359999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>2.17206</v>
+        <v>2.1084</v>
       </c>
       <c r="F27" t="n">
-        <v>2.34231</v>
+        <v>2.24462</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>2.67704</v>
+        <v>2.7071</v>
       </c>
       <c r="C28" t="n">
-        <v>3.44303</v>
+        <v>3.50395</v>
       </c>
       <c r="D28" t="n">
-        <v>10.4514</v>
+        <v>10.1606</v>
       </c>
       <c r="E28" t="n">
-        <v>2.20742</v>
+        <v>2.15209</v>
       </c>
       <c r="F28" t="n">
-        <v>2.39949</v>
+        <v>2.31571</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>2.80414</v>
+        <v>2.77945</v>
       </c>
       <c r="C29" t="n">
-        <v>3.56189</v>
+        <v>3.6006</v>
       </c>
       <c r="D29" t="n">
-        <v>10.811</v>
+        <v>10.4903</v>
       </c>
       <c r="E29" t="n">
-        <v>2.27224</v>
+        <v>2.21577</v>
       </c>
       <c r="F29" t="n">
-        <v>2.47811</v>
+        <v>2.39635</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>2.91226</v>
+        <v>2.93489</v>
       </c>
       <c r="C30" t="n">
-        <v>3.70356</v>
+        <v>3.72051</v>
       </c>
       <c r="D30" t="n">
-        <v>11.0923</v>
+        <v>10.768</v>
       </c>
       <c r="E30" t="n">
-        <v>2.32117</v>
+        <v>2.26333</v>
       </c>
       <c r="F30" t="n">
-        <v>2.54934</v>
+        <v>2.49074</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.13591</v>
+        <v>3.12186</v>
       </c>
       <c r="C31" t="n">
-        <v>3.85696</v>
+        <v>3.86336</v>
       </c>
       <c r="D31" t="n">
-        <v>11.3636</v>
+        <v>11.0431</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3818</v>
+        <v>2.32879</v>
       </c>
       <c r="F31" t="n">
-        <v>2.61938</v>
+        <v>2.5526</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.38177</v>
+        <v>3.37758</v>
       </c>
       <c r="C32" t="n">
-        <v>4.07947</v>
+        <v>4.05485</v>
       </c>
       <c r="D32" t="n">
-        <v>11.6444</v>
+        <v>11.2901</v>
       </c>
       <c r="E32" t="n">
-        <v>2.48847</v>
+        <v>2.43693</v>
       </c>
       <c r="F32" t="n">
-        <v>2.72532</v>
+        <v>2.66993</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>3.86728</v>
+        <v>3.88526</v>
       </c>
       <c r="C33" t="n">
-        <v>4.51565</v>
+        <v>4.48908</v>
       </c>
       <c r="D33" t="n">
-        <v>11.9551</v>
+        <v>11.5911</v>
       </c>
       <c r="E33" t="n">
-        <v>2.62626</v>
+        <v>2.60332</v>
       </c>
       <c r="F33" t="n">
-        <v>2.90029</v>
+        <v>2.83961</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.65561</v>
+        <v>4.51539</v>
       </c>
       <c r="C34" t="n">
-        <v>5.14502</v>
+        <v>5.1349</v>
       </c>
       <c r="D34" t="n">
-        <v>12.2318</v>
+        <v>11.8929</v>
       </c>
       <c r="E34" t="n">
-        <v>2.88981</v>
+        <v>2.86279</v>
       </c>
       <c r="F34" t="n">
-        <v>3.14181</v>
+        <v>3.08507</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.66962</v>
+        <v>5.55751</v>
       </c>
       <c r="C35" t="n">
-        <v>6.06951</v>
+        <v>5.9573</v>
       </c>
       <c r="D35" t="n">
-        <v>8.739190000000001</v>
+        <v>8.39142</v>
       </c>
       <c r="E35" t="n">
-        <v>2.07305</v>
+        <v>1.98704</v>
       </c>
       <c r="F35" t="n">
-        <v>2.27492</v>
+        <v>2.17989</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.44555</v>
+        <v>7.22098</v>
       </c>
       <c r="C36" t="n">
-        <v>7.45185</v>
+        <v>7.26768</v>
       </c>
       <c r="D36" t="n">
-        <v>9.07931</v>
+        <v>8.68843</v>
       </c>
       <c r="E36" t="n">
-        <v>2.08494</v>
+        <v>2.01375</v>
       </c>
       <c r="F36" t="n">
-        <v>2.30714</v>
+        <v>2.20642</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>9.658950000000001</v>
+        <v>9.62777</v>
       </c>
       <c r="C37" t="n">
-        <v>3.25583</v>
+        <v>3.33888</v>
       </c>
       <c r="D37" t="n">
-        <v>9.36734</v>
+        <v>9.053419999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>2.11175</v>
+        <v>2.04277</v>
       </c>
       <c r="F37" t="n">
-        <v>2.34626</v>
+        <v>2.24113</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.50448</v>
+        <v>2.50949</v>
       </c>
       <c r="C38" t="n">
-        <v>3.28214</v>
+        <v>3.34215</v>
       </c>
       <c r="D38" t="n">
-        <v>9.683540000000001</v>
+        <v>9.355270000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>2.1337</v>
+        <v>2.06535</v>
       </c>
       <c r="F38" t="n">
-        <v>2.3748</v>
+        <v>2.26816</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.54909</v>
+        <v>2.5524</v>
       </c>
       <c r="C39" t="n">
-        <v>3.33293</v>
+        <v>3.35932</v>
       </c>
       <c r="D39" t="n">
-        <v>10.0277</v>
+        <v>9.66386</v>
       </c>
       <c r="E39" t="n">
-        <v>2.1665</v>
+        <v>2.09478</v>
       </c>
       <c r="F39" t="n">
-        <v>2.41168</v>
+        <v>2.31873</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.59173</v>
+        <v>2.61814</v>
       </c>
       <c r="C40" t="n">
-        <v>3.35272</v>
+        <v>3.39136</v>
       </c>
       <c r="D40" t="n">
-        <v>10.3248</v>
+        <v>9.985049999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>2.1938</v>
+        <v>2.12069</v>
       </c>
       <c r="F40" t="n">
-        <v>2.42851</v>
+        <v>2.33805</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>2.6356</v>
+        <v>2.63821</v>
       </c>
       <c r="C41" t="n">
-        <v>3.41617</v>
+        <v>3.44225</v>
       </c>
       <c r="D41" t="n">
-        <v>10.5928</v>
+        <v>10.262</v>
       </c>
       <c r="E41" t="n">
-        <v>2.21087</v>
+        <v>2.15325</v>
       </c>
       <c r="F41" t="n">
-        <v>2.46607</v>
+        <v>2.37374</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>2.72487</v>
+        <v>2.7232</v>
       </c>
       <c r="C42" t="n">
-        <v>3.4781</v>
+        <v>3.49723</v>
       </c>
       <c r="D42" t="n">
-        <v>10.8908</v>
+        <v>10.5749</v>
       </c>
       <c r="E42" t="n">
-        <v>2.25269</v>
+        <v>2.19167</v>
       </c>
       <c r="F42" t="n">
-        <v>2.51621</v>
+        <v>2.42497</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>2.8244</v>
+        <v>2.84564</v>
       </c>
       <c r="C43" t="n">
-        <v>3.56524</v>
+        <v>3.58534</v>
       </c>
       <c r="D43" t="n">
-        <v>11.2297</v>
+        <v>10.8903</v>
       </c>
       <c r="E43" t="n">
-        <v>2.29604</v>
+        <v>2.23567</v>
       </c>
       <c r="F43" t="n">
-        <v>2.5573</v>
+        <v>2.48467</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>2.95508</v>
+        <v>2.93601</v>
       </c>
       <c r="C44" t="n">
-        <v>3.68628</v>
+        <v>3.73135</v>
       </c>
       <c r="D44" t="n">
-        <v>11.5011</v>
+        <v>11.1451</v>
       </c>
       <c r="E44" t="n">
-        <v>2.35179</v>
+        <v>2.30337</v>
       </c>
       <c r="F44" t="n">
-        <v>2.64516</v>
+        <v>2.56468</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.1103</v>
+        <v>3.12912</v>
       </c>
       <c r="C45" t="n">
-        <v>3.89741</v>
+        <v>3.94238</v>
       </c>
       <c r="D45" t="n">
-        <v>11.7677</v>
+        <v>11.4129</v>
       </c>
       <c r="E45" t="n">
-        <v>2.42109</v>
+        <v>2.3759</v>
       </c>
       <c r="F45" t="n">
-        <v>2.72126</v>
+        <v>2.63621</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>3.37955</v>
+        <v>3.38828</v>
       </c>
       <c r="C46" t="n">
-        <v>4.11961</v>
+        <v>4.12384</v>
       </c>
       <c r="D46" t="n">
-        <v>12.0531</v>
+        <v>11.6826</v>
       </c>
       <c r="E46" t="n">
-        <v>2.52878</v>
+        <v>2.47792</v>
       </c>
       <c r="F46" t="n">
-        <v>2.82273</v>
+        <v>2.73906</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>3.80611</v>
+        <v>3.76092</v>
       </c>
       <c r="C47" t="n">
-        <v>4.49584</v>
+        <v>4.49619</v>
       </c>
       <c r="D47" t="n">
-        <v>12.2959</v>
+        <v>11.8756</v>
       </c>
       <c r="E47" t="n">
-        <v>2.67075</v>
+        <v>2.64483</v>
       </c>
       <c r="F47" t="n">
-        <v>2.97273</v>
+        <v>2.92482</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.34642</v>
+        <v>4.41306</v>
       </c>
       <c r="C48" t="n">
-        <v>5.08516</v>
+        <v>5.01755</v>
       </c>
       <c r="D48" t="n">
-        <v>12.6244</v>
+        <v>12.2167</v>
       </c>
       <c r="E48" t="n">
-        <v>2.92486</v>
+        <v>2.90745</v>
       </c>
       <c r="F48" t="n">
-        <v>3.21886</v>
+        <v>3.15599</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.21517</v>
+        <v>5.23881</v>
       </c>
       <c r="C49" t="n">
-        <v>5.87728</v>
+        <v>5.7984</v>
       </c>
       <c r="D49" t="n">
-        <v>12.9032</v>
+        <v>12.4748</v>
       </c>
       <c r="E49" t="n">
-        <v>3.27834</v>
+        <v>3.28353</v>
       </c>
       <c r="F49" t="n">
-        <v>3.55542</v>
+        <v>3.51782</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>6.40675</v>
+        <v>6.50401</v>
       </c>
       <c r="C50" t="n">
-        <v>7.14111</v>
+        <v>7.13126</v>
       </c>
       <c r="D50" t="n">
-        <v>9.180429999999999</v>
+        <v>8.802009999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>2.12262</v>
+        <v>2.04508</v>
       </c>
       <c r="F50" t="n">
-        <v>2.34835</v>
+        <v>2.26467</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>8.455920000000001</v>
+        <v>8.401759999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>3.27923</v>
+        <v>3.33654</v>
       </c>
       <c r="D51" t="n">
-        <v>9.49865</v>
+        <v>9.13499</v>
       </c>
       <c r="E51" t="n">
-        <v>2.13382</v>
+        <v>2.06761</v>
       </c>
       <c r="F51" t="n">
-        <v>2.37907</v>
+        <v>2.29316</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>11.5636</v>
+        <v>11.5868</v>
       </c>
       <c r="C52" t="n">
-        <v>3.31436</v>
+        <v>3.37927</v>
       </c>
       <c r="D52" t="n">
-        <v>9.826549999999999</v>
+        <v>9.489050000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>2.16088</v>
+        <v>2.09292</v>
       </c>
       <c r="F52" t="n">
-        <v>2.40302</v>
+        <v>2.32308</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>2.57116</v>
+        <v>2.57923</v>
       </c>
       <c r="C53" t="n">
-        <v>3.34091</v>
+        <v>3.39775</v>
       </c>
       <c r="D53" t="n">
-        <v>10.1318</v>
+        <v>9.79426</v>
       </c>
       <c r="E53" t="n">
-        <v>2.18666</v>
+        <v>2.11741</v>
       </c>
       <c r="F53" t="n">
-        <v>2.43425</v>
+        <v>2.36905</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>2.59244</v>
+        <v>2.60756</v>
       </c>
       <c r="C54" t="n">
-        <v>3.37784</v>
+        <v>3.42631</v>
       </c>
       <c r="D54" t="n">
-        <v>10.4808</v>
+        <v>10.1186</v>
       </c>
       <c r="E54" t="n">
-        <v>2.20792</v>
+        <v>2.14193</v>
       </c>
       <c r="F54" t="n">
-        <v>2.4835</v>
+        <v>2.39436</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>2.68433</v>
+        <v>2.66749</v>
       </c>
       <c r="C55" t="n">
-        <v>3.43168</v>
+        <v>3.46505</v>
       </c>
       <c r="D55" t="n">
-        <v>10.7993</v>
+        <v>10.435</v>
       </c>
       <c r="E55" t="n">
-        <v>2.24153</v>
+        <v>2.17819</v>
       </c>
       <c r="F55" t="n">
-        <v>2.51032</v>
+        <v>2.45197</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>2.7255</v>
+        <v>2.73218</v>
       </c>
       <c r="C56" t="n">
-        <v>3.48116</v>
+        <v>3.54866</v>
       </c>
       <c r="D56" t="n">
-        <v>11.0968</v>
+        <v>10.7539</v>
       </c>
       <c r="E56" t="n">
-        <v>2.2774</v>
+        <v>2.22981</v>
       </c>
       <c r="F56" t="n">
-        <v>2.56973</v>
+        <v>2.49232</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>2.83221</v>
+        <v>2.8466</v>
       </c>
       <c r="C57" t="n">
-        <v>3.55676</v>
+        <v>3.59656</v>
       </c>
       <c r="D57" t="n">
-        <v>11.3829</v>
+        <v>11.0445</v>
       </c>
       <c r="E57" t="n">
-        <v>2.32648</v>
+        <v>2.28065</v>
       </c>
       <c r="F57" t="n">
-        <v>2.6339</v>
+        <v>2.57414</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>2.96943</v>
+        <v>2.97597</v>
       </c>
       <c r="C58" t="n">
-        <v>3.68605</v>
+        <v>3.72922</v>
       </c>
       <c r="D58" t="n">
-        <v>11.6953</v>
+        <v>11.3297</v>
       </c>
       <c r="E58" t="n">
-        <v>2.3795</v>
+        <v>2.34311</v>
       </c>
       <c r="F58" t="n">
-        <v>2.68588</v>
+        <v>2.63589</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.11923</v>
+        <v>3.14128</v>
       </c>
       <c r="C59" t="n">
-        <v>3.83756</v>
+        <v>3.87327</v>
       </c>
       <c r="D59" t="n">
-        <v>11.9415</v>
+        <v>11.5727</v>
       </c>
       <c r="E59" t="n">
-        <v>2.44848</v>
+        <v>2.4061</v>
       </c>
       <c r="F59" t="n">
-        <v>2.79207</v>
+        <v>2.74029</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>3.36143</v>
+        <v>3.42902</v>
       </c>
       <c r="C60" t="n">
-        <v>4.09607</v>
+        <v>4.1191</v>
       </c>
       <c r="D60" t="n">
-        <v>12.2136</v>
+        <v>11.8692</v>
       </c>
       <c r="E60" t="n">
-        <v>2.53184</v>
+        <v>2.52033</v>
       </c>
       <c r="F60" t="n">
-        <v>2.88556</v>
+        <v>2.84434</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>3.70215</v>
+        <v>3.74759</v>
       </c>
       <c r="C61" t="n">
-        <v>4.39923</v>
+        <v>4.40732</v>
       </c>
       <c r="D61" t="n">
-        <v>12.5325</v>
+        <v>12.1826</v>
       </c>
       <c r="E61" t="n">
-        <v>2.66863</v>
+        <v>2.67654</v>
       </c>
       <c r="F61" t="n">
-        <v>3.00987</v>
+        <v>2.98811</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.20247</v>
+        <v>4.23026</v>
       </c>
       <c r="C62" t="n">
-        <v>4.91166</v>
+        <v>4.92472</v>
       </c>
       <c r="D62" t="n">
-        <v>12.8216</v>
+        <v>12.5186</v>
       </c>
       <c r="E62" t="n">
-        <v>2.89747</v>
+        <v>2.88739</v>
       </c>
       <c r="F62" t="n">
-        <v>3.2589</v>
+        <v>3.2043</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.98132</v>
+        <v>4.92914</v>
       </c>
       <c r="C63" t="n">
-        <v>5.70879</v>
+        <v>5.60179</v>
       </c>
       <c r="D63" t="n">
-        <v>13.2456</v>
+        <v>12.8702</v>
       </c>
       <c r="E63" t="n">
-        <v>3.23815</v>
+        <v>3.23636</v>
       </c>
       <c r="F63" t="n">
-        <v>3.59962</v>
+        <v>3.56279</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.09163</v>
+        <v>6.14375</v>
       </c>
       <c r="C64" t="n">
-        <v>6.81453</v>
+        <v>6.76233</v>
       </c>
       <c r="D64" t="n">
-        <v>9.35768</v>
+        <v>9.0959</v>
       </c>
       <c r="E64" t="n">
-        <v>2.45439</v>
+        <v>2.41399</v>
       </c>
       <c r="F64" t="n">
-        <v>2.73936</v>
+        <v>2.69564</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>7.89345</v>
+        <v>7.8322</v>
       </c>
       <c r="C65" t="n">
-        <v>3.8108</v>
+        <v>3.79246</v>
       </c>
       <c r="D65" t="n">
-        <v>9.685930000000001</v>
+        <v>9.48133</v>
       </c>
       <c r="E65" t="n">
-        <v>2.48843</v>
+        <v>2.43638</v>
       </c>
       <c r="F65" t="n">
-        <v>2.7741</v>
+        <v>2.70612</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>10.8815</v>
+        <v>10.8177</v>
       </c>
       <c r="C66" t="n">
-        <v>3.85163</v>
+        <v>3.81831</v>
       </c>
       <c r="D66" t="n">
-        <v>10.1011</v>
+        <v>9.88734</v>
       </c>
       <c r="E66" t="n">
-        <v>2.50585</v>
+        <v>2.47092</v>
       </c>
       <c r="F66" t="n">
-        <v>2.82163</v>
+        <v>2.75715</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>2.8851</v>
+        <v>2.89862</v>
       </c>
       <c r="C67" t="n">
-        <v>3.88704</v>
+        <v>3.86687</v>
       </c>
       <c r="D67" t="n">
-        <v>10.5926</v>
+        <v>10.3726</v>
       </c>
       <c r="E67" t="n">
-        <v>2.51324</v>
+        <v>2.50571</v>
       </c>
       <c r="F67" t="n">
-        <v>2.8725</v>
+        <v>2.81804</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>2.93471</v>
+        <v>2.93835</v>
       </c>
       <c r="C68" t="n">
-        <v>3.92449</v>
+        <v>3.88401</v>
       </c>
       <c r="D68" t="n">
-        <v>11.1341</v>
+        <v>11.072</v>
       </c>
       <c r="E68" t="n">
-        <v>2.53291</v>
+        <v>2.52961</v>
       </c>
       <c r="F68" t="n">
-        <v>2.8976</v>
+        <v>2.85353</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>2.98593</v>
+        <v>3.01582</v>
       </c>
       <c r="C69" t="n">
-        <v>3.9478</v>
+        <v>3.97554</v>
       </c>
       <c r="D69" t="n">
-        <v>11.6277</v>
+        <v>11.294</v>
       </c>
       <c r="E69" t="n">
-        <v>2.56436</v>
+        <v>2.5452</v>
       </c>
       <c r="F69" t="n">
-        <v>2.9837</v>
+        <v>2.92363</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.07201</v>
+        <v>3.09072</v>
       </c>
       <c r="C70" t="n">
-        <v>3.99639</v>
+        <v>4.03269</v>
       </c>
       <c r="D70" t="n">
-        <v>12.1749</v>
+        <v>12.1313</v>
       </c>
       <c r="E70" t="n">
-        <v>2.58741</v>
+        <v>2.59218</v>
       </c>
       <c r="F70" t="n">
-        <v>3.04351</v>
+        <v>2.97852</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.14595</v>
+        <v>3.17493</v>
       </c>
       <c r="C71" t="n">
-        <v>4.08627</v>
+        <v>4.03144</v>
       </c>
       <c r="D71" t="n">
-        <v>13.086</v>
+        <v>12.4639</v>
       </c>
       <c r="E71" t="n">
-        <v>2.64299</v>
+        <v>2.63516</v>
       </c>
       <c r="F71" t="n">
-        <v>3.10715</v>
+        <v>3.0568</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.28005</v>
+        <v>3.28912</v>
       </c>
       <c r="C72" t="n">
-        <v>4.17834</v>
+        <v>4.18883</v>
       </c>
       <c r="D72" t="n">
-        <v>14.0454</v>
+        <v>12.963</v>
       </c>
       <c r="E72" t="n">
-        <v>2.70401</v>
+        <v>2.69626</v>
       </c>
       <c r="F72" t="n">
-        <v>3.21337</v>
+        <v>3.16527</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>3.42631</v>
+        <v>3.4419</v>
       </c>
       <c r="C73" t="n">
-        <v>4.30069</v>
+        <v>4.27922</v>
       </c>
       <c r="D73" t="n">
-        <v>14.7208</v>
+        <v>13.9428</v>
       </c>
       <c r="E73" t="n">
-        <v>2.77289</v>
+        <v>2.76485</v>
       </c>
       <c r="F73" t="n">
-        <v>3.29042</v>
+        <v>3.25391</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>3.64312</v>
+        <v>3.65505</v>
       </c>
       <c r="C74" t="n">
-        <v>4.52403</v>
+        <v>4.48049</v>
       </c>
       <c r="D74" t="n">
-        <v>15.9369</v>
+        <v>15.0016</v>
       </c>
       <c r="E74" t="n">
-        <v>2.87707</v>
+        <v>2.84903</v>
       </c>
       <c r="F74" t="n">
-        <v>3.43966</v>
+        <v>3.37032</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>3.96018</v>
+        <v>3.93866</v>
       </c>
       <c r="C75" t="n">
-        <v>4.81202</v>
+        <v>4.84691</v>
       </c>
       <c r="D75" t="n">
-        <v>16.9455</v>
+        <v>15.7683</v>
       </c>
       <c r="E75" t="n">
-        <v>3.01029</v>
+        <v>3.03012</v>
       </c>
       <c r="F75" t="n">
-        <v>3.60682</v>
+        <v>3.53748</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>4.43314</v>
+        <v>4.42363</v>
       </c>
       <c r="C76" t="n">
-        <v>5.27144</v>
+        <v>5.24099</v>
       </c>
       <c r="D76" t="n">
-        <v>17.8101</v>
+        <v>17.1099</v>
       </c>
       <c r="E76" t="n">
-        <v>3.21045</v>
+        <v>3.24548</v>
       </c>
       <c r="F76" t="n">
-        <v>3.82642</v>
+        <v>3.76494</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.08169</v>
+        <v>5.13341</v>
       </c>
       <c r="C77" t="n">
-        <v>5.94381</v>
+        <v>5.96932</v>
       </c>
       <c r="D77" t="n">
-        <v>19.463</v>
+        <v>17.7973</v>
       </c>
       <c r="E77" t="n">
-        <v>3.52201</v>
+        <v>3.56682</v>
       </c>
       <c r="F77" t="n">
-        <v>4.16053</v>
+        <v>4.08498</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.13602</v>
+        <v>6.11537</v>
       </c>
       <c r="C78" t="n">
-        <v>7.0011</v>
+        <v>6.98785</v>
       </c>
       <c r="D78" t="n">
-        <v>16.1126</v>
+        <v>15.4315</v>
       </c>
       <c r="E78" t="n">
-        <v>2.70881</v>
+        <v>2.67702</v>
       </c>
       <c r="F78" t="n">
-        <v>3.20516</v>
+        <v>3.14819</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.73949</v>
+        <v>7.66491</v>
       </c>
       <c r="C79" t="n">
-        <v>4.18125</v>
+        <v>4.13569</v>
       </c>
       <c r="D79" t="n">
-        <v>17.1212</v>
+        <v>16.5782</v>
       </c>
       <c r="E79" t="n">
-        <v>2.7215</v>
+        <v>2.70859</v>
       </c>
       <c r="F79" t="n">
-        <v>3.23585</v>
+        <v>3.19509</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>10.384</v>
+        <v>10.3026</v>
       </c>
       <c r="C80" t="n">
-        <v>4.20458</v>
+        <v>4.19603</v>
       </c>
       <c r="D80" t="n">
-        <v>17.9837</v>
+        <v>17.6543</v>
       </c>
       <c r="E80" t="n">
-        <v>2.73854</v>
+        <v>2.71913</v>
       </c>
       <c r="F80" t="n">
-        <v>3.28525</v>
+        <v>3.24419</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>3.44849</v>
+        <v>3.487</v>
       </c>
       <c r="C81" t="n">
-        <v>4.21363</v>
+        <v>4.22376</v>
       </c>
       <c r="D81" t="n">
-        <v>18.9709</v>
+        <v>18.7663</v>
       </c>
       <c r="E81" t="n">
-        <v>2.76379</v>
+        <v>2.75206</v>
       </c>
       <c r="F81" t="n">
-        <v>3.32622</v>
+        <v>3.28636</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>3.50109</v>
+        <v>3.51506</v>
       </c>
       <c r="C82" t="n">
-        <v>4.24963</v>
+        <v>4.30012</v>
       </c>
       <c r="D82" t="n">
-        <v>19.9715</v>
+        <v>19.7122</v>
       </c>
       <c r="E82" t="n">
-        <v>2.79154</v>
+        <v>2.77927</v>
       </c>
       <c r="F82" t="n">
-        <v>3.38748</v>
+        <v>3.33176</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>3.56411</v>
+        <v>3.60626</v>
       </c>
       <c r="C83" t="n">
-        <v>4.32971</v>
+        <v>4.30558</v>
       </c>
       <c r="D83" t="n">
-        <v>21.0676</v>
+        <v>20.816</v>
       </c>
       <c r="E83" t="n">
-        <v>2.79739</v>
+        <v>2.80822</v>
       </c>
       <c r="F83" t="n">
-        <v>3.44517</v>
+        <v>3.37668</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>3.62726</v>
+        <v>3.67335</v>
       </c>
       <c r="C84" t="n">
-        <v>4.36464</v>
+        <v>4.34066</v>
       </c>
       <c r="D84" t="n">
-        <v>22.0684</v>
+        <v>21.93</v>
       </c>
       <c r="E84" t="n">
-        <v>2.83822</v>
+        <v>2.83701</v>
       </c>
       <c r="F84" t="n">
-        <v>3.52118</v>
+        <v>3.46726</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>3.75903</v>
+        <v>3.77169</v>
       </c>
       <c r="C85" t="n">
-        <v>4.44259</v>
+        <v>4.46508</v>
       </c>
       <c r="D85" t="n">
-        <v>23.2455</v>
+        <v>23.0191</v>
       </c>
       <c r="E85" t="n">
-        <v>2.89127</v>
+        <v>2.87858</v>
       </c>
       <c r="F85" t="n">
-        <v>3.62703</v>
+        <v>3.53063</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>3.86073</v>
+        <v>3.87256</v>
       </c>
       <c r="C86" t="n">
-        <v>4.56645</v>
+        <v>4.56774</v>
       </c>
       <c r="D86" t="n">
-        <v>24.3604</v>
+        <v>24.0735</v>
       </c>
       <c r="E86" t="n">
-        <v>2.95247</v>
+        <v>2.96029</v>
       </c>
       <c r="F86" t="n">
-        <v>3.74134</v>
+        <v>3.64677</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.00821</v>
+        <v>4.03886</v>
       </c>
       <c r="C87" t="n">
-        <v>4.68512</v>
+        <v>4.72955</v>
       </c>
       <c r="D87" t="n">
-        <v>25.491</v>
+        <v>25.2927</v>
       </c>
       <c r="E87" t="n">
-        <v>3.01274</v>
+        <v>3.06633</v>
       </c>
       <c r="F87" t="n">
-        <v>3.86999</v>
+        <v>3.77564</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.22264</v>
+        <v>4.24658</v>
       </c>
       <c r="C88" t="n">
-        <v>4.92422</v>
+        <v>4.94336</v>
       </c>
       <c r="D88" t="n">
-        <v>26.6635</v>
+        <v>26.4783</v>
       </c>
       <c r="E88" t="n">
-        <v>3.13998</v>
+        <v>3.22999</v>
       </c>
       <c r="F88" t="n">
-        <v>4.07261</v>
+        <v>3.9661</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>4.5601</v>
+        <v>4.54368</v>
       </c>
       <c r="C89" t="n">
-        <v>5.34028</v>
+        <v>5.29827</v>
       </c>
       <c r="D89" t="n">
-        <v>27.9413</v>
+        <v>27.7257</v>
       </c>
       <c r="E89" t="n">
-        <v>3.3032</v>
+        <v>3.47954</v>
       </c>
       <c r="F89" t="n">
-        <v>4.46166</v>
+        <v>4.20226</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>5.06155</v>
+        <v>5.02837</v>
       </c>
       <c r="C90" t="n">
-        <v>5.88649</v>
+        <v>5.91829</v>
       </c>
       <c r="D90" t="n">
-        <v>29.1777</v>
+        <v>29.023</v>
       </c>
       <c r="E90" t="n">
-        <v>3.58667</v>
+        <v>3.84351</v>
       </c>
       <c r="F90" t="n">
-        <v>4.93904</v>
+        <v>4.68844</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>5.76095</v>
+        <v>5.78787</v>
       </c>
       <c r="C91" t="n">
-        <v>6.71323</v>
+        <v>6.71669</v>
       </c>
       <c r="D91" t="n">
-        <v>30.548</v>
+        <v>30.2598</v>
       </c>
       <c r="E91" t="n">
-        <v>3.99658</v>
+        <v>4.30534</v>
       </c>
       <c r="F91" t="n">
-        <v>5.66693</v>
+        <v>5.42236</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>6.92282</v>
+        <v>6.98175</v>
       </c>
       <c r="C92" t="n">
-        <v>7.98574</v>
+        <v>7.93246</v>
       </c>
       <c r="D92" t="n">
-        <v>24.7116</v>
+        <v>24.5722</v>
       </c>
       <c r="E92" t="n">
-        <v>2.91013</v>
+        <v>2.94988</v>
       </c>
       <c r="F92" t="n">
-        <v>3.63995</v>
+        <v>3.56113</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>8.81617</v>
+        <v>8.81377</v>
       </c>
       <c r="C93" t="n">
-        <v>9.69131</v>
+        <v>9.678929999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>25.5943</v>
+        <v>25.5015</v>
       </c>
       <c r="E93" t="n">
-        <v>2.97136</v>
+        <v>3.03639</v>
       </c>
       <c r="F93" t="n">
-        <v>3.84102</v>
+        <v>3.71807</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>11.6135</v>
+        <v>11.5775</v>
       </c>
       <c r="C94" t="n">
-        <v>4.84993</v>
+        <v>4.85181</v>
       </c>
       <c r="D94" t="n">
-        <v>26.4752</v>
+        <v>26.488</v>
       </c>
       <c r="E94" t="n">
-        <v>3.05835</v>
+        <v>3.18579</v>
       </c>
       <c r="F94" t="n">
-        <v>4.08002</v>
+        <v>3.99618</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.13138</v>
+        <v>4.1697</v>
       </c>
       <c r="C95" t="n">
-        <v>5.06245</v>
+        <v>5.06814</v>
       </c>
       <c r="D95" t="n">
-        <v>27.5292</v>
+        <v>27.2961</v>
       </c>
       <c r="E95" t="n">
-        <v>3.1695</v>
+        <v>3.43959</v>
       </c>
       <c r="F95" t="n">
-        <v>4.4261</v>
+        <v>4.34324</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>4.44897</v>
+        <v>4.51529</v>
       </c>
       <c r="C96" t="n">
-        <v>5.24843</v>
+        <v>5.32926</v>
       </c>
       <c r="D96" t="n">
-        <v>28.4133</v>
+        <v>28.314</v>
       </c>
       <c r="E96" t="n">
-        <v>3.35218</v>
+        <v>3.72631</v>
       </c>
       <c r="F96" t="n">
-        <v>4.91819</v>
+        <v>4.72753</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>4.80712</v>
+        <v>4.87965</v>
       </c>
       <c r="C97" t="n">
-        <v>5.54502</v>
+        <v>5.56982</v>
       </c>
       <c r="D97" t="n">
-        <v>29.4984</v>
+        <v>29.2303</v>
       </c>
       <c r="E97" t="n">
-        <v>3.59654</v>
+        <v>3.96845</v>
       </c>
       <c r="F97" t="n">
-        <v>5.42063</v>
+        <v>5.27281</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>5.32585</v>
+        <v>5.33278</v>
       </c>
       <c r="C98" t="n">
-        <v>5.81268</v>
+        <v>5.81991</v>
       </c>
       <c r="D98" t="n">
-        <v>30.3904</v>
+        <v>30.2824</v>
       </c>
       <c r="E98" t="n">
-        <v>3.87801</v>
+        <v>4.25625</v>
       </c>
       <c r="F98" t="n">
-        <v>5.92485</v>
+        <v>5.78041</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>5.81483</v>
+        <v>5.78862</v>
       </c>
       <c r="C99" t="n">
-        <v>6.06558</v>
+        <v>6.09163</v>
       </c>
       <c r="D99" t="n">
-        <v>31.3713</v>
+        <v>31.2856</v>
       </c>
       <c r="E99" t="n">
-        <v>4.20824</v>
+        <v>4.45446</v>
       </c>
       <c r="F99" t="n">
-        <v>6.541</v>
+        <v>6.36514</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>6.25914</v>
+        <v>6.30952</v>
       </c>
       <c r="C100" t="n">
-        <v>6.3852</v>
+        <v>6.3503</v>
       </c>
       <c r="D100" t="n">
-        <v>32.4777</v>
+        <v>32.4252</v>
       </c>
       <c r="E100" t="n">
-        <v>4.52167</v>
+        <v>4.66101</v>
       </c>
       <c r="F100" t="n">
-        <v>7.12708</v>
+        <v>6.95419</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>6.81015</v>
+        <v>6.82136</v>
       </c>
       <c r="C101" t="n">
-        <v>6.655</v>
+        <v>6.67225</v>
       </c>
       <c r="D101" t="n">
-        <v>33.6137</v>
+        <v>33.5394</v>
       </c>
       <c r="E101" t="n">
-        <v>4.78947</v>
+        <v>4.87953</v>
       </c>
       <c r="F101" t="n">
-        <v>7.60495</v>
+        <v>7.50323</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.38198</v>
+        <v>7.44024</v>
       </c>
       <c r="C102" t="n">
-        <v>7.0342</v>
+        <v>6.99828</v>
       </c>
       <c r="D102" t="n">
-        <v>34.828</v>
+        <v>34.7162</v>
       </c>
       <c r="E102" t="n">
-        <v>5.10395</v>
+        <v>5.05063</v>
       </c>
       <c r="F102" t="n">
-        <v>8.08611</v>
+        <v>8.012180000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>7.91375</v>
+        <v>7.93217</v>
       </c>
       <c r="C103" t="n">
-        <v>7.4589</v>
+        <v>7.39744</v>
       </c>
       <c r="D103" t="n">
-        <v>36.0679</v>
+        <v>35.8989</v>
       </c>
       <c r="E103" t="n">
-        <v>5.35459</v>
+        <v>5.28285</v>
       </c>
       <c r="F103" t="n">
-        <v>8.55156</v>
+        <v>8.505269999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>8.555070000000001</v>
+        <v>8.66377</v>
       </c>
       <c r="C104" t="n">
-        <v>8.04261</v>
+        <v>7.99959</v>
       </c>
       <c r="D104" t="n">
-        <v>37.2476</v>
+        <v>37.1033</v>
       </c>
       <c r="E104" t="n">
-        <v>5.65307</v>
+        <v>5.56509</v>
       </c>
       <c r="F104" t="n">
-        <v>9.08038</v>
+        <v>8.98882</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>9.34615</v>
+        <v>9.38274</v>
       </c>
       <c r="C105" t="n">
-        <v>8.836650000000001</v>
+        <v>8.75704</v>
       </c>
       <c r="D105" t="n">
-        <v>38.585</v>
+        <v>38.3199</v>
       </c>
       <c r="E105" t="n">
-        <v>6.05021</v>
+        <v>5.93931</v>
       </c>
       <c r="F105" t="n">
-        <v>9.67934</v>
+        <v>9.639900000000001</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>10.3764</v>
+        <v>10.4004</v>
       </c>
       <c r="C106" t="n">
-        <v>9.992509999999999</v>
+        <v>9.86692</v>
       </c>
       <c r="D106" t="n">
-        <v>39.7928</v>
+        <v>39.8006</v>
       </c>
       <c r="E106" t="n">
-        <v>6.63848</v>
+        <v>6.48214</v>
       </c>
       <c r="F106" t="n">
-        <v>10.5269</v>
+        <v>10.4758</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>11.8302</v>
+        <v>11.8502</v>
       </c>
       <c r="C107" t="n">
-        <v>11.5109</v>
+        <v>11.423</v>
       </c>
       <c r="D107" t="n">
-        <v>30.4864</v>
+        <v>30.4582</v>
       </c>
       <c r="E107" t="n">
-        <v>4.67677</v>
+        <v>4.63468</v>
       </c>
       <c r="F107" t="n">
-        <v>6.88002</v>
+        <v>6.81223</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>14.012</v>
+        <v>14.0644</v>
       </c>
       <c r="C108" t="n">
-        <v>6.43585</v>
+        <v>6.41359</v>
       </c>
       <c r="D108" t="n">
-        <v>31.5222</v>
+        <v>31.3483</v>
       </c>
       <c r="E108" t="n">
-        <v>4.7904</v>
+        <v>4.74196</v>
       </c>
       <c r="F108" t="n">
-        <v>7.11294</v>
+        <v>7.02599</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>17.5422</v>
+        <v>17.2961</v>
       </c>
       <c r="C109" t="n">
-        <v>6.58028</v>
+        <v>6.53338</v>
       </c>
       <c r="D109" t="n">
-        <v>32.3978</v>
+        <v>32.1668</v>
       </c>
       <c r="E109" t="n">
-        <v>4.93524</v>
+        <v>4.8383</v>
       </c>
       <c r="F109" t="n">
-        <v>7.32273</v>
+        <v>7.24082</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.05217</v>
+        <v>7.11629</v>
       </c>
       <c r="C110" t="n">
-        <v>6.71469</v>
+        <v>6.67395</v>
       </c>
       <c r="D110" t="n">
-        <v>33.1248</v>
+        <v>33.0604</v>
       </c>
       <c r="E110" t="n">
-        <v>5.0548</v>
+        <v>4.96605</v>
       </c>
       <c r="F110" t="n">
-        <v>7.5425</v>
+        <v>7.47592</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.28746</v>
+        <v>7.33268</v>
       </c>
       <c r="C111" t="n">
-        <v>6.86078</v>
+        <v>6.82283</v>
       </c>
       <c r="D111" t="n">
-        <v>34.2435</v>
+        <v>34.0338</v>
       </c>
       <c r="E111" t="n">
-        <v>5.18259</v>
+        <v>5.08442</v>
       </c>
       <c r="F111" t="n">
-        <v>7.82108</v>
+        <v>7.72512</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.48679</v>
+        <v>7.50305</v>
       </c>
       <c r="C112" t="n">
-        <v>7.02284</v>
+        <v>6.98439</v>
       </c>
       <c r="D112" t="n">
-        <v>35.203</v>
+        <v>35.0157</v>
       </c>
       <c r="E112" t="n">
-        <v>5.33828</v>
+        <v>5.22876</v>
       </c>
       <c r="F112" t="n">
-        <v>8.040100000000001</v>
+        <v>7.98119</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>7.70739</v>
+        <v>7.74223</v>
       </c>
       <c r="C113" t="n">
-        <v>7.20343</v>
+        <v>7.15275</v>
       </c>
       <c r="D113" t="n">
-        <v>36.1293</v>
+        <v>36.1062</v>
       </c>
       <c r="E113" t="n">
-        <v>5.47471</v>
+        <v>5.36088</v>
       </c>
       <c r="F113" t="n">
-        <v>8.307930000000001</v>
+        <v>8.216620000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.008609999999999</v>
+        <v>8.030329999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>7.44333</v>
+        <v>7.37597</v>
       </c>
       <c r="D114" t="n">
-        <v>37.0391</v>
+        <v>36.969</v>
       </c>
       <c r="E114" t="n">
-        <v>5.62961</v>
+        <v>5.52528</v>
       </c>
       <c r="F114" t="n">
-        <v>8.608890000000001</v>
+        <v>8.51168</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>8.27847</v>
+        <v>8.34722</v>
       </c>
       <c r="C115" t="n">
-        <v>7.69126</v>
+        <v>7.64319</v>
       </c>
       <c r="D115" t="n">
-        <v>38.1584</v>
+        <v>38.1426</v>
       </c>
       <c r="E115" t="n">
-        <v>5.80419</v>
+        <v>5.69488</v>
       </c>
       <c r="F115" t="n">
-        <v>8.92506</v>
+        <v>8.84423</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>8.611980000000001</v>
+        <v>8.64791</v>
       </c>
       <c r="C116" t="n">
-        <v>8.014889999999999</v>
+        <v>7.95859</v>
       </c>
       <c r="D116" t="n">
-        <v>39.4888</v>
+        <v>39.2401</v>
       </c>
       <c r="E116" t="n">
-        <v>5.99634</v>
+        <v>5.91284</v>
       </c>
       <c r="F116" t="n">
-        <v>9.220789999999999</v>
+        <v>9.15748</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>9.02361</v>
+        <v>9.088789999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>8.45499</v>
+        <v>8.35487</v>
       </c>
       <c r="D117" t="n">
-        <v>40.3975</v>
+        <v>40.1948</v>
       </c>
       <c r="E117" t="n">
-        <v>6.27723</v>
+        <v>6.11615</v>
       </c>
       <c r="F117" t="n">
-        <v>9.665179999999999</v>
+        <v>9.57569</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>9.58695</v>
+        <v>9.625360000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>9.01666</v>
+        <v>8.898210000000001</v>
       </c>
       <c r="D118" t="n">
-        <v>41.9454</v>
+        <v>41.5792</v>
       </c>
       <c r="E118" t="n">
-        <v>6.58952</v>
+        <v>6.42564</v>
       </c>
       <c r="F118" t="n">
-        <v>10.1484</v>
+        <v>10.0536</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>10.2764</v>
+        <v>10.3346</v>
       </c>
       <c r="C119" t="n">
-        <v>9.77872</v>
+        <v>9.66155</v>
       </c>
       <c r="D119" t="n">
-        <v>43.0319</v>
+        <v>42.8643</v>
       </c>
       <c r="E119" t="n">
-        <v>6.95255</v>
+        <v>6.8142</v>
       </c>
       <c r="F119" t="n">
-        <v>10.7105</v>
+        <v>10.6439</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>11.2641</v>
+        <v>11.3003</v>
       </c>
       <c r="C120" t="n">
-        <v>10.8842</v>
+        <v>10.7636</v>
       </c>
       <c r="D120" t="n">
-        <v>44.2761</v>
+        <v>44.3082</v>
       </c>
       <c r="E120" t="n">
-        <v>7.50497</v>
+        <v>7.3519</v>
       </c>
       <c r="F120" t="n">
-        <v>11.5665</v>
+        <v>11.4556</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>12.6232</v>
+        <v>12.6807</v>
       </c>
       <c r="C121" t="n">
-        <v>12.4639</v>
+        <v>12.3232</v>
       </c>
       <c r="D121" t="n">
-        <v>33.2879</v>
+        <v>33.2584</v>
       </c>
       <c r="E121" t="n">
-        <v>5.0304</v>
+        <v>5.05697</v>
       </c>
       <c r="F121" t="n">
-        <v>7.41159</v>
+        <v>7.3144</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>14.6165</v>
+        <v>14.639</v>
       </c>
       <c r="C122" t="n">
-        <v>6.81715</v>
+        <v>6.77919</v>
       </c>
       <c r="D122" t="n">
-        <v>34.32</v>
+        <v>34.1798</v>
       </c>
       <c r="E122" t="n">
-        <v>5.15759</v>
+        <v>5.19249</v>
       </c>
       <c r="F122" t="n">
-        <v>7.6278</v>
+        <v>7.53738</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>17.844</v>
+        <v>17.9333</v>
       </c>
       <c r="C123" t="n">
-        <v>6.92494</v>
+        <v>6.89555</v>
       </c>
       <c r="D123" t="n">
-        <v>35.1104</v>
+        <v>34.9888</v>
       </c>
       <c r="E123" t="n">
-        <v>5.27713</v>
+        <v>5.31558</v>
       </c>
       <c r="F123" t="n">
-        <v>7.84306</v>
+        <v>7.75837</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>7.46987</v>
+        <v>7.48761</v>
       </c>
       <c r="C124" t="n">
-        <v>7.0998</v>
+        <v>7.04873</v>
       </c>
       <c r="D124" t="n">
-        <v>36.0874</v>
+        <v>35.8488</v>
       </c>
       <c r="E124" t="n">
-        <v>5.41599</v>
+        <v>5.48899</v>
       </c>
       <c r="F124" t="n">
-        <v>8.1187</v>
+        <v>8.007720000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>7.67051</v>
+        <v>7.64221</v>
       </c>
       <c r="C125" t="n">
-        <v>7.23049</v>
+        <v>7.18954</v>
       </c>
       <c r="D125" t="n">
-        <v>36.9911</v>
+        <v>36.8025</v>
       </c>
       <c r="E125" t="n">
-        <v>5.54918</v>
+        <v>5.60925</v>
       </c>
       <c r="F125" t="n">
-        <v>8.33014</v>
+        <v>8.248950000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>7.87417</v>
+        <v>7.87031</v>
       </c>
       <c r="C126" t="n">
-        <v>7.40444</v>
+        <v>7.37236</v>
       </c>
       <c r="D126" t="n">
-        <v>38.0258</v>
+        <v>37.6962</v>
       </c>
       <c r="E126" t="n">
-        <v>5.69132</v>
+        <v>5.82023</v>
       </c>
       <c r="F126" t="n">
-        <v>8.628489999999999</v>
+        <v>8.511699999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>8.05828</v>
+        <v>8.121510000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>7.59188</v>
+        <v>7.52488</v>
       </c>
       <c r="D127" t="n">
-        <v>39.0059</v>
+        <v>38.7763</v>
       </c>
       <c r="E127" t="n">
-        <v>5.84278</v>
+        <v>6.00598</v>
       </c>
       <c r="F127" t="n">
-        <v>8.893269999999999</v>
+        <v>8.813190000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>8.372820000000001</v>
+        <v>8.37885</v>
       </c>
       <c r="C128" t="n">
-        <v>7.84117</v>
+        <v>7.79567</v>
       </c>
       <c r="D128" t="n">
-        <v>39.8644</v>
+        <v>39.6903</v>
       </c>
       <c r="E128" t="n">
-        <v>5.98512</v>
+        <v>6.20414</v>
       </c>
       <c r="F128" t="n">
-        <v>9.22166</v>
+        <v>9.104939999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>8.64058</v>
+        <v>8.65875</v>
       </c>
       <c r="C129" t="n">
-        <v>8.10642</v>
+        <v>8.03979</v>
       </c>
       <c r="D129" t="n">
-        <v>40.9883</v>
+        <v>40.6733</v>
       </c>
       <c r="E129" t="n">
-        <v>6.1936</v>
+        <v>6.41255</v>
       </c>
       <c r="F129" t="n">
-        <v>9.5595</v>
+        <v>9.43009</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>9.0252</v>
+        <v>8.996449999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>8.423410000000001</v>
+        <v>8.357839999999999</v>
       </c>
       <c r="D130" t="n">
-        <v>41.9628</v>
+        <v>41.9314</v>
       </c>
       <c r="E130" t="n">
-        <v>6.3861</v>
+        <v>6.71721</v>
       </c>
       <c r="F130" t="n">
-        <v>9.925280000000001</v>
+        <v>9.80552</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>9.43956</v>
+        <v>9.428290000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>8.842639999999999</v>
+        <v>8.77726</v>
       </c>
       <c r="D131" t="n">
-        <v>43.1042</v>
+        <v>43.1343</v>
       </c>
       <c r="E131" t="n">
-        <v>6.68288</v>
+        <v>7.0553</v>
       </c>
       <c r="F131" t="n">
-        <v>10.4085</v>
+        <v>10.234</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>9.951309999999999</v>
+        <v>9.974869999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>9.445130000000001</v>
+        <v>9.33878</v>
       </c>
       <c r="D132" t="n">
-        <v>44.5559</v>
+        <v>44.2105</v>
       </c>
       <c r="E132" t="n">
-        <v>6.96817</v>
+        <v>7.37898</v>
       </c>
       <c r="F132" t="n">
-        <v>10.8742</v>
+        <v>10.7237</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>10.6305</v>
+        <v>10.6323</v>
       </c>
       <c r="C133" t="n">
-        <v>10.1607</v>
+        <v>10.1142</v>
       </c>
       <c r="D133" t="n">
-        <v>45.7218</v>
+        <v>45.4275</v>
       </c>
       <c r="E133" t="n">
-        <v>7.37907</v>
+        <v>7.80268</v>
       </c>
       <c r="F133" t="n">
-        <v>11.5693</v>
+        <v>11.2944</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>11.5936</v>
+        <v>11.5896</v>
       </c>
       <c r="C134" t="n">
-        <v>11.2512</v>
+        <v>11.1282</v>
       </c>
       <c r="D134" t="n">
-        <v>46.9746</v>
+        <v>46.743</v>
       </c>
       <c r="E134" t="n">
-        <v>7.9213</v>
+        <v>8.334849999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>12.3561</v>
+        <v>12.1238</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>12.8906</v>
+        <v>12.9253</v>
       </c>
       <c r="C135" t="n">
-        <v>12.7907</v>
+        <v>12.6742</v>
       </c>
       <c r="D135" t="n">
-        <v>34.7596</v>
+        <v>34.4994</v>
       </c>
       <c r="E135" t="n">
-        <v>11.6198</v>
+        <v>11.4239</v>
       </c>
       <c r="F135" t="n">
-        <v>14.2789</v>
+        <v>13.5537</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>14.7955</v>
+        <v>14.7766</v>
       </c>
       <c r="C136" t="n">
-        <v>15.5126</v>
+        <v>15.4273</v>
       </c>
       <c r="D136" t="n">
-        <v>35.7053</v>
+        <v>35.5017</v>
       </c>
       <c r="E136" t="n">
-        <v>11.7376</v>
+        <v>11.5013</v>
       </c>
       <c r="F136" t="n">
-        <v>14.5176</v>
+        <v>13.7319</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7412</v>
+        <v>17.7415</v>
       </c>
       <c r="C137" t="n">
-        <v>15.6982</v>
+        <v>15.5745</v>
       </c>
       <c r="D137" t="n">
-        <v>36.7302</v>
+        <v>36.2453</v>
       </c>
       <c r="E137" t="n">
-        <v>11.829</v>
+        <v>11.6787</v>
       </c>
       <c r="F137" t="n">
-        <v>14.6678</v>
+        <v>13.9452</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>13.3117</v>
+        <v>13.2494</v>
       </c>
       <c r="C138" t="n">
-        <v>15.8214</v>
+        <v>15.611</v>
       </c>
       <c r="D138" t="n">
-        <v>37.4791</v>
+        <v>37.1596</v>
       </c>
       <c r="E138" t="n">
-        <v>11.9034</v>
+        <v>11.8424</v>
       </c>
       <c r="F138" t="n">
-        <v>14.9281</v>
+        <v>14.1931</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>13.345</v>
+        <v>13.3883</v>
       </c>
       <c r="C139" t="n">
-        <v>15.9525</v>
+        <v>15.8408</v>
       </c>
       <c r="D139" t="n">
-        <v>38.4097</v>
+        <v>38.302</v>
       </c>
       <c r="E139" t="n">
-        <v>12.0122</v>
+        <v>11.9772</v>
       </c>
       <c r="F139" t="n">
-        <v>15.1665</v>
+        <v>14.3882</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.4941</v>
+        <v>13.4566</v>
       </c>
       <c r="C140" t="n">
-        <v>16.1421</v>
+        <v>16.0183</v>
       </c>
       <c r="D140" t="n">
-        <v>39.4052</v>
+        <v>39.2569</v>
       </c>
       <c r="E140" t="n">
-        <v>12.1738</v>
+        <v>12.133</v>
       </c>
       <c r="F140" t="n">
-        <v>15.4683</v>
+        <v>14.6459</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>13.6899</v>
+        <v>13.6761</v>
       </c>
       <c r="C141" t="n">
-        <v>16.2626</v>
+        <v>16.1917</v>
       </c>
       <c r="D141" t="n">
-        <v>40.5023</v>
+        <v>40.0818</v>
       </c>
       <c r="E141" t="n">
-        <v>12.2246</v>
+        <v>12.3029</v>
       </c>
       <c r="F141" t="n">
-        <v>15.7133</v>
+        <v>15.0011</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>13.8462</v>
+        <v>13.7947</v>
       </c>
       <c r="C142" t="n">
-        <v>16.4483</v>
+        <v>16.4171</v>
       </c>
       <c r="D142" t="n">
-        <v>41.5283</v>
+        <v>41.2639</v>
       </c>
       <c r="E142" t="n">
-        <v>12.4478</v>
+        <v>12.5059</v>
       </c>
       <c r="F142" t="n">
-        <v>16.0468</v>
+        <v>15.226</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>14.1914</v>
+        <v>14.0692</v>
       </c>
       <c r="C143" t="n">
-        <v>16.6716</v>
+        <v>16.7043</v>
       </c>
       <c r="D143" t="n">
-        <v>42.5433</v>
+        <v>42.3722</v>
       </c>
       <c r="E143" t="n">
-        <v>12.6162</v>
+        <v>12.6763</v>
       </c>
       <c r="F143" t="n">
-        <v>16.3944</v>
+        <v>15.6307</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.58003</v>
+        <v>2.53828</v>
       </c>
       <c r="C2" t="n">
-        <v>3.57639</v>
+        <v>3.57482</v>
       </c>
       <c r="D2" t="n">
-        <v>8.18013</v>
+        <v>8.23091</v>
       </c>
       <c r="E2" t="n">
-        <v>2.15548</v>
+        <v>2.12577</v>
       </c>
       <c r="F2" t="n">
-        <v>2.15039</v>
+        <v>2.23438</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.64692</v>
+        <v>2.60941</v>
       </c>
       <c r="C3" t="n">
-        <v>3.69991</v>
+        <v>3.70767</v>
       </c>
       <c r="D3" t="n">
-        <v>8.478199999999999</v>
+        <v>8.561529999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.25463</v>
+        <v>2.22749</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2647</v>
+        <v>2.32404</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.76653</v>
+        <v>2.70741</v>
       </c>
       <c r="C4" t="n">
-        <v>3.95729</v>
+        <v>3.94923</v>
       </c>
       <c r="D4" t="n">
-        <v>8.743830000000001</v>
+        <v>8.82948</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3366</v>
+        <v>2.3159</v>
       </c>
       <c r="F4" t="n">
-        <v>2.35595</v>
+        <v>2.41391</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1561</v>
+        <v>3.08547</v>
       </c>
       <c r="C5" t="n">
-        <v>4.386</v>
+        <v>4.38307</v>
       </c>
       <c r="D5" t="n">
-        <v>9.18031</v>
+        <v>9.26735</v>
       </c>
       <c r="E5" t="n">
-        <v>2.45972</v>
+        <v>2.40526</v>
       </c>
       <c r="F5" t="n">
-        <v>2.48484</v>
+        <v>2.50769</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.75016</v>
+        <v>3.7448</v>
       </c>
       <c r="C6" t="n">
-        <v>4.9474</v>
+        <v>4.94373</v>
       </c>
       <c r="D6" t="n">
-        <v>9.50009</v>
+        <v>9.623279999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>2.65004</v>
+        <v>2.59238</v>
       </c>
       <c r="F6" t="n">
-        <v>2.71792</v>
+        <v>2.701</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>5.13836</v>
+        <v>5.28376</v>
       </c>
       <c r="C7" t="n">
-        <v>6.07208</v>
+        <v>6.0993</v>
       </c>
       <c r="D7" t="n">
-        <v>6.97386</v>
+        <v>6.98646</v>
       </c>
       <c r="E7" t="n">
-        <v>1.91985</v>
+        <v>1.905</v>
       </c>
       <c r="F7" t="n">
-        <v>1.90859</v>
+        <v>2.00072</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>7.38722</v>
+        <v>7.27136</v>
       </c>
       <c r="C8" t="n">
-        <v>3.20868</v>
+        <v>3.22307</v>
       </c>
       <c r="D8" t="n">
-        <v>7.31945</v>
+        <v>7.3072</v>
       </c>
       <c r="E8" t="n">
-        <v>1.93434</v>
+        <v>1.92186</v>
       </c>
       <c r="F8" t="n">
-        <v>1.92106</v>
+        <v>2.01559</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>10.3572</v>
+        <v>9.77894</v>
       </c>
       <c r="C9" t="n">
-        <v>3.23378</v>
+        <v>3.23346</v>
       </c>
       <c r="D9" t="n">
-        <v>7.62132</v>
+        <v>7.66153</v>
       </c>
       <c r="E9" t="n">
-        <v>1.94906</v>
+        <v>1.93117</v>
       </c>
       <c r="F9" t="n">
-        <v>1.93975</v>
+        <v>2.02418</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.34244</v>
+        <v>2.38376</v>
       </c>
       <c r="C10" t="n">
-        <v>3.26322</v>
+        <v>3.26495</v>
       </c>
       <c r="D10" t="n">
-        <v>7.8764</v>
+        <v>7.99436</v>
       </c>
       <c r="E10" t="n">
-        <v>1.97753</v>
+        <v>1.95638</v>
       </c>
       <c r="F10" t="n">
-        <v>1.96686</v>
+        <v>2.04714</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.37377</v>
+        <v>2.3987</v>
       </c>
       <c r="C11" t="n">
-        <v>3.28846</v>
+        <v>3.31058</v>
       </c>
       <c r="D11" t="n">
-        <v>8.21115</v>
+        <v>8.29833</v>
       </c>
       <c r="E11" t="n">
-        <v>2.00096</v>
+        <v>1.97668</v>
       </c>
       <c r="F11" t="n">
-        <v>1.98913</v>
+        <v>2.06973</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.42395</v>
+        <v>2.43082</v>
       </c>
       <c r="C12" t="n">
-        <v>3.32773</v>
+        <v>3.34283</v>
       </c>
       <c r="D12" t="n">
-        <v>8.552809999999999</v>
+        <v>8.673170000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.02626</v>
+        <v>2.00378</v>
       </c>
       <c r="F12" t="n">
-        <v>2.015</v>
+        <v>2.08882</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.46576</v>
+        <v>2.474</v>
       </c>
       <c r="C13" t="n">
-        <v>3.3537</v>
+        <v>3.38004</v>
       </c>
       <c r="D13" t="n">
-        <v>8.848750000000001</v>
+        <v>8.94689</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0401</v>
+        <v>2.0224</v>
       </c>
       <c r="F13" t="n">
-        <v>2.03665</v>
+        <v>2.12041</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.52019</v>
+        <v>2.51179</v>
       </c>
       <c r="C14" t="n">
-        <v>3.44511</v>
+        <v>3.47339</v>
       </c>
       <c r="D14" t="n">
-        <v>9.14528</v>
+        <v>9.2895</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08973</v>
+        <v>2.05812</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0792</v>
+        <v>2.15771</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.60998</v>
+        <v>2.60018</v>
       </c>
       <c r="C15" t="n">
-        <v>3.51803</v>
+        <v>3.55053</v>
       </c>
       <c r="D15" t="n">
-        <v>9.405519999999999</v>
+        <v>9.55269</v>
       </c>
       <c r="E15" t="n">
-        <v>2.13005</v>
+        <v>2.10627</v>
       </c>
       <c r="F15" t="n">
-        <v>2.13555</v>
+        <v>2.20774</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.71517</v>
+        <v>2.689</v>
       </c>
       <c r="C16" t="n">
-        <v>3.67816</v>
+        <v>3.70696</v>
       </c>
       <c r="D16" t="n">
-        <v>9.75953</v>
+        <v>9.85993</v>
       </c>
       <c r="E16" t="n">
-        <v>2.19197</v>
+        <v>2.15715</v>
       </c>
       <c r="F16" t="n">
-        <v>2.191</v>
+        <v>2.25055</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>2.8876</v>
+        <v>2.82137</v>
       </c>
       <c r="C17" t="n">
-        <v>3.8576</v>
+        <v>3.85275</v>
       </c>
       <c r="D17" t="n">
-        <v>10.0459</v>
+        <v>10.2125</v>
       </c>
       <c r="E17" t="n">
-        <v>2.26453</v>
+        <v>2.2192</v>
       </c>
       <c r="F17" t="n">
-        <v>2.27003</v>
+        <v>2.32389</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.14995</v>
+        <v>3.0918</v>
       </c>
       <c r="C18" t="n">
-        <v>4.05925</v>
+        <v>4.10031</v>
       </c>
       <c r="D18" t="n">
-        <v>10.4017</v>
+        <v>10.4643</v>
       </c>
       <c r="E18" t="n">
-        <v>2.38255</v>
+        <v>2.33351</v>
       </c>
       <c r="F18" t="n">
-        <v>2.39458</v>
+        <v>2.43686</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.53958</v>
+        <v>3.45858</v>
       </c>
       <c r="C19" t="n">
-        <v>4.56919</v>
+        <v>4.56741</v>
       </c>
       <c r="D19" t="n">
-        <v>10.7048</v>
+        <v>10.837</v>
       </c>
       <c r="E19" t="n">
-        <v>2.53206</v>
+        <v>2.47824</v>
       </c>
       <c r="F19" t="n">
-        <v>2.58137</v>
+        <v>2.60188</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.28591</v>
+        <v>4.20932</v>
       </c>
       <c r="C20" t="n">
-        <v>5.21428</v>
+        <v>5.24584</v>
       </c>
       <c r="D20" t="n">
-        <v>10.9963</v>
+        <v>11.11</v>
       </c>
       <c r="E20" t="n">
-        <v>2.79336</v>
+        <v>2.75977</v>
       </c>
       <c r="F20" t="n">
-        <v>2.86042</v>
+        <v>2.90383</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.40478</v>
+        <v>5.28013</v>
       </c>
       <c r="C21" t="n">
-        <v>6.13769</v>
+        <v>6.13858</v>
       </c>
       <c r="D21" t="n">
-        <v>8.04541</v>
+        <v>8.09337</v>
       </c>
       <c r="E21" t="n">
-        <v>1.96294</v>
+        <v>1.94721</v>
       </c>
       <c r="F21" t="n">
-        <v>1.98345</v>
+        <v>2.05765</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>7.17769</v>
+        <v>7.08745</v>
       </c>
       <c r="C22" t="n">
-        <v>3.27947</v>
+        <v>3.27039</v>
       </c>
       <c r="D22" t="n">
-        <v>8.33675</v>
+        <v>8.416320000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.97033</v>
+        <v>1.9649</v>
       </c>
       <c r="F22" t="n">
-        <v>2.013</v>
+        <v>2.08873</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>9.60375</v>
+        <v>9.75916</v>
       </c>
       <c r="C23" t="n">
-        <v>3.27856</v>
+        <v>3.28315</v>
       </c>
       <c r="D23" t="n">
-        <v>8.62594</v>
+        <v>8.69651</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0037</v>
+        <v>1.97723</v>
       </c>
       <c r="F23" t="n">
-        <v>2.03616</v>
+        <v>2.11409</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.47819</v>
+        <v>2.46939</v>
       </c>
       <c r="C24" t="n">
-        <v>3.34289</v>
+        <v>3.32505</v>
       </c>
       <c r="D24" t="n">
-        <v>8.95735</v>
+        <v>9.01562</v>
       </c>
       <c r="E24" t="n">
-        <v>2.01324</v>
+        <v>2.01738</v>
       </c>
       <c r="F24" t="n">
-        <v>2.08003</v>
+        <v>2.16311</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.51078</v>
+        <v>2.493</v>
       </c>
       <c r="C25" t="n">
-        <v>3.33435</v>
+        <v>3.34866</v>
       </c>
       <c r="D25" t="n">
-        <v>9.26765</v>
+        <v>9.33132</v>
       </c>
       <c r="E25" t="n">
-        <v>2.04933</v>
+        <v>2.03607</v>
       </c>
       <c r="F25" t="n">
-        <v>2.13275</v>
+        <v>2.2088</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.58328</v>
+        <v>2.5566</v>
       </c>
       <c r="C26" t="n">
-        <v>3.42354</v>
+        <v>3.40626</v>
       </c>
       <c r="D26" t="n">
-        <v>9.57161</v>
+        <v>9.65451</v>
       </c>
       <c r="E26" t="n">
-        <v>2.08714</v>
+        <v>2.06651</v>
       </c>
       <c r="F26" t="n">
-        <v>2.19202</v>
+        <v>2.26541</v>
       </c>
     </row>
     <row r="27">
@@ -5582,16 +5582,16 @@
         <v>2.61581</v>
       </c>
       <c r="C27" t="n">
-        <v>3.43787</v>
+        <v>3.4359</v>
       </c>
       <c r="D27" t="n">
-        <v>9.884359999999999</v>
+        <v>9.972910000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>2.1084</v>
+        <v>2.09282</v>
       </c>
       <c r="F27" t="n">
-        <v>2.24462</v>
+        <v>2.31823</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>2.7071</v>
+        <v>2.6669</v>
       </c>
       <c r="C28" t="n">
-        <v>3.50395</v>
+        <v>3.493</v>
       </c>
       <c r="D28" t="n">
-        <v>10.1606</v>
+        <v>10.2222</v>
       </c>
       <c r="E28" t="n">
-        <v>2.15209</v>
+        <v>2.14541</v>
       </c>
       <c r="F28" t="n">
-        <v>2.31571</v>
+        <v>2.3804</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>2.77945</v>
+        <v>2.77812</v>
       </c>
       <c r="C29" t="n">
-        <v>3.6006</v>
+        <v>3.62246</v>
       </c>
       <c r="D29" t="n">
-        <v>10.4903</v>
+        <v>10.5372</v>
       </c>
       <c r="E29" t="n">
-        <v>2.21577</v>
+        <v>2.20726</v>
       </c>
       <c r="F29" t="n">
-        <v>2.39635</v>
+        <v>2.46569</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>2.93489</v>
+        <v>2.92872</v>
       </c>
       <c r="C30" t="n">
-        <v>3.72051</v>
+        <v>3.72598</v>
       </c>
       <c r="D30" t="n">
-        <v>10.768</v>
+        <v>10.8467</v>
       </c>
       <c r="E30" t="n">
-        <v>2.26333</v>
+        <v>2.25762</v>
       </c>
       <c r="F30" t="n">
-        <v>2.49074</v>
+        <v>2.52416</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.12186</v>
+        <v>3.14381</v>
       </c>
       <c r="C31" t="n">
-        <v>3.86336</v>
+        <v>3.88109</v>
       </c>
       <c r="D31" t="n">
-        <v>11.0431</v>
+        <v>11.1252</v>
       </c>
       <c r="E31" t="n">
-        <v>2.32879</v>
+        <v>2.32061</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5526</v>
+        <v>2.606</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.37758</v>
+        <v>3.35795</v>
       </c>
       <c r="C32" t="n">
-        <v>4.05485</v>
+        <v>4.08348</v>
       </c>
       <c r="D32" t="n">
-        <v>11.2901</v>
+        <v>11.327</v>
       </c>
       <c r="E32" t="n">
-        <v>2.43693</v>
+        <v>2.41876</v>
       </c>
       <c r="F32" t="n">
-        <v>2.66993</v>
+        <v>2.70274</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>3.88526</v>
+        <v>3.79086</v>
       </c>
       <c r="C33" t="n">
-        <v>4.48908</v>
+        <v>4.50032</v>
       </c>
       <c r="D33" t="n">
-        <v>11.5911</v>
+        <v>11.6834</v>
       </c>
       <c r="E33" t="n">
-        <v>2.60332</v>
+        <v>2.56031</v>
       </c>
       <c r="F33" t="n">
-        <v>2.83961</v>
+        <v>2.86778</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.51539</v>
+        <v>4.54162</v>
       </c>
       <c r="C34" t="n">
-        <v>5.1349</v>
+        <v>5.10739</v>
       </c>
       <c r="D34" t="n">
-        <v>11.8929</v>
+        <v>11.9268</v>
       </c>
       <c r="E34" t="n">
-        <v>2.86279</v>
+        <v>2.83605</v>
       </c>
       <c r="F34" t="n">
-        <v>3.08507</v>
+        <v>3.11561</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.55751</v>
+        <v>5.59921</v>
       </c>
       <c r="C35" t="n">
-        <v>5.9573</v>
+        <v>6.05068</v>
       </c>
       <c r="D35" t="n">
-        <v>8.39142</v>
+        <v>8.44624</v>
       </c>
       <c r="E35" t="n">
-        <v>1.98704</v>
+        <v>1.99298</v>
       </c>
       <c r="F35" t="n">
-        <v>2.17989</v>
+        <v>2.24226</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.22098</v>
+        <v>7.24712</v>
       </c>
       <c r="C36" t="n">
-        <v>7.26768</v>
+        <v>7.35811</v>
       </c>
       <c r="D36" t="n">
-        <v>8.68843</v>
+        <v>8.766719999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>2.01375</v>
+        <v>2.01261</v>
       </c>
       <c r="F36" t="n">
-        <v>2.20642</v>
+        <v>2.28236</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>9.62777</v>
+        <v>9.629390000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>3.33888</v>
+        <v>3.31088</v>
       </c>
       <c r="D37" t="n">
-        <v>9.053419999999999</v>
+        <v>9.09272</v>
       </c>
       <c r="E37" t="n">
-        <v>2.04277</v>
+        <v>2.03626</v>
       </c>
       <c r="F37" t="n">
-        <v>2.24113</v>
+        <v>2.3021</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.50949</v>
+        <v>2.51258</v>
       </c>
       <c r="C38" t="n">
-        <v>3.34215</v>
+        <v>3.3353</v>
       </c>
       <c r="D38" t="n">
-        <v>9.355270000000001</v>
+        <v>9.398680000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>2.06535</v>
+        <v>2.06021</v>
       </c>
       <c r="F38" t="n">
-        <v>2.26816</v>
+        <v>2.32759</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.5524</v>
+        <v>2.54653</v>
       </c>
       <c r="C39" t="n">
-        <v>3.35932</v>
+        <v>3.36312</v>
       </c>
       <c r="D39" t="n">
-        <v>9.66386</v>
+        <v>9.740970000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>2.09478</v>
+        <v>2.08424</v>
       </c>
       <c r="F39" t="n">
-        <v>2.31873</v>
+        <v>2.37111</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.61814</v>
+        <v>2.60063</v>
       </c>
       <c r="C40" t="n">
-        <v>3.39136</v>
+        <v>3.40677</v>
       </c>
       <c r="D40" t="n">
-        <v>9.985049999999999</v>
+        <v>10.066</v>
       </c>
       <c r="E40" t="n">
-        <v>2.12069</v>
+        <v>2.11951</v>
       </c>
       <c r="F40" t="n">
-        <v>2.33805</v>
+        <v>2.41287</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>2.63821</v>
+        <v>2.68423</v>
       </c>
       <c r="C41" t="n">
-        <v>3.44225</v>
+        <v>3.46005</v>
       </c>
       <c r="D41" t="n">
-        <v>10.262</v>
+        <v>10.3617</v>
       </c>
       <c r="E41" t="n">
-        <v>2.15325</v>
+        <v>2.15315</v>
       </c>
       <c r="F41" t="n">
-        <v>2.37374</v>
+        <v>2.45032</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>2.7232</v>
+        <v>2.72898</v>
       </c>
       <c r="C42" t="n">
-        <v>3.49723</v>
+        <v>3.5095</v>
       </c>
       <c r="D42" t="n">
-        <v>10.5749</v>
+        <v>10.6464</v>
       </c>
       <c r="E42" t="n">
-        <v>2.19167</v>
+        <v>2.17932</v>
       </c>
       <c r="F42" t="n">
-        <v>2.42497</v>
+        <v>2.48292</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>2.84564</v>
+        <v>2.82924</v>
       </c>
       <c r="C43" t="n">
-        <v>3.58534</v>
+        <v>3.57636</v>
       </c>
       <c r="D43" t="n">
-        <v>10.8903</v>
+        <v>10.9589</v>
       </c>
       <c r="E43" t="n">
-        <v>2.23567</v>
+        <v>2.22852</v>
       </c>
       <c r="F43" t="n">
-        <v>2.48467</v>
+        <v>2.54504</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>2.93601</v>
+        <v>2.9699</v>
       </c>
       <c r="C44" t="n">
-        <v>3.73135</v>
+        <v>3.7078</v>
       </c>
       <c r="D44" t="n">
-        <v>11.1451</v>
+        <v>11.2153</v>
       </c>
       <c r="E44" t="n">
-        <v>2.30337</v>
+        <v>2.29021</v>
       </c>
       <c r="F44" t="n">
-        <v>2.56468</v>
+        <v>2.60941</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.12912</v>
+        <v>3.11676</v>
       </c>
       <c r="C45" t="n">
-        <v>3.94238</v>
+        <v>3.88671</v>
       </c>
       <c r="D45" t="n">
-        <v>11.4129</v>
+        <v>11.4833</v>
       </c>
       <c r="E45" t="n">
-        <v>2.3759</v>
+        <v>2.36633</v>
       </c>
       <c r="F45" t="n">
-        <v>2.63621</v>
+        <v>2.68483</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>3.38828</v>
+        <v>3.37112</v>
       </c>
       <c r="C46" t="n">
-        <v>4.12384</v>
+        <v>4.11883</v>
       </c>
       <c r="D46" t="n">
-        <v>11.6826</v>
+        <v>11.7481</v>
       </c>
       <c r="E46" t="n">
-        <v>2.47792</v>
+        <v>2.46708</v>
       </c>
       <c r="F46" t="n">
-        <v>2.73906</v>
+        <v>2.77596</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>3.76092</v>
+        <v>3.75636</v>
       </c>
       <c r="C47" t="n">
-        <v>4.49619</v>
+        <v>4.47686</v>
       </c>
       <c r="D47" t="n">
-        <v>11.8756</v>
+        <v>11.9992</v>
       </c>
       <c r="E47" t="n">
-        <v>2.64483</v>
+        <v>2.63663</v>
       </c>
       <c r="F47" t="n">
-        <v>2.92482</v>
+        <v>2.95324</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.41306</v>
+        <v>4.41655</v>
       </c>
       <c r="C48" t="n">
-        <v>5.01755</v>
+        <v>5.03124</v>
       </c>
       <c r="D48" t="n">
-        <v>12.2167</v>
+        <v>12.2727</v>
       </c>
       <c r="E48" t="n">
-        <v>2.90745</v>
+        <v>2.88627</v>
       </c>
       <c r="F48" t="n">
-        <v>3.15599</v>
+        <v>3.18673</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.23881</v>
+        <v>5.30385</v>
       </c>
       <c r="C49" t="n">
-        <v>5.7984</v>
+        <v>5.83282</v>
       </c>
       <c r="D49" t="n">
-        <v>12.4748</v>
+        <v>12.5355</v>
       </c>
       <c r="E49" t="n">
-        <v>3.28353</v>
+        <v>3.2577</v>
       </c>
       <c r="F49" t="n">
-        <v>3.51782</v>
+        <v>3.54638</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>6.50401</v>
+        <v>6.55403</v>
       </c>
       <c r="C50" t="n">
-        <v>7.13126</v>
+        <v>7.08803</v>
       </c>
       <c r="D50" t="n">
-        <v>8.802009999999999</v>
+        <v>8.88054</v>
       </c>
       <c r="E50" t="n">
-        <v>2.04508</v>
+        <v>2.03589</v>
       </c>
       <c r="F50" t="n">
-        <v>2.26467</v>
+        <v>2.3127</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>8.401759999999999</v>
+        <v>8.59243</v>
       </c>
       <c r="C51" t="n">
-        <v>3.33654</v>
+        <v>3.35584</v>
       </c>
       <c r="D51" t="n">
-        <v>9.13499</v>
+        <v>9.212960000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>2.06761</v>
+        <v>2.06208</v>
       </c>
       <c r="F51" t="n">
-        <v>2.29316</v>
+        <v>2.33702</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>11.5868</v>
+        <v>11.5972</v>
       </c>
       <c r="C52" t="n">
-        <v>3.37927</v>
+        <v>3.37057</v>
       </c>
       <c r="D52" t="n">
-        <v>9.489050000000001</v>
+        <v>9.561360000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>2.09292</v>
+        <v>2.0835</v>
       </c>
       <c r="F52" t="n">
-        <v>2.32308</v>
+        <v>2.35395</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>2.57923</v>
+        <v>2.55577</v>
       </c>
       <c r="C53" t="n">
-        <v>3.39775</v>
+        <v>3.4192</v>
       </c>
       <c r="D53" t="n">
-        <v>9.79426</v>
+        <v>9.87618</v>
       </c>
       <c r="E53" t="n">
-        <v>2.11741</v>
+        <v>2.11146</v>
       </c>
       <c r="F53" t="n">
-        <v>2.36905</v>
+        <v>2.38892</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>2.60756</v>
+        <v>2.60864</v>
       </c>
       <c r="C54" t="n">
-        <v>3.42631</v>
+        <v>3.44507</v>
       </c>
       <c r="D54" t="n">
-        <v>10.1186</v>
+        <v>10.2076</v>
       </c>
       <c r="E54" t="n">
-        <v>2.14193</v>
+        <v>2.12956</v>
       </c>
       <c r="F54" t="n">
-        <v>2.39436</v>
+        <v>2.4406</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>2.66749</v>
+        <v>2.67188</v>
       </c>
       <c r="C55" t="n">
-        <v>3.46505</v>
+        <v>3.48448</v>
       </c>
       <c r="D55" t="n">
-        <v>10.435</v>
+        <v>10.5286</v>
       </c>
       <c r="E55" t="n">
-        <v>2.17819</v>
+        <v>2.17559</v>
       </c>
       <c r="F55" t="n">
-        <v>2.45197</v>
+        <v>2.49365</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>2.73218</v>
+        <v>2.75138</v>
       </c>
       <c r="C56" t="n">
-        <v>3.54866</v>
+        <v>3.53511</v>
       </c>
       <c r="D56" t="n">
-        <v>10.7539</v>
+        <v>10.8427</v>
       </c>
       <c r="E56" t="n">
-        <v>2.22981</v>
+        <v>2.21617</v>
       </c>
       <c r="F56" t="n">
-        <v>2.49232</v>
+        <v>2.52805</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>2.8466</v>
+        <v>2.80622</v>
       </c>
       <c r="C57" t="n">
-        <v>3.59656</v>
+        <v>3.59445</v>
       </c>
       <c r="D57" t="n">
-        <v>11.0445</v>
+        <v>11.1583</v>
       </c>
       <c r="E57" t="n">
-        <v>2.28065</v>
+        <v>2.26351</v>
       </c>
       <c r="F57" t="n">
-        <v>2.57414</v>
+        <v>2.58724</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>2.97597</v>
+        <v>2.9666</v>
       </c>
       <c r="C58" t="n">
-        <v>3.72922</v>
+        <v>3.74339</v>
       </c>
       <c r="D58" t="n">
-        <v>11.3297</v>
+        <v>11.4306</v>
       </c>
       <c r="E58" t="n">
-        <v>2.34311</v>
+        <v>2.31638</v>
       </c>
       <c r="F58" t="n">
-        <v>2.63589</v>
+        <v>2.66919</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.14128</v>
+        <v>3.13195</v>
       </c>
       <c r="C59" t="n">
-        <v>3.87327</v>
+        <v>3.84954</v>
       </c>
       <c r="D59" t="n">
-        <v>11.5727</v>
+        <v>11.7157</v>
       </c>
       <c r="E59" t="n">
-        <v>2.4061</v>
+        <v>2.40169</v>
       </c>
       <c r="F59" t="n">
-        <v>2.74029</v>
+        <v>2.76893</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>3.42902</v>
+        <v>3.39402</v>
       </c>
       <c r="C60" t="n">
-        <v>4.1191</v>
+        <v>4.08655</v>
       </c>
       <c r="D60" t="n">
-        <v>11.8692</v>
+        <v>12.0323</v>
       </c>
       <c r="E60" t="n">
-        <v>2.52033</v>
+        <v>2.4933</v>
       </c>
       <c r="F60" t="n">
-        <v>2.84434</v>
+        <v>2.87146</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>3.74759</v>
+        <v>3.75524</v>
       </c>
       <c r="C61" t="n">
-        <v>4.40732</v>
+        <v>4.42733</v>
       </c>
       <c r="D61" t="n">
-        <v>12.1826</v>
+        <v>12.4399</v>
       </c>
       <c r="E61" t="n">
-        <v>2.67654</v>
+        <v>2.63699</v>
       </c>
       <c r="F61" t="n">
-        <v>2.98811</v>
+        <v>3.03808</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.23026</v>
+        <v>4.24023</v>
       </c>
       <c r="C62" t="n">
-        <v>4.92472</v>
+        <v>4.9045</v>
       </c>
       <c r="D62" t="n">
-        <v>12.5186</v>
+        <v>12.7716</v>
       </c>
       <c r="E62" t="n">
-        <v>2.88739</v>
+        <v>2.84241</v>
       </c>
       <c r="F62" t="n">
-        <v>3.2043</v>
+        <v>3.25531</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.92914</v>
+        <v>4.98615</v>
       </c>
       <c r="C63" t="n">
-        <v>5.60179</v>
+        <v>5.703</v>
       </c>
       <c r="D63" t="n">
-        <v>12.8702</v>
+        <v>13.0522</v>
       </c>
       <c r="E63" t="n">
-        <v>3.23636</v>
+        <v>3.21973</v>
       </c>
       <c r="F63" t="n">
-        <v>3.56279</v>
+        <v>3.60761</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.14375</v>
+        <v>6.12993</v>
       </c>
       <c r="C64" t="n">
-        <v>6.76233</v>
+        <v>6.8254</v>
       </c>
       <c r="D64" t="n">
-        <v>9.0959</v>
+        <v>9.08677</v>
       </c>
       <c r="E64" t="n">
-        <v>2.41399</v>
+        <v>2.42093</v>
       </c>
       <c r="F64" t="n">
-        <v>2.69564</v>
+        <v>2.70647</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>7.8322</v>
+        <v>7.92917</v>
       </c>
       <c r="C65" t="n">
-        <v>3.79246</v>
+        <v>3.8101</v>
       </c>
       <c r="D65" t="n">
-        <v>9.48133</v>
+        <v>9.44422</v>
       </c>
       <c r="E65" t="n">
-        <v>2.43638</v>
+        <v>2.44009</v>
       </c>
       <c r="F65" t="n">
-        <v>2.70612</v>
+        <v>2.7408</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>10.8177</v>
+        <v>10.729</v>
       </c>
       <c r="C66" t="n">
-        <v>3.81831</v>
+        <v>3.81937</v>
       </c>
       <c r="D66" t="n">
-        <v>9.88734</v>
+        <v>10.0747</v>
       </c>
       <c r="E66" t="n">
-        <v>2.47092</v>
+        <v>2.44492</v>
       </c>
       <c r="F66" t="n">
-        <v>2.75715</v>
+        <v>2.77155</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>2.89862</v>
+        <v>2.89716</v>
       </c>
       <c r="C67" t="n">
-        <v>3.86687</v>
+        <v>3.85299</v>
       </c>
       <c r="D67" t="n">
-        <v>10.3726</v>
+        <v>10.3246</v>
       </c>
       <c r="E67" t="n">
-        <v>2.50571</v>
+        <v>2.4813</v>
       </c>
       <c r="F67" t="n">
-        <v>2.81804</v>
+        <v>2.83041</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>2.93835</v>
+        <v>2.93542</v>
       </c>
       <c r="C68" t="n">
-        <v>3.88401</v>
+        <v>3.89884</v>
       </c>
       <c r="D68" t="n">
-        <v>11.072</v>
+        <v>10.884</v>
       </c>
       <c r="E68" t="n">
-        <v>2.52961</v>
+        <v>2.511</v>
       </c>
       <c r="F68" t="n">
-        <v>2.85353</v>
+        <v>2.8799</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.01582</v>
+        <v>2.98057</v>
       </c>
       <c r="C69" t="n">
-        <v>3.97554</v>
+        <v>3.96561</v>
       </c>
       <c r="D69" t="n">
-        <v>11.294</v>
+        <v>11.442</v>
       </c>
       <c r="E69" t="n">
-        <v>2.5452</v>
+        <v>2.5418</v>
       </c>
       <c r="F69" t="n">
-        <v>2.92363</v>
+        <v>2.93048</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.09072</v>
+        <v>3.07652</v>
       </c>
       <c r="C70" t="n">
-        <v>4.03269</v>
+        <v>3.95312</v>
       </c>
       <c r="D70" t="n">
-        <v>12.1313</v>
+        <v>11.8496</v>
       </c>
       <c r="E70" t="n">
-        <v>2.59218</v>
+        <v>2.56148</v>
       </c>
       <c r="F70" t="n">
-        <v>2.97852</v>
+        <v>2.99146</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.17493</v>
+        <v>3.16565</v>
       </c>
       <c r="C71" t="n">
-        <v>4.03144</v>
+        <v>4.05849</v>
       </c>
       <c r="D71" t="n">
-        <v>12.4639</v>
+        <v>12.0731</v>
       </c>
       <c r="E71" t="n">
-        <v>2.63516</v>
+        <v>2.60645</v>
       </c>
       <c r="F71" t="n">
-        <v>3.0568</v>
+        <v>3.07669</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.28912</v>
+        <v>3.27604</v>
       </c>
       <c r="C72" t="n">
-        <v>4.18883</v>
+        <v>4.19188</v>
       </c>
       <c r="D72" t="n">
-        <v>12.963</v>
+        <v>12.8426</v>
       </c>
       <c r="E72" t="n">
-        <v>2.69626</v>
+        <v>2.66522</v>
       </c>
       <c r="F72" t="n">
-        <v>3.16527</v>
+        <v>3.12905</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>3.4419</v>
+        <v>3.42248</v>
       </c>
       <c r="C73" t="n">
-        <v>4.27922</v>
+        <v>4.33412</v>
       </c>
       <c r="D73" t="n">
-        <v>13.9428</v>
+        <v>13.1356</v>
       </c>
       <c r="E73" t="n">
-        <v>2.76485</v>
+        <v>2.74729</v>
       </c>
       <c r="F73" t="n">
-        <v>3.25391</v>
+        <v>3.23906</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>3.65505</v>
+        <v>3.66077</v>
       </c>
       <c r="C74" t="n">
-        <v>4.48049</v>
+        <v>4.56523</v>
       </c>
       <c r="D74" t="n">
-        <v>15.0016</v>
+        <v>13.9634</v>
       </c>
       <c r="E74" t="n">
-        <v>2.84903</v>
+        <v>2.84195</v>
       </c>
       <c r="F74" t="n">
-        <v>3.37032</v>
+        <v>3.37527</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>3.93866</v>
+        <v>3.97518</v>
       </c>
       <c r="C75" t="n">
-        <v>4.84691</v>
+        <v>4.80059</v>
       </c>
       <c r="D75" t="n">
-        <v>15.7683</v>
+        <v>15.3542</v>
       </c>
       <c r="E75" t="n">
-        <v>3.03012</v>
+        <v>2.97633</v>
       </c>
       <c r="F75" t="n">
-        <v>3.53748</v>
+        <v>3.53802</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>4.42363</v>
+        <v>4.41068</v>
       </c>
       <c r="C76" t="n">
-        <v>5.24099</v>
+        <v>5.3011</v>
       </c>
       <c r="D76" t="n">
-        <v>17.1099</v>
+        <v>16.7966</v>
       </c>
       <c r="E76" t="n">
-        <v>3.24548</v>
+        <v>3.17182</v>
       </c>
       <c r="F76" t="n">
-        <v>3.76494</v>
+        <v>3.7721</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.13341</v>
+        <v>5.09308</v>
       </c>
       <c r="C77" t="n">
-        <v>5.96932</v>
+        <v>5.94249</v>
       </c>
       <c r="D77" t="n">
-        <v>17.7973</v>
+        <v>17.6402</v>
       </c>
       <c r="E77" t="n">
-        <v>3.56682</v>
+        <v>3.48785</v>
       </c>
       <c r="F77" t="n">
-        <v>4.08498</v>
+        <v>4.10504</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.11537</v>
+        <v>6.14893</v>
       </c>
       <c r="C78" t="n">
-        <v>6.98785</v>
+        <v>6.9881</v>
       </c>
       <c r="D78" t="n">
-        <v>15.4315</v>
+        <v>15.4419</v>
       </c>
       <c r="E78" t="n">
-        <v>2.67702</v>
+        <v>2.69396</v>
       </c>
       <c r="F78" t="n">
-        <v>3.14819</v>
+        <v>3.14737</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.66491</v>
+        <v>7.73313</v>
       </c>
       <c r="C79" t="n">
-        <v>4.13569</v>
+        <v>4.16818</v>
       </c>
       <c r="D79" t="n">
-        <v>16.5782</v>
+        <v>16.5848</v>
       </c>
       <c r="E79" t="n">
-        <v>2.70859</v>
+        <v>2.70959</v>
       </c>
       <c r="F79" t="n">
-        <v>3.19509</v>
+        <v>3.18273</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>10.3026</v>
+        <v>10.3909</v>
       </c>
       <c r="C80" t="n">
-        <v>4.19603</v>
+        <v>4.18985</v>
       </c>
       <c r="D80" t="n">
-        <v>17.6543</v>
+        <v>17.6715</v>
       </c>
       <c r="E80" t="n">
-        <v>2.71913</v>
+        <v>2.722</v>
       </c>
       <c r="F80" t="n">
-        <v>3.24419</v>
+        <v>3.25548</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>3.487</v>
+        <v>3.47443</v>
       </c>
       <c r="C81" t="n">
-        <v>4.22376</v>
+        <v>4.22235</v>
       </c>
       <c r="D81" t="n">
-        <v>18.7663</v>
+        <v>18.7522</v>
       </c>
       <c r="E81" t="n">
-        <v>2.75206</v>
+        <v>2.73982</v>
       </c>
       <c r="F81" t="n">
-        <v>3.28636</v>
+        <v>3.29411</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>3.51506</v>
+        <v>3.50946</v>
       </c>
       <c r="C82" t="n">
-        <v>4.30012</v>
+        <v>4.26058</v>
       </c>
       <c r="D82" t="n">
-        <v>19.7122</v>
+        <v>19.7388</v>
       </c>
       <c r="E82" t="n">
-        <v>2.77927</v>
+        <v>2.77957</v>
       </c>
       <c r="F82" t="n">
-        <v>3.33176</v>
+        <v>3.34733</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>3.60626</v>
+        <v>3.58224</v>
       </c>
       <c r="C83" t="n">
-        <v>4.30558</v>
+        <v>4.28365</v>
       </c>
       <c r="D83" t="n">
-        <v>20.816</v>
+        <v>20.8409</v>
       </c>
       <c r="E83" t="n">
-        <v>2.80822</v>
+        <v>2.79587</v>
       </c>
       <c r="F83" t="n">
-        <v>3.37668</v>
+        <v>3.38853</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>3.67335</v>
+        <v>3.65096</v>
       </c>
       <c r="C84" t="n">
-        <v>4.34066</v>
+        <v>4.33308</v>
       </c>
       <c r="D84" t="n">
-        <v>21.93</v>
+        <v>21.9215</v>
       </c>
       <c r="E84" t="n">
-        <v>2.83701</v>
+        <v>2.83878</v>
       </c>
       <c r="F84" t="n">
-        <v>3.46726</v>
+        <v>3.47127</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>3.77169</v>
+        <v>3.77162</v>
       </c>
       <c r="C85" t="n">
-        <v>4.46508</v>
+        <v>4.41376</v>
       </c>
       <c r="D85" t="n">
-        <v>23.0191</v>
+        <v>22.9446</v>
       </c>
       <c r="E85" t="n">
-        <v>2.87858</v>
+        <v>2.87691</v>
       </c>
       <c r="F85" t="n">
-        <v>3.53063</v>
+        <v>3.54742</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>3.87256</v>
+        <v>3.87804</v>
       </c>
       <c r="C86" t="n">
-        <v>4.56774</v>
+        <v>4.53015</v>
       </c>
       <c r="D86" t="n">
-        <v>24.0735</v>
+        <v>24.0481</v>
       </c>
       <c r="E86" t="n">
-        <v>2.96029</v>
+        <v>2.90703</v>
       </c>
       <c r="F86" t="n">
-        <v>3.64677</v>
+        <v>3.64298</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.03886</v>
+        <v>4.0051</v>
       </c>
       <c r="C87" t="n">
-        <v>4.72955</v>
+        <v>4.69233</v>
       </c>
       <c r="D87" t="n">
-        <v>25.2927</v>
+        <v>25.3255</v>
       </c>
       <c r="E87" t="n">
-        <v>3.06633</v>
+        <v>3.0039</v>
       </c>
       <c r="F87" t="n">
-        <v>3.77564</v>
+        <v>3.77487</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.24658</v>
+        <v>4.24931</v>
       </c>
       <c r="C88" t="n">
-        <v>4.94336</v>
+        <v>4.98819</v>
       </c>
       <c r="D88" t="n">
-        <v>26.4783</v>
+        <v>26.4378</v>
       </c>
       <c r="E88" t="n">
-        <v>3.22999</v>
+        <v>3.10761</v>
       </c>
       <c r="F88" t="n">
-        <v>3.9661</v>
+        <v>3.95909</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>4.54368</v>
+        <v>4.51456</v>
       </c>
       <c r="C89" t="n">
-        <v>5.29827</v>
+        <v>5.3545</v>
       </c>
       <c r="D89" t="n">
-        <v>27.7257</v>
+        <v>27.7044</v>
       </c>
       <c r="E89" t="n">
-        <v>3.47954</v>
+        <v>3.26674</v>
       </c>
       <c r="F89" t="n">
-        <v>4.20226</v>
+        <v>4.25993</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>5.02837</v>
+        <v>4.99309</v>
       </c>
       <c r="C90" t="n">
-        <v>5.91829</v>
+        <v>5.87879</v>
       </c>
       <c r="D90" t="n">
-        <v>29.023</v>
+        <v>29.0426</v>
       </c>
       <c r="E90" t="n">
-        <v>3.84351</v>
+        <v>3.51642</v>
       </c>
       <c r="F90" t="n">
-        <v>4.68844</v>
+        <v>4.73698</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>5.78787</v>
+        <v>5.74554</v>
       </c>
       <c r="C91" t="n">
-        <v>6.71669</v>
+        <v>6.7226</v>
       </c>
       <c r="D91" t="n">
-        <v>30.2598</v>
+        <v>30.3803</v>
       </c>
       <c r="E91" t="n">
-        <v>4.30534</v>
+        <v>3.92591</v>
       </c>
       <c r="F91" t="n">
-        <v>5.42236</v>
+        <v>5.65601</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>6.98175</v>
+        <v>6.89931</v>
       </c>
       <c r="C92" t="n">
-        <v>7.93246</v>
+        <v>7.93405</v>
       </c>
       <c r="D92" t="n">
-        <v>24.5722</v>
+        <v>24.6766</v>
       </c>
       <c r="E92" t="n">
-        <v>2.94988</v>
+        <v>2.89113</v>
       </c>
       <c r="F92" t="n">
-        <v>3.56113</v>
+        <v>3.56115</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>8.81377</v>
+        <v>8.738490000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>9.678929999999999</v>
+        <v>9.638339999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>25.5015</v>
+        <v>25.4871</v>
       </c>
       <c r="E93" t="n">
-        <v>3.03639</v>
+        <v>2.93565</v>
       </c>
       <c r="F93" t="n">
-        <v>3.71807</v>
+        <v>3.74171</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>11.5775</v>
+        <v>11.5058</v>
       </c>
       <c r="C94" t="n">
-        <v>4.85181</v>
+        <v>4.81922</v>
       </c>
       <c r="D94" t="n">
-        <v>26.488</v>
+        <v>26.359</v>
       </c>
       <c r="E94" t="n">
-        <v>3.18579</v>
+        <v>2.97686</v>
       </c>
       <c r="F94" t="n">
-        <v>3.99618</v>
+        <v>3.99285</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.1697</v>
+        <v>4.14396</v>
       </c>
       <c r="C95" t="n">
-        <v>5.06814</v>
+        <v>5.0517</v>
       </c>
       <c r="D95" t="n">
-        <v>27.2961</v>
+        <v>27.3916</v>
       </c>
       <c r="E95" t="n">
-        <v>3.43959</v>
+        <v>3.10774</v>
       </c>
       <c r="F95" t="n">
-        <v>4.34324</v>
+        <v>4.38786</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>4.51529</v>
+        <v>4.46822</v>
       </c>
       <c r="C96" t="n">
-        <v>5.32926</v>
+        <v>5.31506</v>
       </c>
       <c r="D96" t="n">
-        <v>28.314</v>
+        <v>28.2883</v>
       </c>
       <c r="E96" t="n">
-        <v>3.72631</v>
+        <v>3.28167</v>
       </c>
       <c r="F96" t="n">
-        <v>4.72753</v>
+        <v>4.82447</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>4.87965</v>
+        <v>4.79826</v>
       </c>
       <c r="C97" t="n">
-        <v>5.56982</v>
+        <v>5.59573</v>
       </c>
       <c r="D97" t="n">
-        <v>29.2303</v>
+        <v>29.2219</v>
       </c>
       <c r="E97" t="n">
-        <v>3.96845</v>
+        <v>3.54905</v>
       </c>
       <c r="F97" t="n">
-        <v>5.27281</v>
+        <v>5.27233</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>5.33278</v>
+        <v>5.35994</v>
       </c>
       <c r="C98" t="n">
-        <v>5.81991</v>
+        <v>5.78788</v>
       </c>
       <c r="D98" t="n">
-        <v>30.2824</v>
+        <v>30.1639</v>
       </c>
       <c r="E98" t="n">
-        <v>4.25625</v>
+        <v>3.7998</v>
       </c>
       <c r="F98" t="n">
-        <v>5.78041</v>
+        <v>5.90961</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>5.78862</v>
+        <v>5.78315</v>
       </c>
       <c r="C99" t="n">
-        <v>6.09163</v>
+        <v>6.07457</v>
       </c>
       <c r="D99" t="n">
-        <v>31.2856</v>
+        <v>31.36</v>
       </c>
       <c r="E99" t="n">
-        <v>4.45446</v>
+        <v>4.11566</v>
       </c>
       <c r="F99" t="n">
-        <v>6.36514</v>
+        <v>6.39798</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>6.30952</v>
+        <v>6.23514</v>
       </c>
       <c r="C100" t="n">
-        <v>6.3503</v>
+        <v>6.36197</v>
       </c>
       <c r="D100" t="n">
-        <v>32.4252</v>
+        <v>32.2775</v>
       </c>
       <c r="E100" t="n">
-        <v>4.66101</v>
+        <v>4.4073</v>
       </c>
       <c r="F100" t="n">
-        <v>6.95419</v>
+        <v>6.93967</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>6.82136</v>
+        <v>6.83117</v>
       </c>
       <c r="C101" t="n">
-        <v>6.67225</v>
+        <v>6.66059</v>
       </c>
       <c r="D101" t="n">
-        <v>33.5394</v>
+        <v>33.513</v>
       </c>
       <c r="E101" t="n">
-        <v>4.87953</v>
+        <v>4.67766</v>
       </c>
       <c r="F101" t="n">
-        <v>7.50323</v>
+        <v>7.51898</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.44024</v>
+        <v>7.36625</v>
       </c>
       <c r="C102" t="n">
-        <v>6.99828</v>
+        <v>6.98958</v>
       </c>
       <c r="D102" t="n">
-        <v>34.7162</v>
+        <v>34.5499</v>
       </c>
       <c r="E102" t="n">
-        <v>5.05063</v>
+        <v>4.9527</v>
       </c>
       <c r="F102" t="n">
-        <v>8.012180000000001</v>
+        <v>7.96409</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>7.93217</v>
+        <v>7.94288</v>
       </c>
       <c r="C103" t="n">
-        <v>7.39744</v>
+        <v>7.44719</v>
       </c>
       <c r="D103" t="n">
-        <v>35.8989</v>
+        <v>35.8061</v>
       </c>
       <c r="E103" t="n">
-        <v>5.28285</v>
+        <v>5.22522</v>
       </c>
       <c r="F103" t="n">
-        <v>8.505269999999999</v>
+        <v>8.45543</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>8.66377</v>
+        <v>8.60319</v>
       </c>
       <c r="C104" t="n">
-        <v>7.99959</v>
+        <v>8.02256</v>
       </c>
       <c r="D104" t="n">
-        <v>37.1033</v>
+        <v>37.0763</v>
       </c>
       <c r="E104" t="n">
-        <v>5.56509</v>
+        <v>5.5013</v>
       </c>
       <c r="F104" t="n">
-        <v>8.98882</v>
+        <v>8.929360000000001</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>9.38274</v>
+        <v>9.201610000000001</v>
       </c>
       <c r="C105" t="n">
-        <v>8.75704</v>
+        <v>8.81306</v>
       </c>
       <c r="D105" t="n">
-        <v>38.3199</v>
+        <v>38.4474</v>
       </c>
       <c r="E105" t="n">
-        <v>5.93931</v>
+        <v>5.92257</v>
       </c>
       <c r="F105" t="n">
-        <v>9.639900000000001</v>
+        <v>9.573589999999999</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>10.4004</v>
+        <v>10.3125</v>
       </c>
       <c r="C106" t="n">
-        <v>9.86692</v>
+        <v>9.926030000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>39.8006</v>
+        <v>39.6448</v>
       </c>
       <c r="E106" t="n">
-        <v>6.48214</v>
+        <v>6.46975</v>
       </c>
       <c r="F106" t="n">
-        <v>10.4758</v>
+        <v>10.3232</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>11.8502</v>
+        <v>11.7924</v>
       </c>
       <c r="C107" t="n">
-        <v>11.423</v>
+        <v>11.5107</v>
       </c>
       <c r="D107" t="n">
-        <v>30.4582</v>
+        <v>30.212</v>
       </c>
       <c r="E107" t="n">
-        <v>4.63468</v>
+        <v>4.56088</v>
       </c>
       <c r="F107" t="n">
-        <v>6.81223</v>
+        <v>6.82027</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>14.0644</v>
+        <v>13.9978</v>
       </c>
       <c r="C108" t="n">
-        <v>6.41359</v>
+        <v>6.41691</v>
       </c>
       <c r="D108" t="n">
-        <v>31.3483</v>
+        <v>31.2753</v>
       </c>
       <c r="E108" t="n">
-        <v>4.74196</v>
+        <v>4.70732</v>
       </c>
       <c r="F108" t="n">
-        <v>7.02599</v>
+        <v>7.03025</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>17.2961</v>
+        <v>17.5411</v>
       </c>
       <c r="C109" t="n">
-        <v>6.53338</v>
+        <v>6.52952</v>
       </c>
       <c r="D109" t="n">
-        <v>32.1668</v>
+        <v>32.2161</v>
       </c>
       <c r="E109" t="n">
-        <v>4.8383</v>
+        <v>4.8052</v>
       </c>
       <c r="F109" t="n">
-        <v>7.24082</v>
+        <v>7.23644</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.11629</v>
+        <v>7.05473</v>
       </c>
       <c r="C110" t="n">
-        <v>6.67395</v>
+        <v>6.67377</v>
       </c>
       <c r="D110" t="n">
-        <v>33.0604</v>
+        <v>33.088</v>
       </c>
       <c r="E110" t="n">
-        <v>4.96605</v>
+        <v>4.94866</v>
       </c>
       <c r="F110" t="n">
-        <v>7.47592</v>
+        <v>7.43332</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.33268</v>
+        <v>7.26857</v>
       </c>
       <c r="C111" t="n">
-        <v>6.82283</v>
+        <v>6.81937</v>
       </c>
       <c r="D111" t="n">
-        <v>34.0338</v>
+        <v>34.0163</v>
       </c>
       <c r="E111" t="n">
-        <v>5.08442</v>
+        <v>5.06999</v>
       </c>
       <c r="F111" t="n">
-        <v>7.72512</v>
+        <v>7.69775</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.50305</v>
+        <v>7.52362</v>
       </c>
       <c r="C112" t="n">
-        <v>6.98439</v>
+        <v>6.97975</v>
       </c>
       <c r="D112" t="n">
-        <v>35.0157</v>
+        <v>34.8706</v>
       </c>
       <c r="E112" t="n">
-        <v>5.22876</v>
+        <v>5.2272</v>
       </c>
       <c r="F112" t="n">
-        <v>7.98119</v>
+        <v>7.95788</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>7.74223</v>
+        <v>7.73471</v>
       </c>
       <c r="C113" t="n">
-        <v>7.15275</v>
+        <v>7.17179</v>
       </c>
       <c r="D113" t="n">
-        <v>36.1062</v>
+        <v>35.9829</v>
       </c>
       <c r="E113" t="n">
-        <v>5.36088</v>
+        <v>5.35637</v>
       </c>
       <c r="F113" t="n">
-        <v>8.216620000000001</v>
+        <v>8.18868</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.030329999999999</v>
+        <v>7.99407</v>
       </c>
       <c r="C114" t="n">
-        <v>7.37597</v>
+        <v>7.38812</v>
       </c>
       <c r="D114" t="n">
-        <v>36.969</v>
+        <v>37.0015</v>
       </c>
       <c r="E114" t="n">
-        <v>5.52528</v>
+        <v>5.52652</v>
       </c>
       <c r="F114" t="n">
-        <v>8.51168</v>
+        <v>8.475580000000001</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>8.34722</v>
+        <v>8.30857</v>
       </c>
       <c r="C115" t="n">
-        <v>7.64319</v>
+        <v>7.67605</v>
       </c>
       <c r="D115" t="n">
-        <v>38.1426</v>
+        <v>38.0525</v>
       </c>
       <c r="E115" t="n">
-        <v>5.69488</v>
+        <v>5.68343</v>
       </c>
       <c r="F115" t="n">
-        <v>8.84423</v>
+        <v>8.790319999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>8.64791</v>
+        <v>8.62965</v>
       </c>
       <c r="C116" t="n">
-        <v>7.95859</v>
+        <v>7.9909</v>
       </c>
       <c r="D116" t="n">
-        <v>39.2401</v>
+        <v>39.1855</v>
       </c>
       <c r="E116" t="n">
-        <v>5.91284</v>
+        <v>5.88744</v>
       </c>
       <c r="F116" t="n">
-        <v>9.15748</v>
+        <v>9.099629999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>9.088789999999999</v>
+        <v>9.026160000000001</v>
       </c>
       <c r="C117" t="n">
-        <v>8.35487</v>
+        <v>8.3781</v>
       </c>
       <c r="D117" t="n">
-        <v>40.1948</v>
+        <v>40.3032</v>
       </c>
       <c r="E117" t="n">
-        <v>6.11615</v>
+        <v>6.14204</v>
       </c>
       <c r="F117" t="n">
-        <v>9.57569</v>
+        <v>9.539249999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>9.625360000000001</v>
+        <v>9.61664</v>
       </c>
       <c r="C118" t="n">
-        <v>8.898210000000001</v>
+        <v>8.9664</v>
       </c>
       <c r="D118" t="n">
-        <v>41.5792</v>
+        <v>41.4323</v>
       </c>
       <c r="E118" t="n">
-        <v>6.42564</v>
+        <v>6.42061</v>
       </c>
       <c r="F118" t="n">
-        <v>10.0536</v>
+        <v>10.0128</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>10.3346</v>
+        <v>10.3105</v>
       </c>
       <c r="C119" t="n">
-        <v>9.66155</v>
+        <v>9.702019999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>42.8643</v>
+        <v>42.6413</v>
       </c>
       <c r="E119" t="n">
-        <v>6.8142</v>
+        <v>6.82181</v>
       </c>
       <c r="F119" t="n">
-        <v>10.6439</v>
+        <v>10.6147</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>11.3003</v>
+        <v>11.2562</v>
       </c>
       <c r="C120" t="n">
-        <v>10.7636</v>
+        <v>10.8249</v>
       </c>
       <c r="D120" t="n">
-        <v>44.3082</v>
+        <v>44.1431</v>
       </c>
       <c r="E120" t="n">
-        <v>7.3519</v>
+        <v>7.35202</v>
       </c>
       <c r="F120" t="n">
-        <v>11.4556</v>
+        <v>11.3741</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>12.6807</v>
+        <v>12.6507</v>
       </c>
       <c r="C121" t="n">
-        <v>12.3232</v>
+        <v>12.4107</v>
       </c>
       <c r="D121" t="n">
-        <v>33.2584</v>
+        <v>33.0175</v>
       </c>
       <c r="E121" t="n">
-        <v>5.05697</v>
+        <v>4.97446</v>
       </c>
       <c r="F121" t="n">
-        <v>7.3144</v>
+        <v>7.30166</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>14.639</v>
+        <v>14.6429</v>
       </c>
       <c r="C122" t="n">
-        <v>6.77919</v>
+        <v>6.759</v>
       </c>
       <c r="D122" t="n">
-        <v>34.1798</v>
+        <v>33.9033</v>
       </c>
       <c r="E122" t="n">
-        <v>5.19249</v>
+        <v>5.07359</v>
       </c>
       <c r="F122" t="n">
-        <v>7.53738</v>
+        <v>7.52157</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>17.9333</v>
+        <v>17.8124</v>
       </c>
       <c r="C123" t="n">
-        <v>6.89555</v>
+        <v>6.91264</v>
       </c>
       <c r="D123" t="n">
-        <v>34.9888</v>
+        <v>34.9835</v>
       </c>
       <c r="E123" t="n">
-        <v>5.31558</v>
+        <v>5.19527</v>
       </c>
       <c r="F123" t="n">
-        <v>7.75837</v>
+        <v>7.74857</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>7.48761</v>
+        <v>7.46133</v>
       </c>
       <c r="C124" t="n">
-        <v>7.04873</v>
+        <v>7.04638</v>
       </c>
       <c r="D124" t="n">
-        <v>35.8488</v>
+        <v>35.7911</v>
       </c>
       <c r="E124" t="n">
-        <v>5.48899</v>
+        <v>5.32125</v>
       </c>
       <c r="F124" t="n">
-        <v>8.007720000000001</v>
+        <v>7.98525</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>7.64221</v>
+        <v>7.65098</v>
       </c>
       <c r="C125" t="n">
-        <v>7.18954</v>
+        <v>7.18547</v>
       </c>
       <c r="D125" t="n">
-        <v>36.8025</v>
+        <v>36.6765</v>
       </c>
       <c r="E125" t="n">
-        <v>5.60925</v>
+        <v>5.46148</v>
       </c>
       <c r="F125" t="n">
-        <v>8.248950000000001</v>
+        <v>8.21773</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>7.87031</v>
+        <v>7.84768</v>
       </c>
       <c r="C126" t="n">
-        <v>7.37236</v>
+        <v>7.35289</v>
       </c>
       <c r="D126" t="n">
-        <v>37.6962</v>
+        <v>37.6149</v>
       </c>
       <c r="E126" t="n">
-        <v>5.82023</v>
+        <v>5.58682</v>
       </c>
       <c r="F126" t="n">
-        <v>8.511699999999999</v>
+        <v>8.48419</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>8.121510000000001</v>
+        <v>8.09501</v>
       </c>
       <c r="C127" t="n">
-        <v>7.52488</v>
+        <v>7.55766</v>
       </c>
       <c r="D127" t="n">
-        <v>38.7763</v>
+        <v>38.6049</v>
       </c>
       <c r="E127" t="n">
-        <v>6.00598</v>
+        <v>5.7486</v>
       </c>
       <c r="F127" t="n">
-        <v>8.813190000000001</v>
+        <v>8.769399999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>8.37885</v>
+        <v>8.335760000000001</v>
       </c>
       <c r="C128" t="n">
-        <v>7.79567</v>
+        <v>7.78677</v>
       </c>
       <c r="D128" t="n">
-        <v>39.6903</v>
+        <v>39.6201</v>
       </c>
       <c r="E128" t="n">
-        <v>6.20414</v>
+        <v>5.93015</v>
       </c>
       <c r="F128" t="n">
-        <v>9.104939999999999</v>
+        <v>9.09375</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>8.65875</v>
+        <v>8.628159999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>8.03979</v>
+        <v>8.05045</v>
       </c>
       <c r="D129" t="n">
-        <v>40.6733</v>
+        <v>40.6284</v>
       </c>
       <c r="E129" t="n">
-        <v>6.41255</v>
+        <v>6.0861</v>
       </c>
       <c r="F129" t="n">
-        <v>9.43009</v>
+        <v>9.429740000000001</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>8.996449999999999</v>
+        <v>9.01667</v>
       </c>
       <c r="C130" t="n">
-        <v>8.357839999999999</v>
+        <v>8.369350000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>41.9314</v>
+        <v>41.655</v>
       </c>
       <c r="E130" t="n">
-        <v>6.71721</v>
+        <v>6.30459</v>
       </c>
       <c r="F130" t="n">
-        <v>9.80552</v>
+        <v>9.819520000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>9.428290000000001</v>
+        <v>9.420489999999999</v>
       </c>
       <c r="C131" t="n">
-        <v>8.77726</v>
+        <v>8.80711</v>
       </c>
       <c r="D131" t="n">
-        <v>43.1343</v>
+        <v>42.9507</v>
       </c>
       <c r="E131" t="n">
-        <v>7.0553</v>
+        <v>6.56024</v>
       </c>
       <c r="F131" t="n">
-        <v>10.234</v>
+        <v>10.3021</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>9.974869999999999</v>
+        <v>9.93994</v>
       </c>
       <c r="C132" t="n">
-        <v>9.33878</v>
+        <v>9.39068</v>
       </c>
       <c r="D132" t="n">
-        <v>44.2105</v>
+        <v>44.2318</v>
       </c>
       <c r="E132" t="n">
-        <v>7.37898</v>
+        <v>6.86188</v>
       </c>
       <c r="F132" t="n">
-        <v>10.7237</v>
+        <v>10.7724</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>10.6323</v>
+        <v>10.6497</v>
       </c>
       <c r="C133" t="n">
-        <v>10.1142</v>
+        <v>10.1787</v>
       </c>
       <c r="D133" t="n">
-        <v>45.4275</v>
+        <v>45.5255</v>
       </c>
       <c r="E133" t="n">
-        <v>7.80268</v>
+        <v>7.27076</v>
       </c>
       <c r="F133" t="n">
-        <v>11.2944</v>
+        <v>11.321</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>11.5896</v>
+        <v>11.5571</v>
       </c>
       <c r="C134" t="n">
-        <v>11.1282</v>
+        <v>11.2091</v>
       </c>
       <c r="D134" t="n">
-        <v>46.743</v>
+        <v>46.8444</v>
       </c>
       <c r="E134" t="n">
-        <v>8.334849999999999</v>
+        <v>7.75205</v>
       </c>
       <c r="F134" t="n">
-        <v>12.1238</v>
+        <v>12.1462</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>12.9253</v>
+        <v>12.879</v>
       </c>
       <c r="C135" t="n">
-        <v>12.6742</v>
+        <v>12.7218</v>
       </c>
       <c r="D135" t="n">
-        <v>34.4994</v>
+        <v>34.5344</v>
       </c>
       <c r="E135" t="n">
-        <v>11.4239</v>
+        <v>10.9757</v>
       </c>
       <c r="F135" t="n">
-        <v>13.5537</v>
+        <v>13.5614</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>14.7766</v>
+        <v>14.7654</v>
       </c>
       <c r="C136" t="n">
-        <v>15.4273</v>
+        <v>15.3086</v>
       </c>
       <c r="D136" t="n">
-        <v>35.5017</v>
+        <v>35.507</v>
       </c>
       <c r="E136" t="n">
-        <v>11.5013</v>
+        <v>11.0554</v>
       </c>
       <c r="F136" t="n">
-        <v>13.7319</v>
+        <v>13.7328</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7415</v>
+        <v>17.7295</v>
       </c>
       <c r="C137" t="n">
-        <v>15.5745</v>
+        <v>15.5629</v>
       </c>
       <c r="D137" t="n">
-        <v>36.2453</v>
+        <v>36.3931</v>
       </c>
       <c r="E137" t="n">
-        <v>11.6787</v>
+        <v>11.1945</v>
       </c>
       <c r="F137" t="n">
-        <v>13.9452</v>
+        <v>13.9829</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>13.2494</v>
+        <v>13.2093</v>
       </c>
       <c r="C138" t="n">
-        <v>15.611</v>
+        <v>15.7112</v>
       </c>
       <c r="D138" t="n">
-        <v>37.1596</v>
+        <v>37.3667</v>
       </c>
       <c r="E138" t="n">
-        <v>11.8424</v>
+        <v>11.2713</v>
       </c>
       <c r="F138" t="n">
-        <v>14.1931</v>
+        <v>14.1697</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>13.3883</v>
+        <v>13.3751</v>
       </c>
       <c r="C139" t="n">
-        <v>15.8408</v>
+        <v>15.8165</v>
       </c>
       <c r="D139" t="n">
-        <v>38.302</v>
+        <v>38.2906</v>
       </c>
       <c r="E139" t="n">
-        <v>11.9772</v>
+        <v>11.3939</v>
       </c>
       <c r="F139" t="n">
-        <v>14.3882</v>
+        <v>14.4223</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.4566</v>
+        <v>13.5659</v>
       </c>
       <c r="C140" t="n">
-        <v>16.0183</v>
+        <v>16.0224</v>
       </c>
       <c r="D140" t="n">
-        <v>39.2569</v>
+        <v>39.1891</v>
       </c>
       <c r="E140" t="n">
-        <v>12.133</v>
+        <v>11.5097</v>
       </c>
       <c r="F140" t="n">
-        <v>14.6459</v>
+        <v>14.6587</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>13.6761</v>
+        <v>13.6229</v>
       </c>
       <c r="C141" t="n">
-        <v>16.1917</v>
+        <v>16.2452</v>
       </c>
       <c r="D141" t="n">
-        <v>40.0818</v>
+        <v>40.0685</v>
       </c>
       <c r="E141" t="n">
-        <v>12.3029</v>
+        <v>11.6497</v>
       </c>
       <c r="F141" t="n">
-        <v>15.0011</v>
+        <v>15.0164</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>13.7947</v>
+        <v>13.886</v>
       </c>
       <c r="C142" t="n">
-        <v>16.4171</v>
+        <v>16.3168</v>
       </c>
       <c r="D142" t="n">
-        <v>41.2639</v>
+        <v>41.1866</v>
       </c>
       <c r="E142" t="n">
-        <v>12.5059</v>
+        <v>11.8202</v>
       </c>
       <c r="F142" t="n">
-        <v>15.226</v>
+        <v>15.2666</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>14.0692</v>
+        <v>13.9963</v>
       </c>
       <c r="C143" t="n">
-        <v>16.7043</v>
+        <v>16.4973</v>
       </c>
       <c r="D143" t="n">
-        <v>42.3722</v>
+        <v>42.1133</v>
       </c>
       <c r="E143" t="n">
-        <v>12.6763</v>
+        <v>11.8618</v>
       </c>
       <c r="F143" t="n">
-        <v>15.6307</v>
+        <v>15.5748</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.53828</v>
+        <v>2.53952</v>
       </c>
       <c r="C2" t="n">
-        <v>3.57482</v>
+        <v>3.59073</v>
       </c>
       <c r="D2" t="n">
-        <v>8.23091</v>
+        <v>8.22372</v>
       </c>
       <c r="E2" t="n">
-        <v>2.12577</v>
+        <v>2.12591</v>
       </c>
       <c r="F2" t="n">
-        <v>2.23438</v>
+        <v>2.2305</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.60941</v>
+        <v>2.68225</v>
       </c>
       <c r="C3" t="n">
-        <v>3.70767</v>
+        <v>3.71393</v>
       </c>
       <c r="D3" t="n">
-        <v>8.561529999999999</v>
+        <v>8.56372</v>
       </c>
       <c r="E3" t="n">
-        <v>2.22749</v>
+        <v>2.2314</v>
       </c>
       <c r="F3" t="n">
-        <v>2.32404</v>
+        <v>2.30897</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.70741</v>
+        <v>2.89918</v>
       </c>
       <c r="C4" t="n">
-        <v>3.94923</v>
+        <v>3.96832</v>
       </c>
       <c r="D4" t="n">
-        <v>8.82948</v>
+        <v>8.83202</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3159</v>
+        <v>2.31136</v>
       </c>
       <c r="F4" t="n">
-        <v>2.41391</v>
+        <v>2.41552</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.08547</v>
+        <v>3.24399</v>
       </c>
       <c r="C5" t="n">
-        <v>4.38307</v>
+        <v>4.40228</v>
       </c>
       <c r="D5" t="n">
-        <v>9.26735</v>
+        <v>9.252140000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.40526</v>
+        <v>2.40082</v>
       </c>
       <c r="F5" t="n">
-        <v>2.50769</v>
+        <v>2.50342</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.7448</v>
+        <v>3.88487</v>
       </c>
       <c r="C6" t="n">
-        <v>4.94373</v>
+        <v>4.97335</v>
       </c>
       <c r="D6" t="n">
-        <v>9.623279999999999</v>
+        <v>9.66531</v>
       </c>
       <c r="E6" t="n">
-        <v>2.59238</v>
+        <v>2.59687</v>
       </c>
       <c r="F6" t="n">
-        <v>2.701</v>
+        <v>2.69458</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>5.28376</v>
+        <v>5.55964</v>
       </c>
       <c r="C7" t="n">
-        <v>6.0993</v>
+        <v>6.07572</v>
       </c>
       <c r="D7" t="n">
-        <v>6.98646</v>
+        <v>7.02962</v>
       </c>
       <c r="E7" t="n">
-        <v>1.905</v>
+        <v>1.90408</v>
       </c>
       <c r="F7" t="n">
-        <v>2.00072</v>
+        <v>2.0021</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>7.27136</v>
+        <v>7.36407</v>
       </c>
       <c r="C8" t="n">
-        <v>3.22307</v>
+        <v>3.21422</v>
       </c>
       <c r="D8" t="n">
-        <v>7.3072</v>
+        <v>7.3287</v>
       </c>
       <c r="E8" t="n">
-        <v>1.92186</v>
+        <v>1.91485</v>
       </c>
       <c r="F8" t="n">
-        <v>2.01559</v>
+        <v>2.01169</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>9.77894</v>
+        <v>10.557</v>
       </c>
       <c r="C9" t="n">
-        <v>3.23346</v>
+        <v>3.22955</v>
       </c>
       <c r="D9" t="n">
-        <v>7.66153</v>
+        <v>7.66652</v>
       </c>
       <c r="E9" t="n">
-        <v>1.93117</v>
+        <v>1.93413</v>
       </c>
       <c r="F9" t="n">
-        <v>2.02418</v>
+        <v>2.02964</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.38376</v>
+        <v>2.38519</v>
       </c>
       <c r="C10" t="n">
-        <v>3.26495</v>
+        <v>3.27572</v>
       </c>
       <c r="D10" t="n">
-        <v>7.99436</v>
+        <v>8.00483</v>
       </c>
       <c r="E10" t="n">
-        <v>1.95638</v>
+        <v>1.95308</v>
       </c>
       <c r="F10" t="n">
-        <v>2.04714</v>
+        <v>2.04729</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.3987</v>
+        <v>2.40938</v>
       </c>
       <c r="C11" t="n">
-        <v>3.31058</v>
+        <v>3.31097</v>
       </c>
       <c r="D11" t="n">
-        <v>8.29833</v>
+        <v>8.29856</v>
       </c>
       <c r="E11" t="n">
-        <v>1.97668</v>
+        <v>1.97878</v>
       </c>
       <c r="F11" t="n">
-        <v>2.06973</v>
+        <v>2.07248</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.43082</v>
+        <v>2.43999</v>
       </c>
       <c r="C12" t="n">
-        <v>3.34283</v>
+        <v>3.32912</v>
       </c>
       <c r="D12" t="n">
-        <v>8.673170000000001</v>
+        <v>8.650410000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.00378</v>
+        <v>1.99763</v>
       </c>
       <c r="F12" t="n">
-        <v>2.08882</v>
+        <v>2.08741</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.474</v>
+        <v>2.46425</v>
       </c>
       <c r="C13" t="n">
-        <v>3.38004</v>
+        <v>3.37839</v>
       </c>
       <c r="D13" t="n">
-        <v>8.94689</v>
+        <v>8.945830000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0224</v>
+        <v>2.02177</v>
       </c>
       <c r="F13" t="n">
-        <v>2.12041</v>
+        <v>2.11451</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.51179</v>
+        <v>2.50031</v>
       </c>
       <c r="C14" t="n">
-        <v>3.47339</v>
+        <v>3.4695</v>
       </c>
       <c r="D14" t="n">
-        <v>9.2895</v>
+        <v>9.2605</v>
       </c>
       <c r="E14" t="n">
-        <v>2.05812</v>
+        <v>2.05912</v>
       </c>
       <c r="F14" t="n">
-        <v>2.15771</v>
+        <v>2.14573</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.60018</v>
+        <v>2.59602</v>
       </c>
       <c r="C15" t="n">
-        <v>3.55053</v>
+        <v>3.54406</v>
       </c>
       <c r="D15" t="n">
-        <v>9.55269</v>
+        <v>9.551729999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.10627</v>
+        <v>2.10863</v>
       </c>
       <c r="F15" t="n">
-        <v>2.20774</v>
+        <v>2.2097</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.689</v>
+        <v>2.69547</v>
       </c>
       <c r="C16" t="n">
-        <v>3.70696</v>
+        <v>3.72975</v>
       </c>
       <c r="D16" t="n">
-        <v>9.85993</v>
+        <v>9.89733</v>
       </c>
       <c r="E16" t="n">
-        <v>2.15715</v>
+        <v>2.15957</v>
       </c>
       <c r="F16" t="n">
-        <v>2.25055</v>
+        <v>2.24827</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>2.82137</v>
+        <v>2.83659</v>
       </c>
       <c r="C17" t="n">
-        <v>3.85275</v>
+        <v>3.86058</v>
       </c>
       <c r="D17" t="n">
-        <v>10.2125</v>
+        <v>10.1731</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2192</v>
+        <v>2.23013</v>
       </c>
       <c r="F17" t="n">
-        <v>2.32389</v>
+        <v>2.32551</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.0918</v>
+        <v>3.07316</v>
       </c>
       <c r="C18" t="n">
-        <v>4.10031</v>
+        <v>4.11375</v>
       </c>
       <c r="D18" t="n">
-        <v>10.4643</v>
+        <v>10.5061</v>
       </c>
       <c r="E18" t="n">
-        <v>2.33351</v>
+        <v>2.33432</v>
       </c>
       <c r="F18" t="n">
-        <v>2.43686</v>
+        <v>2.44583</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.45858</v>
+        <v>3.41995</v>
       </c>
       <c r="C19" t="n">
-        <v>4.56741</v>
+        <v>4.57116</v>
       </c>
       <c r="D19" t="n">
-        <v>10.837</v>
+        <v>10.809</v>
       </c>
       <c r="E19" t="n">
-        <v>2.47824</v>
+        <v>2.47902</v>
       </c>
       <c r="F19" t="n">
-        <v>2.60188</v>
+        <v>2.61324</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.20932</v>
+        <v>4.18072</v>
       </c>
       <c r="C20" t="n">
-        <v>5.24584</v>
+        <v>5.2526</v>
       </c>
       <c r="D20" t="n">
-        <v>11.11</v>
+        <v>11.1371</v>
       </c>
       <c r="E20" t="n">
-        <v>2.75977</v>
+        <v>2.77103</v>
       </c>
       <c r="F20" t="n">
-        <v>2.90383</v>
+        <v>2.91562</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.28013</v>
+        <v>5.34151</v>
       </c>
       <c r="C21" t="n">
-        <v>6.13858</v>
+        <v>6.18927</v>
       </c>
       <c r="D21" t="n">
-        <v>8.09337</v>
+        <v>8.09872</v>
       </c>
       <c r="E21" t="n">
-        <v>1.94721</v>
+        <v>1.94669</v>
       </c>
       <c r="F21" t="n">
-        <v>2.05765</v>
+        <v>2.05866</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>7.08745</v>
+        <v>7.05214</v>
       </c>
       <c r="C22" t="n">
-        <v>3.27039</v>
+        <v>3.27428</v>
       </c>
       <c r="D22" t="n">
-        <v>8.416320000000001</v>
+        <v>8.393359999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9649</v>
+        <v>1.97404</v>
       </c>
       <c r="F22" t="n">
-        <v>2.08873</v>
+        <v>2.08812</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>9.75916</v>
+        <v>9.503500000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>3.28315</v>
+        <v>3.29914</v>
       </c>
       <c r="D23" t="n">
-        <v>8.69651</v>
+        <v>8.685890000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>1.97723</v>
+        <v>1.9788</v>
       </c>
       <c r="F23" t="n">
-        <v>2.11409</v>
+        <v>2.11234</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.46939</v>
+        <v>2.45082</v>
       </c>
       <c r="C24" t="n">
-        <v>3.32505</v>
+        <v>3.32531</v>
       </c>
       <c r="D24" t="n">
-        <v>9.01562</v>
+        <v>8.998659999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>2.01738</v>
+        <v>2.00363</v>
       </c>
       <c r="F24" t="n">
-        <v>2.16311</v>
+        <v>2.14753</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.493</v>
+        <v>2.50848</v>
       </c>
       <c r="C25" t="n">
-        <v>3.34866</v>
+        <v>3.3459</v>
       </c>
       <c r="D25" t="n">
-        <v>9.33132</v>
+        <v>9.319889999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>2.03607</v>
+        <v>2.02736</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2088</v>
+        <v>2.19454</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.5566</v>
+        <v>2.54182</v>
       </c>
       <c r="C26" t="n">
-        <v>3.40626</v>
+        <v>3.41368</v>
       </c>
       <c r="D26" t="n">
-        <v>9.65451</v>
+        <v>9.62989</v>
       </c>
       <c r="E26" t="n">
-        <v>2.06651</v>
+        <v>2.0597</v>
       </c>
       <c r="F26" t="n">
-        <v>2.26541</v>
+        <v>2.25633</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.61581</v>
+        <v>2.5981</v>
       </c>
       <c r="C27" t="n">
-        <v>3.4359</v>
+        <v>3.4421</v>
       </c>
       <c r="D27" t="n">
-        <v>9.972910000000001</v>
+        <v>9.94842</v>
       </c>
       <c r="E27" t="n">
-        <v>2.09282</v>
+        <v>2.08274</v>
       </c>
       <c r="F27" t="n">
-        <v>2.31823</v>
+        <v>2.29537</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>2.6669</v>
+        <v>2.68922</v>
       </c>
       <c r="C28" t="n">
-        <v>3.493</v>
+        <v>3.49292</v>
       </c>
       <c r="D28" t="n">
-        <v>10.2222</v>
+        <v>10.2111</v>
       </c>
       <c r="E28" t="n">
-        <v>2.14541</v>
+        <v>2.13754</v>
       </c>
       <c r="F28" t="n">
-        <v>2.3804</v>
+        <v>2.37385</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>2.77812</v>
+        <v>2.76924</v>
       </c>
       <c r="C29" t="n">
-        <v>3.62246</v>
+        <v>3.62294</v>
       </c>
       <c r="D29" t="n">
-        <v>10.5372</v>
+        <v>10.5217</v>
       </c>
       <c r="E29" t="n">
-        <v>2.20726</v>
+        <v>2.19836</v>
       </c>
       <c r="F29" t="n">
-        <v>2.46569</v>
+        <v>2.44044</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>2.92872</v>
+        <v>2.94102</v>
       </c>
       <c r="C30" t="n">
-        <v>3.72598</v>
+        <v>3.72013</v>
       </c>
       <c r="D30" t="n">
-        <v>10.8467</v>
+        <v>10.8278</v>
       </c>
       <c r="E30" t="n">
-        <v>2.25762</v>
+        <v>2.25263</v>
       </c>
       <c r="F30" t="n">
-        <v>2.52416</v>
+        <v>2.52938</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.14381</v>
+        <v>3.11429</v>
       </c>
       <c r="C31" t="n">
-        <v>3.88109</v>
+        <v>3.86477</v>
       </c>
       <c r="D31" t="n">
-        <v>11.1252</v>
+        <v>11.1011</v>
       </c>
       <c r="E31" t="n">
-        <v>2.32061</v>
+        <v>2.31237</v>
       </c>
       <c r="F31" t="n">
-        <v>2.606</v>
+        <v>2.58911</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.35795</v>
+        <v>3.40498</v>
       </c>
       <c r="C32" t="n">
-        <v>4.08348</v>
+        <v>4.13178</v>
       </c>
       <c r="D32" t="n">
-        <v>11.327</v>
+        <v>11.3606</v>
       </c>
       <c r="E32" t="n">
-        <v>2.41876</v>
+        <v>2.41018</v>
       </c>
       <c r="F32" t="n">
-        <v>2.70274</v>
+        <v>2.69758</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>3.79086</v>
+        <v>3.89368</v>
       </c>
       <c r="C33" t="n">
-        <v>4.50032</v>
+        <v>4.48023</v>
       </c>
       <c r="D33" t="n">
-        <v>11.6834</v>
+        <v>11.6639</v>
       </c>
       <c r="E33" t="n">
-        <v>2.56031</v>
+        <v>2.56015</v>
       </c>
       <c r="F33" t="n">
-        <v>2.86778</v>
+        <v>2.87068</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.54162</v>
+        <v>4.57202</v>
       </c>
       <c r="C34" t="n">
-        <v>5.10739</v>
+        <v>5.10448</v>
       </c>
       <c r="D34" t="n">
-        <v>11.9268</v>
+        <v>11.9376</v>
       </c>
       <c r="E34" t="n">
-        <v>2.83605</v>
+        <v>2.85296</v>
       </c>
       <c r="F34" t="n">
-        <v>3.11561</v>
+        <v>3.1337</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.59921</v>
+        <v>5.61813</v>
       </c>
       <c r="C35" t="n">
-        <v>6.05068</v>
+        <v>6.06279</v>
       </c>
       <c r="D35" t="n">
-        <v>8.44624</v>
+        <v>8.427569999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>1.99298</v>
+        <v>1.99201</v>
       </c>
       <c r="F35" t="n">
-        <v>2.24226</v>
+        <v>2.25537</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.24712</v>
+        <v>7.02843</v>
       </c>
       <c r="C36" t="n">
-        <v>7.35811</v>
+        <v>7.32381</v>
       </c>
       <c r="D36" t="n">
-        <v>8.766719999999999</v>
+        <v>8.740170000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>2.01261</v>
+        <v>2.00868</v>
       </c>
       <c r="F36" t="n">
-        <v>2.28236</v>
+        <v>2.27955</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>9.629390000000001</v>
+        <v>9.637169999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>3.31088</v>
+        <v>3.33105</v>
       </c>
       <c r="D37" t="n">
-        <v>9.09272</v>
+        <v>9.07377</v>
       </c>
       <c r="E37" t="n">
-        <v>2.03626</v>
+        <v>2.03141</v>
       </c>
       <c r="F37" t="n">
-        <v>2.3021</v>
+        <v>2.31112</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.51258</v>
+        <v>2.48665</v>
       </c>
       <c r="C38" t="n">
-        <v>3.3353</v>
+        <v>3.34563</v>
       </c>
       <c r="D38" t="n">
-        <v>9.398680000000001</v>
+        <v>9.37715</v>
       </c>
       <c r="E38" t="n">
-        <v>2.06021</v>
+        <v>2.05376</v>
       </c>
       <c r="F38" t="n">
-        <v>2.32759</v>
+        <v>2.32946</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.54653</v>
+        <v>2.53382</v>
       </c>
       <c r="C39" t="n">
-        <v>3.36312</v>
+        <v>3.38992</v>
       </c>
       <c r="D39" t="n">
-        <v>9.740970000000001</v>
+        <v>9.750959999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>2.08424</v>
+        <v>2.09142</v>
       </c>
       <c r="F39" t="n">
-        <v>2.37111</v>
+        <v>2.3821</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.60063</v>
+        <v>2.60632</v>
       </c>
       <c r="C40" t="n">
-        <v>3.40677</v>
+        <v>3.42736</v>
       </c>
       <c r="D40" t="n">
-        <v>10.066</v>
+        <v>10.0254</v>
       </c>
       <c r="E40" t="n">
-        <v>2.11951</v>
+        <v>2.11424</v>
       </c>
       <c r="F40" t="n">
-        <v>2.41287</v>
+        <v>2.41362</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>2.68423</v>
+        <v>2.65871</v>
       </c>
       <c r="C41" t="n">
-        <v>3.46005</v>
+        <v>3.44798</v>
       </c>
       <c r="D41" t="n">
-        <v>10.3617</v>
+        <v>10.3394</v>
       </c>
       <c r="E41" t="n">
-        <v>2.15315</v>
+        <v>2.14467</v>
       </c>
       <c r="F41" t="n">
-        <v>2.45032</v>
+        <v>2.44624</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>2.72898</v>
+        <v>2.7394</v>
       </c>
       <c r="C42" t="n">
-        <v>3.5095</v>
+        <v>3.50708</v>
       </c>
       <c r="D42" t="n">
-        <v>10.6464</v>
+        <v>10.6232</v>
       </c>
       <c r="E42" t="n">
-        <v>2.17932</v>
+        <v>2.17754</v>
       </c>
       <c r="F42" t="n">
-        <v>2.48292</v>
+        <v>2.48854</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>2.82924</v>
+        <v>2.80531</v>
       </c>
       <c r="C43" t="n">
-        <v>3.57636</v>
+        <v>3.58928</v>
       </c>
       <c r="D43" t="n">
-        <v>10.9589</v>
+        <v>10.9336</v>
       </c>
       <c r="E43" t="n">
-        <v>2.22852</v>
+        <v>2.22521</v>
       </c>
       <c r="F43" t="n">
-        <v>2.54504</v>
+        <v>2.54435</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>2.9699</v>
+        <v>2.95867</v>
       </c>
       <c r="C44" t="n">
-        <v>3.7078</v>
+        <v>3.70957</v>
       </c>
       <c r="D44" t="n">
-        <v>11.2153</v>
+        <v>11.1807</v>
       </c>
       <c r="E44" t="n">
-        <v>2.29021</v>
+        <v>2.29135</v>
       </c>
       <c r="F44" t="n">
-        <v>2.60941</v>
+        <v>2.61488</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.11676</v>
+        <v>3.15496</v>
       </c>
       <c r="C45" t="n">
-        <v>3.88671</v>
+        <v>3.92765</v>
       </c>
       <c r="D45" t="n">
-        <v>11.4833</v>
+        <v>11.4515</v>
       </c>
       <c r="E45" t="n">
-        <v>2.36633</v>
+        <v>2.36822</v>
       </c>
       <c r="F45" t="n">
-        <v>2.68483</v>
+        <v>2.69105</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>3.37112</v>
+        <v>3.44063</v>
       </c>
       <c r="C46" t="n">
-        <v>4.11883</v>
+        <v>4.13286</v>
       </c>
       <c r="D46" t="n">
-        <v>11.7481</v>
+        <v>11.7087</v>
       </c>
       <c r="E46" t="n">
-        <v>2.46708</v>
+        <v>2.46489</v>
       </c>
       <c r="F46" t="n">
-        <v>2.77596</v>
+        <v>2.79169</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>3.75636</v>
+        <v>3.81533</v>
       </c>
       <c r="C47" t="n">
-        <v>4.47686</v>
+        <v>4.49179</v>
       </c>
       <c r="D47" t="n">
-        <v>11.9992</v>
+        <v>11.9907</v>
       </c>
       <c r="E47" t="n">
-        <v>2.63663</v>
+        <v>2.62682</v>
       </c>
       <c r="F47" t="n">
-        <v>2.95324</v>
+        <v>2.94835</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.41655</v>
+        <v>4.38524</v>
       </c>
       <c r="C48" t="n">
-        <v>5.03124</v>
+        <v>5.04509</v>
       </c>
       <c r="D48" t="n">
-        <v>12.2727</v>
+        <v>12.2678</v>
       </c>
       <c r="E48" t="n">
-        <v>2.88627</v>
+        <v>2.89816</v>
       </c>
       <c r="F48" t="n">
-        <v>3.18673</v>
+        <v>3.20906</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.30385</v>
+        <v>5.32752</v>
       </c>
       <c r="C49" t="n">
-        <v>5.83282</v>
+        <v>5.87381</v>
       </c>
       <c r="D49" t="n">
-        <v>12.5355</v>
+        <v>12.555</v>
       </c>
       <c r="E49" t="n">
-        <v>3.2577</v>
+        <v>3.25744</v>
       </c>
       <c r="F49" t="n">
-        <v>3.54638</v>
+        <v>3.54751</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>6.55403</v>
+        <v>6.59383</v>
       </c>
       <c r="C50" t="n">
-        <v>7.08803</v>
+        <v>7.08004</v>
       </c>
       <c r="D50" t="n">
-        <v>8.88054</v>
+        <v>8.85078</v>
       </c>
       <c r="E50" t="n">
-        <v>2.03589</v>
+        <v>2.03194</v>
       </c>
       <c r="F50" t="n">
-        <v>2.3127</v>
+        <v>2.32599</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>8.59243</v>
+        <v>8.649279999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>3.35584</v>
+        <v>3.34278</v>
       </c>
       <c r="D51" t="n">
-        <v>9.212960000000001</v>
+        <v>9.1874</v>
       </c>
       <c r="E51" t="n">
-        <v>2.06208</v>
+        <v>2.05171</v>
       </c>
       <c r="F51" t="n">
-        <v>2.33702</v>
+        <v>2.33869</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>11.5972</v>
+        <v>11.7941</v>
       </c>
       <c r="C52" t="n">
-        <v>3.37057</v>
+        <v>3.34515</v>
       </c>
       <c r="D52" t="n">
-        <v>9.561360000000001</v>
+        <v>9.50981</v>
       </c>
       <c r="E52" t="n">
-        <v>2.0835</v>
+        <v>2.07593</v>
       </c>
       <c r="F52" t="n">
-        <v>2.35395</v>
+        <v>2.3755</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>2.55577</v>
+        <v>2.55394</v>
       </c>
       <c r="C53" t="n">
-        <v>3.4192</v>
+        <v>3.39392</v>
       </c>
       <c r="D53" t="n">
-        <v>9.87618</v>
+        <v>9.85239</v>
       </c>
       <c r="E53" t="n">
-        <v>2.11146</v>
+        <v>2.10511</v>
       </c>
       <c r="F53" t="n">
-        <v>2.38892</v>
+        <v>2.40826</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>2.60864</v>
+        <v>2.61636</v>
       </c>
       <c r="C54" t="n">
-        <v>3.44507</v>
+        <v>3.42171</v>
       </c>
       <c r="D54" t="n">
-        <v>10.2076</v>
+        <v>10.1596</v>
       </c>
       <c r="E54" t="n">
-        <v>2.12956</v>
+        <v>2.13571</v>
       </c>
       <c r="F54" t="n">
-        <v>2.4406</v>
+        <v>2.4519</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>2.67188</v>
+        <v>2.67977</v>
       </c>
       <c r="C55" t="n">
-        <v>3.48448</v>
+        <v>3.459</v>
       </c>
       <c r="D55" t="n">
-        <v>10.5286</v>
+        <v>10.4581</v>
       </c>
       <c r="E55" t="n">
-        <v>2.17559</v>
+        <v>2.1661</v>
       </c>
       <c r="F55" t="n">
-        <v>2.49365</v>
+        <v>2.50235</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>2.75138</v>
+        <v>2.7493</v>
       </c>
       <c r="C56" t="n">
-        <v>3.53511</v>
+        <v>3.51617</v>
       </c>
       <c r="D56" t="n">
-        <v>10.8427</v>
+        <v>10.7482</v>
       </c>
       <c r="E56" t="n">
-        <v>2.21617</v>
+        <v>2.2079</v>
       </c>
       <c r="F56" t="n">
-        <v>2.52805</v>
+        <v>2.54535</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>2.80622</v>
+        <v>2.82575</v>
       </c>
       <c r="C57" t="n">
-        <v>3.59445</v>
+        <v>3.58978</v>
       </c>
       <c r="D57" t="n">
-        <v>11.1583</v>
+        <v>11.0575</v>
       </c>
       <c r="E57" t="n">
-        <v>2.26351</v>
+        <v>2.25982</v>
       </c>
       <c r="F57" t="n">
-        <v>2.58724</v>
+        <v>2.61666</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>2.9666</v>
+        <v>2.95726</v>
       </c>
       <c r="C58" t="n">
-        <v>3.74339</v>
+        <v>3.70725</v>
       </c>
       <c r="D58" t="n">
-        <v>11.4306</v>
+        <v>11.3263</v>
       </c>
       <c r="E58" t="n">
-        <v>2.31638</v>
+        <v>2.31332</v>
       </c>
       <c r="F58" t="n">
-        <v>2.66919</v>
+        <v>2.6588</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.13195</v>
+        <v>3.12896</v>
       </c>
       <c r="C59" t="n">
-        <v>3.84954</v>
+        <v>3.8292</v>
       </c>
       <c r="D59" t="n">
-        <v>11.7157</v>
+        <v>11.5782</v>
       </c>
       <c r="E59" t="n">
-        <v>2.40169</v>
+        <v>2.39013</v>
       </c>
       <c r="F59" t="n">
-        <v>2.76893</v>
+        <v>2.74276</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>3.39402</v>
+        <v>3.39919</v>
       </c>
       <c r="C60" t="n">
-        <v>4.08655</v>
+        <v>4.06906</v>
       </c>
       <c r="D60" t="n">
-        <v>12.0323</v>
+        <v>11.8451</v>
       </c>
       <c r="E60" t="n">
-        <v>2.4933</v>
+        <v>2.49342</v>
       </c>
       <c r="F60" t="n">
-        <v>2.87146</v>
+        <v>2.86594</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>3.75524</v>
+        <v>3.71468</v>
       </c>
       <c r="C61" t="n">
-        <v>4.42733</v>
+        <v>4.38662</v>
       </c>
       <c r="D61" t="n">
-        <v>12.4399</v>
+        <v>12.1559</v>
       </c>
       <c r="E61" t="n">
-        <v>2.63699</v>
+        <v>2.63961</v>
       </c>
       <c r="F61" t="n">
-        <v>3.03808</v>
+        <v>3.01716</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.24023</v>
+        <v>4.21963</v>
       </c>
       <c r="C62" t="n">
-        <v>4.9045</v>
+        <v>4.90903</v>
       </c>
       <c r="D62" t="n">
-        <v>12.7716</v>
+        <v>12.4673</v>
       </c>
       <c r="E62" t="n">
-        <v>2.84241</v>
+        <v>2.85274</v>
       </c>
       <c r="F62" t="n">
-        <v>3.25531</v>
+        <v>3.2444</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.98615</v>
+        <v>4.93461</v>
       </c>
       <c r="C63" t="n">
-        <v>5.703</v>
+        <v>5.67972</v>
       </c>
       <c r="D63" t="n">
-        <v>13.0522</v>
+        <v>12.8241</v>
       </c>
       <c r="E63" t="n">
-        <v>3.21973</v>
+        <v>3.20354</v>
       </c>
       <c r="F63" t="n">
-        <v>3.60761</v>
+        <v>3.57148</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.12993</v>
+        <v>6.15716</v>
       </c>
       <c r="C64" t="n">
-        <v>6.8254</v>
+        <v>6.78037</v>
       </c>
       <c r="D64" t="n">
-        <v>9.08677</v>
+        <v>9.07132</v>
       </c>
       <c r="E64" t="n">
-        <v>2.42093</v>
+        <v>2.412</v>
       </c>
       <c r="F64" t="n">
-        <v>2.70647</v>
+        <v>2.7008</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>7.92917</v>
+        <v>7.92876</v>
       </c>
       <c r="C65" t="n">
-        <v>3.8101</v>
+        <v>3.79518</v>
       </c>
       <c r="D65" t="n">
-        <v>9.44422</v>
+        <v>9.40391</v>
       </c>
       <c r="E65" t="n">
-        <v>2.44009</v>
+        <v>2.439</v>
       </c>
       <c r="F65" t="n">
-        <v>2.7408</v>
+        <v>2.72916</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>10.729</v>
+        <v>10.8499</v>
       </c>
       <c r="C66" t="n">
-        <v>3.81937</v>
+        <v>3.83316</v>
       </c>
       <c r="D66" t="n">
-        <v>10.0747</v>
+        <v>9.796580000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>2.44492</v>
+        <v>2.44386</v>
       </c>
       <c r="F66" t="n">
-        <v>2.77155</v>
+        <v>2.76361</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>2.89716</v>
+        <v>2.90129</v>
       </c>
       <c r="C67" t="n">
-        <v>3.85299</v>
+        <v>3.86443</v>
       </c>
       <c r="D67" t="n">
-        <v>10.3246</v>
+        <v>10.2035</v>
       </c>
       <c r="E67" t="n">
-        <v>2.4813</v>
+        <v>2.46734</v>
       </c>
       <c r="F67" t="n">
-        <v>2.83041</v>
+        <v>2.8091</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>2.93542</v>
+        <v>2.95314</v>
       </c>
       <c r="C68" t="n">
-        <v>3.89884</v>
+        <v>3.89528</v>
       </c>
       <c r="D68" t="n">
-        <v>10.884</v>
+        <v>10.6065</v>
       </c>
       <c r="E68" t="n">
-        <v>2.511</v>
+        <v>2.48996</v>
       </c>
       <c r="F68" t="n">
-        <v>2.8799</v>
+        <v>2.86369</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>2.98057</v>
+        <v>3.00887</v>
       </c>
       <c r="C69" t="n">
-        <v>3.96561</v>
+        <v>3.94822</v>
       </c>
       <c r="D69" t="n">
-        <v>11.442</v>
+        <v>11.0833</v>
       </c>
       <c r="E69" t="n">
-        <v>2.5418</v>
+        <v>2.53919</v>
       </c>
       <c r="F69" t="n">
-        <v>2.93048</v>
+        <v>2.92449</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.07652</v>
+        <v>3.08301</v>
       </c>
       <c r="C70" t="n">
-        <v>3.95312</v>
+        <v>3.96872</v>
       </c>
       <c r="D70" t="n">
-        <v>11.8496</v>
+        <v>11.5987</v>
       </c>
       <c r="E70" t="n">
-        <v>2.56148</v>
+        <v>2.57811</v>
       </c>
       <c r="F70" t="n">
-        <v>2.99146</v>
+        <v>3.00437</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.16565</v>
+        <v>3.16323</v>
       </c>
       <c r="C71" t="n">
-        <v>4.05849</v>
+        <v>4.11052</v>
       </c>
       <c r="D71" t="n">
-        <v>12.0731</v>
+        <v>12.0659</v>
       </c>
       <c r="E71" t="n">
-        <v>2.60645</v>
+        <v>2.6213</v>
       </c>
       <c r="F71" t="n">
-        <v>3.07669</v>
+        <v>3.07516</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.27604</v>
+        <v>3.27162</v>
       </c>
       <c r="C72" t="n">
-        <v>4.19188</v>
+        <v>4.12973</v>
       </c>
       <c r="D72" t="n">
-        <v>12.8426</v>
+        <v>12.7068</v>
       </c>
       <c r="E72" t="n">
-        <v>2.66522</v>
+        <v>2.6592</v>
       </c>
       <c r="F72" t="n">
-        <v>3.12905</v>
+        <v>3.12792</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>3.42248</v>
+        <v>3.42062</v>
       </c>
       <c r="C73" t="n">
-        <v>4.33412</v>
+        <v>4.28282</v>
       </c>
       <c r="D73" t="n">
-        <v>13.1356</v>
+        <v>13.3285</v>
       </c>
       <c r="E73" t="n">
-        <v>2.74729</v>
+        <v>2.74155</v>
       </c>
       <c r="F73" t="n">
-        <v>3.23906</v>
+        <v>3.24766</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>3.66077</v>
+        <v>3.64813</v>
       </c>
       <c r="C74" t="n">
-        <v>4.56523</v>
+        <v>4.49302</v>
       </c>
       <c r="D74" t="n">
-        <v>13.9634</v>
+        <v>14.1802</v>
       </c>
       <c r="E74" t="n">
-        <v>2.84195</v>
+        <v>2.84052</v>
       </c>
       <c r="F74" t="n">
-        <v>3.37527</v>
+        <v>3.3743</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>3.97518</v>
+        <v>3.95177</v>
       </c>
       <c r="C75" t="n">
-        <v>4.80059</v>
+        <v>4.79338</v>
       </c>
       <c r="D75" t="n">
-        <v>15.3542</v>
+        <v>15.1446</v>
       </c>
       <c r="E75" t="n">
-        <v>2.97633</v>
+        <v>2.98173</v>
       </c>
       <c r="F75" t="n">
-        <v>3.53802</v>
+        <v>3.53754</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>4.41068</v>
+        <v>4.39536</v>
       </c>
       <c r="C76" t="n">
-        <v>5.3011</v>
+        <v>5.29233</v>
       </c>
       <c r="D76" t="n">
-        <v>16.7966</v>
+        <v>16.3571</v>
       </c>
       <c r="E76" t="n">
-        <v>3.17182</v>
+        <v>3.16511</v>
       </c>
       <c r="F76" t="n">
-        <v>3.7721</v>
+        <v>3.77552</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.09308</v>
+        <v>5.05422</v>
       </c>
       <c r="C77" t="n">
-        <v>5.94249</v>
+        <v>5.93025</v>
       </c>
       <c r="D77" t="n">
-        <v>17.6402</v>
+        <v>18.1599</v>
       </c>
       <c r="E77" t="n">
-        <v>3.48785</v>
+        <v>3.49057</v>
       </c>
       <c r="F77" t="n">
-        <v>4.10504</v>
+        <v>4.09338</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.14893</v>
+        <v>6.09432</v>
       </c>
       <c r="C78" t="n">
-        <v>6.9881</v>
+        <v>6.98725</v>
       </c>
       <c r="D78" t="n">
-        <v>15.4419</v>
+        <v>15.572</v>
       </c>
       <c r="E78" t="n">
-        <v>2.69396</v>
+        <v>2.67697</v>
       </c>
       <c r="F78" t="n">
-        <v>3.14737</v>
+        <v>3.15201</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.73313</v>
+        <v>7.79736</v>
       </c>
       <c r="C79" t="n">
-        <v>4.16818</v>
+        <v>4.19118</v>
       </c>
       <c r="D79" t="n">
-        <v>16.5848</v>
+        <v>16.8186</v>
       </c>
       <c r="E79" t="n">
-        <v>2.70959</v>
+        <v>2.69541</v>
       </c>
       <c r="F79" t="n">
-        <v>3.18273</v>
+        <v>3.18667</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>10.3909</v>
+        <v>10.4093</v>
       </c>
       <c r="C80" t="n">
-        <v>4.18985</v>
+        <v>4.19701</v>
       </c>
       <c r="D80" t="n">
-        <v>17.6715</v>
+        <v>17.6843</v>
       </c>
       <c r="E80" t="n">
-        <v>2.722</v>
+        <v>2.70991</v>
       </c>
       <c r="F80" t="n">
-        <v>3.25548</v>
+        <v>3.23225</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>3.47443</v>
+        <v>3.49382</v>
       </c>
       <c r="C81" t="n">
-        <v>4.22235</v>
+        <v>4.25276</v>
       </c>
       <c r="D81" t="n">
-        <v>18.7522</v>
+        <v>18.6249</v>
       </c>
       <c r="E81" t="n">
-        <v>2.73982</v>
+        <v>2.74251</v>
       </c>
       <c r="F81" t="n">
-        <v>3.29411</v>
+        <v>3.29625</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>3.50946</v>
+        <v>3.55327</v>
       </c>
       <c r="C82" t="n">
-        <v>4.26058</v>
+        <v>4.25782</v>
       </c>
       <c r="D82" t="n">
-        <v>19.7388</v>
+        <v>19.6527</v>
       </c>
       <c r="E82" t="n">
-        <v>2.77957</v>
+        <v>2.75916</v>
       </c>
       <c r="F82" t="n">
-        <v>3.34733</v>
+        <v>3.33662</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>3.58224</v>
+        <v>3.61467</v>
       </c>
       <c r="C83" t="n">
-        <v>4.28365</v>
+        <v>4.30972</v>
       </c>
       <c r="D83" t="n">
-        <v>20.8409</v>
+        <v>20.8144</v>
       </c>
       <c r="E83" t="n">
-        <v>2.79587</v>
+        <v>2.78139</v>
       </c>
       <c r="F83" t="n">
-        <v>3.38853</v>
+        <v>3.39149</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>3.65096</v>
+        <v>3.67398</v>
       </c>
       <c r="C84" t="n">
-        <v>4.33308</v>
+        <v>4.3426</v>
       </c>
       <c r="D84" t="n">
-        <v>21.9215</v>
+        <v>21.952</v>
       </c>
       <c r="E84" t="n">
-        <v>2.83878</v>
+        <v>2.82099</v>
       </c>
       <c r="F84" t="n">
-        <v>3.47127</v>
+        <v>3.46511</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>3.77162</v>
+        <v>3.78691</v>
       </c>
       <c r="C85" t="n">
-        <v>4.41376</v>
+        <v>4.4877</v>
       </c>
       <c r="D85" t="n">
-        <v>22.9446</v>
+        <v>22.9739</v>
       </c>
       <c r="E85" t="n">
-        <v>2.87691</v>
+        <v>2.85649</v>
       </c>
       <c r="F85" t="n">
-        <v>3.54742</v>
+        <v>3.53152</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>3.87804</v>
+        <v>3.87412</v>
       </c>
       <c r="C86" t="n">
-        <v>4.53015</v>
+        <v>4.57285</v>
       </c>
       <c r="D86" t="n">
-        <v>24.0481</v>
+        <v>24.186</v>
       </c>
       <c r="E86" t="n">
-        <v>2.90703</v>
+        <v>2.90369</v>
       </c>
       <c r="F86" t="n">
-        <v>3.64298</v>
+        <v>3.64202</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.0051</v>
+        <v>4.05665</v>
       </c>
       <c r="C87" t="n">
-        <v>4.69233</v>
+        <v>4.69208</v>
       </c>
       <c r="D87" t="n">
-        <v>25.3255</v>
+        <v>25.2816</v>
       </c>
       <c r="E87" t="n">
-        <v>3.0039</v>
+        <v>2.98991</v>
       </c>
       <c r="F87" t="n">
-        <v>3.77487</v>
+        <v>3.78795</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.24931</v>
+        <v>4.24175</v>
       </c>
       <c r="C88" t="n">
-        <v>4.98819</v>
+        <v>4.93167</v>
       </c>
       <c r="D88" t="n">
-        <v>26.4378</v>
+        <v>26.4922</v>
       </c>
       <c r="E88" t="n">
-        <v>3.10761</v>
+        <v>3.08616</v>
       </c>
       <c r="F88" t="n">
-        <v>3.95909</v>
+        <v>4.01316</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>4.51456</v>
+        <v>4.56062</v>
       </c>
       <c r="C89" t="n">
-        <v>5.3545</v>
+        <v>5.36107</v>
       </c>
       <c r="D89" t="n">
-        <v>27.7044</v>
+        <v>27.762</v>
       </c>
       <c r="E89" t="n">
-        <v>3.26674</v>
+        <v>3.25917</v>
       </c>
       <c r="F89" t="n">
-        <v>4.25993</v>
+        <v>4.26822</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>4.99309</v>
+        <v>5.03537</v>
       </c>
       <c r="C90" t="n">
-        <v>5.87879</v>
+        <v>5.84562</v>
       </c>
       <c r="D90" t="n">
-        <v>29.0426</v>
+        <v>28.9797</v>
       </c>
       <c r="E90" t="n">
-        <v>3.51642</v>
+        <v>3.52002</v>
       </c>
       <c r="F90" t="n">
-        <v>4.73698</v>
+        <v>4.7611</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>5.74554</v>
+        <v>5.7894</v>
       </c>
       <c r="C91" t="n">
-        <v>6.7226</v>
+        <v>6.70426</v>
       </c>
       <c r="D91" t="n">
-        <v>30.3803</v>
+        <v>30.3843</v>
       </c>
       <c r="E91" t="n">
-        <v>3.92591</v>
+        <v>3.93965</v>
       </c>
       <c r="F91" t="n">
-        <v>5.65601</v>
+        <v>5.6563</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>6.89931</v>
+        <v>6.90507</v>
       </c>
       <c r="C92" t="n">
-        <v>7.93405</v>
+        <v>7.99966</v>
       </c>
       <c r="D92" t="n">
-        <v>24.6766</v>
+        <v>24.5353</v>
       </c>
       <c r="E92" t="n">
-        <v>2.89113</v>
+        <v>2.88482</v>
       </c>
       <c r="F92" t="n">
-        <v>3.56115</v>
+        <v>3.5894</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>8.738490000000001</v>
+        <v>8.74708</v>
       </c>
       <c r="C93" t="n">
-        <v>9.638339999999999</v>
+        <v>9.654210000000001</v>
       </c>
       <c r="D93" t="n">
-        <v>25.4871</v>
+        <v>25.5432</v>
       </c>
       <c r="E93" t="n">
-        <v>2.93565</v>
+        <v>2.92167</v>
       </c>
       <c r="F93" t="n">
-        <v>3.74171</v>
+        <v>3.76262</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>11.5058</v>
+        <v>11.603</v>
       </c>
       <c r="C94" t="n">
-        <v>4.81922</v>
+        <v>4.80888</v>
       </c>
       <c r="D94" t="n">
-        <v>26.359</v>
+        <v>26.421</v>
       </c>
       <c r="E94" t="n">
-        <v>2.97686</v>
+        <v>2.9765</v>
       </c>
       <c r="F94" t="n">
-        <v>3.99285</v>
+        <v>3.99028</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.14396</v>
+        <v>4.13331</v>
       </c>
       <c r="C95" t="n">
-        <v>5.0517</v>
+        <v>5.01765</v>
       </c>
       <c r="D95" t="n">
-        <v>27.3916</v>
+        <v>27.4032</v>
       </c>
       <c r="E95" t="n">
-        <v>3.10774</v>
+        <v>3.09508</v>
       </c>
       <c r="F95" t="n">
-        <v>4.38786</v>
+        <v>4.38377</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>4.46822</v>
+        <v>4.39277</v>
       </c>
       <c r="C96" t="n">
-        <v>5.31506</v>
+        <v>5.33083</v>
       </c>
       <c r="D96" t="n">
-        <v>28.2883</v>
+        <v>28.2374</v>
       </c>
       <c r="E96" t="n">
-        <v>3.28167</v>
+        <v>3.33815</v>
       </c>
       <c r="F96" t="n">
-        <v>4.82447</v>
+        <v>4.82872</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>4.79826</v>
+        <v>4.86425</v>
       </c>
       <c r="C97" t="n">
-        <v>5.59573</v>
+        <v>5.53779</v>
       </c>
       <c r="D97" t="n">
-        <v>29.2219</v>
+        <v>29.1921</v>
       </c>
       <c r="E97" t="n">
-        <v>3.54905</v>
+        <v>3.55782</v>
       </c>
       <c r="F97" t="n">
-        <v>5.27233</v>
+        <v>5.30145</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>5.35994</v>
+        <v>5.29204</v>
       </c>
       <c r="C98" t="n">
-        <v>5.78788</v>
+        <v>5.82364</v>
       </c>
       <c r="D98" t="n">
-        <v>30.1639</v>
+        <v>30.1709</v>
       </c>
       <c r="E98" t="n">
-        <v>3.7998</v>
+        <v>3.80036</v>
       </c>
       <c r="F98" t="n">
-        <v>5.90961</v>
+        <v>5.87218</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>5.78315</v>
+        <v>5.77788</v>
       </c>
       <c r="C99" t="n">
-        <v>6.07457</v>
+        <v>6.04826</v>
       </c>
       <c r="D99" t="n">
-        <v>31.36</v>
+        <v>31.3018</v>
       </c>
       <c r="E99" t="n">
-        <v>4.11566</v>
+        <v>4.14593</v>
       </c>
       <c r="F99" t="n">
-        <v>6.39798</v>
+        <v>6.46515</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>6.23514</v>
+        <v>6.30227</v>
       </c>
       <c r="C100" t="n">
-        <v>6.36197</v>
+        <v>6.341</v>
       </c>
       <c r="D100" t="n">
-        <v>32.2775</v>
+        <v>32.3738</v>
       </c>
       <c r="E100" t="n">
-        <v>4.4073</v>
+        <v>4.43356</v>
       </c>
       <c r="F100" t="n">
-        <v>6.93967</v>
+        <v>7.02207</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>6.83117</v>
+        <v>6.88015</v>
       </c>
       <c r="C101" t="n">
-        <v>6.66059</v>
+        <v>6.65799</v>
       </c>
       <c r="D101" t="n">
-        <v>33.513</v>
+        <v>33.4685</v>
       </c>
       <c r="E101" t="n">
-        <v>4.67766</v>
+        <v>4.70333</v>
       </c>
       <c r="F101" t="n">
-        <v>7.51898</v>
+        <v>7.49326</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.36625</v>
+        <v>7.35046</v>
       </c>
       <c r="C102" t="n">
-        <v>6.98958</v>
+        <v>6.97776</v>
       </c>
       <c r="D102" t="n">
-        <v>34.5499</v>
+        <v>34.5198</v>
       </c>
       <c r="E102" t="n">
-        <v>4.9527</v>
+        <v>4.96427</v>
       </c>
       <c r="F102" t="n">
-        <v>7.96409</v>
+        <v>7.9803</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>7.94288</v>
+        <v>7.95062</v>
       </c>
       <c r="C103" t="n">
-        <v>7.44719</v>
+        <v>7.42594</v>
       </c>
       <c r="D103" t="n">
-        <v>35.8061</v>
+        <v>35.8621</v>
       </c>
       <c r="E103" t="n">
-        <v>5.22522</v>
+        <v>5.25814</v>
       </c>
       <c r="F103" t="n">
-        <v>8.45543</v>
+        <v>8.50778</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>8.60319</v>
+        <v>8.628130000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>8.02256</v>
+        <v>7.98591</v>
       </c>
       <c r="D104" t="n">
-        <v>37.0763</v>
+        <v>37.1114</v>
       </c>
       <c r="E104" t="n">
-        <v>5.5013</v>
+        <v>5.51496</v>
       </c>
       <c r="F104" t="n">
-        <v>8.929360000000001</v>
+        <v>8.95706</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>9.201610000000001</v>
+        <v>9.404909999999999</v>
       </c>
       <c r="C105" t="n">
-        <v>8.81306</v>
+        <v>8.77852</v>
       </c>
       <c r="D105" t="n">
-        <v>38.4474</v>
+        <v>38.4176</v>
       </c>
       <c r="E105" t="n">
-        <v>5.92257</v>
+        <v>6.20458</v>
       </c>
       <c r="F105" t="n">
-        <v>9.573589999999999</v>
+        <v>9.804349999999999</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>10.3125</v>
+        <v>10.3667</v>
       </c>
       <c r="C106" t="n">
-        <v>9.926030000000001</v>
+        <v>9.91808</v>
       </c>
       <c r="D106" t="n">
-        <v>39.6448</v>
+        <v>39.8005</v>
       </c>
       <c r="E106" t="n">
-        <v>6.46975</v>
+        <v>6.49209</v>
       </c>
       <c r="F106" t="n">
-        <v>10.3232</v>
+        <v>10.3861</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>11.7924</v>
+        <v>11.7801</v>
       </c>
       <c r="C107" t="n">
-        <v>11.5107</v>
+        <v>11.4898</v>
       </c>
       <c r="D107" t="n">
-        <v>30.212</v>
+        <v>30.4105</v>
       </c>
       <c r="E107" t="n">
-        <v>4.56088</v>
+        <v>4.59884</v>
       </c>
       <c r="F107" t="n">
-        <v>6.82027</v>
+        <v>6.79871</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.9978</v>
+        <v>14.0036</v>
       </c>
       <c r="C108" t="n">
-        <v>6.41691</v>
+        <v>6.40496</v>
       </c>
       <c r="D108" t="n">
-        <v>31.2753</v>
+        <v>31.2363</v>
       </c>
       <c r="E108" t="n">
-        <v>4.70732</v>
+        <v>4.72625</v>
       </c>
       <c r="F108" t="n">
-        <v>7.03025</v>
+        <v>7.04027</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>17.5411</v>
+        <v>17.5522</v>
       </c>
       <c r="C109" t="n">
-        <v>6.52952</v>
+        <v>6.52649</v>
       </c>
       <c r="D109" t="n">
-        <v>32.2161</v>
+        <v>32.0231</v>
       </c>
       <c r="E109" t="n">
-        <v>4.8052</v>
+        <v>4.84149</v>
       </c>
       <c r="F109" t="n">
-        <v>7.23644</v>
+        <v>7.23545</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.05473</v>
+        <v>7.08812</v>
       </c>
       <c r="C110" t="n">
-        <v>6.67377</v>
+        <v>6.66969</v>
       </c>
       <c r="D110" t="n">
-        <v>33.088</v>
+        <v>32.9483</v>
       </c>
       <c r="E110" t="n">
-        <v>4.94866</v>
+        <v>4.96917</v>
       </c>
       <c r="F110" t="n">
-        <v>7.43332</v>
+        <v>7.49654</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.26857</v>
+        <v>7.27966</v>
       </c>
       <c r="C111" t="n">
-        <v>6.81937</v>
+        <v>6.80818</v>
       </c>
       <c r="D111" t="n">
-        <v>34.0163</v>
+        <v>33.8519</v>
       </c>
       <c r="E111" t="n">
-        <v>5.06999</v>
+        <v>5.11253</v>
       </c>
       <c r="F111" t="n">
-        <v>7.69775</v>
+        <v>7.7195</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.52362</v>
+        <v>7.48812</v>
       </c>
       <c r="C112" t="n">
-        <v>6.97975</v>
+        <v>6.97809</v>
       </c>
       <c r="D112" t="n">
-        <v>34.8706</v>
+        <v>34.9373</v>
       </c>
       <c r="E112" t="n">
-        <v>5.2272</v>
+        <v>5.25508</v>
       </c>
       <c r="F112" t="n">
-        <v>7.95788</v>
+        <v>7.98645</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>7.73471</v>
+        <v>7.7649</v>
       </c>
       <c r="C113" t="n">
-        <v>7.17179</v>
+        <v>7.17987</v>
       </c>
       <c r="D113" t="n">
-        <v>35.9829</v>
+        <v>35.8584</v>
       </c>
       <c r="E113" t="n">
-        <v>5.35637</v>
+        <v>5.3788</v>
       </c>
       <c r="F113" t="n">
-        <v>8.18868</v>
+        <v>8.221</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>7.99407</v>
+        <v>8.00028</v>
       </c>
       <c r="C114" t="n">
-        <v>7.38812</v>
+        <v>7.38899</v>
       </c>
       <c r="D114" t="n">
-        <v>37.0015</v>
+        <v>37.0635</v>
       </c>
       <c r="E114" t="n">
-        <v>5.52652</v>
+        <v>5.54812</v>
       </c>
       <c r="F114" t="n">
-        <v>8.475580000000001</v>
+        <v>8.534179999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>8.30857</v>
+        <v>8.313980000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>7.67605</v>
+        <v>7.63285</v>
       </c>
       <c r="D115" t="n">
-        <v>38.0525</v>
+        <v>38.0681</v>
       </c>
       <c r="E115" t="n">
-        <v>5.68343</v>
+        <v>5.71751</v>
       </c>
       <c r="F115" t="n">
-        <v>8.790319999999999</v>
+        <v>8.82785</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>8.62965</v>
+        <v>8.665889999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>7.9909</v>
+        <v>8.012740000000001</v>
       </c>
       <c r="D116" t="n">
-        <v>39.1855</v>
+        <v>39.2376</v>
       </c>
       <c r="E116" t="n">
-        <v>5.88744</v>
+        <v>5.91257</v>
       </c>
       <c r="F116" t="n">
-        <v>9.099629999999999</v>
+        <v>9.153549999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>9.026160000000001</v>
+        <v>9.09484</v>
       </c>
       <c r="C117" t="n">
-        <v>8.3781</v>
+        <v>8.370950000000001</v>
       </c>
       <c r="D117" t="n">
-        <v>40.3032</v>
+        <v>40.3766</v>
       </c>
       <c r="E117" t="n">
-        <v>6.14204</v>
+        <v>6.16474</v>
       </c>
       <c r="F117" t="n">
-        <v>9.539249999999999</v>
+        <v>9.587949999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>9.61664</v>
+        <v>9.622780000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>8.9664</v>
+        <v>8.950390000000001</v>
       </c>
       <c r="D118" t="n">
-        <v>41.4323</v>
+        <v>41.5782</v>
       </c>
       <c r="E118" t="n">
-        <v>6.42061</v>
+        <v>6.44761</v>
       </c>
       <c r="F118" t="n">
-        <v>10.0128</v>
+        <v>10.0456</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>10.3105</v>
+        <v>10.3291</v>
       </c>
       <c r="C119" t="n">
-        <v>9.702019999999999</v>
+        <v>9.777810000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>42.6413</v>
+        <v>42.7854</v>
       </c>
       <c r="E119" t="n">
-        <v>6.82181</v>
+        <v>6.81363</v>
       </c>
       <c r="F119" t="n">
-        <v>10.6147</v>
+        <v>10.6423</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>11.2562</v>
+        <v>11.2892</v>
       </c>
       <c r="C120" t="n">
-        <v>10.8249</v>
+        <v>10.8153</v>
       </c>
       <c r="D120" t="n">
-        <v>44.1431</v>
+        <v>44.2064</v>
       </c>
       <c r="E120" t="n">
-        <v>7.35202</v>
+        <v>7.37157</v>
       </c>
       <c r="F120" t="n">
-        <v>11.3741</v>
+        <v>11.4363</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>12.6507</v>
+        <v>12.6599</v>
       </c>
       <c r="C121" t="n">
-        <v>12.4107</v>
+        <v>12.4047</v>
       </c>
       <c r="D121" t="n">
-        <v>33.0175</v>
+        <v>33.0379</v>
       </c>
       <c r="E121" t="n">
-        <v>4.97446</v>
+        <v>4.96753</v>
       </c>
       <c r="F121" t="n">
-        <v>7.30166</v>
+        <v>7.27662</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>14.6429</v>
+        <v>14.6187</v>
       </c>
       <c r="C122" t="n">
-        <v>6.759</v>
+        <v>6.76237</v>
       </c>
       <c r="D122" t="n">
-        <v>33.9033</v>
+        <v>34.0274</v>
       </c>
       <c r="E122" t="n">
-        <v>5.07359</v>
+        <v>5.09254</v>
       </c>
       <c r="F122" t="n">
-        <v>7.52157</v>
+        <v>7.52657</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>17.8124</v>
+        <v>17.8544</v>
       </c>
       <c r="C123" t="n">
-        <v>6.91264</v>
+        <v>6.898</v>
       </c>
       <c r="D123" t="n">
-        <v>34.9835</v>
+        <v>34.768</v>
       </c>
       <c r="E123" t="n">
-        <v>5.19527</v>
+        <v>5.17448</v>
       </c>
       <c r="F123" t="n">
-        <v>7.74857</v>
+        <v>7.73467</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>7.46133</v>
+        <v>7.44512</v>
       </c>
       <c r="C124" t="n">
-        <v>7.04638</v>
+        <v>7.02997</v>
       </c>
       <c r="D124" t="n">
-        <v>35.7911</v>
+        <v>35.8953</v>
       </c>
       <c r="E124" t="n">
-        <v>5.32125</v>
+        <v>5.30382</v>
       </c>
       <c r="F124" t="n">
-        <v>7.98525</v>
+        <v>7.94961</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>7.65098</v>
+        <v>7.66597</v>
       </c>
       <c r="C125" t="n">
-        <v>7.18547</v>
+        <v>7.21358</v>
       </c>
       <c r="D125" t="n">
-        <v>36.6765</v>
+        <v>36.869</v>
       </c>
       <c r="E125" t="n">
-        <v>5.46148</v>
+        <v>5.42763</v>
       </c>
       <c r="F125" t="n">
-        <v>8.21773</v>
+        <v>8.182829999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>7.84768</v>
+        <v>7.88748</v>
       </c>
       <c r="C126" t="n">
-        <v>7.35289</v>
+        <v>7.36485</v>
       </c>
       <c r="D126" t="n">
-        <v>37.6149</v>
+        <v>37.7594</v>
       </c>
       <c r="E126" t="n">
-        <v>5.58682</v>
+        <v>5.58356</v>
       </c>
       <c r="F126" t="n">
-        <v>8.48419</v>
+        <v>8.51004</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>8.09501</v>
+        <v>8.07319</v>
       </c>
       <c r="C127" t="n">
-        <v>7.55766</v>
+        <v>7.5712</v>
       </c>
       <c r="D127" t="n">
-        <v>38.6049</v>
+        <v>38.7342</v>
       </c>
       <c r="E127" t="n">
-        <v>5.7486</v>
+        <v>5.72873</v>
       </c>
       <c r="F127" t="n">
-        <v>8.769399999999999</v>
+        <v>8.77365</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>8.335760000000001</v>
+        <v>8.375310000000001</v>
       </c>
       <c r="C128" t="n">
-        <v>7.78677</v>
+        <v>7.76899</v>
       </c>
       <c r="D128" t="n">
-        <v>39.6201</v>
+        <v>39.5617</v>
       </c>
       <c r="E128" t="n">
-        <v>5.93015</v>
+        <v>5.90234</v>
       </c>
       <c r="F128" t="n">
-        <v>9.09375</v>
+        <v>9.10263</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>8.628159999999999</v>
+        <v>8.687749999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>8.05045</v>
+        <v>8.04034</v>
       </c>
       <c r="D129" t="n">
-        <v>40.6284</v>
+        <v>40.6245</v>
       </c>
       <c r="E129" t="n">
-        <v>6.0861</v>
+        <v>6.08347</v>
       </c>
       <c r="F129" t="n">
-        <v>9.429740000000001</v>
+        <v>9.433909999999999</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>9.01667</v>
+        <v>8.99741</v>
       </c>
       <c r="C130" t="n">
-        <v>8.369350000000001</v>
+        <v>8.368460000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>41.655</v>
+        <v>41.9094</v>
       </c>
       <c r="E130" t="n">
-        <v>6.30459</v>
+        <v>6.3286</v>
       </c>
       <c r="F130" t="n">
-        <v>9.819520000000001</v>
+        <v>9.79537</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>9.420489999999999</v>
+        <v>9.43052</v>
       </c>
       <c r="C131" t="n">
-        <v>8.80711</v>
+        <v>8.79683</v>
       </c>
       <c r="D131" t="n">
-        <v>42.9507</v>
+        <v>42.9211</v>
       </c>
       <c r="E131" t="n">
-        <v>6.56024</v>
+        <v>6.53845</v>
       </c>
       <c r="F131" t="n">
-        <v>10.3021</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>9.93994</v>
+        <v>9.95439</v>
       </c>
       <c r="C132" t="n">
-        <v>9.39068</v>
+        <v>9.36922</v>
       </c>
       <c r="D132" t="n">
-        <v>44.2318</v>
+        <v>44.0545</v>
       </c>
       <c r="E132" t="n">
-        <v>6.86188</v>
+        <v>6.84087</v>
       </c>
       <c r="F132" t="n">
-        <v>10.7724</v>
+        <v>10.7285</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>10.6497</v>
+        <v>10.66</v>
       </c>
       <c r="C133" t="n">
-        <v>10.1787</v>
+        <v>10.1661</v>
       </c>
       <c r="D133" t="n">
-        <v>45.5255</v>
+        <v>45.3394</v>
       </c>
       <c r="E133" t="n">
-        <v>7.27076</v>
+        <v>7.24386</v>
       </c>
       <c r="F133" t="n">
-        <v>11.321</v>
+        <v>11.3607</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>11.5571</v>
+        <v>11.572</v>
       </c>
       <c r="C134" t="n">
-        <v>11.2091</v>
+        <v>11.2094</v>
       </c>
       <c r="D134" t="n">
-        <v>46.8444</v>
+        <v>46.8251</v>
       </c>
       <c r="E134" t="n">
-        <v>7.75205</v>
+        <v>7.73654</v>
       </c>
       <c r="F134" t="n">
-        <v>12.1462</v>
+        <v>12.1354</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>12.879</v>
+        <v>12.8979</v>
       </c>
       <c r="C135" t="n">
-        <v>12.7218</v>
+        <v>12.684</v>
       </c>
       <c r="D135" t="n">
-        <v>34.5344</v>
+        <v>34.6242</v>
       </c>
       <c r="E135" t="n">
-        <v>10.9757</v>
+        <v>10.9636</v>
       </c>
       <c r="F135" t="n">
-        <v>13.5614</v>
+        <v>13.4737</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>14.7654</v>
+        <v>14.7556</v>
       </c>
       <c r="C136" t="n">
-        <v>15.3086</v>
+        <v>15.3626</v>
       </c>
       <c r="D136" t="n">
-        <v>35.507</v>
+        <v>35.4157</v>
       </c>
       <c r="E136" t="n">
-        <v>11.0554</v>
+        <v>11.0413</v>
       </c>
       <c r="F136" t="n">
-        <v>13.7328</v>
+        <v>13.6596</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7295</v>
+        <v>17.7246</v>
       </c>
       <c r="C137" t="n">
-        <v>15.5629</v>
+        <v>15.5101</v>
       </c>
       <c r="D137" t="n">
-        <v>36.3931</v>
+        <v>36.332</v>
       </c>
       <c r="E137" t="n">
-        <v>11.1945</v>
+        <v>11.172</v>
       </c>
       <c r="F137" t="n">
-        <v>13.9829</v>
+        <v>13.9747</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>13.2093</v>
+        <v>13.2414</v>
       </c>
       <c r="C138" t="n">
-        <v>15.7112</v>
+        <v>15.6702</v>
       </c>
       <c r="D138" t="n">
-        <v>37.3667</v>
+        <v>37.3757</v>
       </c>
       <c r="E138" t="n">
-        <v>11.2713</v>
+        <v>11.1906</v>
       </c>
       <c r="F138" t="n">
-        <v>14.1697</v>
+        <v>14.1012</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>13.3751</v>
+        <v>13.2349</v>
       </c>
       <c r="C139" t="n">
-        <v>15.8165</v>
+        <v>15.8831</v>
       </c>
       <c r="D139" t="n">
-        <v>38.2906</v>
+        <v>38.1641</v>
       </c>
       <c r="E139" t="n">
-        <v>11.3939</v>
+        <v>11.3734</v>
       </c>
       <c r="F139" t="n">
-        <v>14.4223</v>
+        <v>14.4776</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.5659</v>
+        <v>13.4543</v>
       </c>
       <c r="C140" t="n">
-        <v>16.0224</v>
+        <v>16.0226</v>
       </c>
       <c r="D140" t="n">
-        <v>39.1891</v>
+        <v>39.1972</v>
       </c>
       <c r="E140" t="n">
-        <v>11.5097</v>
+        <v>11.4681</v>
       </c>
       <c r="F140" t="n">
-        <v>14.6587</v>
+        <v>14.5771</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>13.6229</v>
+        <v>13.6069</v>
       </c>
       <c r="C141" t="n">
-        <v>16.2452</v>
+        <v>16.1954</v>
       </c>
       <c r="D141" t="n">
-        <v>40.0685</v>
+        <v>40.0462</v>
       </c>
       <c r="E141" t="n">
-        <v>11.6497</v>
+        <v>11.627</v>
       </c>
       <c r="F141" t="n">
-        <v>15.0164</v>
+        <v>14.9834</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>13.886</v>
+        <v>13.7124</v>
       </c>
       <c r="C142" t="n">
-        <v>16.3168</v>
+        <v>16.3835</v>
       </c>
       <c r="D142" t="n">
-        <v>41.1866</v>
+        <v>41.1295</v>
       </c>
       <c r="E142" t="n">
-        <v>11.8202</v>
+        <v>11.7898</v>
       </c>
       <c r="F142" t="n">
-        <v>15.2666</v>
+        <v>15.2556</v>
       </c>
     </row>
     <row r="143">
@@ -7899,16 +7899,16 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>13.9963</v>
+        <v>13.9229</v>
       </c>
       <c r="C143" t="n">
-        <v>16.4973</v>
+        <v>16.5706</v>
       </c>
       <c r="D143" t="n">
-        <v>42.1133</v>
+        <v>42.4385</v>
       </c>
       <c r="E143" t="n">
-        <v>11.8618</v>
+        <v>11.8983</v>
       </c>
       <c r="F143" t="n">
         <v>15.5748</v>

--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.53952</v>
+        <v>2.61752</v>
       </c>
       <c r="C2" t="n">
-        <v>3.59073</v>
+        <v>3.76935</v>
       </c>
       <c r="D2" t="n">
-        <v>8.22372</v>
+        <v>8.38654</v>
       </c>
       <c r="E2" t="n">
-        <v>2.12591</v>
+        <v>2.51107</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2305</v>
+        <v>2.51658</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.68225</v>
+        <v>2.74736</v>
       </c>
       <c r="C3" t="n">
-        <v>3.71393</v>
+        <v>3.95982</v>
       </c>
       <c r="D3" t="n">
-        <v>8.56372</v>
+        <v>8.64716</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2314</v>
+        <v>2.55674</v>
       </c>
       <c r="F3" t="n">
-        <v>2.30897</v>
+        <v>2.57231</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.89918</v>
+        <v>2.88086</v>
       </c>
       <c r="C4" t="n">
-        <v>3.96832</v>
+        <v>4.29754</v>
       </c>
       <c r="D4" t="n">
-        <v>8.83202</v>
+        <v>9.048539999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>2.31136</v>
+        <v>2.62757</v>
       </c>
       <c r="F4" t="n">
-        <v>2.41552</v>
+        <v>2.65917</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.24399</v>
+        <v>3.26135</v>
       </c>
       <c r="C5" t="n">
-        <v>4.40228</v>
+        <v>4.65402</v>
       </c>
       <c r="D5" t="n">
-        <v>9.252140000000001</v>
+        <v>9.45002</v>
       </c>
       <c r="E5" t="n">
-        <v>2.40082</v>
+        <v>2.75559</v>
       </c>
       <c r="F5" t="n">
-        <v>2.50342</v>
+        <v>2.77504</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.88487</v>
+        <v>3.95635</v>
       </c>
       <c r="C6" t="n">
-        <v>4.97335</v>
+        <v>5.44404</v>
       </c>
       <c r="D6" t="n">
-        <v>9.66531</v>
+        <v>9.83756</v>
       </c>
       <c r="E6" t="n">
-        <v>2.59687</v>
+        <v>2.97973</v>
       </c>
       <c r="F6" t="n">
-        <v>2.69458</v>
+        <v>2.98802</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>5.55964</v>
+        <v>4.91616</v>
       </c>
       <c r="C7" t="n">
-        <v>6.07572</v>
+        <v>6.62371</v>
       </c>
       <c r="D7" t="n">
-        <v>7.02962</v>
+        <v>7.12411</v>
       </c>
       <c r="E7" t="n">
-        <v>1.90408</v>
+        <v>2.29291</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0021</v>
+        <v>2.30101</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>7.36407</v>
+        <v>6.92258</v>
       </c>
       <c r="C8" t="n">
-        <v>3.21422</v>
+        <v>3.33399</v>
       </c>
       <c r="D8" t="n">
-        <v>7.3287</v>
+        <v>7.4786</v>
       </c>
       <c r="E8" t="n">
-        <v>1.91485</v>
+        <v>2.31716</v>
       </c>
       <c r="F8" t="n">
-        <v>2.01169</v>
+        <v>2.3186</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>10.557</v>
+        <v>9.871869999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>3.22955</v>
+        <v>3.35382</v>
       </c>
       <c r="D9" t="n">
-        <v>7.66652</v>
+        <v>7.81852</v>
       </c>
       <c r="E9" t="n">
-        <v>1.93413</v>
+        <v>2.32921</v>
       </c>
       <c r="F9" t="n">
-        <v>2.02964</v>
+        <v>2.33072</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.38519</v>
+        <v>2.36011</v>
       </c>
       <c r="C10" t="n">
-        <v>3.27572</v>
+        <v>3.3749</v>
       </c>
       <c r="D10" t="n">
-        <v>8.00483</v>
+        <v>8.13926</v>
       </c>
       <c r="E10" t="n">
-        <v>1.95308</v>
+        <v>2.34288</v>
       </c>
       <c r="F10" t="n">
-        <v>2.04729</v>
+        <v>2.34412</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.40938</v>
+        <v>2.39559</v>
       </c>
       <c r="C11" t="n">
-        <v>3.31097</v>
+        <v>3.39127</v>
       </c>
       <c r="D11" t="n">
-        <v>8.29856</v>
+        <v>8.474830000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>1.97878</v>
+        <v>2.35876</v>
       </c>
       <c r="F11" t="n">
-        <v>2.07248</v>
+        <v>2.36271</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.43999</v>
+        <v>2.44901</v>
       </c>
       <c r="C12" t="n">
-        <v>3.32912</v>
+        <v>3.44774</v>
       </c>
       <c r="D12" t="n">
-        <v>8.650410000000001</v>
+        <v>8.818759999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.99763</v>
+        <v>2.39507</v>
       </c>
       <c r="F12" t="n">
-        <v>2.08741</v>
+        <v>2.41089</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.46425</v>
+        <v>2.48628</v>
       </c>
       <c r="C13" t="n">
-        <v>3.37839</v>
+        <v>3.48725</v>
       </c>
       <c r="D13" t="n">
-        <v>8.945830000000001</v>
+        <v>9.090960000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.02177</v>
+        <v>2.41373</v>
       </c>
       <c r="F13" t="n">
-        <v>2.11451</v>
+        <v>2.43354</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.50031</v>
+        <v>2.50728</v>
       </c>
       <c r="C14" t="n">
-        <v>3.4695</v>
+        <v>3.5579</v>
       </c>
       <c r="D14" t="n">
-        <v>9.2605</v>
+        <v>9.426259999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.05912</v>
+        <v>2.45147</v>
       </c>
       <c r="F14" t="n">
-        <v>2.14573</v>
+        <v>2.46397</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.59602</v>
+        <v>2.58179</v>
       </c>
       <c r="C15" t="n">
-        <v>3.54406</v>
+        <v>3.64</v>
       </c>
       <c r="D15" t="n">
-        <v>9.551729999999999</v>
+        <v>9.75318</v>
       </c>
       <c r="E15" t="n">
-        <v>2.10863</v>
+        <v>2.49062</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2097</v>
+        <v>2.50828</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.69547</v>
+        <v>2.65526</v>
       </c>
       <c r="C16" t="n">
-        <v>3.72975</v>
+        <v>3.7578</v>
       </c>
       <c r="D16" t="n">
-        <v>9.89733</v>
+        <v>10.0436</v>
       </c>
       <c r="E16" t="n">
-        <v>2.15957</v>
+        <v>2.54897</v>
       </c>
       <c r="F16" t="n">
-        <v>2.24827</v>
+        <v>2.58848</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>2.83659</v>
+        <v>2.79473</v>
       </c>
       <c r="C17" t="n">
-        <v>3.86058</v>
+        <v>3.9574</v>
       </c>
       <c r="D17" t="n">
-        <v>10.1731</v>
+        <v>10.3328</v>
       </c>
       <c r="E17" t="n">
-        <v>2.23013</v>
+        <v>2.62241</v>
       </c>
       <c r="F17" t="n">
-        <v>2.32551</v>
+        <v>2.66482</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.07316</v>
+        <v>2.99316</v>
       </c>
       <c r="C18" t="n">
-        <v>4.11375</v>
+        <v>4.20972</v>
       </c>
       <c r="D18" t="n">
-        <v>10.5061</v>
+        <v>10.6541</v>
       </c>
       <c r="E18" t="n">
-        <v>2.33432</v>
+        <v>2.69808</v>
       </c>
       <c r="F18" t="n">
-        <v>2.44583</v>
+        <v>2.75749</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.41995</v>
+        <v>3.33325</v>
       </c>
       <c r="C19" t="n">
-        <v>4.57116</v>
+        <v>4.65448</v>
       </c>
       <c r="D19" t="n">
-        <v>10.809</v>
+        <v>10.9993</v>
       </c>
       <c r="E19" t="n">
-        <v>2.47902</v>
+        <v>2.81662</v>
       </c>
       <c r="F19" t="n">
-        <v>2.61324</v>
+        <v>2.89584</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.18072</v>
+        <v>4.08485</v>
       </c>
       <c r="C20" t="n">
-        <v>5.2526</v>
+        <v>5.3453</v>
       </c>
       <c r="D20" t="n">
-        <v>11.1371</v>
+        <v>11.2948</v>
       </c>
       <c r="E20" t="n">
-        <v>2.77103</v>
+        <v>3.09702</v>
       </c>
       <c r="F20" t="n">
-        <v>2.91562</v>
+        <v>3.16916</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.34151</v>
+        <v>5.27856</v>
       </c>
       <c r="C21" t="n">
-        <v>6.18927</v>
+        <v>6.54731</v>
       </c>
       <c r="D21" t="n">
-        <v>8.09872</v>
+        <v>8.29345</v>
       </c>
       <c r="E21" t="n">
-        <v>1.94669</v>
+        <v>2.30701</v>
       </c>
       <c r="F21" t="n">
-        <v>2.05866</v>
+        <v>2.33402</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>7.05214</v>
+        <v>6.9261</v>
       </c>
       <c r="C22" t="n">
-        <v>3.27428</v>
+        <v>3.41595</v>
       </c>
       <c r="D22" t="n">
-        <v>8.393359999999999</v>
+        <v>8.61214</v>
       </c>
       <c r="E22" t="n">
-        <v>1.97404</v>
+        <v>2.32748</v>
       </c>
       <c r="F22" t="n">
-        <v>2.08812</v>
+        <v>2.37121</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>9.503500000000001</v>
+        <v>9.41057</v>
       </c>
       <c r="C23" t="n">
-        <v>3.29914</v>
+        <v>3.43504</v>
       </c>
       <c r="D23" t="n">
-        <v>8.685890000000001</v>
+        <v>8.897919999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9788</v>
+        <v>2.34875</v>
       </c>
       <c r="F23" t="n">
-        <v>2.11234</v>
+        <v>2.4048</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.45082</v>
+        <v>2.43194</v>
       </c>
       <c r="C24" t="n">
-        <v>3.32531</v>
+        <v>3.46138</v>
       </c>
       <c r="D24" t="n">
-        <v>8.998659999999999</v>
+        <v>9.22757</v>
       </c>
       <c r="E24" t="n">
-        <v>2.00363</v>
+        <v>2.36658</v>
       </c>
       <c r="F24" t="n">
-        <v>2.14753</v>
+        <v>2.44504</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.50848</v>
+        <v>2.49613</v>
       </c>
       <c r="C25" t="n">
-        <v>3.3459</v>
+        <v>3.49925</v>
       </c>
       <c r="D25" t="n">
-        <v>9.319889999999999</v>
+        <v>9.527480000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>2.02736</v>
+        <v>2.39253</v>
       </c>
       <c r="F25" t="n">
-        <v>2.19454</v>
+        <v>2.49434</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.54182</v>
+        <v>2.53674</v>
       </c>
       <c r="C26" t="n">
-        <v>3.41368</v>
+        <v>3.53199</v>
       </c>
       <c r="D26" t="n">
-        <v>9.62989</v>
+        <v>9.79186</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0597</v>
+        <v>2.41326</v>
       </c>
       <c r="F26" t="n">
-        <v>2.25633</v>
+        <v>2.55442</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.5981</v>
+        <v>2.62621</v>
       </c>
       <c r="C27" t="n">
-        <v>3.4421</v>
+        <v>3.58566</v>
       </c>
       <c r="D27" t="n">
-        <v>9.94842</v>
+        <v>10.0932</v>
       </c>
       <c r="E27" t="n">
-        <v>2.08274</v>
+        <v>2.45278</v>
       </c>
       <c r="F27" t="n">
-        <v>2.29537</v>
+        <v>2.60637</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>2.68922</v>
+        <v>2.68715</v>
       </c>
       <c r="C28" t="n">
-        <v>3.49292</v>
+        <v>3.64498</v>
       </c>
       <c r="D28" t="n">
-        <v>10.2111</v>
+        <v>10.4127</v>
       </c>
       <c r="E28" t="n">
-        <v>2.13754</v>
+        <v>2.4892</v>
       </c>
       <c r="F28" t="n">
-        <v>2.37385</v>
+        <v>2.67963</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>2.76924</v>
+        <v>2.78141</v>
       </c>
       <c r="C29" t="n">
-        <v>3.62294</v>
+        <v>3.72749</v>
       </c>
       <c r="D29" t="n">
-        <v>10.5217</v>
+        <v>10.7155</v>
       </c>
       <c r="E29" t="n">
-        <v>2.19836</v>
+        <v>2.54897</v>
       </c>
       <c r="F29" t="n">
-        <v>2.44044</v>
+        <v>2.76148</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>2.94102</v>
+        <v>2.94079</v>
       </c>
       <c r="C30" t="n">
-        <v>3.72013</v>
+        <v>3.8592</v>
       </c>
       <c r="D30" t="n">
-        <v>10.8278</v>
+        <v>10.9979</v>
       </c>
       <c r="E30" t="n">
-        <v>2.25263</v>
+        <v>2.5962</v>
       </c>
       <c r="F30" t="n">
-        <v>2.52938</v>
+        <v>2.83442</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.11429</v>
+        <v>3.14792</v>
       </c>
       <c r="C31" t="n">
-        <v>3.86477</v>
+        <v>4.02535</v>
       </c>
       <c r="D31" t="n">
-        <v>11.1011</v>
+        <v>11.2749</v>
       </c>
       <c r="E31" t="n">
-        <v>2.31237</v>
+        <v>2.67684</v>
       </c>
       <c r="F31" t="n">
-        <v>2.58911</v>
+        <v>2.93378</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.40498</v>
+        <v>3.36831</v>
       </c>
       <c r="C32" t="n">
-        <v>4.13178</v>
+        <v>4.2659</v>
       </c>
       <c r="D32" t="n">
-        <v>11.3606</v>
+        <v>11.5033</v>
       </c>
       <c r="E32" t="n">
-        <v>2.41018</v>
+        <v>2.77053</v>
       </c>
       <c r="F32" t="n">
-        <v>2.69758</v>
+        <v>3.02905</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>3.89368</v>
+        <v>3.80613</v>
       </c>
       <c r="C33" t="n">
-        <v>4.48023</v>
+        <v>4.59692</v>
       </c>
       <c r="D33" t="n">
-        <v>11.6639</v>
+        <v>11.8385</v>
       </c>
       <c r="E33" t="n">
-        <v>2.56015</v>
+        <v>2.88403</v>
       </c>
       <c r="F33" t="n">
-        <v>2.87068</v>
+        <v>3.15111</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.57202</v>
+        <v>4.55492</v>
       </c>
       <c r="C34" t="n">
-        <v>5.10448</v>
+        <v>5.32167</v>
       </c>
       <c r="D34" t="n">
-        <v>11.9376</v>
+        <v>12.1231</v>
       </c>
       <c r="E34" t="n">
-        <v>2.85296</v>
+        <v>3.14155</v>
       </c>
       <c r="F34" t="n">
-        <v>3.1337</v>
+        <v>3.4066</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.61813</v>
+        <v>5.48036</v>
       </c>
       <c r="C35" t="n">
-        <v>6.06279</v>
+        <v>6.37133</v>
       </c>
       <c r="D35" t="n">
-        <v>8.427569999999999</v>
+        <v>8.69664</v>
       </c>
       <c r="E35" t="n">
-        <v>1.99201</v>
+        <v>2.35023</v>
       </c>
       <c r="F35" t="n">
-        <v>2.25537</v>
+        <v>2.54019</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.02843</v>
+        <v>7.24058</v>
       </c>
       <c r="C36" t="n">
-        <v>7.32381</v>
+        <v>8.012869999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>8.740170000000001</v>
+        <v>9.006399999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>2.00868</v>
+        <v>2.36899</v>
       </c>
       <c r="F36" t="n">
-        <v>2.27955</v>
+        <v>2.55765</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>9.637169999999999</v>
+        <v>9.43913</v>
       </c>
       <c r="C37" t="n">
-        <v>3.33105</v>
+        <v>3.46331</v>
       </c>
       <c r="D37" t="n">
-        <v>9.07377</v>
+        <v>9.28786</v>
       </c>
       <c r="E37" t="n">
-        <v>2.03141</v>
+        <v>2.37888</v>
       </c>
       <c r="F37" t="n">
-        <v>2.31112</v>
+        <v>2.58071</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.48665</v>
+        <v>2.4966</v>
       </c>
       <c r="C38" t="n">
-        <v>3.34563</v>
+        <v>3.49491</v>
       </c>
       <c r="D38" t="n">
-        <v>9.37715</v>
+        <v>9.595789999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>2.05376</v>
+        <v>2.41517</v>
       </c>
       <c r="F38" t="n">
-        <v>2.32946</v>
+        <v>2.63351</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.53382</v>
+        <v>2.53948</v>
       </c>
       <c r="C39" t="n">
-        <v>3.38992</v>
+        <v>3.51595</v>
       </c>
       <c r="D39" t="n">
-        <v>9.750959999999999</v>
+        <v>9.92074</v>
       </c>
       <c r="E39" t="n">
-        <v>2.09142</v>
+        <v>2.43605</v>
       </c>
       <c r="F39" t="n">
-        <v>2.3821</v>
+        <v>2.66983</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.60632</v>
+        <v>2.61707</v>
       </c>
       <c r="C40" t="n">
-        <v>3.42736</v>
+        <v>3.54649</v>
       </c>
       <c r="D40" t="n">
-        <v>10.0254</v>
+        <v>10.2362</v>
       </c>
       <c r="E40" t="n">
-        <v>2.11424</v>
+        <v>2.4679</v>
       </c>
       <c r="F40" t="n">
-        <v>2.41362</v>
+        <v>2.69161</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>2.65871</v>
+        <v>2.66281</v>
       </c>
       <c r="C41" t="n">
-        <v>3.44798</v>
+        <v>3.59355</v>
       </c>
       <c r="D41" t="n">
-        <v>10.3394</v>
+        <v>10.5193</v>
       </c>
       <c r="E41" t="n">
-        <v>2.14467</v>
+        <v>2.4958</v>
       </c>
       <c r="F41" t="n">
-        <v>2.44624</v>
+        <v>2.7501</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>2.7394</v>
+        <v>2.717</v>
       </c>
       <c r="C42" t="n">
-        <v>3.50708</v>
+        <v>3.65363</v>
       </c>
       <c r="D42" t="n">
-        <v>10.6232</v>
+        <v>10.8142</v>
       </c>
       <c r="E42" t="n">
-        <v>2.17754</v>
+        <v>2.53721</v>
       </c>
       <c r="F42" t="n">
-        <v>2.48854</v>
+        <v>2.78857</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>2.80531</v>
+        <v>2.80022</v>
       </c>
       <c r="C43" t="n">
-        <v>3.58928</v>
+        <v>3.75359</v>
       </c>
       <c r="D43" t="n">
-        <v>10.9336</v>
+        <v>11.1275</v>
       </c>
       <c r="E43" t="n">
-        <v>2.22521</v>
+        <v>2.58148</v>
       </c>
       <c r="F43" t="n">
-        <v>2.54435</v>
+        <v>2.85105</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>2.95867</v>
+        <v>2.94664</v>
       </c>
       <c r="C44" t="n">
-        <v>3.70957</v>
+        <v>3.88151</v>
       </c>
       <c r="D44" t="n">
-        <v>11.1807</v>
+        <v>11.4153</v>
       </c>
       <c r="E44" t="n">
-        <v>2.29135</v>
+        <v>2.64834</v>
       </c>
       <c r="F44" t="n">
-        <v>2.61488</v>
+        <v>2.93599</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.15496</v>
+        <v>3.1295</v>
       </c>
       <c r="C45" t="n">
-        <v>3.92765</v>
+        <v>4.0483</v>
       </c>
       <c r="D45" t="n">
-        <v>11.4515</v>
+        <v>11.673</v>
       </c>
       <c r="E45" t="n">
-        <v>2.36822</v>
+        <v>2.71858</v>
       </c>
       <c r="F45" t="n">
-        <v>2.69105</v>
+        <v>3.02135</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>3.44063</v>
+        <v>3.39897</v>
       </c>
       <c r="C46" t="n">
-        <v>4.13286</v>
+        <v>4.27121</v>
       </c>
       <c r="D46" t="n">
-        <v>11.7087</v>
+        <v>11.9413</v>
       </c>
       <c r="E46" t="n">
-        <v>2.46489</v>
+        <v>2.82854</v>
       </c>
       <c r="F46" t="n">
-        <v>2.79169</v>
+        <v>3.12523</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>3.81533</v>
+        <v>3.78489</v>
       </c>
       <c r="C47" t="n">
-        <v>4.49179</v>
+        <v>4.65444</v>
       </c>
       <c r="D47" t="n">
-        <v>11.9907</v>
+        <v>12.1939</v>
       </c>
       <c r="E47" t="n">
-        <v>2.62682</v>
+        <v>2.96713</v>
       </c>
       <c r="F47" t="n">
-        <v>2.94835</v>
+        <v>3.25614</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.38524</v>
+        <v>4.39867</v>
       </c>
       <c r="C48" t="n">
-        <v>5.04509</v>
+        <v>5.25188</v>
       </c>
       <c r="D48" t="n">
-        <v>12.2678</v>
+        <v>12.5088</v>
       </c>
       <c r="E48" t="n">
-        <v>2.89816</v>
+        <v>3.24401</v>
       </c>
       <c r="F48" t="n">
-        <v>3.20906</v>
+        <v>3.51168</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.32752</v>
+        <v>5.2537</v>
       </c>
       <c r="C49" t="n">
-        <v>5.87381</v>
+        <v>6.13665</v>
       </c>
       <c r="D49" t="n">
-        <v>12.555</v>
+        <v>12.7558</v>
       </c>
       <c r="E49" t="n">
-        <v>3.25744</v>
+        <v>3.62898</v>
       </c>
       <c r="F49" t="n">
-        <v>3.54751</v>
+        <v>3.90364</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>6.59383</v>
+        <v>6.53299</v>
       </c>
       <c r="C50" t="n">
-        <v>7.08004</v>
+        <v>7.40579</v>
       </c>
       <c r="D50" t="n">
-        <v>8.85078</v>
+        <v>9.08616</v>
       </c>
       <c r="E50" t="n">
-        <v>2.03194</v>
+        <v>2.40132</v>
       </c>
       <c r="F50" t="n">
-        <v>2.32599</v>
+        <v>2.65986</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>8.649279999999999</v>
+        <v>8.575200000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>3.34278</v>
+        <v>3.51742</v>
       </c>
       <c r="D51" t="n">
-        <v>9.1874</v>
+        <v>9.43333</v>
       </c>
       <c r="E51" t="n">
-        <v>2.05171</v>
+        <v>2.42575</v>
       </c>
       <c r="F51" t="n">
-        <v>2.33869</v>
+        <v>2.69793</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>11.7941</v>
+        <v>11.4283</v>
       </c>
       <c r="C52" t="n">
-        <v>3.34515</v>
+        <v>3.53241</v>
       </c>
       <c r="D52" t="n">
-        <v>9.50981</v>
+        <v>9.764250000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>2.07593</v>
+        <v>2.45343</v>
       </c>
       <c r="F52" t="n">
-        <v>2.3755</v>
+        <v>2.73753</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>2.55394</v>
+        <v>2.56604</v>
       </c>
       <c r="C53" t="n">
-        <v>3.39392</v>
+        <v>3.57036</v>
       </c>
       <c r="D53" t="n">
-        <v>9.85239</v>
+        <v>10.0694</v>
       </c>
       <c r="E53" t="n">
-        <v>2.10511</v>
+        <v>2.48015</v>
       </c>
       <c r="F53" t="n">
-        <v>2.40826</v>
+        <v>2.77681</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>2.61636</v>
+        <v>2.63175</v>
       </c>
       <c r="C54" t="n">
-        <v>3.42171</v>
+        <v>3.6127</v>
       </c>
       <c r="D54" t="n">
-        <v>10.1596</v>
+        <v>10.3788</v>
       </c>
       <c r="E54" t="n">
-        <v>2.13571</v>
+        <v>2.50562</v>
       </c>
       <c r="F54" t="n">
-        <v>2.4519</v>
+        <v>2.80257</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>2.67977</v>
+        <v>2.69195</v>
       </c>
       <c r="C55" t="n">
-        <v>3.459</v>
+        <v>3.65949</v>
       </c>
       <c r="D55" t="n">
-        <v>10.4581</v>
+        <v>10.6934</v>
       </c>
       <c r="E55" t="n">
-        <v>2.1661</v>
+        <v>2.55001</v>
       </c>
       <c r="F55" t="n">
-        <v>2.50235</v>
+        <v>2.86466</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>2.7493</v>
+        <v>2.74942</v>
       </c>
       <c r="C56" t="n">
-        <v>3.51617</v>
+        <v>3.72528</v>
       </c>
       <c r="D56" t="n">
-        <v>10.7482</v>
+        <v>10.9805</v>
       </c>
       <c r="E56" t="n">
-        <v>2.2079</v>
+        <v>2.58838</v>
       </c>
       <c r="F56" t="n">
-        <v>2.54535</v>
+        <v>2.92068</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>2.82575</v>
+        <v>2.84905</v>
       </c>
       <c r="C57" t="n">
-        <v>3.58978</v>
+        <v>3.79208</v>
       </c>
       <c r="D57" t="n">
-        <v>11.0575</v>
+        <v>11.2967</v>
       </c>
       <c r="E57" t="n">
-        <v>2.25982</v>
+        <v>2.634</v>
       </c>
       <c r="F57" t="n">
-        <v>2.61666</v>
+        <v>2.97769</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>2.95726</v>
+        <v>2.97566</v>
       </c>
       <c r="C58" t="n">
-        <v>3.70725</v>
+        <v>3.92349</v>
       </c>
       <c r="D58" t="n">
-        <v>11.3263</v>
+        <v>11.5534</v>
       </c>
       <c r="E58" t="n">
-        <v>2.31332</v>
+        <v>2.69254</v>
       </c>
       <c r="F58" t="n">
-        <v>2.6588</v>
+        <v>3.01423</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.12896</v>
+        <v>3.14753</v>
       </c>
       <c r="C59" t="n">
-        <v>3.8292</v>
+        <v>4.08527</v>
       </c>
       <c r="D59" t="n">
-        <v>11.5782</v>
+        <v>11.7854</v>
       </c>
       <c r="E59" t="n">
-        <v>2.39013</v>
+        <v>2.75488</v>
       </c>
       <c r="F59" t="n">
-        <v>2.74276</v>
+        <v>3.11893</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>3.39919</v>
+        <v>3.3855</v>
       </c>
       <c r="C60" t="n">
-        <v>4.06906</v>
+        <v>4.35453</v>
       </c>
       <c r="D60" t="n">
-        <v>11.8451</v>
+        <v>12.0521</v>
       </c>
       <c r="E60" t="n">
-        <v>2.49342</v>
+        <v>2.87758</v>
       </c>
       <c r="F60" t="n">
-        <v>2.86594</v>
+        <v>3.24655</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>3.71468</v>
+        <v>3.70946</v>
       </c>
       <c r="C61" t="n">
-        <v>4.38662</v>
+        <v>4.70789</v>
       </c>
       <c r="D61" t="n">
-        <v>12.1559</v>
+        <v>12.3454</v>
       </c>
       <c r="E61" t="n">
-        <v>2.63961</v>
+        <v>3.03747</v>
       </c>
       <c r="F61" t="n">
-        <v>3.01716</v>
+        <v>3.38926</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.21963</v>
+        <v>4.23997</v>
       </c>
       <c r="C62" t="n">
-        <v>4.90903</v>
+        <v>5.21303</v>
       </c>
       <c r="D62" t="n">
-        <v>12.4673</v>
+        <v>12.6873</v>
       </c>
       <c r="E62" t="n">
-        <v>2.85274</v>
+        <v>3.2747</v>
       </c>
       <c r="F62" t="n">
-        <v>3.2444</v>
+        <v>3.63912</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.93461</v>
+        <v>4.93843</v>
       </c>
       <c r="C63" t="n">
-        <v>5.67972</v>
+        <v>6.01946</v>
       </c>
       <c r="D63" t="n">
-        <v>12.8241</v>
+        <v>13.0633</v>
       </c>
       <c r="E63" t="n">
-        <v>3.20354</v>
+        <v>3.61705</v>
       </c>
       <c r="F63" t="n">
-        <v>3.57148</v>
+        <v>4.01506</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.15716</v>
+        <v>6.16962</v>
       </c>
       <c r="C64" t="n">
-        <v>6.78037</v>
+        <v>7.21755</v>
       </c>
       <c r="D64" t="n">
-        <v>9.07132</v>
+        <v>9.257110000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>2.412</v>
+        <v>2.80026</v>
       </c>
       <c r="F64" t="n">
-        <v>2.7008</v>
+        <v>3.10372</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>7.92876</v>
+        <v>8.03253</v>
       </c>
       <c r="C65" t="n">
-        <v>3.79518</v>
+        <v>4.15572</v>
       </c>
       <c r="D65" t="n">
-        <v>9.40391</v>
+        <v>9.682919999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>2.439</v>
+        <v>2.83022</v>
       </c>
       <c r="F65" t="n">
-        <v>2.72916</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>10.8499</v>
+        <v>10.8834</v>
       </c>
       <c r="C66" t="n">
-        <v>3.83316</v>
+        <v>4.1678</v>
       </c>
       <c r="D66" t="n">
-        <v>9.796580000000001</v>
+        <v>10.082</v>
       </c>
       <c r="E66" t="n">
-        <v>2.44386</v>
+        <v>2.85904</v>
       </c>
       <c r="F66" t="n">
-        <v>2.76361</v>
+        <v>3.1746</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>2.90129</v>
+        <v>2.89521</v>
       </c>
       <c r="C67" t="n">
-        <v>3.86443</v>
+        <v>4.21908</v>
       </c>
       <c r="D67" t="n">
-        <v>10.2035</v>
+        <v>10.5977</v>
       </c>
       <c r="E67" t="n">
-        <v>2.46734</v>
+        <v>2.87326</v>
       </c>
       <c r="F67" t="n">
-        <v>2.8091</v>
+        <v>3.22579</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>2.95314</v>
+        <v>2.93269</v>
       </c>
       <c r="C68" t="n">
-        <v>3.89528</v>
+        <v>4.24164</v>
       </c>
       <c r="D68" t="n">
-        <v>10.6065</v>
+        <v>11.1312</v>
       </c>
       <c r="E68" t="n">
-        <v>2.48996</v>
+        <v>2.90819</v>
       </c>
       <c r="F68" t="n">
-        <v>2.86369</v>
+        <v>3.28336</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.00887</v>
+        <v>2.99318</v>
       </c>
       <c r="C69" t="n">
-        <v>3.94822</v>
+        <v>4.29126</v>
       </c>
       <c r="D69" t="n">
-        <v>11.0833</v>
+        <v>11.607</v>
       </c>
       <c r="E69" t="n">
-        <v>2.53919</v>
+        <v>2.92992</v>
       </c>
       <c r="F69" t="n">
-        <v>2.92449</v>
+        <v>3.34306</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.08301</v>
+        <v>3.06809</v>
       </c>
       <c r="C70" t="n">
-        <v>3.96872</v>
+        <v>4.34838</v>
       </c>
       <c r="D70" t="n">
-        <v>11.5987</v>
+        <v>11.9843</v>
       </c>
       <c r="E70" t="n">
-        <v>2.57811</v>
+        <v>2.98128</v>
       </c>
       <c r="F70" t="n">
-        <v>3.00437</v>
+        <v>3.42525</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.16323</v>
+        <v>3.14504</v>
       </c>
       <c r="C71" t="n">
-        <v>4.11052</v>
+        <v>4.38586</v>
       </c>
       <c r="D71" t="n">
-        <v>12.0659</v>
+        <v>12.7601</v>
       </c>
       <c r="E71" t="n">
-        <v>2.6213</v>
+        <v>3.01739</v>
       </c>
       <c r="F71" t="n">
-        <v>3.07516</v>
+        <v>3.49956</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.27162</v>
+        <v>3.28389</v>
       </c>
       <c r="C72" t="n">
-        <v>4.12973</v>
+        <v>4.51024</v>
       </c>
       <c r="D72" t="n">
-        <v>12.7068</v>
+        <v>13.2189</v>
       </c>
       <c r="E72" t="n">
-        <v>2.6592</v>
+        <v>3.07075</v>
       </c>
       <c r="F72" t="n">
-        <v>3.12792</v>
+        <v>3.61027</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>3.42062</v>
+        <v>3.4203</v>
       </c>
       <c r="C73" t="n">
-        <v>4.28282</v>
+        <v>4.63575</v>
       </c>
       <c r="D73" t="n">
-        <v>13.3285</v>
+        <v>13.8686</v>
       </c>
       <c r="E73" t="n">
-        <v>2.74155</v>
+        <v>3.13867</v>
       </c>
       <c r="F73" t="n">
-        <v>3.24766</v>
+        <v>3.67456</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>3.64813</v>
+        <v>3.62838</v>
       </c>
       <c r="C74" t="n">
-        <v>4.49302</v>
+        <v>4.84533</v>
       </c>
       <c r="D74" t="n">
-        <v>14.1802</v>
+        <v>14.8853</v>
       </c>
       <c r="E74" t="n">
-        <v>2.84052</v>
+        <v>3.24436</v>
       </c>
       <c r="F74" t="n">
-        <v>3.3743</v>
+        <v>3.83342</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>3.95177</v>
+        <v>3.92823</v>
       </c>
       <c r="C75" t="n">
-        <v>4.79338</v>
+        <v>5.16555</v>
       </c>
       <c r="D75" t="n">
-        <v>15.1446</v>
+        <v>15.6038</v>
       </c>
       <c r="E75" t="n">
-        <v>2.98173</v>
+        <v>3.37466</v>
       </c>
       <c r="F75" t="n">
-        <v>3.53754</v>
+        <v>3.97342</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>4.39536</v>
+        <v>4.35593</v>
       </c>
       <c r="C76" t="n">
-        <v>5.29233</v>
+        <v>5.61807</v>
       </c>
       <c r="D76" t="n">
-        <v>16.3571</v>
+        <v>17.0438</v>
       </c>
       <c r="E76" t="n">
-        <v>3.16511</v>
+        <v>3.58315</v>
       </c>
       <c r="F76" t="n">
-        <v>3.77552</v>
+        <v>4.23432</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.05422</v>
+        <v>5.06857</v>
       </c>
       <c r="C77" t="n">
-        <v>5.93025</v>
+        <v>6.35379</v>
       </c>
       <c r="D77" t="n">
-        <v>18.1599</v>
+        <v>17.9852</v>
       </c>
       <c r="E77" t="n">
-        <v>3.49057</v>
+        <v>3.92446</v>
       </c>
       <c r="F77" t="n">
-        <v>4.09338</v>
+        <v>4.54706</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.09432</v>
+        <v>6.06503</v>
       </c>
       <c r="C78" t="n">
-        <v>6.98725</v>
+        <v>7.41706</v>
       </c>
       <c r="D78" t="n">
-        <v>15.572</v>
+        <v>15.5781</v>
       </c>
       <c r="E78" t="n">
-        <v>2.67697</v>
+        <v>3.10932</v>
       </c>
       <c r="F78" t="n">
-        <v>3.15201</v>
+        <v>3.55624</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.79736</v>
+        <v>7.69681</v>
       </c>
       <c r="C79" t="n">
-        <v>4.19118</v>
+        <v>4.55192</v>
       </c>
       <c r="D79" t="n">
-        <v>16.8186</v>
+        <v>16.7638</v>
       </c>
       <c r="E79" t="n">
-        <v>2.69541</v>
+        <v>3.12699</v>
       </c>
       <c r="F79" t="n">
-        <v>3.18667</v>
+        <v>3.60978</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>10.4093</v>
+        <v>10.2496</v>
       </c>
       <c r="C80" t="n">
-        <v>4.19701</v>
+        <v>4.59057</v>
       </c>
       <c r="D80" t="n">
-        <v>17.6843</v>
+        <v>17.734</v>
       </c>
       <c r="E80" t="n">
-        <v>2.70991</v>
+        <v>3.15794</v>
       </c>
       <c r="F80" t="n">
-        <v>3.23225</v>
+        <v>3.66341</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>3.49382</v>
+        <v>3.48006</v>
       </c>
       <c r="C81" t="n">
-        <v>4.25276</v>
+        <v>4.6202</v>
       </c>
       <c r="D81" t="n">
-        <v>18.6249</v>
+        <v>18.7937</v>
       </c>
       <c r="E81" t="n">
-        <v>2.74251</v>
+        <v>3.18184</v>
       </c>
       <c r="F81" t="n">
-        <v>3.29625</v>
+        <v>3.72339</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>3.55327</v>
+        <v>3.51319</v>
       </c>
       <c r="C82" t="n">
-        <v>4.25782</v>
+        <v>4.64731</v>
       </c>
       <c r="D82" t="n">
-        <v>19.6527</v>
+        <v>19.8971</v>
       </c>
       <c r="E82" t="n">
-        <v>2.75916</v>
+        <v>3.20247</v>
       </c>
       <c r="F82" t="n">
-        <v>3.33662</v>
+        <v>3.77556</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>3.61467</v>
+        <v>3.58912</v>
       </c>
       <c r="C83" t="n">
-        <v>4.30972</v>
+        <v>4.69989</v>
       </c>
       <c r="D83" t="n">
-        <v>20.8144</v>
+        <v>20.918</v>
       </c>
       <c r="E83" t="n">
-        <v>2.78139</v>
+        <v>3.21859</v>
       </c>
       <c r="F83" t="n">
-        <v>3.39149</v>
+        <v>3.84808</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>3.67398</v>
+        <v>3.68634</v>
       </c>
       <c r="C84" t="n">
-        <v>4.3426</v>
+        <v>4.75801</v>
       </c>
       <c r="D84" t="n">
-        <v>21.952</v>
+        <v>22.0638</v>
       </c>
       <c r="E84" t="n">
-        <v>2.82099</v>
+        <v>3.26644</v>
       </c>
       <c r="F84" t="n">
-        <v>3.46511</v>
+        <v>3.92365</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>3.78691</v>
+        <v>3.7732</v>
       </c>
       <c r="C85" t="n">
-        <v>4.4877</v>
+        <v>4.81519</v>
       </c>
       <c r="D85" t="n">
-        <v>22.9739</v>
+        <v>23.1255</v>
       </c>
       <c r="E85" t="n">
-        <v>2.85649</v>
+        <v>3.30442</v>
       </c>
       <c r="F85" t="n">
-        <v>3.53152</v>
+        <v>3.99598</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>3.87412</v>
+        <v>3.88575</v>
       </c>
       <c r="C86" t="n">
-        <v>4.57285</v>
+        <v>4.94489</v>
       </c>
       <c r="D86" t="n">
-        <v>24.186</v>
+        <v>24.2753</v>
       </c>
       <c r="E86" t="n">
-        <v>2.90369</v>
+        <v>3.37892</v>
       </c>
       <c r="F86" t="n">
-        <v>3.64202</v>
+        <v>4.08681</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.05665</v>
+        <v>4.01406</v>
       </c>
       <c r="C87" t="n">
-        <v>4.69208</v>
+        <v>5.08604</v>
       </c>
       <c r="D87" t="n">
-        <v>25.2816</v>
+        <v>25.471</v>
       </c>
       <c r="E87" t="n">
-        <v>2.98991</v>
+        <v>3.46041</v>
       </c>
       <c r="F87" t="n">
-        <v>3.78795</v>
+        <v>4.23262</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.24175</v>
+        <v>4.24317</v>
       </c>
       <c r="C88" t="n">
-        <v>4.93167</v>
+        <v>5.33381</v>
       </c>
       <c r="D88" t="n">
-        <v>26.4922</v>
+        <v>26.5813</v>
       </c>
       <c r="E88" t="n">
-        <v>3.08616</v>
+        <v>3.55393</v>
       </c>
       <c r="F88" t="n">
-        <v>4.01316</v>
+        <v>4.44252</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>4.56062</v>
+        <v>4.55583</v>
       </c>
       <c r="C89" t="n">
-        <v>5.36107</v>
+        <v>5.68879</v>
       </c>
       <c r="D89" t="n">
-        <v>27.762</v>
+        <v>27.7408</v>
       </c>
       <c r="E89" t="n">
-        <v>3.25917</v>
+        <v>3.72331</v>
       </c>
       <c r="F89" t="n">
-        <v>4.26822</v>
+        <v>4.73911</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>5.03537</v>
+        <v>5.02453</v>
       </c>
       <c r="C90" t="n">
-        <v>5.84562</v>
+        <v>6.32217</v>
       </c>
       <c r="D90" t="n">
-        <v>28.9797</v>
+        <v>29.0328</v>
       </c>
       <c r="E90" t="n">
-        <v>3.52002</v>
+        <v>3.99303</v>
       </c>
       <c r="F90" t="n">
-        <v>4.7611</v>
+        <v>5.31468</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>5.7894</v>
+        <v>5.76844</v>
       </c>
       <c r="C91" t="n">
-        <v>6.70426</v>
+        <v>7.19995</v>
       </c>
       <c r="D91" t="n">
-        <v>30.3843</v>
+        <v>30.4642</v>
       </c>
       <c r="E91" t="n">
-        <v>3.93965</v>
+        <v>4.43938</v>
       </c>
       <c r="F91" t="n">
-        <v>5.6563</v>
+        <v>6.10627</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>6.90507</v>
+        <v>6.95346</v>
       </c>
       <c r="C92" t="n">
-        <v>7.99966</v>
+        <v>8.475849999999999</v>
       </c>
       <c r="D92" t="n">
-        <v>24.5353</v>
+        <v>24.6571</v>
       </c>
       <c r="E92" t="n">
-        <v>2.88482</v>
+        <v>3.36392</v>
       </c>
       <c r="F92" t="n">
-        <v>3.5894</v>
+        <v>4.07222</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>8.74708</v>
+        <v>8.748239999999999</v>
       </c>
       <c r="C93" t="n">
-        <v>9.654210000000001</v>
+        <v>10.318</v>
       </c>
       <c r="D93" t="n">
-        <v>25.5432</v>
+        <v>25.5422</v>
       </c>
       <c r="E93" t="n">
-        <v>2.92167</v>
+        <v>3.39667</v>
       </c>
       <c r="F93" t="n">
-        <v>3.76262</v>
+        <v>4.28626</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>11.603</v>
+        <v>11.5503</v>
       </c>
       <c r="C94" t="n">
-        <v>4.80888</v>
+        <v>5.2403</v>
       </c>
       <c r="D94" t="n">
-        <v>26.421</v>
+        <v>26.5468</v>
       </c>
       <c r="E94" t="n">
-        <v>2.9765</v>
+        <v>3.50742</v>
       </c>
       <c r="F94" t="n">
-        <v>3.99028</v>
+        <v>4.5643</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.13331</v>
+        <v>4.18446</v>
       </c>
       <c r="C95" t="n">
-        <v>5.01765</v>
+        <v>5.46974</v>
       </c>
       <c r="D95" t="n">
-        <v>27.4032</v>
+        <v>27.5037</v>
       </c>
       <c r="E95" t="n">
-        <v>3.09508</v>
+        <v>3.59049</v>
       </c>
       <c r="F95" t="n">
-        <v>4.38377</v>
+        <v>4.94408</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>4.39277</v>
+        <v>4.49821</v>
       </c>
       <c r="C96" t="n">
-        <v>5.33083</v>
+        <v>5.67815</v>
       </c>
       <c r="D96" t="n">
-        <v>28.2374</v>
+        <v>28.4404</v>
       </c>
       <c r="E96" t="n">
-        <v>3.33815</v>
+        <v>3.82893</v>
       </c>
       <c r="F96" t="n">
-        <v>4.82872</v>
+        <v>5.32174</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>4.86425</v>
+        <v>4.85028</v>
       </c>
       <c r="C97" t="n">
-        <v>5.53779</v>
+        <v>5.95328</v>
       </c>
       <c r="D97" t="n">
-        <v>29.1921</v>
+        <v>29.412</v>
       </c>
       <c r="E97" t="n">
-        <v>3.55782</v>
+        <v>4.03973</v>
       </c>
       <c r="F97" t="n">
-        <v>5.30145</v>
+        <v>5.86708</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>5.29204</v>
+        <v>5.27011</v>
       </c>
       <c r="C98" t="n">
-        <v>5.82364</v>
+        <v>6.16951</v>
       </c>
       <c r="D98" t="n">
-        <v>30.1709</v>
+        <v>30.3814</v>
       </c>
       <c r="E98" t="n">
-        <v>3.80036</v>
+        <v>4.31489</v>
       </c>
       <c r="F98" t="n">
-        <v>5.87218</v>
+        <v>6.39611</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>5.77788</v>
+        <v>5.76974</v>
       </c>
       <c r="C99" t="n">
-        <v>6.04826</v>
+        <v>6.45427</v>
       </c>
       <c r="D99" t="n">
-        <v>31.3018</v>
+        <v>31.3088</v>
       </c>
       <c r="E99" t="n">
-        <v>4.14593</v>
+        <v>4.66543</v>
       </c>
       <c r="F99" t="n">
-        <v>6.46515</v>
+        <v>7.03493</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>6.30227</v>
+        <v>6.28644</v>
       </c>
       <c r="C100" t="n">
-        <v>6.341</v>
+        <v>6.71916</v>
       </c>
       <c r="D100" t="n">
-        <v>32.3738</v>
+        <v>32.3234</v>
       </c>
       <c r="E100" t="n">
-        <v>4.43356</v>
+        <v>4.892</v>
       </c>
       <c r="F100" t="n">
-        <v>7.02207</v>
+        <v>7.5769</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>6.88015</v>
+        <v>6.75142</v>
       </c>
       <c r="C101" t="n">
-        <v>6.65799</v>
+        <v>7.03342</v>
       </c>
       <c r="D101" t="n">
-        <v>33.4685</v>
+        <v>33.5875</v>
       </c>
       <c r="E101" t="n">
-        <v>4.70333</v>
+        <v>5.15993</v>
       </c>
       <c r="F101" t="n">
-        <v>7.49326</v>
+        <v>8.06245</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.35046</v>
+        <v>7.40652</v>
       </c>
       <c r="C102" t="n">
-        <v>6.97776</v>
+        <v>7.38127</v>
       </c>
       <c r="D102" t="n">
-        <v>34.5198</v>
+        <v>34.6153</v>
       </c>
       <c r="E102" t="n">
-        <v>4.96427</v>
+        <v>5.41562</v>
       </c>
       <c r="F102" t="n">
-        <v>7.9803</v>
+        <v>8.508319999999999</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>7.95062</v>
+        <v>7.9449</v>
       </c>
       <c r="C103" t="n">
-        <v>7.42594</v>
+        <v>7.81571</v>
       </c>
       <c r="D103" t="n">
-        <v>35.8621</v>
+        <v>35.9682</v>
       </c>
       <c r="E103" t="n">
-        <v>5.25814</v>
+        <v>5.70609</v>
       </c>
       <c r="F103" t="n">
-        <v>8.50778</v>
+        <v>9.02976</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>8.628130000000001</v>
+        <v>8.55073</v>
       </c>
       <c r="C104" t="n">
-        <v>7.98591</v>
+        <v>8.428599999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>37.1114</v>
+        <v>37.0983</v>
       </c>
       <c r="E104" t="n">
-        <v>5.51496</v>
+        <v>6.03085</v>
       </c>
       <c r="F104" t="n">
-        <v>8.95706</v>
+        <v>9.56771</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>9.404909999999999</v>
+        <v>9.36712</v>
       </c>
       <c r="C105" t="n">
-        <v>8.77852</v>
+        <v>9.25034</v>
       </c>
       <c r="D105" t="n">
-        <v>38.4176</v>
+        <v>38.5601</v>
       </c>
       <c r="E105" t="n">
-        <v>6.20458</v>
+        <v>6.43555</v>
       </c>
       <c r="F105" t="n">
-        <v>9.804349999999999</v>
+        <v>10.2134</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>10.3667</v>
+        <v>10.3514</v>
       </c>
       <c r="C106" t="n">
-        <v>9.91808</v>
+        <v>10.3615</v>
       </c>
       <c r="D106" t="n">
-        <v>39.8005</v>
+        <v>39.7887</v>
       </c>
       <c r="E106" t="n">
-        <v>6.49209</v>
+        <v>7.0203</v>
       </c>
       <c r="F106" t="n">
-        <v>10.3861</v>
+        <v>11.0735</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>11.7801</v>
+        <v>11.8335</v>
       </c>
       <c r="C107" t="n">
-        <v>11.4898</v>
+        <v>11.9761</v>
       </c>
       <c r="D107" t="n">
-        <v>30.4105</v>
+        <v>30.542</v>
       </c>
       <c r="E107" t="n">
-        <v>4.59884</v>
+        <v>5.03477</v>
       </c>
       <c r="F107" t="n">
-        <v>6.79871</v>
+        <v>7.31878</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>14.0036</v>
+        <v>13.9631</v>
       </c>
       <c r="C108" t="n">
-        <v>6.40496</v>
+        <v>6.7816</v>
       </c>
       <c r="D108" t="n">
-        <v>31.2363</v>
+        <v>31.3689</v>
       </c>
       <c r="E108" t="n">
-        <v>4.72625</v>
+        <v>5.18688</v>
       </c>
       <c r="F108" t="n">
-        <v>7.04027</v>
+        <v>7.54399</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>17.5522</v>
+        <v>17.5495</v>
       </c>
       <c r="C109" t="n">
-        <v>6.52649</v>
+        <v>6.92821</v>
       </c>
       <c r="D109" t="n">
-        <v>32.0231</v>
+        <v>32.0967</v>
       </c>
       <c r="E109" t="n">
-        <v>4.84149</v>
+        <v>5.31515</v>
       </c>
       <c r="F109" t="n">
-        <v>7.23545</v>
+        <v>7.82555</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.08812</v>
+        <v>7.0769</v>
       </c>
       <c r="C110" t="n">
-        <v>6.66969</v>
+        <v>7.05257</v>
       </c>
       <c r="D110" t="n">
-        <v>32.9483</v>
+        <v>32.9301</v>
       </c>
       <c r="E110" t="n">
-        <v>4.96917</v>
+        <v>5.43251</v>
       </c>
       <c r="F110" t="n">
-        <v>7.49654</v>
+        <v>8.073359999999999</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.27966</v>
+        <v>7.30137</v>
       </c>
       <c r="C111" t="n">
-        <v>6.80818</v>
+        <v>7.19565</v>
       </c>
       <c r="D111" t="n">
-        <v>33.8519</v>
+        <v>34.1394</v>
       </c>
       <c r="E111" t="n">
-        <v>5.11253</v>
+        <v>5.59012</v>
       </c>
       <c r="F111" t="n">
-        <v>7.7195</v>
+        <v>8.29265</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.48812</v>
+        <v>7.51848</v>
       </c>
       <c r="C112" t="n">
-        <v>6.97809</v>
+        <v>7.35628</v>
       </c>
       <c r="D112" t="n">
-        <v>34.9373</v>
+        <v>34.8899</v>
       </c>
       <c r="E112" t="n">
-        <v>5.25508</v>
+        <v>5.71623</v>
       </c>
       <c r="F112" t="n">
-        <v>7.98645</v>
+        <v>8.571210000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>7.7649</v>
+        <v>7.7671</v>
       </c>
       <c r="C113" t="n">
-        <v>7.17987</v>
+        <v>7.54208</v>
       </c>
       <c r="D113" t="n">
-        <v>35.8584</v>
+        <v>35.8704</v>
       </c>
       <c r="E113" t="n">
-        <v>5.3788</v>
+        <v>5.87992</v>
       </c>
       <c r="F113" t="n">
-        <v>8.221</v>
+        <v>8.83367</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.00028</v>
+        <v>8.03964</v>
       </c>
       <c r="C114" t="n">
-        <v>7.38899</v>
+        <v>7.76143</v>
       </c>
       <c r="D114" t="n">
-        <v>37.0635</v>
+        <v>36.9727</v>
       </c>
       <c r="E114" t="n">
-        <v>5.54812</v>
+        <v>6.05476</v>
       </c>
       <c r="F114" t="n">
-        <v>8.534179999999999</v>
+        <v>9.12297</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>8.313980000000001</v>
+        <v>8.320360000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>7.63285</v>
+        <v>8.032579999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>38.0681</v>
+        <v>38.1679</v>
       </c>
       <c r="E115" t="n">
-        <v>5.71751</v>
+        <v>6.21624</v>
       </c>
       <c r="F115" t="n">
-        <v>8.82785</v>
+        <v>9.46518</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>8.665889999999999</v>
+        <v>8.65944</v>
       </c>
       <c r="C116" t="n">
-        <v>8.012740000000001</v>
+        <v>8.368309999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>39.2376</v>
+        <v>39.263</v>
       </c>
       <c r="E116" t="n">
-        <v>5.91257</v>
+        <v>6.44404</v>
       </c>
       <c r="F116" t="n">
-        <v>9.153549999999999</v>
+        <v>9.78698</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>9.09484</v>
+        <v>9.10168</v>
       </c>
       <c r="C117" t="n">
-        <v>8.370950000000001</v>
+        <v>8.78739</v>
       </c>
       <c r="D117" t="n">
-        <v>40.3766</v>
+        <v>40.4112</v>
       </c>
       <c r="E117" t="n">
-        <v>6.16474</v>
+        <v>6.68176</v>
       </c>
       <c r="F117" t="n">
-        <v>9.587949999999999</v>
+        <v>10.2208</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>9.622780000000001</v>
+        <v>9.602650000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>8.950390000000001</v>
+        <v>9.37495</v>
       </c>
       <c r="D118" t="n">
-        <v>41.5782</v>
+        <v>41.6069</v>
       </c>
       <c r="E118" t="n">
-        <v>6.44761</v>
+        <v>6.96551</v>
       </c>
       <c r="F118" t="n">
-        <v>10.0456</v>
+        <v>10.6981</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>10.3291</v>
+        <v>10.3587</v>
       </c>
       <c r="C119" t="n">
-        <v>9.777810000000001</v>
+        <v>10.153</v>
       </c>
       <c r="D119" t="n">
-        <v>42.7854</v>
+        <v>42.8152</v>
       </c>
       <c r="E119" t="n">
-        <v>6.81363</v>
+        <v>7.38138</v>
       </c>
       <c r="F119" t="n">
-        <v>10.6423</v>
+        <v>11.3429</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>11.2892</v>
+        <v>11.2638</v>
       </c>
       <c r="C120" t="n">
-        <v>10.8153</v>
+        <v>11.2503</v>
       </c>
       <c r="D120" t="n">
-        <v>44.2064</v>
+        <v>44.2475</v>
       </c>
       <c r="E120" t="n">
-        <v>7.37157</v>
+        <v>7.93649</v>
       </c>
       <c r="F120" t="n">
-        <v>11.4363</v>
+        <v>12.1534</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>12.6599</v>
+        <v>12.6313</v>
       </c>
       <c r="C121" t="n">
-        <v>12.4047</v>
+        <v>12.873</v>
       </c>
       <c r="D121" t="n">
-        <v>33.0379</v>
+        <v>33.1187</v>
       </c>
       <c r="E121" t="n">
-        <v>4.96753</v>
+        <v>5.48513</v>
       </c>
       <c r="F121" t="n">
-        <v>7.27662</v>
+        <v>7.8355</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>14.6187</v>
+        <v>14.6372</v>
       </c>
       <c r="C122" t="n">
-        <v>6.76237</v>
+        <v>7.10351</v>
       </c>
       <c r="D122" t="n">
-        <v>34.0274</v>
+        <v>33.9333</v>
       </c>
       <c r="E122" t="n">
-        <v>5.09254</v>
+        <v>5.60872</v>
       </c>
       <c r="F122" t="n">
-        <v>7.52657</v>
+        <v>8.075240000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>17.8544</v>
+        <v>17.8502</v>
       </c>
       <c r="C123" t="n">
-        <v>6.898</v>
+        <v>7.26364</v>
       </c>
       <c r="D123" t="n">
-        <v>34.768</v>
+        <v>34.994</v>
       </c>
       <c r="E123" t="n">
-        <v>5.17448</v>
+        <v>5.71183</v>
       </c>
       <c r="F123" t="n">
-        <v>7.73467</v>
+        <v>8.323919999999999</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>7.44512</v>
+        <v>7.4607</v>
       </c>
       <c r="C124" t="n">
-        <v>7.02997</v>
+        <v>7.37338</v>
       </c>
       <c r="D124" t="n">
-        <v>35.8953</v>
+        <v>35.9</v>
       </c>
       <c r="E124" t="n">
-        <v>5.30382</v>
+        <v>5.878</v>
       </c>
       <c r="F124" t="n">
-        <v>7.94961</v>
+        <v>8.54505</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>7.66597</v>
+        <v>7.65469</v>
       </c>
       <c r="C125" t="n">
-        <v>7.21358</v>
+        <v>7.54041</v>
       </c>
       <c r="D125" t="n">
-        <v>36.869</v>
+        <v>36.9013</v>
       </c>
       <c r="E125" t="n">
-        <v>5.42763</v>
+        <v>5.97785</v>
       </c>
       <c r="F125" t="n">
-        <v>8.182829999999999</v>
+        <v>8.83418</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>7.88748</v>
+        <v>7.85719</v>
       </c>
       <c r="C126" t="n">
-        <v>7.36485</v>
+        <v>7.69937</v>
       </c>
       <c r="D126" t="n">
-        <v>37.7594</v>
+        <v>37.7831</v>
       </c>
       <c r="E126" t="n">
-        <v>5.58356</v>
+        <v>6.12591</v>
       </c>
       <c r="F126" t="n">
-        <v>8.51004</v>
+        <v>9.07098</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>8.07319</v>
+        <v>8.09676</v>
       </c>
       <c r="C127" t="n">
-        <v>7.5712</v>
+        <v>7.90506</v>
       </c>
       <c r="D127" t="n">
-        <v>38.7342</v>
+        <v>38.7863</v>
       </c>
       <c r="E127" t="n">
-        <v>5.72873</v>
+        <v>6.28124</v>
       </c>
       <c r="F127" t="n">
-        <v>8.77365</v>
+        <v>9.391450000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>8.375310000000001</v>
+        <v>8.33881</v>
       </c>
       <c r="C128" t="n">
-        <v>7.76899</v>
+        <v>8.09896</v>
       </c>
       <c r="D128" t="n">
-        <v>39.5617</v>
+        <v>39.8036</v>
       </c>
       <c r="E128" t="n">
-        <v>5.90234</v>
+        <v>6.42922</v>
       </c>
       <c r="F128" t="n">
-        <v>9.10263</v>
+        <v>9.696210000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>8.687749999999999</v>
+        <v>8.654339999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>8.04034</v>
+        <v>8.38317</v>
       </c>
       <c r="D129" t="n">
-        <v>40.6245</v>
+        <v>40.6586</v>
       </c>
       <c r="E129" t="n">
-        <v>6.08347</v>
+        <v>6.64447</v>
       </c>
       <c r="F129" t="n">
-        <v>9.433909999999999</v>
+        <v>10.0311</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>8.99741</v>
+        <v>8.987360000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>8.368460000000001</v>
+        <v>8.719749999999999</v>
       </c>
       <c r="D130" t="n">
-        <v>41.9094</v>
+        <v>41.751</v>
       </c>
       <c r="E130" t="n">
-        <v>6.3286</v>
+        <v>6.86258</v>
       </c>
       <c r="F130" t="n">
-        <v>9.79537</v>
+        <v>10.448</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>9.43052</v>
+        <v>9.40269</v>
       </c>
       <c r="C131" t="n">
-        <v>8.79683</v>
+        <v>9.13706</v>
       </c>
       <c r="D131" t="n">
-        <v>42.9211</v>
+        <v>43.1226</v>
       </c>
       <c r="E131" t="n">
-        <v>6.53845</v>
+        <v>7.08994</v>
       </c>
       <c r="F131" t="n">
-        <v>10.196</v>
+        <v>10.8865</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>9.95439</v>
+        <v>9.953419999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>9.36922</v>
+        <v>9.71758</v>
       </c>
       <c r="D132" t="n">
-        <v>44.0545</v>
+        <v>44.1915</v>
       </c>
       <c r="E132" t="n">
-        <v>6.84087</v>
+        <v>7.42937</v>
       </c>
       <c r="F132" t="n">
-        <v>10.7285</v>
+        <v>11.4073</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>10.66</v>
+        <v>10.6174</v>
       </c>
       <c r="C133" t="n">
-        <v>10.1661</v>
+        <v>10.494</v>
       </c>
       <c r="D133" t="n">
-        <v>45.3394</v>
+        <v>45.5153</v>
       </c>
       <c r="E133" t="n">
-        <v>7.24386</v>
+        <v>7.80788</v>
       </c>
       <c r="F133" t="n">
-        <v>11.3607</v>
+        <v>12.0202</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>11.572</v>
+        <v>11.5562</v>
       </c>
       <c r="C134" t="n">
-        <v>11.2094</v>
+        <v>11.5808</v>
       </c>
       <c r="D134" t="n">
-        <v>46.8251</v>
+        <v>46.9381</v>
       </c>
       <c r="E134" t="n">
-        <v>7.73654</v>
+        <v>8.37917</v>
       </c>
       <c r="F134" t="n">
-        <v>12.1354</v>
+        <v>12.8707</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>12.8979</v>
+        <v>12.8872</v>
       </c>
       <c r="C135" t="n">
-        <v>12.684</v>
+        <v>13.1233</v>
       </c>
       <c r="D135" t="n">
-        <v>34.6242</v>
+        <v>34.6995</v>
       </c>
       <c r="E135" t="n">
-        <v>10.9636</v>
+        <v>11.8335</v>
       </c>
       <c r="F135" t="n">
-        <v>13.4737</v>
+        <v>14.4919</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>14.7556</v>
+        <v>14.8007</v>
       </c>
       <c r="C136" t="n">
-        <v>15.3626</v>
+        <v>16.5341</v>
       </c>
       <c r="D136" t="n">
-        <v>35.4157</v>
+        <v>35.5875</v>
       </c>
       <c r="E136" t="n">
-        <v>11.0413</v>
+        <v>11.9731</v>
       </c>
       <c r="F136" t="n">
-        <v>13.6596</v>
+        <v>14.7476</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7246</v>
+        <v>17.6524</v>
       </c>
       <c r="C137" t="n">
-        <v>15.5101</v>
+        <v>16.7176</v>
       </c>
       <c r="D137" t="n">
-        <v>36.332</v>
+        <v>36.534</v>
       </c>
       <c r="E137" t="n">
-        <v>11.172</v>
+        <v>12.051</v>
       </c>
       <c r="F137" t="n">
-        <v>13.9747</v>
+        <v>15.0049</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>13.2414</v>
+        <v>13.2568</v>
       </c>
       <c r="C138" t="n">
-        <v>15.6702</v>
+        <v>16.9096</v>
       </c>
       <c r="D138" t="n">
-        <v>37.3757</v>
+        <v>37.2463</v>
       </c>
       <c r="E138" t="n">
-        <v>11.1906</v>
+        <v>12.1226</v>
       </c>
       <c r="F138" t="n">
-        <v>14.1012</v>
+        <v>15.225</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>13.2349</v>
+        <v>13.2747</v>
       </c>
       <c r="C139" t="n">
-        <v>15.8831</v>
+        <v>17.0636</v>
       </c>
       <c r="D139" t="n">
-        <v>38.1641</v>
+        <v>38.325</v>
       </c>
       <c r="E139" t="n">
-        <v>11.3734</v>
+        <v>12.2819</v>
       </c>
       <c r="F139" t="n">
-        <v>14.4776</v>
+        <v>15.5302</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.4543</v>
+        <v>13.4291</v>
       </c>
       <c r="C140" t="n">
-        <v>16.0226</v>
+        <v>17.2199</v>
       </c>
       <c r="D140" t="n">
-        <v>39.1972</v>
+        <v>39.1315</v>
       </c>
       <c r="E140" t="n">
-        <v>11.4681</v>
+        <v>12.4199</v>
       </c>
       <c r="F140" t="n">
-        <v>14.5771</v>
+        <v>15.7891</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>13.6069</v>
+        <v>13.5777</v>
       </c>
       <c r="C141" t="n">
-        <v>16.1954</v>
+        <v>17.4468</v>
       </c>
       <c r="D141" t="n">
-        <v>40.0462</v>
+        <v>40.0977</v>
       </c>
       <c r="E141" t="n">
-        <v>11.627</v>
+        <v>12.5352</v>
       </c>
       <c r="F141" t="n">
-        <v>14.9834</v>
+        <v>16.1158</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>13.7124</v>
+        <v>13.8404</v>
       </c>
       <c r="C142" t="n">
-        <v>16.3835</v>
+        <v>17.7143</v>
       </c>
       <c r="D142" t="n">
-        <v>41.1295</v>
+        <v>41.2612</v>
       </c>
       <c r="E142" t="n">
-        <v>11.7898</v>
+        <v>12.6419</v>
       </c>
       <c r="F142" t="n">
-        <v>15.2556</v>
+        <v>16.3811</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>13.9229</v>
+        <v>13.9335</v>
       </c>
       <c r="C143" t="n">
-        <v>16.5706</v>
+        <v>17.8624</v>
       </c>
       <c r="D143" t="n">
-        <v>42.4385</v>
+        <v>42.2396</v>
       </c>
       <c r="E143" t="n">
-        <v>11.8983</v>
+        <v>12.8797</v>
       </c>
       <c r="F143" t="n">
-        <v>15.5748</v>
+        <v>16.7772</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.61752</v>
+        <v>3.12249</v>
       </c>
       <c r="C2" t="n">
-        <v>3.76935</v>
+        <v>3.78421</v>
       </c>
       <c r="D2" t="n">
-        <v>8.38654</v>
+        <v>8.70107</v>
       </c>
       <c r="E2" t="n">
-        <v>2.51107</v>
+        <v>2.2426</v>
       </c>
       <c r="F2" t="n">
-        <v>2.51658</v>
+        <v>2.16641</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.74736</v>
+        <v>3.20426</v>
       </c>
       <c r="C3" t="n">
-        <v>3.95982</v>
+        <v>3.90386</v>
       </c>
       <c r="D3" t="n">
-        <v>8.64716</v>
+        <v>8.89687</v>
       </c>
       <c r="E3" t="n">
-        <v>2.55674</v>
+        <v>2.33722</v>
       </c>
       <c r="F3" t="n">
-        <v>2.57231</v>
+        <v>2.25976</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.88086</v>
+        <v>3.37396</v>
       </c>
       <c r="C4" t="n">
-        <v>4.29754</v>
+        <v>4.1268</v>
       </c>
       <c r="D4" t="n">
-        <v>9.048539999999999</v>
+        <v>9.28185</v>
       </c>
       <c r="E4" t="n">
-        <v>2.62757</v>
+        <v>2.44068</v>
       </c>
       <c r="F4" t="n">
-        <v>2.65917</v>
+        <v>2.34758</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.26135</v>
+        <v>3.61988</v>
       </c>
       <c r="C5" t="n">
-        <v>4.65402</v>
+        <v>4.49899</v>
       </c>
       <c r="D5" t="n">
-        <v>9.45002</v>
+        <v>9.587199999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>2.75559</v>
+        <v>1.97958</v>
       </c>
       <c r="F5" t="n">
-        <v>2.77504</v>
+        <v>1.89081</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.95635</v>
+        <v>4.32334</v>
       </c>
       <c r="C6" t="n">
-        <v>5.44404</v>
+        <v>5.06992</v>
       </c>
       <c r="D6" t="n">
-        <v>9.83756</v>
+        <v>10.0981</v>
       </c>
       <c r="E6" t="n">
-        <v>2.97973</v>
+        <v>1.99017</v>
       </c>
       <c r="F6" t="n">
-        <v>2.98802</v>
+        <v>1.90648</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>4.91616</v>
+        <v>5.54405</v>
       </c>
       <c r="C7" t="n">
-        <v>6.62371</v>
+        <v>6.15263</v>
       </c>
       <c r="D7" t="n">
-        <v>7.12411</v>
+        <v>7.20638</v>
       </c>
       <c r="E7" t="n">
-        <v>2.29291</v>
+        <v>2.00629</v>
       </c>
       <c r="F7" t="n">
-        <v>2.30101</v>
+        <v>1.9272</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>6.92258</v>
+        <v>7.61474</v>
       </c>
       <c r="C8" t="n">
-        <v>3.33399</v>
+        <v>3.43264</v>
       </c>
       <c r="D8" t="n">
-        <v>7.4786</v>
+        <v>7.5915</v>
       </c>
       <c r="E8" t="n">
-        <v>2.31716</v>
+        <v>2.02122</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3186</v>
+        <v>1.93801</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>9.871869999999999</v>
+        <v>11.1035</v>
       </c>
       <c r="C9" t="n">
-        <v>3.35382</v>
+        <v>3.46731</v>
       </c>
       <c r="D9" t="n">
-        <v>7.81852</v>
+        <v>7.92991</v>
       </c>
       <c r="E9" t="n">
-        <v>2.32921</v>
+        <v>2.03356</v>
       </c>
       <c r="F9" t="n">
-        <v>2.33072</v>
+        <v>1.95638</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.36011</v>
+        <v>2.85563</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3749</v>
+        <v>3.48231</v>
       </c>
       <c r="D10" t="n">
-        <v>8.13926</v>
+        <v>8.294510000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.34288</v>
+        <v>2.05497</v>
       </c>
       <c r="F10" t="n">
-        <v>2.34412</v>
+        <v>1.98378</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.39559</v>
+        <v>2.88226</v>
       </c>
       <c r="C11" t="n">
-        <v>3.39127</v>
+        <v>3.52412</v>
       </c>
       <c r="D11" t="n">
-        <v>8.474830000000001</v>
+        <v>8.624230000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.35876</v>
+        <v>2.07686</v>
       </c>
       <c r="F11" t="n">
-        <v>2.36271</v>
+        <v>2.0054</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.44901</v>
+        <v>2.92533</v>
       </c>
       <c r="C12" t="n">
-        <v>3.44774</v>
+        <v>3.55601</v>
       </c>
       <c r="D12" t="n">
-        <v>8.818759999999999</v>
+        <v>8.969989999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.39507</v>
+        <v>2.10023</v>
       </c>
       <c r="F12" t="n">
-        <v>2.41089</v>
+        <v>2.02813</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.48628</v>
+        <v>2.95595</v>
       </c>
       <c r="C13" t="n">
-        <v>3.48725</v>
+        <v>3.58626</v>
       </c>
       <c r="D13" t="n">
-        <v>9.090960000000001</v>
+        <v>9.294510000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.41373</v>
+        <v>2.10733</v>
       </c>
       <c r="F13" t="n">
-        <v>2.43354</v>
+        <v>2.04787</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.50728</v>
+        <v>3.01609</v>
       </c>
       <c r="C14" t="n">
-        <v>3.5579</v>
+        <v>3.67419</v>
       </c>
       <c r="D14" t="n">
-        <v>9.426259999999999</v>
+        <v>9.59276</v>
       </c>
       <c r="E14" t="n">
-        <v>2.45147</v>
+        <v>2.15577</v>
       </c>
       <c r="F14" t="n">
-        <v>2.46397</v>
+        <v>2.09565</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.58179</v>
+        <v>3.0842</v>
       </c>
       <c r="C15" t="n">
-        <v>3.64</v>
+        <v>3.74799</v>
       </c>
       <c r="D15" t="n">
-        <v>9.75318</v>
+        <v>9.90433</v>
       </c>
       <c r="E15" t="n">
-        <v>2.49062</v>
+        <v>2.20851</v>
       </c>
       <c r="F15" t="n">
-        <v>2.50828</v>
+        <v>2.1494</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.65526</v>
+        <v>3.1788</v>
       </c>
       <c r="C16" t="n">
-        <v>3.7578</v>
+        <v>3.89767</v>
       </c>
       <c r="D16" t="n">
-        <v>10.0436</v>
+        <v>10.1952</v>
       </c>
       <c r="E16" t="n">
-        <v>2.54897</v>
+        <v>2.25194</v>
       </c>
       <c r="F16" t="n">
-        <v>2.58848</v>
+        <v>2.21291</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>2.79473</v>
+        <v>3.30179</v>
       </c>
       <c r="C17" t="n">
-        <v>3.9574</v>
+        <v>4.04832</v>
       </c>
       <c r="D17" t="n">
-        <v>10.3328</v>
+        <v>10.5824</v>
       </c>
       <c r="E17" t="n">
-        <v>2.62241</v>
+        <v>2.32026</v>
       </c>
       <c r="F17" t="n">
-        <v>2.66482</v>
+        <v>2.27631</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>2.99316</v>
+        <v>3.51767</v>
       </c>
       <c r="C18" t="n">
-        <v>4.20972</v>
+        <v>4.26929</v>
       </c>
       <c r="D18" t="n">
-        <v>10.6541</v>
+        <v>10.8755</v>
       </c>
       <c r="E18" t="n">
-        <v>2.69808</v>
+        <v>2.41058</v>
       </c>
       <c r="F18" t="n">
-        <v>2.75749</v>
+        <v>2.39329</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.33325</v>
+        <v>3.87921</v>
       </c>
       <c r="C19" t="n">
-        <v>4.65448</v>
+        <v>4.7175</v>
       </c>
       <c r="D19" t="n">
-        <v>10.9993</v>
+        <v>11.2438</v>
       </c>
       <c r="E19" t="n">
-        <v>2.81662</v>
+        <v>2.56789</v>
       </c>
       <c r="F19" t="n">
-        <v>2.89584</v>
+        <v>2.58638</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.08485</v>
+        <v>4.53912</v>
       </c>
       <c r="C20" t="n">
-        <v>5.3453</v>
+        <v>5.37732</v>
       </c>
       <c r="D20" t="n">
-        <v>11.2948</v>
+        <v>11.5035</v>
       </c>
       <c r="E20" t="n">
-        <v>3.09702</v>
+        <v>2.01192</v>
       </c>
       <c r="F20" t="n">
-        <v>3.16916</v>
+        <v>1.96254</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.27856</v>
+        <v>5.64908</v>
       </c>
       <c r="C21" t="n">
-        <v>6.54731</v>
+        <v>6.25478</v>
       </c>
       <c r="D21" t="n">
-        <v>8.29345</v>
+        <v>8.36469</v>
       </c>
       <c r="E21" t="n">
-        <v>2.30701</v>
+        <v>2.02591</v>
       </c>
       <c r="F21" t="n">
-        <v>2.33402</v>
+        <v>1.9819</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>6.9261</v>
+        <v>7.40628</v>
       </c>
       <c r="C22" t="n">
-        <v>3.41595</v>
+        <v>3.47725</v>
       </c>
       <c r="D22" t="n">
-        <v>8.61214</v>
+        <v>8.671849999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2.32748</v>
+        <v>2.04708</v>
       </c>
       <c r="F22" t="n">
-        <v>2.37121</v>
+        <v>2.01838</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>9.41057</v>
+        <v>9.997210000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>3.43504</v>
+        <v>3.48276</v>
       </c>
       <c r="D23" t="n">
-        <v>8.897919999999999</v>
+        <v>8.97627</v>
       </c>
       <c r="E23" t="n">
-        <v>2.34875</v>
+        <v>2.0594</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4048</v>
+        <v>2.05361</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.43194</v>
+        <v>2.94156</v>
       </c>
       <c r="C24" t="n">
-        <v>3.46138</v>
+        <v>3.53076</v>
       </c>
       <c r="D24" t="n">
-        <v>9.22757</v>
+        <v>9.319190000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.36658</v>
+        <v>2.08774</v>
       </c>
       <c r="F24" t="n">
-        <v>2.44504</v>
+        <v>2.10358</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.49613</v>
+        <v>2.95024</v>
       </c>
       <c r="C25" t="n">
-        <v>3.49925</v>
+        <v>3.54979</v>
       </c>
       <c r="D25" t="n">
-        <v>9.527480000000001</v>
+        <v>9.60595</v>
       </c>
       <c r="E25" t="n">
-        <v>2.39253</v>
+        <v>2.1134</v>
       </c>
       <c r="F25" t="n">
-        <v>2.49434</v>
+        <v>2.15522</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.53674</v>
+        <v>3.03759</v>
       </c>
       <c r="C26" t="n">
-        <v>3.53199</v>
+        <v>3.58632</v>
       </c>
       <c r="D26" t="n">
-        <v>9.79186</v>
+        <v>9.86937</v>
       </c>
       <c r="E26" t="n">
-        <v>2.41326</v>
+        <v>2.14257</v>
       </c>
       <c r="F26" t="n">
-        <v>2.55442</v>
+        <v>2.21882</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.62621</v>
+        <v>3.0929</v>
       </c>
       <c r="C27" t="n">
-        <v>3.58566</v>
+        <v>3.61345</v>
       </c>
       <c r="D27" t="n">
-        <v>10.0932</v>
+        <v>10.2109</v>
       </c>
       <c r="E27" t="n">
-        <v>2.45278</v>
+        <v>2.17093</v>
       </c>
       <c r="F27" t="n">
-        <v>2.60637</v>
+        <v>2.26087</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>2.68715</v>
+        <v>3.17748</v>
       </c>
       <c r="C28" t="n">
-        <v>3.64498</v>
+        <v>3.66147</v>
       </c>
       <c r="D28" t="n">
-        <v>10.4127</v>
+        <v>10.5371</v>
       </c>
       <c r="E28" t="n">
-        <v>2.4892</v>
+        <v>2.21709</v>
       </c>
       <c r="F28" t="n">
-        <v>2.67963</v>
+        <v>2.34713</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>2.78141</v>
+        <v>3.2537</v>
       </c>
       <c r="C29" t="n">
-        <v>3.72749</v>
+        <v>3.77021</v>
       </c>
       <c r="D29" t="n">
-        <v>10.7155</v>
+        <v>10.8405</v>
       </c>
       <c r="E29" t="n">
-        <v>2.54897</v>
+        <v>2.26783</v>
       </c>
       <c r="F29" t="n">
-        <v>2.76148</v>
+        <v>2.42454</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>2.94079</v>
+        <v>3.36315</v>
       </c>
       <c r="C30" t="n">
-        <v>3.8592</v>
+        <v>3.90992</v>
       </c>
       <c r="D30" t="n">
-        <v>10.9979</v>
+        <v>11.1229</v>
       </c>
       <c r="E30" t="n">
-        <v>2.5962</v>
+        <v>2.32154</v>
       </c>
       <c r="F30" t="n">
-        <v>2.83442</v>
+        <v>2.49316</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.14792</v>
+        <v>3.56842</v>
       </c>
       <c r="C31" t="n">
-        <v>4.02535</v>
+        <v>4.0227</v>
       </c>
       <c r="D31" t="n">
-        <v>11.2749</v>
+        <v>11.4302</v>
       </c>
       <c r="E31" t="n">
-        <v>2.67684</v>
+        <v>2.37829</v>
       </c>
       <c r="F31" t="n">
-        <v>2.93378</v>
+        <v>2.57318</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.36831</v>
+        <v>3.82645</v>
       </c>
       <c r="C32" t="n">
-        <v>4.2659</v>
+        <v>4.25542</v>
       </c>
       <c r="D32" t="n">
-        <v>11.5033</v>
+        <v>11.7043</v>
       </c>
       <c r="E32" t="n">
-        <v>2.77053</v>
+        <v>2.48141</v>
       </c>
       <c r="F32" t="n">
-        <v>3.02905</v>
+        <v>2.68064</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>3.80613</v>
+        <v>4.36729</v>
       </c>
       <c r="C33" t="n">
-        <v>4.59692</v>
+        <v>4.62206</v>
       </c>
       <c r="D33" t="n">
-        <v>11.8385</v>
+        <v>12.0498</v>
       </c>
       <c r="E33" t="n">
-        <v>2.88403</v>
+        <v>2.63724</v>
       </c>
       <c r="F33" t="n">
-        <v>3.15111</v>
+        <v>2.84863</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.55492</v>
+        <v>5.07451</v>
       </c>
       <c r="C34" t="n">
-        <v>5.32167</v>
+        <v>5.21456</v>
       </c>
       <c r="D34" t="n">
-        <v>12.1231</v>
+        <v>12.3332</v>
       </c>
       <c r="E34" t="n">
-        <v>3.14155</v>
+        <v>2.04736</v>
       </c>
       <c r="F34" t="n">
-        <v>3.4066</v>
+        <v>2.15904</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.48036</v>
+        <v>6.1202</v>
       </c>
       <c r="C35" t="n">
-        <v>6.37133</v>
+        <v>6.09889</v>
       </c>
       <c r="D35" t="n">
-        <v>8.69664</v>
+        <v>8.788629999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>2.35023</v>
+        <v>2.065</v>
       </c>
       <c r="F35" t="n">
-        <v>2.54019</v>
+        <v>2.19289</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.24058</v>
+        <v>7.98614</v>
       </c>
       <c r="C36" t="n">
-        <v>8.012869999999999</v>
+        <v>7.36367</v>
       </c>
       <c r="D36" t="n">
-        <v>9.006399999999999</v>
+        <v>9.093489999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>2.36899</v>
+        <v>2.07902</v>
       </c>
       <c r="F36" t="n">
-        <v>2.55765</v>
+        <v>2.23075</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>9.43913</v>
+        <v>10.5656</v>
       </c>
       <c r="C37" t="n">
-        <v>3.46331</v>
+        <v>3.50319</v>
       </c>
       <c r="D37" t="n">
-        <v>9.28786</v>
+        <v>9.366820000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>2.37888</v>
+        <v>2.10423</v>
       </c>
       <c r="F37" t="n">
-        <v>2.58071</v>
+        <v>2.25412</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.4966</v>
+        <v>2.99415</v>
       </c>
       <c r="C38" t="n">
-        <v>3.49491</v>
+        <v>3.533</v>
       </c>
       <c r="D38" t="n">
-        <v>9.595789999999999</v>
+        <v>9.69924</v>
       </c>
       <c r="E38" t="n">
-        <v>2.41517</v>
+        <v>2.12632</v>
       </c>
       <c r="F38" t="n">
-        <v>2.63351</v>
+        <v>2.28857</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.53948</v>
+        <v>3.00911</v>
       </c>
       <c r="C39" t="n">
-        <v>3.51595</v>
+        <v>3.5764</v>
       </c>
       <c r="D39" t="n">
-        <v>9.92074</v>
+        <v>10.0426</v>
       </c>
       <c r="E39" t="n">
-        <v>2.43605</v>
+        <v>2.15972</v>
       </c>
       <c r="F39" t="n">
-        <v>2.66983</v>
+        <v>2.34517</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.61707</v>
+        <v>3.08971</v>
       </c>
       <c r="C40" t="n">
-        <v>3.54649</v>
+        <v>3.59354</v>
       </c>
       <c r="D40" t="n">
-        <v>10.2362</v>
+        <v>10.3502</v>
       </c>
       <c r="E40" t="n">
-        <v>2.4679</v>
+        <v>2.17989</v>
       </c>
       <c r="F40" t="n">
-        <v>2.69161</v>
+        <v>2.36928</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>2.66281</v>
+        <v>3.11718</v>
       </c>
       <c r="C41" t="n">
-        <v>3.59355</v>
+        <v>3.63851</v>
       </c>
       <c r="D41" t="n">
-        <v>10.5193</v>
+        <v>10.6432</v>
       </c>
       <c r="E41" t="n">
-        <v>2.4958</v>
+        <v>2.2126</v>
       </c>
       <c r="F41" t="n">
-        <v>2.7501</v>
+        <v>2.40064</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>2.717</v>
+        <v>3.20996</v>
       </c>
       <c r="C42" t="n">
-        <v>3.65363</v>
+        <v>3.68292</v>
       </c>
       <c r="D42" t="n">
-        <v>10.8142</v>
+        <v>10.9855</v>
       </c>
       <c r="E42" t="n">
-        <v>2.53721</v>
+        <v>2.25308</v>
       </c>
       <c r="F42" t="n">
-        <v>2.78857</v>
+        <v>2.4562</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>2.80022</v>
+        <v>3.2845</v>
       </c>
       <c r="C43" t="n">
-        <v>3.75359</v>
+        <v>3.75306</v>
       </c>
       <c r="D43" t="n">
-        <v>11.1275</v>
+        <v>11.261</v>
       </c>
       <c r="E43" t="n">
-        <v>2.58148</v>
+        <v>2.29281</v>
       </c>
       <c r="F43" t="n">
-        <v>2.85105</v>
+        <v>2.51998</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>2.94664</v>
+        <v>3.39944</v>
       </c>
       <c r="C44" t="n">
-        <v>3.88151</v>
+        <v>3.84498</v>
       </c>
       <c r="D44" t="n">
-        <v>11.4153</v>
+        <v>11.5464</v>
       </c>
       <c r="E44" t="n">
-        <v>2.64834</v>
+        <v>2.35212</v>
       </c>
       <c r="F44" t="n">
-        <v>2.93599</v>
+        <v>2.58606</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.1295</v>
+        <v>3.57916</v>
       </c>
       <c r="C45" t="n">
-        <v>4.0483</v>
+        <v>4.04668</v>
       </c>
       <c r="D45" t="n">
-        <v>11.673</v>
+        <v>11.8479</v>
       </c>
       <c r="E45" t="n">
-        <v>2.71858</v>
+        <v>2.42716</v>
       </c>
       <c r="F45" t="n">
-        <v>3.02135</v>
+        <v>2.6778</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>3.39897</v>
+        <v>3.85885</v>
       </c>
       <c r="C46" t="n">
-        <v>4.27121</v>
+        <v>4.2791</v>
       </c>
       <c r="D46" t="n">
-        <v>11.9413</v>
+        <v>12.1121</v>
       </c>
       <c r="E46" t="n">
-        <v>2.82854</v>
+        <v>2.52718</v>
       </c>
       <c r="F46" t="n">
-        <v>3.12523</v>
+        <v>2.78868</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>3.78489</v>
+        <v>4.2627</v>
       </c>
       <c r="C47" t="n">
-        <v>4.65444</v>
+        <v>4.60446</v>
       </c>
       <c r="D47" t="n">
-        <v>12.1939</v>
+        <v>12.4497</v>
       </c>
       <c r="E47" t="n">
-        <v>2.96713</v>
+        <v>2.68817</v>
       </c>
       <c r="F47" t="n">
-        <v>3.25614</v>
+        <v>2.94192</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.39867</v>
+        <v>4.91148</v>
       </c>
       <c r="C48" t="n">
-        <v>5.25188</v>
+        <v>5.14858</v>
       </c>
       <c r="D48" t="n">
-        <v>12.5088</v>
+        <v>12.751</v>
       </c>
       <c r="E48" t="n">
-        <v>3.24401</v>
+        <v>2.08185</v>
       </c>
       <c r="F48" t="n">
-        <v>3.51168</v>
+        <v>2.22856</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.2537</v>
+        <v>5.83176</v>
       </c>
       <c r="C49" t="n">
-        <v>6.13665</v>
+        <v>5.92155</v>
       </c>
       <c r="D49" t="n">
-        <v>12.7558</v>
+        <v>13.0042</v>
       </c>
       <c r="E49" t="n">
-        <v>3.62898</v>
+        <v>2.09194</v>
       </c>
       <c r="F49" t="n">
-        <v>3.90364</v>
+        <v>2.27185</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>6.53299</v>
+        <v>7.29556</v>
       </c>
       <c r="C50" t="n">
-        <v>7.40579</v>
+        <v>7.09115</v>
       </c>
       <c r="D50" t="n">
-        <v>9.08616</v>
+        <v>9.237830000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>2.40132</v>
+        <v>2.11504</v>
       </c>
       <c r="F50" t="n">
-        <v>2.65986</v>
+        <v>2.28732</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>8.575200000000001</v>
+        <v>9.36238</v>
       </c>
       <c r="C51" t="n">
-        <v>3.51742</v>
+        <v>3.51937</v>
       </c>
       <c r="D51" t="n">
-        <v>9.43333</v>
+        <v>9.520960000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>2.42575</v>
+        <v>2.13297</v>
       </c>
       <c r="F51" t="n">
-        <v>2.69793</v>
+        <v>2.30781</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>11.4283</v>
+        <v>12.7421</v>
       </c>
       <c r="C52" t="n">
-        <v>3.53241</v>
+        <v>3.53059</v>
       </c>
       <c r="D52" t="n">
-        <v>9.764250000000001</v>
+        <v>9.88556</v>
       </c>
       <c r="E52" t="n">
-        <v>2.45343</v>
+        <v>2.15674</v>
       </c>
       <c r="F52" t="n">
-        <v>2.73753</v>
+        <v>2.35571</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>2.56604</v>
+        <v>3.01744</v>
       </c>
       <c r="C53" t="n">
-        <v>3.57036</v>
+        <v>3.5641</v>
       </c>
       <c r="D53" t="n">
-        <v>10.0694</v>
+        <v>10.1993</v>
       </c>
       <c r="E53" t="n">
-        <v>2.48015</v>
+        <v>2.17812</v>
       </c>
       <c r="F53" t="n">
-        <v>2.77681</v>
+        <v>2.39656</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>2.63175</v>
+        <v>3.08452</v>
       </c>
       <c r="C54" t="n">
-        <v>3.6127</v>
+        <v>3.59382</v>
       </c>
       <c r="D54" t="n">
-        <v>10.3788</v>
+        <v>10.5664</v>
       </c>
       <c r="E54" t="n">
-        <v>2.50562</v>
+        <v>2.19749</v>
       </c>
       <c r="F54" t="n">
-        <v>2.80257</v>
+        <v>2.41635</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>2.69195</v>
+        <v>3.13187</v>
       </c>
       <c r="C55" t="n">
-        <v>3.65949</v>
+        <v>3.63173</v>
       </c>
       <c r="D55" t="n">
-        <v>10.6934</v>
+        <v>10.8697</v>
       </c>
       <c r="E55" t="n">
-        <v>2.55001</v>
+        <v>2.23253</v>
       </c>
       <c r="F55" t="n">
-        <v>2.86466</v>
+        <v>2.48441</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>2.74942</v>
+        <v>3.19739</v>
       </c>
       <c r="C56" t="n">
-        <v>3.72528</v>
+        <v>3.68242</v>
       </c>
       <c r="D56" t="n">
-        <v>10.9805</v>
+        <v>11.1988</v>
       </c>
       <c r="E56" t="n">
-        <v>2.58838</v>
+        <v>2.27433</v>
       </c>
       <c r="F56" t="n">
-        <v>2.92068</v>
+        <v>2.5612</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>2.84905</v>
+        <v>3.28452</v>
       </c>
       <c r="C57" t="n">
-        <v>3.79208</v>
+        <v>3.75545</v>
       </c>
       <c r="D57" t="n">
-        <v>11.2967</v>
+        <v>11.5136</v>
       </c>
       <c r="E57" t="n">
-        <v>2.634</v>
+        <v>2.32147</v>
       </c>
       <c r="F57" t="n">
-        <v>2.97769</v>
+        <v>2.62018</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>2.97566</v>
+        <v>3.41373</v>
       </c>
       <c r="C58" t="n">
-        <v>3.92349</v>
+        <v>3.86176</v>
       </c>
       <c r="D58" t="n">
-        <v>11.5534</v>
+        <v>11.8131</v>
       </c>
       <c r="E58" t="n">
-        <v>2.69254</v>
+        <v>2.36434</v>
       </c>
       <c r="F58" t="n">
-        <v>3.01423</v>
+        <v>2.68558</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.14753</v>
+        <v>3.57139</v>
       </c>
       <c r="C59" t="n">
-        <v>4.08527</v>
+        <v>4.00006</v>
       </c>
       <c r="D59" t="n">
-        <v>11.7854</v>
+        <v>12.1027</v>
       </c>
       <c r="E59" t="n">
-        <v>2.75488</v>
+        <v>2.44642</v>
       </c>
       <c r="F59" t="n">
-        <v>3.11893</v>
+        <v>2.78045</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>3.3855</v>
+        <v>3.85803</v>
       </c>
       <c r="C60" t="n">
-        <v>4.35453</v>
+        <v>4.21862</v>
       </c>
       <c r="D60" t="n">
-        <v>12.0521</v>
+        <v>12.4028</v>
       </c>
       <c r="E60" t="n">
-        <v>2.87758</v>
+        <v>2.54784</v>
       </c>
       <c r="F60" t="n">
-        <v>3.24655</v>
+        <v>2.89833</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>3.70946</v>
+        <v>4.23225</v>
       </c>
       <c r="C61" t="n">
-        <v>4.70789</v>
+        <v>4.54057</v>
       </c>
       <c r="D61" t="n">
-        <v>12.3454</v>
+        <v>12.6827</v>
       </c>
       <c r="E61" t="n">
-        <v>3.03747</v>
+        <v>2.67963</v>
       </c>
       <c r="F61" t="n">
-        <v>3.38926</v>
+        <v>3.04938</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.23997</v>
+        <v>4.72607</v>
       </c>
       <c r="C62" t="n">
-        <v>5.21303</v>
+        <v>5.0027</v>
       </c>
       <c r="D62" t="n">
-        <v>12.6873</v>
+        <v>13.021</v>
       </c>
       <c r="E62" t="n">
-        <v>3.2747</v>
+        <v>2.91102</v>
       </c>
       <c r="F62" t="n">
-        <v>3.63912</v>
+        <v>3.2828</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.93843</v>
+        <v>5.54147</v>
       </c>
       <c r="C63" t="n">
-        <v>6.01946</v>
+        <v>5.73686</v>
       </c>
       <c r="D63" t="n">
-        <v>13.0633</v>
+        <v>13.3968</v>
       </c>
       <c r="E63" t="n">
-        <v>3.61705</v>
+        <v>2.42636</v>
       </c>
       <c r="F63" t="n">
-        <v>4.01506</v>
+        <v>2.68212</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.16962</v>
+        <v>6.74955</v>
       </c>
       <c r="C64" t="n">
-        <v>7.21755</v>
+        <v>6.84707</v>
       </c>
       <c r="D64" t="n">
-        <v>9.257110000000001</v>
+        <v>9.54429</v>
       </c>
       <c r="E64" t="n">
-        <v>2.80026</v>
+        <v>2.45467</v>
       </c>
       <c r="F64" t="n">
-        <v>3.10372</v>
+        <v>2.73362</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>8.03253</v>
+        <v>8.78232</v>
       </c>
       <c r="C65" t="n">
-        <v>4.15572</v>
+        <v>3.84451</v>
       </c>
       <c r="D65" t="n">
-        <v>9.682919999999999</v>
+        <v>9.857659999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>2.83022</v>
+        <v>2.47487</v>
       </c>
       <c r="F65" t="n">
-        <v>3.14</v>
+        <v>2.76145</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>10.8834</v>
+        <v>11.6628</v>
       </c>
       <c r="C66" t="n">
-        <v>4.1678</v>
+        <v>3.86019</v>
       </c>
       <c r="D66" t="n">
-        <v>10.082</v>
+        <v>10.5034</v>
       </c>
       <c r="E66" t="n">
-        <v>2.85904</v>
+        <v>2.48656</v>
       </c>
       <c r="F66" t="n">
-        <v>3.1746</v>
+        <v>2.80328</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>2.89521</v>
+        <v>3.29089</v>
       </c>
       <c r="C67" t="n">
-        <v>4.21908</v>
+        <v>3.89105</v>
       </c>
       <c r="D67" t="n">
-        <v>10.5977</v>
+        <v>10.7506</v>
       </c>
       <c r="E67" t="n">
-        <v>2.87326</v>
+        <v>2.5102</v>
       </c>
       <c r="F67" t="n">
-        <v>3.22579</v>
+        <v>2.85309</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>2.93269</v>
+        <v>3.36078</v>
       </c>
       <c r="C68" t="n">
-        <v>4.24164</v>
+        <v>3.91685</v>
       </c>
       <c r="D68" t="n">
-        <v>11.1312</v>
+        <v>11.2708</v>
       </c>
       <c r="E68" t="n">
-        <v>2.90819</v>
+        <v>2.53131</v>
       </c>
       <c r="F68" t="n">
-        <v>3.28336</v>
+        <v>2.88477</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>2.99318</v>
+        <v>3.40607</v>
       </c>
       <c r="C69" t="n">
-        <v>4.29126</v>
+        <v>3.98179</v>
       </c>
       <c r="D69" t="n">
-        <v>11.607</v>
+        <v>12.0122</v>
       </c>
       <c r="E69" t="n">
-        <v>2.92992</v>
+        <v>2.56832</v>
       </c>
       <c r="F69" t="n">
-        <v>3.34306</v>
+        <v>2.94383</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.06809</v>
+        <v>3.51016</v>
       </c>
       <c r="C70" t="n">
-        <v>4.34838</v>
+        <v>4.02475</v>
       </c>
       <c r="D70" t="n">
-        <v>11.9843</v>
+        <v>12.555</v>
       </c>
       <c r="E70" t="n">
-        <v>2.98128</v>
+        <v>2.60069</v>
       </c>
       <c r="F70" t="n">
-        <v>3.42525</v>
+        <v>2.98117</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.14504</v>
+        <v>3.59707</v>
       </c>
       <c r="C71" t="n">
-        <v>4.38586</v>
+        <v>4.14765</v>
       </c>
       <c r="D71" t="n">
-        <v>12.7601</v>
+        <v>13.1291</v>
       </c>
       <c r="E71" t="n">
-        <v>3.01739</v>
+        <v>2.64018</v>
       </c>
       <c r="F71" t="n">
-        <v>3.49956</v>
+        <v>3.07832</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.28389</v>
+        <v>3.72075</v>
       </c>
       <c r="C72" t="n">
-        <v>4.51024</v>
+        <v>4.17674</v>
       </c>
       <c r="D72" t="n">
-        <v>13.2189</v>
+        <v>14.0787</v>
       </c>
       <c r="E72" t="n">
-        <v>3.07075</v>
+        <v>2.70316</v>
       </c>
       <c r="F72" t="n">
-        <v>3.61027</v>
+        <v>3.14449</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>3.4203</v>
+        <v>3.90719</v>
       </c>
       <c r="C73" t="n">
-        <v>4.63575</v>
+        <v>4.36165</v>
       </c>
       <c r="D73" t="n">
-        <v>13.8686</v>
+        <v>14.7305</v>
       </c>
       <c r="E73" t="n">
-        <v>3.13867</v>
+        <v>2.76348</v>
       </c>
       <c r="F73" t="n">
-        <v>3.67456</v>
+        <v>3.26397</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>3.62838</v>
+        <v>4.11785</v>
       </c>
       <c r="C74" t="n">
-        <v>4.84533</v>
+        <v>4.53364</v>
       </c>
       <c r="D74" t="n">
-        <v>14.8853</v>
+        <v>13.8758</v>
       </c>
       <c r="E74" t="n">
-        <v>3.24436</v>
+        <v>2.87922</v>
       </c>
       <c r="F74" t="n">
-        <v>3.83342</v>
+        <v>3.40523</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>3.92823</v>
+        <v>4.49149</v>
       </c>
       <c r="C75" t="n">
-        <v>5.16555</v>
+        <v>4.8524</v>
       </c>
       <c r="D75" t="n">
-        <v>15.6038</v>
+        <v>14.8334</v>
       </c>
       <c r="E75" t="n">
-        <v>3.37466</v>
+        <v>3.0105</v>
       </c>
       <c r="F75" t="n">
-        <v>3.97342</v>
+        <v>3.54418</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>4.35593</v>
+        <v>5.00681</v>
       </c>
       <c r="C76" t="n">
-        <v>5.61807</v>
+        <v>5.30395</v>
       </c>
       <c r="D76" t="n">
-        <v>17.0438</v>
+        <v>16.15</v>
       </c>
       <c r="E76" t="n">
-        <v>3.58315</v>
+        <v>3.20246</v>
       </c>
       <c r="F76" t="n">
-        <v>4.23432</v>
+        <v>3.79614</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.06857</v>
+        <v>5.74025</v>
       </c>
       <c r="C77" t="n">
-        <v>6.35379</v>
+        <v>5.98711</v>
       </c>
       <c r="D77" t="n">
-        <v>17.9852</v>
+        <v>17.2436</v>
       </c>
       <c r="E77" t="n">
-        <v>3.92446</v>
+        <v>2.66037</v>
       </c>
       <c r="F77" t="n">
-        <v>4.54706</v>
+        <v>3.11043</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.06503</v>
+        <v>6.78903</v>
       </c>
       <c r="C78" t="n">
-        <v>7.41706</v>
+        <v>7.04449</v>
       </c>
       <c r="D78" t="n">
-        <v>15.5781</v>
+        <v>15.5922</v>
       </c>
       <c r="E78" t="n">
-        <v>3.10932</v>
+        <v>2.70173</v>
       </c>
       <c r="F78" t="n">
-        <v>3.55624</v>
+        <v>3.15359</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.69681</v>
+        <v>8.51735</v>
       </c>
       <c r="C79" t="n">
-        <v>4.55192</v>
+        <v>4.20084</v>
       </c>
       <c r="D79" t="n">
-        <v>16.7638</v>
+        <v>16.5554</v>
       </c>
       <c r="E79" t="n">
-        <v>3.12699</v>
+        <v>2.72292</v>
       </c>
       <c r="F79" t="n">
-        <v>3.60978</v>
+        <v>3.21694</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>10.2496</v>
+        <v>11.2561</v>
       </c>
       <c r="C80" t="n">
-        <v>4.59057</v>
+        <v>4.22409</v>
       </c>
       <c r="D80" t="n">
-        <v>17.734</v>
+        <v>17.75</v>
       </c>
       <c r="E80" t="n">
-        <v>3.15794</v>
+        <v>2.73733</v>
       </c>
       <c r="F80" t="n">
-        <v>3.66341</v>
+        <v>3.26174</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>3.48006</v>
+        <v>3.8825</v>
       </c>
       <c r="C81" t="n">
-        <v>4.6202</v>
+        <v>4.22399</v>
       </c>
       <c r="D81" t="n">
-        <v>18.7937</v>
+        <v>18.6915</v>
       </c>
       <c r="E81" t="n">
-        <v>3.18184</v>
+        <v>2.76534</v>
       </c>
       <c r="F81" t="n">
-        <v>3.72339</v>
+        <v>3.31471</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>3.51319</v>
+        <v>3.93845</v>
       </c>
       <c r="C82" t="n">
-        <v>4.64731</v>
+        <v>4.25989</v>
       </c>
       <c r="D82" t="n">
-        <v>19.8971</v>
+        <v>19.7274</v>
       </c>
       <c r="E82" t="n">
-        <v>3.20247</v>
+        <v>2.79035</v>
       </c>
       <c r="F82" t="n">
-        <v>3.77556</v>
+        <v>3.3559</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>3.58912</v>
+        <v>3.99904</v>
       </c>
       <c r="C83" t="n">
-        <v>4.69989</v>
+        <v>4.30429</v>
       </c>
       <c r="D83" t="n">
-        <v>20.918</v>
+        <v>20.9787</v>
       </c>
       <c r="E83" t="n">
-        <v>3.21859</v>
+        <v>2.81052</v>
       </c>
       <c r="F83" t="n">
-        <v>3.84808</v>
+        <v>3.39993</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>3.68634</v>
+        <v>4.08742</v>
       </c>
       <c r="C84" t="n">
-        <v>4.75801</v>
+        <v>4.36905</v>
       </c>
       <c r="D84" t="n">
-        <v>22.0638</v>
+        <v>22.0089</v>
       </c>
       <c r="E84" t="n">
-        <v>3.26644</v>
+        <v>2.85542</v>
       </c>
       <c r="F84" t="n">
-        <v>3.92365</v>
+        <v>3.47587</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>3.7732</v>
+        <v>4.17972</v>
       </c>
       <c r="C85" t="n">
-        <v>4.81519</v>
+        <v>4.45039</v>
       </c>
       <c r="D85" t="n">
-        <v>23.1255</v>
+        <v>23.2048</v>
       </c>
       <c r="E85" t="n">
-        <v>3.30442</v>
+        <v>2.89542</v>
       </c>
       <c r="F85" t="n">
-        <v>3.99598</v>
+        <v>3.54528</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>3.88575</v>
+        <v>4.31632</v>
       </c>
       <c r="C86" t="n">
-        <v>4.94489</v>
+        <v>4.56241</v>
       </c>
       <c r="D86" t="n">
-        <v>24.2753</v>
+        <v>24.1968</v>
       </c>
       <c r="E86" t="n">
-        <v>3.37892</v>
+        <v>2.94596</v>
       </c>
       <c r="F86" t="n">
-        <v>4.08681</v>
+        <v>3.6495</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.01406</v>
+        <v>4.46734</v>
       </c>
       <c r="C87" t="n">
-        <v>5.08604</v>
+        <v>4.7107</v>
       </c>
       <c r="D87" t="n">
-        <v>25.471</v>
+        <v>25.4819</v>
       </c>
       <c r="E87" t="n">
-        <v>3.46041</v>
+        <v>3.02536</v>
       </c>
       <c r="F87" t="n">
-        <v>4.23262</v>
+        <v>3.79263</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.24317</v>
+        <v>4.71724</v>
       </c>
       <c r="C88" t="n">
-        <v>5.33381</v>
+        <v>4.96693</v>
       </c>
       <c r="D88" t="n">
-        <v>26.5813</v>
+        <v>26.6944</v>
       </c>
       <c r="E88" t="n">
-        <v>3.55393</v>
+        <v>3.12814</v>
       </c>
       <c r="F88" t="n">
-        <v>4.44252</v>
+        <v>3.98984</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>4.55583</v>
+        <v>5.06107</v>
       </c>
       <c r="C89" t="n">
-        <v>5.68879</v>
+        <v>5.3715</v>
       </c>
       <c r="D89" t="n">
-        <v>27.7408</v>
+        <v>27.9183</v>
       </c>
       <c r="E89" t="n">
-        <v>3.72331</v>
+        <v>3.3069</v>
       </c>
       <c r="F89" t="n">
-        <v>4.73911</v>
+        <v>4.30037</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>5.02453</v>
+        <v>5.55962</v>
       </c>
       <c r="C90" t="n">
-        <v>6.32217</v>
+        <v>5.95211</v>
       </c>
       <c r="D90" t="n">
-        <v>29.0328</v>
+        <v>29.2467</v>
       </c>
       <c r="E90" t="n">
-        <v>3.99303</v>
+        <v>3.55436</v>
       </c>
       <c r="F90" t="n">
-        <v>5.31468</v>
+        <v>4.89013</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>5.76844</v>
+        <v>6.37316</v>
       </c>
       <c r="C91" t="n">
-        <v>7.19995</v>
+        <v>6.76504</v>
       </c>
       <c r="D91" t="n">
-        <v>30.4642</v>
+        <v>30.5853</v>
       </c>
       <c r="E91" t="n">
-        <v>4.43938</v>
+        <v>2.87479</v>
       </c>
       <c r="F91" t="n">
-        <v>6.10627</v>
+        <v>3.48623</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>6.95346</v>
+        <v>7.53128</v>
       </c>
       <c r="C92" t="n">
-        <v>8.475849999999999</v>
+        <v>7.98293</v>
       </c>
       <c r="D92" t="n">
-        <v>24.6571</v>
+        <v>24.7561</v>
       </c>
       <c r="E92" t="n">
-        <v>3.36392</v>
+        <v>2.89513</v>
       </c>
       <c r="F92" t="n">
-        <v>4.07222</v>
+        <v>3.60591</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>8.748239999999999</v>
+        <v>9.59765</v>
       </c>
       <c r="C93" t="n">
-        <v>10.318</v>
+        <v>9.64263</v>
       </c>
       <c r="D93" t="n">
-        <v>25.5422</v>
+        <v>25.6289</v>
       </c>
       <c r="E93" t="n">
-        <v>3.39667</v>
+        <v>2.95913</v>
       </c>
       <c r="F93" t="n">
-        <v>4.28626</v>
+        <v>3.84398</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>11.5503</v>
+        <v>12.629</v>
       </c>
       <c r="C94" t="n">
-        <v>5.2403</v>
+        <v>4.81087</v>
       </c>
       <c r="D94" t="n">
-        <v>26.5468</v>
+        <v>26.4668</v>
       </c>
       <c r="E94" t="n">
-        <v>3.50742</v>
+        <v>3.02563</v>
       </c>
       <c r="F94" t="n">
-        <v>4.5643</v>
+        <v>4.06818</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.18446</v>
+        <v>4.58597</v>
       </c>
       <c r="C95" t="n">
-        <v>5.46974</v>
+        <v>5.06145</v>
       </c>
       <c r="D95" t="n">
-        <v>27.5037</v>
+        <v>27.4085</v>
       </c>
       <c r="E95" t="n">
-        <v>3.59049</v>
+        <v>3.14995</v>
       </c>
       <c r="F95" t="n">
-        <v>4.94408</v>
+        <v>4.46749</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>4.49821</v>
+        <v>4.92915</v>
       </c>
       <c r="C96" t="n">
-        <v>5.67815</v>
+        <v>5.30305</v>
       </c>
       <c r="D96" t="n">
-        <v>28.4404</v>
+        <v>28.308</v>
       </c>
       <c r="E96" t="n">
-        <v>3.82893</v>
+        <v>3.29391</v>
       </c>
       <c r="F96" t="n">
-        <v>5.32174</v>
+        <v>4.85517</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>4.85028</v>
+        <v>5.27134</v>
       </c>
       <c r="C97" t="n">
-        <v>5.95328</v>
+        <v>5.54148</v>
       </c>
       <c r="D97" t="n">
-        <v>29.412</v>
+        <v>29.4264</v>
       </c>
       <c r="E97" t="n">
-        <v>4.03973</v>
+        <v>3.52758</v>
       </c>
       <c r="F97" t="n">
-        <v>5.86708</v>
+        <v>5.3355</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>5.27011</v>
+        <v>5.75425</v>
       </c>
       <c r="C98" t="n">
-        <v>6.16951</v>
+        <v>5.80625</v>
       </c>
       <c r="D98" t="n">
-        <v>30.3814</v>
+        <v>30.3887</v>
       </c>
       <c r="E98" t="n">
-        <v>4.31489</v>
+        <v>3.8112</v>
       </c>
       <c r="F98" t="n">
-        <v>6.39611</v>
+        <v>5.86072</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>5.76974</v>
+        <v>6.23174</v>
       </c>
       <c r="C99" t="n">
-        <v>6.45427</v>
+        <v>6.04604</v>
       </c>
       <c r="D99" t="n">
-        <v>31.3088</v>
+        <v>31.406</v>
       </c>
       <c r="E99" t="n">
-        <v>4.66543</v>
+        <v>4.10552</v>
       </c>
       <c r="F99" t="n">
-        <v>7.03493</v>
+        <v>6.43867</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>6.28644</v>
+        <v>6.83958</v>
       </c>
       <c r="C100" t="n">
-        <v>6.71916</v>
+        <v>6.36192</v>
       </c>
       <c r="D100" t="n">
-        <v>32.3234</v>
+        <v>32.5084</v>
       </c>
       <c r="E100" t="n">
-        <v>4.892</v>
+        <v>4.40664</v>
       </c>
       <c r="F100" t="n">
-        <v>7.5769</v>
+        <v>7.01211</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>6.75142</v>
+        <v>7.37195</v>
       </c>
       <c r="C101" t="n">
-        <v>7.03342</v>
+        <v>6.65117</v>
       </c>
       <c r="D101" t="n">
-        <v>33.5875</v>
+        <v>33.544</v>
       </c>
       <c r="E101" t="n">
-        <v>5.15993</v>
+        <v>4.69779</v>
       </c>
       <c r="F101" t="n">
-        <v>8.06245</v>
+        <v>7.49502</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.40652</v>
+        <v>7.91305</v>
       </c>
       <c r="C102" t="n">
-        <v>7.38127</v>
+        <v>6.97878</v>
       </c>
       <c r="D102" t="n">
-        <v>34.6153</v>
+        <v>34.6916</v>
       </c>
       <c r="E102" t="n">
-        <v>5.41562</v>
+        <v>4.99403</v>
       </c>
       <c r="F102" t="n">
-        <v>8.508319999999999</v>
+        <v>7.98215</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>7.9449</v>
+        <v>8.52891</v>
       </c>
       <c r="C103" t="n">
-        <v>7.81571</v>
+        <v>7.46325</v>
       </c>
       <c r="D103" t="n">
-        <v>35.9682</v>
+        <v>35.9439</v>
       </c>
       <c r="E103" t="n">
-        <v>5.70609</v>
+        <v>5.2433</v>
       </c>
       <c r="F103" t="n">
-        <v>9.02976</v>
+        <v>8.49367</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>8.55073</v>
+        <v>9.2273</v>
       </c>
       <c r="C104" t="n">
-        <v>8.428599999999999</v>
+        <v>8.00116</v>
       </c>
       <c r="D104" t="n">
-        <v>37.0983</v>
+        <v>37.2424</v>
       </c>
       <c r="E104" t="n">
-        <v>6.03085</v>
+        <v>5.57596</v>
       </c>
       <c r="F104" t="n">
-        <v>9.56771</v>
+        <v>8.94514</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>9.36712</v>
+        <v>9.99959</v>
       </c>
       <c r="C105" t="n">
-        <v>9.25034</v>
+        <v>8.82761</v>
       </c>
       <c r="D105" t="n">
-        <v>38.5601</v>
+        <v>38.5409</v>
       </c>
       <c r="E105" t="n">
-        <v>6.43555</v>
+        <v>4.3059</v>
       </c>
       <c r="F105" t="n">
-        <v>10.2134</v>
+        <v>6.33493</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>10.3514</v>
+        <v>11.1124</v>
       </c>
       <c r="C106" t="n">
-        <v>10.3615</v>
+        <v>9.914</v>
       </c>
       <c r="D106" t="n">
-        <v>39.7887</v>
+        <v>39.8892</v>
       </c>
       <c r="E106" t="n">
-        <v>7.0203</v>
+        <v>4.44065</v>
       </c>
       <c r="F106" t="n">
-        <v>11.0735</v>
+        <v>6.55256</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>11.8335</v>
+        <v>12.685</v>
       </c>
       <c r="C107" t="n">
-        <v>11.9761</v>
+        <v>11.4501</v>
       </c>
       <c r="D107" t="n">
-        <v>30.542</v>
+        <v>30.3104</v>
       </c>
       <c r="E107" t="n">
-        <v>5.03477</v>
+        <v>4.59464</v>
       </c>
       <c r="F107" t="n">
-        <v>7.31878</v>
+        <v>6.824</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.9631</v>
+        <v>15.094</v>
       </c>
       <c r="C108" t="n">
-        <v>6.7816</v>
+        <v>6.40378</v>
       </c>
       <c r="D108" t="n">
-        <v>31.3689</v>
+        <v>31.3238</v>
       </c>
       <c r="E108" t="n">
-        <v>5.18688</v>
+        <v>4.72713</v>
       </c>
       <c r="F108" t="n">
-        <v>7.54399</v>
+        <v>7.02658</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>17.5495</v>
+        <v>19.0003</v>
       </c>
       <c r="C109" t="n">
-        <v>6.92821</v>
+        <v>6.52988</v>
       </c>
       <c r="D109" t="n">
-        <v>32.0967</v>
+        <v>32.2632</v>
       </c>
       <c r="E109" t="n">
-        <v>5.31515</v>
+        <v>4.84421</v>
       </c>
       <c r="F109" t="n">
-        <v>7.82555</v>
+        <v>7.25439</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.0769</v>
+        <v>7.5947</v>
       </c>
       <c r="C110" t="n">
-        <v>7.05257</v>
+        <v>6.66606</v>
       </c>
       <c r="D110" t="n">
-        <v>32.9301</v>
+        <v>33.1053</v>
       </c>
       <c r="E110" t="n">
-        <v>5.43251</v>
+        <v>4.96464</v>
       </c>
       <c r="F110" t="n">
-        <v>8.073359999999999</v>
+        <v>7.49672</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.30137</v>
+        <v>7.8351</v>
       </c>
       <c r="C111" t="n">
-        <v>7.19565</v>
+        <v>6.80621</v>
       </c>
       <c r="D111" t="n">
-        <v>34.1394</v>
+        <v>34.0429</v>
       </c>
       <c r="E111" t="n">
-        <v>5.59012</v>
+        <v>5.11097</v>
       </c>
       <c r="F111" t="n">
-        <v>8.29265</v>
+        <v>7.71566</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.51848</v>
+        <v>8.091419999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>7.35628</v>
+        <v>6.98013</v>
       </c>
       <c r="D112" t="n">
-        <v>34.8899</v>
+        <v>34.9559</v>
       </c>
       <c r="E112" t="n">
-        <v>5.71623</v>
+        <v>5.25843</v>
       </c>
       <c r="F112" t="n">
-        <v>8.571210000000001</v>
+        <v>7.98296</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>7.7671</v>
+        <v>8.295030000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>7.54208</v>
+        <v>7.16943</v>
       </c>
       <c r="D113" t="n">
-        <v>35.8704</v>
+        <v>36.0448</v>
       </c>
       <c r="E113" t="n">
-        <v>5.87992</v>
+        <v>5.39259</v>
       </c>
       <c r="F113" t="n">
-        <v>8.83367</v>
+        <v>8.20889</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.03964</v>
+        <v>8.559850000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>7.76143</v>
+        <v>7.38639</v>
       </c>
       <c r="D114" t="n">
-        <v>36.9727</v>
+        <v>37.0958</v>
       </c>
       <c r="E114" t="n">
-        <v>6.05476</v>
+        <v>5.55727</v>
       </c>
       <c r="F114" t="n">
-        <v>9.12297</v>
+        <v>8.490360000000001</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>8.320360000000001</v>
+        <v>8.89514</v>
       </c>
       <c r="C115" t="n">
-        <v>8.032579999999999</v>
+        <v>7.6262</v>
       </c>
       <c r="D115" t="n">
-        <v>38.1679</v>
+        <v>38.0822</v>
       </c>
       <c r="E115" t="n">
-        <v>6.21624</v>
+        <v>5.74835</v>
       </c>
       <c r="F115" t="n">
-        <v>9.46518</v>
+        <v>8.83399</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>8.65944</v>
+        <v>9.22743</v>
       </c>
       <c r="C116" t="n">
-        <v>8.368309999999999</v>
+        <v>7.95349</v>
       </c>
       <c r="D116" t="n">
-        <v>39.263</v>
+        <v>39.4234</v>
       </c>
       <c r="E116" t="n">
-        <v>6.44404</v>
+        <v>5.94755</v>
       </c>
       <c r="F116" t="n">
-        <v>9.78698</v>
+        <v>9.158659999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>9.10168</v>
+        <v>9.69478</v>
       </c>
       <c r="C117" t="n">
-        <v>8.78739</v>
+        <v>8.382389999999999</v>
       </c>
       <c r="D117" t="n">
-        <v>40.4112</v>
+        <v>40.458</v>
       </c>
       <c r="E117" t="n">
-        <v>6.68176</v>
+        <v>6.1886</v>
       </c>
       <c r="F117" t="n">
-        <v>10.2208</v>
+        <v>9.566229999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>9.602650000000001</v>
+        <v>10.2797</v>
       </c>
       <c r="C118" t="n">
-        <v>9.37495</v>
+        <v>8.953440000000001</v>
       </c>
       <c r="D118" t="n">
-        <v>41.6069</v>
+        <v>41.619</v>
       </c>
       <c r="E118" t="n">
-        <v>6.96551</v>
+        <v>6.48375</v>
       </c>
       <c r="F118" t="n">
-        <v>10.6981</v>
+        <v>10.0552</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>10.3587</v>
+        <v>11.0263</v>
       </c>
       <c r="C119" t="n">
-        <v>10.153</v>
+        <v>9.75116</v>
       </c>
       <c r="D119" t="n">
-        <v>42.8152</v>
+        <v>43.0049</v>
       </c>
       <c r="E119" t="n">
-        <v>7.38138</v>
+        <v>4.83238</v>
       </c>
       <c r="F119" t="n">
-        <v>11.3429</v>
+        <v>6.93798</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>11.2638</v>
+        <v>12.0605</v>
       </c>
       <c r="C120" t="n">
-        <v>11.2503</v>
+        <v>10.8053</v>
       </c>
       <c r="D120" t="n">
-        <v>44.2475</v>
+        <v>44.3832</v>
       </c>
       <c r="E120" t="n">
-        <v>7.93649</v>
+        <v>4.91665</v>
       </c>
       <c r="F120" t="n">
-        <v>12.1534</v>
+        <v>7.12532</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>12.6313</v>
+        <v>13.5344</v>
       </c>
       <c r="C121" t="n">
-        <v>12.873</v>
+        <v>12.3743</v>
       </c>
       <c r="D121" t="n">
-        <v>33.1187</v>
+        <v>33.0554</v>
       </c>
       <c r="E121" t="n">
-        <v>5.48513</v>
+        <v>5.05389</v>
       </c>
       <c r="F121" t="n">
-        <v>7.8355</v>
+        <v>7.34034</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>14.6372</v>
+        <v>15.7318</v>
       </c>
       <c r="C122" t="n">
-        <v>7.10351</v>
+        <v>6.76183</v>
       </c>
       <c r="D122" t="n">
-        <v>33.9333</v>
+        <v>34.1191</v>
       </c>
       <c r="E122" t="n">
-        <v>5.60872</v>
+        <v>5.13184</v>
       </c>
       <c r="F122" t="n">
-        <v>8.075240000000001</v>
+        <v>7.54121</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>17.8502</v>
+        <v>19.226</v>
       </c>
       <c r="C123" t="n">
-        <v>7.26364</v>
+        <v>6.88571</v>
       </c>
       <c r="D123" t="n">
-        <v>34.994</v>
+        <v>34.9589</v>
       </c>
       <c r="E123" t="n">
-        <v>5.71183</v>
+        <v>5.26706</v>
       </c>
       <c r="F123" t="n">
-        <v>8.323919999999999</v>
+        <v>7.77684</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>7.4607</v>
+        <v>8.00475</v>
       </c>
       <c r="C124" t="n">
-        <v>7.37338</v>
+        <v>7.0461</v>
       </c>
       <c r="D124" t="n">
-        <v>35.9</v>
+        <v>35.8943</v>
       </c>
       <c r="E124" t="n">
-        <v>5.878</v>
+        <v>5.3751</v>
       </c>
       <c r="F124" t="n">
-        <v>8.54505</v>
+        <v>7.98209</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>7.65469</v>
+        <v>8.22695</v>
       </c>
       <c r="C125" t="n">
-        <v>7.54041</v>
+        <v>7.18943</v>
       </c>
       <c r="D125" t="n">
-        <v>36.9013</v>
+        <v>36.7308</v>
       </c>
       <c r="E125" t="n">
-        <v>5.97785</v>
+        <v>5.52157</v>
       </c>
       <c r="F125" t="n">
-        <v>8.83418</v>
+        <v>8.2685</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>7.85719</v>
+        <v>8.45064</v>
       </c>
       <c r="C126" t="n">
-        <v>7.69937</v>
+        <v>7.35226</v>
       </c>
       <c r="D126" t="n">
-        <v>37.7831</v>
+        <v>37.7276</v>
       </c>
       <c r="E126" t="n">
-        <v>6.12591</v>
+        <v>5.64962</v>
       </c>
       <c r="F126" t="n">
-        <v>9.07098</v>
+        <v>8.53829</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>8.09676</v>
+        <v>8.69848</v>
       </c>
       <c r="C127" t="n">
-        <v>7.90506</v>
+        <v>7.5314</v>
       </c>
       <c r="D127" t="n">
-        <v>38.7863</v>
+        <v>38.6511</v>
       </c>
       <c r="E127" t="n">
-        <v>6.28124</v>
+        <v>5.81717</v>
       </c>
       <c r="F127" t="n">
-        <v>9.391450000000001</v>
+        <v>8.82799</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>8.33881</v>
+        <v>8.96771</v>
       </c>
       <c r="C128" t="n">
-        <v>8.09896</v>
+        <v>7.77064</v>
       </c>
       <c r="D128" t="n">
-        <v>39.8036</v>
+        <v>39.7265</v>
       </c>
       <c r="E128" t="n">
-        <v>6.42922</v>
+        <v>5.98118</v>
       </c>
       <c r="F128" t="n">
-        <v>9.696210000000001</v>
+        <v>9.13317</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>8.654339999999999</v>
+        <v>9.237130000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>8.38317</v>
+        <v>8.02505</v>
       </c>
       <c r="D129" t="n">
-        <v>40.6586</v>
+        <v>40.9186</v>
       </c>
       <c r="E129" t="n">
-        <v>6.64447</v>
+        <v>6.16535</v>
       </c>
       <c r="F129" t="n">
-        <v>10.0311</v>
+        <v>9.45049</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>8.987360000000001</v>
+        <v>9.629099999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>8.719749999999999</v>
+        <v>8.386279999999999</v>
       </c>
       <c r="D130" t="n">
-        <v>41.751</v>
+        <v>41.9882</v>
       </c>
       <c r="E130" t="n">
-        <v>6.86258</v>
+        <v>6.37796</v>
       </c>
       <c r="F130" t="n">
-        <v>10.448</v>
+        <v>9.815060000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>9.40269</v>
+        <v>10.062</v>
       </c>
       <c r="C131" t="n">
-        <v>9.13706</v>
+        <v>8.800610000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>43.1226</v>
+        <v>43.076</v>
       </c>
       <c r="E131" t="n">
-        <v>7.08994</v>
+        <v>6.62936</v>
       </c>
       <c r="F131" t="n">
-        <v>10.8865</v>
+        <v>10.2374</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>9.953419999999999</v>
+        <v>10.623</v>
       </c>
       <c r="C132" t="n">
-        <v>9.71758</v>
+        <v>9.38036</v>
       </c>
       <c r="D132" t="n">
-        <v>44.1915</v>
+        <v>44.4168</v>
       </c>
       <c r="E132" t="n">
-        <v>7.42937</v>
+        <v>6.91138</v>
       </c>
       <c r="F132" t="n">
-        <v>11.4073</v>
+        <v>10.7545</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>10.6174</v>
+        <v>11.3633</v>
       </c>
       <c r="C133" t="n">
-        <v>10.494</v>
+        <v>10.1287</v>
       </c>
       <c r="D133" t="n">
-        <v>45.5153</v>
+        <v>45.6242</v>
       </c>
       <c r="E133" t="n">
-        <v>7.80788</v>
+        <v>7.35687</v>
       </c>
       <c r="F133" t="n">
-        <v>12.0202</v>
+        <v>11.3387</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>11.5562</v>
+        <v>12.3751</v>
       </c>
       <c r="C134" t="n">
-        <v>11.5808</v>
+        <v>11.192</v>
       </c>
       <c r="D134" t="n">
-        <v>46.9381</v>
+        <v>46.823</v>
       </c>
       <c r="E134" t="n">
-        <v>8.37917</v>
+        <v>10.8444</v>
       </c>
       <c r="F134" t="n">
-        <v>12.8707</v>
+        <v>13.2837</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>12.8872</v>
+        <v>13.7743</v>
       </c>
       <c r="C135" t="n">
-        <v>13.1233</v>
+        <v>12.7197</v>
       </c>
       <c r="D135" t="n">
-        <v>34.6995</v>
+        <v>34.5495</v>
       </c>
       <c r="E135" t="n">
-        <v>11.8335</v>
+        <v>10.9665</v>
       </c>
       <c r="F135" t="n">
-        <v>14.4919</v>
+        <v>13.5463</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>14.8007</v>
+        <v>15.8241</v>
       </c>
       <c r="C136" t="n">
-        <v>16.5341</v>
+        <v>15.4222</v>
       </c>
       <c r="D136" t="n">
-        <v>35.5875</v>
+        <v>35.4016</v>
       </c>
       <c r="E136" t="n">
-        <v>11.9731</v>
+        <v>11.0212</v>
       </c>
       <c r="F136" t="n">
-        <v>14.7476</v>
+        <v>13.703</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.6524</v>
+        <v>19.0738</v>
       </c>
       <c r="C137" t="n">
-        <v>16.7176</v>
+        <v>15.5221</v>
       </c>
       <c r="D137" t="n">
-        <v>36.534</v>
+        <v>36.3756</v>
       </c>
       <c r="E137" t="n">
-        <v>12.051</v>
+        <v>11.1663</v>
       </c>
       <c r="F137" t="n">
-        <v>15.0049</v>
+        <v>13.9511</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>13.2568</v>
+        <v>13.8239</v>
       </c>
       <c r="C138" t="n">
-        <v>16.9096</v>
+        <v>15.6343</v>
       </c>
       <c r="D138" t="n">
-        <v>37.2463</v>
+        <v>37.2189</v>
       </c>
       <c r="E138" t="n">
-        <v>12.1226</v>
+        <v>11.2485</v>
       </c>
       <c r="F138" t="n">
-        <v>15.225</v>
+        <v>14.2385</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>13.2747</v>
+        <v>14.001</v>
       </c>
       <c r="C139" t="n">
-        <v>17.0636</v>
+        <v>15.8202</v>
       </c>
       <c r="D139" t="n">
-        <v>38.325</v>
+        <v>38.1623</v>
       </c>
       <c r="E139" t="n">
-        <v>12.2819</v>
+        <v>11.4464</v>
       </c>
       <c r="F139" t="n">
-        <v>15.5302</v>
+        <v>14.4468</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.4291</v>
+        <v>13.9778</v>
       </c>
       <c r="C140" t="n">
-        <v>17.2199</v>
+        <v>16.0193</v>
       </c>
       <c r="D140" t="n">
-        <v>39.1315</v>
+        <v>39.1382</v>
       </c>
       <c r="E140" t="n">
-        <v>12.4199</v>
+        <v>11.5655</v>
       </c>
       <c r="F140" t="n">
-        <v>15.7891</v>
+        <v>14.6997</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>13.5777</v>
+        <v>14.2843</v>
       </c>
       <c r="C141" t="n">
-        <v>17.4468</v>
+        <v>16.1068</v>
       </c>
       <c r="D141" t="n">
-        <v>40.0977</v>
+        <v>40.24</v>
       </c>
       <c r="E141" t="n">
-        <v>12.5352</v>
+        <v>11.6437</v>
       </c>
       <c r="F141" t="n">
-        <v>16.1158</v>
+        <v>14.9925</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>13.8404</v>
+        <v>14.5938</v>
       </c>
       <c r="C142" t="n">
-        <v>17.7143</v>
+        <v>16.3318</v>
       </c>
       <c r="D142" t="n">
-        <v>41.2612</v>
+        <v>41.2368</v>
       </c>
       <c r="E142" t="n">
-        <v>12.6419</v>
+        <v>11.8013</v>
       </c>
       <c r="F142" t="n">
-        <v>16.3811</v>
+        <v>15.2833</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>13.9335</v>
+        <v>14.6579</v>
       </c>
       <c r="C143" t="n">
-        <v>17.8624</v>
+        <v>16.6356</v>
       </c>
       <c r="D143" t="n">
-        <v>42.2396</v>
+        <v>42.3033</v>
       </c>
       <c r="E143" t="n">
-        <v>12.8797</v>
+        <v>11.9953</v>
       </c>
       <c r="F143" t="n">
-        <v>16.7772</v>
+        <v>15.6626</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered unsuccessful looukp.xlsx
+++ b/vs-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.12249</v>
+        <v>2.93522</v>
       </c>
       <c r="C2" t="n">
-        <v>3.78421</v>
+        <v>3.61555</v>
       </c>
       <c r="D2" t="n">
-        <v>8.70107</v>
+        <v>8.218249999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2426</v>
+        <v>2.72574</v>
       </c>
       <c r="F2" t="n">
-        <v>2.16641</v>
+        <v>2.44764</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.20426</v>
+        <v>3.03487</v>
       </c>
       <c r="C3" t="n">
-        <v>3.90386</v>
+        <v>3.75166</v>
       </c>
       <c r="D3" t="n">
-        <v>8.89687</v>
+        <v>8.55965</v>
       </c>
       <c r="E3" t="n">
-        <v>2.33722</v>
+        <v>2.78027</v>
       </c>
       <c r="F3" t="n">
-        <v>2.25976</v>
+        <v>2.51004</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.37396</v>
+        <v>3.18072</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1268</v>
+        <v>3.90418</v>
       </c>
       <c r="D4" t="n">
-        <v>9.28185</v>
+        <v>9.01314</v>
       </c>
       <c r="E4" t="n">
-        <v>2.44068</v>
+        <v>2.81499</v>
       </c>
       <c r="F4" t="n">
-        <v>2.34758</v>
+        <v>2.55702</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.61988</v>
+        <v>3.46289</v>
       </c>
       <c r="C5" t="n">
-        <v>4.49899</v>
+        <v>4.23315</v>
       </c>
       <c r="D5" t="n">
-        <v>9.587199999999999</v>
+        <v>9.390779999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.97958</v>
+        <v>2.44531</v>
       </c>
       <c r="F5" t="n">
-        <v>1.89081</v>
+        <v>2.18013</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.32334</v>
+        <v>4.07193</v>
       </c>
       <c r="C6" t="n">
-        <v>5.06992</v>
+        <v>4.84795</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0981</v>
+        <v>9.788399999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1.99017</v>
+        <v>2.4594</v>
       </c>
       <c r="F6" t="n">
-        <v>1.90648</v>
+        <v>2.18683</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>5.54405</v>
+        <v>5.42396</v>
       </c>
       <c r="C7" t="n">
-        <v>6.15263</v>
+        <v>5.88415</v>
       </c>
       <c r="D7" t="n">
-        <v>7.20638</v>
+        <v>6.77324</v>
       </c>
       <c r="E7" t="n">
-        <v>2.00629</v>
+        <v>2.4719</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9272</v>
+        <v>2.2056</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>7.61474</v>
+        <v>7.51525</v>
       </c>
       <c r="C8" t="n">
-        <v>3.43264</v>
+        <v>3.21123</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5915</v>
+        <v>7.25022</v>
       </c>
       <c r="E8" t="n">
-        <v>2.02122</v>
+        <v>2.49406</v>
       </c>
       <c r="F8" t="n">
-        <v>1.93801</v>
+        <v>2.21528</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>11.1035</v>
+        <v>10.877</v>
       </c>
       <c r="C9" t="n">
-        <v>3.46731</v>
+        <v>3.2185</v>
       </c>
       <c r="D9" t="n">
-        <v>7.92991</v>
+        <v>7.57767</v>
       </c>
       <c r="E9" t="n">
-        <v>2.03356</v>
+        <v>2.48728</v>
       </c>
       <c r="F9" t="n">
-        <v>1.95638</v>
+        <v>2.21553</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.85563</v>
+        <v>2.75667</v>
       </c>
       <c r="C10" t="n">
-        <v>3.48231</v>
+        <v>3.22002</v>
       </c>
       <c r="D10" t="n">
-        <v>8.294510000000001</v>
+        <v>7.92533</v>
       </c>
       <c r="E10" t="n">
-        <v>2.05497</v>
+        <v>2.50109</v>
       </c>
       <c r="F10" t="n">
-        <v>1.98378</v>
+        <v>2.23574</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.88226</v>
+        <v>2.80298</v>
       </c>
       <c r="C11" t="n">
-        <v>3.52412</v>
+        <v>3.24894</v>
       </c>
       <c r="D11" t="n">
-        <v>8.624230000000001</v>
+        <v>8.2681</v>
       </c>
       <c r="E11" t="n">
-        <v>2.07686</v>
+        <v>2.53207</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0054</v>
+        <v>2.25553</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.92533</v>
+        <v>2.85345</v>
       </c>
       <c r="C12" t="n">
-        <v>3.55601</v>
+        <v>3.27372</v>
       </c>
       <c r="D12" t="n">
-        <v>8.969989999999999</v>
+        <v>8.60074</v>
       </c>
       <c r="E12" t="n">
-        <v>2.10023</v>
+        <v>2.55503</v>
       </c>
       <c r="F12" t="n">
-        <v>2.02813</v>
+        <v>2.27315</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.95595</v>
+        <v>2.89479</v>
       </c>
       <c r="C13" t="n">
-        <v>3.58626</v>
+        <v>3.31141</v>
       </c>
       <c r="D13" t="n">
-        <v>9.294510000000001</v>
+        <v>8.94201</v>
       </c>
       <c r="E13" t="n">
-        <v>2.10733</v>
+        <v>2.57214</v>
       </c>
       <c r="F13" t="n">
-        <v>2.04787</v>
+        <v>2.2857</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.01609</v>
+        <v>2.94698</v>
       </c>
       <c r="C14" t="n">
-        <v>3.67419</v>
+        <v>3.381</v>
       </c>
       <c r="D14" t="n">
-        <v>9.59276</v>
+        <v>9.24835</v>
       </c>
       <c r="E14" t="n">
-        <v>2.15577</v>
+        <v>2.60256</v>
       </c>
       <c r="F14" t="n">
-        <v>2.09565</v>
+        <v>2.31945</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.0842</v>
+        <v>3.00018</v>
       </c>
       <c r="C15" t="n">
-        <v>3.74799</v>
+        <v>3.46553</v>
       </c>
       <c r="D15" t="n">
-        <v>9.90433</v>
+        <v>9.57141</v>
       </c>
       <c r="E15" t="n">
-        <v>2.20851</v>
+        <v>2.63729</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1494</v>
+        <v>2.37378</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1788</v>
+        <v>3.1068</v>
       </c>
       <c r="C16" t="n">
-        <v>3.89767</v>
+        <v>3.59129</v>
       </c>
       <c r="D16" t="n">
-        <v>10.1952</v>
+        <v>9.855589999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.25194</v>
+        <v>2.68488</v>
       </c>
       <c r="F16" t="n">
-        <v>2.21291</v>
+        <v>2.41914</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.30179</v>
+        <v>3.21625</v>
       </c>
       <c r="C17" t="n">
-        <v>4.04832</v>
+        <v>3.75693</v>
       </c>
       <c r="D17" t="n">
-        <v>10.5824</v>
+        <v>10.2618</v>
       </c>
       <c r="E17" t="n">
-        <v>2.32026</v>
+        <v>2.74142</v>
       </c>
       <c r="F17" t="n">
-        <v>2.27631</v>
+        <v>2.49693</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.51767</v>
+        <v>3.49457</v>
       </c>
       <c r="C18" t="n">
-        <v>4.26929</v>
+        <v>4.04063</v>
       </c>
       <c r="D18" t="n">
-        <v>10.8755</v>
+        <v>10.6145</v>
       </c>
       <c r="E18" t="n">
-        <v>2.41058</v>
+        <v>2.83616</v>
       </c>
       <c r="F18" t="n">
-        <v>2.39329</v>
+        <v>2.59412</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.87921</v>
+        <v>3.99059</v>
       </c>
       <c r="C19" t="n">
-        <v>4.7175</v>
+        <v>4.38796</v>
       </c>
       <c r="D19" t="n">
-        <v>11.2438</v>
+        <v>10.9743</v>
       </c>
       <c r="E19" t="n">
-        <v>2.56789</v>
+        <v>2.95839</v>
       </c>
       <c r="F19" t="n">
-        <v>2.58638</v>
+        <v>2.72443</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.53912</v>
+        <v>4.79598</v>
       </c>
       <c r="C20" t="n">
-        <v>5.37732</v>
+        <v>4.94872</v>
       </c>
       <c r="D20" t="n">
-        <v>11.5035</v>
+        <v>11.2797</v>
       </c>
       <c r="E20" t="n">
-        <v>2.01192</v>
+        <v>2.47467</v>
       </c>
       <c r="F20" t="n">
-        <v>1.96254</v>
+        <v>2.21952</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.64908</v>
+        <v>6.00206</v>
       </c>
       <c r="C21" t="n">
-        <v>6.25478</v>
+        <v>5.93851</v>
       </c>
       <c r="D21" t="n">
-        <v>8.36469</v>
+        <v>8.016819999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>2.02591</v>
+        <v>2.50749</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9819</v>
+        <v>2.24477</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>7.40628</v>
+        <v>7.95005</v>
       </c>
       <c r="C22" t="n">
-        <v>3.47725</v>
+        <v>3.25587</v>
       </c>
       <c r="D22" t="n">
-        <v>8.671849999999999</v>
+        <v>8.27834</v>
       </c>
       <c r="E22" t="n">
-        <v>2.04708</v>
+        <v>2.51394</v>
       </c>
       <c r="F22" t="n">
-        <v>2.01838</v>
+        <v>2.26351</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>9.997210000000001</v>
+        <v>10.716</v>
       </c>
       <c r="C23" t="n">
-        <v>3.48276</v>
+        <v>3.24814</v>
       </c>
       <c r="D23" t="n">
-        <v>8.97627</v>
+        <v>8.57558</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0594</v>
+        <v>2.52729</v>
       </c>
       <c r="F23" t="n">
-        <v>2.05361</v>
+        <v>2.29958</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.94156</v>
+        <v>2.83622</v>
       </c>
       <c r="C24" t="n">
-        <v>3.53076</v>
+        <v>3.2663</v>
       </c>
       <c r="D24" t="n">
-        <v>9.319190000000001</v>
+        <v>8.90446</v>
       </c>
       <c r="E24" t="n">
-        <v>2.08774</v>
+        <v>2.54952</v>
       </c>
       <c r="F24" t="n">
-        <v>2.10358</v>
+        <v>2.3454</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.95024</v>
+        <v>2.85274</v>
       </c>
       <c r="C25" t="n">
-        <v>3.54979</v>
+        <v>3.31045</v>
       </c>
       <c r="D25" t="n">
-        <v>9.60595</v>
+        <v>9.18506</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1134</v>
+        <v>2.57558</v>
       </c>
       <c r="F25" t="n">
-        <v>2.15522</v>
+        <v>2.38955</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.03759</v>
+        <v>2.87915</v>
       </c>
       <c r="C26" t="n">
-        <v>3.58632</v>
+        <v>3.37672</v>
       </c>
       <c r="D26" t="n">
-        <v>9.86937</v>
+        <v>9.4779</v>
       </c>
       <c r="E26" t="n">
-        <v>2.14257</v>
+        <v>2.60102</v>
       </c>
       <c r="F26" t="n">
-        <v>2.21882</v>
+        <v>2.43772</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.0929</v>
+        <v>2.96864</v>
       </c>
       <c r="C27" t="n">
-        <v>3.61345</v>
+        <v>3.39576</v>
       </c>
       <c r="D27" t="n">
-        <v>10.2109</v>
+        <v>9.79729</v>
       </c>
       <c r="E27" t="n">
-        <v>2.17093</v>
+        <v>2.64068</v>
       </c>
       <c r="F27" t="n">
-        <v>2.26087</v>
+        <v>2.48363</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.17748</v>
+        <v>3.07399</v>
       </c>
       <c r="C28" t="n">
-        <v>3.66147</v>
+        <v>3.50069</v>
       </c>
       <c r="D28" t="n">
-        <v>10.5371</v>
+        <v>10.1477</v>
       </c>
       <c r="E28" t="n">
-        <v>2.21709</v>
+        <v>2.66905</v>
       </c>
       <c r="F28" t="n">
-        <v>2.34713</v>
+        <v>2.53045</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.2537</v>
+        <v>3.1069</v>
       </c>
       <c r="C29" t="n">
-        <v>3.77021</v>
+        <v>3.56998</v>
       </c>
       <c r="D29" t="n">
-        <v>10.8405</v>
+        <v>10.4066</v>
       </c>
       <c r="E29" t="n">
-        <v>2.26783</v>
+        <v>2.69994</v>
       </c>
       <c r="F29" t="n">
-        <v>2.42454</v>
+        <v>2.59328</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.36315</v>
+        <v>3.24266</v>
       </c>
       <c r="C30" t="n">
-        <v>3.90992</v>
+        <v>3.69031</v>
       </c>
       <c r="D30" t="n">
-        <v>11.1229</v>
+        <v>10.7115</v>
       </c>
       <c r="E30" t="n">
-        <v>2.32154</v>
+        <v>2.7499</v>
       </c>
       <c r="F30" t="n">
-        <v>2.49316</v>
+        <v>2.66007</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.56842</v>
+        <v>3.45943</v>
       </c>
       <c r="C31" t="n">
-        <v>4.0227</v>
+        <v>3.84893</v>
       </c>
       <c r="D31" t="n">
-        <v>11.4302</v>
+        <v>11.026</v>
       </c>
       <c r="E31" t="n">
-        <v>2.37829</v>
+        <v>2.81042</v>
       </c>
       <c r="F31" t="n">
-        <v>2.57318</v>
+        <v>2.75669</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.82645</v>
+        <v>3.76455</v>
       </c>
       <c r="C32" t="n">
-        <v>4.25542</v>
+        <v>4.16147</v>
       </c>
       <c r="D32" t="n">
-        <v>11.7043</v>
+        <v>11.3104</v>
       </c>
       <c r="E32" t="n">
-        <v>2.48141</v>
+        <v>2.8982</v>
       </c>
       <c r="F32" t="n">
-        <v>2.68064</v>
+        <v>2.86616</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.36729</v>
+        <v>4.25942</v>
       </c>
       <c r="C33" t="n">
-        <v>4.62206</v>
+        <v>4.59723</v>
       </c>
       <c r="D33" t="n">
-        <v>12.0498</v>
+        <v>11.6635</v>
       </c>
       <c r="E33" t="n">
-        <v>2.63724</v>
+        <v>3.05551</v>
       </c>
       <c r="F33" t="n">
-        <v>2.84863</v>
+        <v>3.01609</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.07451</v>
+        <v>4.9527</v>
       </c>
       <c r="C34" t="n">
-        <v>5.21456</v>
+        <v>5.18841</v>
       </c>
       <c r="D34" t="n">
-        <v>12.3332</v>
+        <v>12.0278</v>
       </c>
       <c r="E34" t="n">
-        <v>2.04736</v>
+        <v>2.50767</v>
       </c>
       <c r="F34" t="n">
-        <v>2.15904</v>
+        <v>2.42086</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>6.1202</v>
+        <v>5.98983</v>
       </c>
       <c r="C35" t="n">
-        <v>6.09889</v>
+        <v>6.06075</v>
       </c>
       <c r="D35" t="n">
-        <v>8.788629999999999</v>
+        <v>8.366400000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>2.065</v>
+        <v>2.52651</v>
       </c>
       <c r="F35" t="n">
-        <v>2.19289</v>
+        <v>2.44076</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>7.98614</v>
+        <v>7.44913</v>
       </c>
       <c r="C36" t="n">
-        <v>7.36367</v>
+        <v>7.53119</v>
       </c>
       <c r="D36" t="n">
-        <v>9.093489999999999</v>
+        <v>8.645379999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>2.07902</v>
+        <v>2.53896</v>
       </c>
       <c r="F36" t="n">
-        <v>2.23075</v>
+        <v>2.47147</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>10.5656</v>
+        <v>9.777570000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>3.50319</v>
+        <v>3.32662</v>
       </c>
       <c r="D37" t="n">
-        <v>9.366820000000001</v>
+        <v>8.961779999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>2.10423</v>
+        <v>2.55969</v>
       </c>
       <c r="F37" t="n">
-        <v>2.25412</v>
+        <v>2.47936</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.99415</v>
+        <v>2.86447</v>
       </c>
       <c r="C38" t="n">
-        <v>3.533</v>
+        <v>3.36205</v>
       </c>
       <c r="D38" t="n">
-        <v>9.69924</v>
+        <v>9.282159999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>2.12632</v>
+        <v>2.57587</v>
       </c>
       <c r="F38" t="n">
-        <v>2.28857</v>
+        <v>2.51037</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.00911</v>
+        <v>2.94743</v>
       </c>
       <c r="C39" t="n">
-        <v>3.5764</v>
+        <v>3.36627</v>
       </c>
       <c r="D39" t="n">
-        <v>10.0426</v>
+        <v>9.61312</v>
       </c>
       <c r="E39" t="n">
-        <v>2.15972</v>
+        <v>2.5973</v>
       </c>
       <c r="F39" t="n">
-        <v>2.34517</v>
+        <v>2.53771</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.08971</v>
+        <v>2.98851</v>
       </c>
       <c r="C40" t="n">
-        <v>3.59354</v>
+        <v>3.40263</v>
       </c>
       <c r="D40" t="n">
-        <v>10.3502</v>
+        <v>9.91001</v>
       </c>
       <c r="E40" t="n">
-        <v>2.17989</v>
+        <v>2.62385</v>
       </c>
       <c r="F40" t="n">
-        <v>2.36928</v>
+        <v>2.57144</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.11718</v>
+        <v>3.03728</v>
       </c>
       <c r="C41" t="n">
-        <v>3.63851</v>
+        <v>3.44823</v>
       </c>
       <c r="D41" t="n">
-        <v>10.6432</v>
+        <v>10.2247</v>
       </c>
       <c r="E41" t="n">
-        <v>2.2126</v>
+        <v>2.63414</v>
       </c>
       <c r="F41" t="n">
-        <v>2.40064</v>
+        <v>2.59297</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.20996</v>
+        <v>3.11968</v>
       </c>
       <c r="C42" t="n">
-        <v>3.68292</v>
+        <v>3.50404</v>
       </c>
       <c r="D42" t="n">
-        <v>10.9855</v>
+        <v>10.5287</v>
       </c>
       <c r="E42" t="n">
-        <v>2.25308</v>
+        <v>2.6721</v>
       </c>
       <c r="F42" t="n">
-        <v>2.4562</v>
+        <v>2.62452</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.2845</v>
+        <v>3.17143</v>
       </c>
       <c r="C43" t="n">
-        <v>3.75306</v>
+        <v>3.58945</v>
       </c>
       <c r="D43" t="n">
-        <v>11.261</v>
+        <v>10.8134</v>
       </c>
       <c r="E43" t="n">
-        <v>2.29281</v>
+        <v>2.70872</v>
       </c>
       <c r="F43" t="n">
-        <v>2.51998</v>
+        <v>2.67623</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.39944</v>
+        <v>3.37033</v>
       </c>
       <c r="C44" t="n">
-        <v>3.84498</v>
+        <v>3.72009</v>
       </c>
       <c r="D44" t="n">
-        <v>11.5464</v>
+        <v>11.129</v>
       </c>
       <c r="E44" t="n">
-        <v>2.35212</v>
+        <v>2.74632</v>
       </c>
       <c r="F44" t="n">
-        <v>2.58606</v>
+        <v>2.72162</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.57916</v>
+        <v>3.58477</v>
       </c>
       <c r="C45" t="n">
-        <v>4.04668</v>
+        <v>3.88671</v>
       </c>
       <c r="D45" t="n">
-        <v>11.8479</v>
+        <v>11.3756</v>
       </c>
       <c r="E45" t="n">
-        <v>2.42716</v>
+        <v>2.81049</v>
       </c>
       <c r="F45" t="n">
-        <v>2.6778</v>
+        <v>2.80207</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>3.85885</v>
+        <v>3.82824</v>
       </c>
       <c r="C46" t="n">
-        <v>4.2791</v>
+        <v>4.08744</v>
       </c>
       <c r="D46" t="n">
-        <v>12.1121</v>
+        <v>11.727</v>
       </c>
       <c r="E46" t="n">
-        <v>2.52718</v>
+        <v>2.89863</v>
       </c>
       <c r="F46" t="n">
-        <v>2.78868</v>
+        <v>2.89148</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.2627</v>
+        <v>4.22728</v>
       </c>
       <c r="C47" t="n">
-        <v>4.60446</v>
+        <v>4.48474</v>
       </c>
       <c r="D47" t="n">
-        <v>12.4497</v>
+        <v>12.0285</v>
       </c>
       <c r="E47" t="n">
-        <v>2.68817</v>
+        <v>3.02439</v>
       </c>
       <c r="F47" t="n">
-        <v>2.94192</v>
+        <v>3.03952</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.91148</v>
+        <v>4.89</v>
       </c>
       <c r="C48" t="n">
-        <v>5.14858</v>
+        <v>4.99324</v>
       </c>
       <c r="D48" t="n">
-        <v>12.751</v>
+        <v>12.306</v>
       </c>
       <c r="E48" t="n">
-        <v>2.08185</v>
+        <v>2.50551</v>
       </c>
       <c r="F48" t="n">
-        <v>2.22856</v>
+        <v>2.41866</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.83176</v>
+        <v>5.84391</v>
       </c>
       <c r="C49" t="n">
-        <v>5.92155</v>
+        <v>5.80157</v>
       </c>
       <c r="D49" t="n">
-        <v>13.0042</v>
+        <v>12.7439</v>
       </c>
       <c r="E49" t="n">
-        <v>2.09194</v>
+        <v>2.51879</v>
       </c>
       <c r="F49" t="n">
-        <v>2.27185</v>
+        <v>2.44301</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>7.29556</v>
+        <v>7.29541</v>
       </c>
       <c r="C50" t="n">
-        <v>7.09115</v>
+        <v>7.04008</v>
       </c>
       <c r="D50" t="n">
-        <v>9.237830000000001</v>
+        <v>8.797129999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>2.11504</v>
+        <v>2.54495</v>
       </c>
       <c r="F50" t="n">
-        <v>2.28732</v>
+        <v>2.47612</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>9.36238</v>
+        <v>9.488860000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>3.51937</v>
+        <v>3.34724</v>
       </c>
       <c r="D51" t="n">
-        <v>9.520960000000001</v>
+        <v>9.11603</v>
       </c>
       <c r="E51" t="n">
-        <v>2.13297</v>
+        <v>2.5662</v>
       </c>
       <c r="F51" t="n">
-        <v>2.30781</v>
+        <v>2.50053</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.7421</v>
+        <v>12.7655</v>
       </c>
       <c r="C52" t="n">
-        <v>3.53059</v>
+        <v>3.36786</v>
       </c>
       <c r="D52" t="n">
-        <v>9.88556</v>
+        <v>9.44659</v>
       </c>
       <c r="E52" t="n">
-        <v>2.15674</v>
+        <v>2.58076</v>
       </c>
       <c r="F52" t="n">
-        <v>2.35571</v>
+        <v>2.5303</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.01744</v>
+        <v>2.94217</v>
       </c>
       <c r="C53" t="n">
-        <v>3.5641</v>
+        <v>3.39545</v>
       </c>
       <c r="D53" t="n">
-        <v>10.1993</v>
+        <v>9.780150000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>2.17812</v>
+        <v>2.60246</v>
       </c>
       <c r="F53" t="n">
-        <v>2.39656</v>
+        <v>2.55974</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.08452</v>
+        <v>2.97754</v>
       </c>
       <c r="C54" t="n">
-        <v>3.59382</v>
+        <v>3.41856</v>
       </c>
       <c r="D54" t="n">
-        <v>10.5664</v>
+        <v>10.0912</v>
       </c>
       <c r="E54" t="n">
-        <v>2.19749</v>
+        <v>2.63222</v>
       </c>
       <c r="F54" t="n">
-        <v>2.41635</v>
+        <v>2.59826</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.13187</v>
+        <v>3.03615</v>
       </c>
       <c r="C55" t="n">
-        <v>3.63173</v>
+        <v>3.46957</v>
       </c>
       <c r="D55" t="n">
-        <v>10.8697</v>
+        <v>10.4018</v>
       </c>
       <c r="E55" t="n">
-        <v>2.23253</v>
+        <v>2.66099</v>
       </c>
       <c r="F55" t="n">
-        <v>2.48441</v>
+        <v>2.63979</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.19739</v>
+        <v>3.11141</v>
       </c>
       <c r="C56" t="n">
-        <v>3.68242</v>
+        <v>3.52383</v>
       </c>
       <c r="D56" t="n">
-        <v>11.1988</v>
+        <v>10.6803</v>
       </c>
       <c r="E56" t="n">
-        <v>2.27433</v>
+        <v>2.68606</v>
       </c>
       <c r="F56" t="n">
-        <v>2.5612</v>
+        <v>2.6754</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.28452</v>
+        <v>3.2241</v>
       </c>
       <c r="C57" t="n">
-        <v>3.75545</v>
+        <v>3.58899</v>
       </c>
       <c r="D57" t="n">
-        <v>11.5136</v>
+        <v>10.9733</v>
       </c>
       <c r="E57" t="n">
-        <v>2.32147</v>
+        <v>2.73837</v>
       </c>
       <c r="F57" t="n">
-        <v>2.62018</v>
+        <v>2.72978</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.41373</v>
+        <v>3.34075</v>
       </c>
       <c r="C58" t="n">
-        <v>3.86176</v>
+        <v>3.68586</v>
       </c>
       <c r="D58" t="n">
-        <v>11.8131</v>
+        <v>11.2618</v>
       </c>
       <c r="E58" t="n">
-        <v>2.36434</v>
+        <v>2.78573</v>
       </c>
       <c r="F58" t="n">
-        <v>2.68558</v>
+        <v>2.7898</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.57139</v>
+        <v>3.54201</v>
       </c>
       <c r="C59" t="n">
-        <v>4.00006</v>
+        <v>3.87217</v>
       </c>
       <c r="D59" t="n">
-        <v>12.1027</v>
+        <v>11.6107</v>
       </c>
       <c r="E59" t="n">
-        <v>2.44642</v>
+        <v>2.84918</v>
       </c>
       <c r="F59" t="n">
-        <v>2.78045</v>
+        <v>2.88144</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>3.85803</v>
+        <v>3.76841</v>
       </c>
       <c r="C60" t="n">
-        <v>4.21862</v>
+        <v>4.09252</v>
       </c>
       <c r="D60" t="n">
-        <v>12.4028</v>
+        <v>11.9022</v>
       </c>
       <c r="E60" t="n">
-        <v>2.54784</v>
+        <v>2.9411</v>
       </c>
       <c r="F60" t="n">
-        <v>2.89833</v>
+        <v>2.97804</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.23225</v>
+        <v>4.16593</v>
       </c>
       <c r="C61" t="n">
-        <v>4.54057</v>
+        <v>4.38767</v>
       </c>
       <c r="D61" t="n">
-        <v>12.6827</v>
+        <v>12.2055</v>
       </c>
       <c r="E61" t="n">
-        <v>2.67963</v>
+        <v>3.062</v>
       </c>
       <c r="F61" t="n">
-        <v>3.04938</v>
+        <v>3.12758</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.72607</v>
+        <v>4.70603</v>
       </c>
       <c r="C62" t="n">
-        <v>5.0027</v>
+        <v>4.94631</v>
       </c>
       <c r="D62" t="n">
-        <v>13.021</v>
+        <v>12.5967</v>
       </c>
       <c r="E62" t="n">
-        <v>2.91102</v>
+        <v>3.26796</v>
       </c>
       <c r="F62" t="n">
-        <v>3.2828</v>
+        <v>3.34873</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.54147</v>
+        <v>5.56142</v>
       </c>
       <c r="C63" t="n">
-        <v>5.73686</v>
+        <v>5.71994</v>
       </c>
       <c r="D63" t="n">
-        <v>13.3968</v>
+        <v>12.9769</v>
       </c>
       <c r="E63" t="n">
-        <v>2.42636</v>
+        <v>2.77994</v>
       </c>
       <c r="F63" t="n">
-        <v>2.68212</v>
+        <v>2.72615</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.74955</v>
+        <v>6.84605</v>
       </c>
       <c r="C64" t="n">
-        <v>6.84707</v>
+        <v>6.84532</v>
       </c>
       <c r="D64" t="n">
-        <v>9.54429</v>
+        <v>9.07291</v>
       </c>
       <c r="E64" t="n">
-        <v>2.45467</v>
+        <v>2.79793</v>
       </c>
       <c r="F64" t="n">
-        <v>2.73362</v>
+        <v>2.77046</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>8.78232</v>
+        <v>8.7174</v>
       </c>
       <c r="C65" t="n">
-        <v>3.84451</v>
+        <v>3.84836</v>
       </c>
       <c r="D65" t="n">
-        <v>9.857659999999999</v>
+        <v>9.51323</v>
       </c>
       <c r="E65" t="n">
-        <v>2.47487</v>
+        <v>2.81877</v>
       </c>
       <c r="F65" t="n">
-        <v>2.76145</v>
+        <v>2.80823</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>11.6628</v>
+        <v>11.6372</v>
       </c>
       <c r="C66" t="n">
-        <v>3.86019</v>
+        <v>3.88976</v>
       </c>
       <c r="D66" t="n">
-        <v>10.5034</v>
+        <v>9.88644</v>
       </c>
       <c r="E66" t="n">
-        <v>2.48656</v>
+        <v>2.84458</v>
       </c>
       <c r="F66" t="n">
-        <v>2.80328</v>
+        <v>2.85009</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.29089</v>
+        <v>3.34073</v>
       </c>
       <c r="C67" t="n">
-        <v>3.89105</v>
+        <v>3.87168</v>
       </c>
       <c r="D67" t="n">
-        <v>10.7506</v>
+        <v>10.3059</v>
       </c>
       <c r="E67" t="n">
-        <v>2.5102</v>
+        <v>2.86564</v>
       </c>
       <c r="F67" t="n">
-        <v>2.85309</v>
+        <v>2.90234</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.36078</v>
+        <v>3.39855</v>
       </c>
       <c r="C68" t="n">
-        <v>3.91685</v>
+        <v>3.94545</v>
       </c>
       <c r="D68" t="n">
-        <v>11.2708</v>
+        <v>10.5525</v>
       </c>
       <c r="E68" t="n">
-        <v>2.53131</v>
+        <v>2.88661</v>
       </c>
       <c r="F68" t="n">
-        <v>2.88477</v>
+        <v>2.95977</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.40607</v>
+        <v>3.45888</v>
       </c>
       <c r="C69" t="n">
-        <v>3.98179</v>
+        <v>3.96971</v>
       </c>
       <c r="D69" t="n">
-        <v>12.0122</v>
+        <v>11.2538</v>
       </c>
       <c r="E69" t="n">
-        <v>2.56832</v>
+        <v>2.92683</v>
       </c>
       <c r="F69" t="n">
-        <v>2.94383</v>
+        <v>3.01119</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.51016</v>
+        <v>3.52289</v>
       </c>
       <c r="C70" t="n">
-        <v>4.02475</v>
+        <v>4.00119</v>
       </c>
       <c r="D70" t="n">
-        <v>12.555</v>
+        <v>11.7993</v>
       </c>
       <c r="E70" t="n">
-        <v>2.60069</v>
+        <v>2.95854</v>
       </c>
       <c r="F70" t="n">
-        <v>2.98117</v>
+        <v>3.05212</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.59707</v>
+        <v>3.6031</v>
       </c>
       <c r="C71" t="n">
-        <v>4.14765</v>
+        <v>4.07621</v>
       </c>
       <c r="D71" t="n">
-        <v>13.1291</v>
+        <v>12.3729</v>
       </c>
       <c r="E71" t="n">
-        <v>2.64018</v>
+        <v>2.99223</v>
       </c>
       <c r="F71" t="n">
-        <v>3.07832</v>
+        <v>3.13838</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>3.72075</v>
+        <v>3.73983</v>
       </c>
       <c r="C72" t="n">
-        <v>4.17674</v>
+        <v>4.14023</v>
       </c>
       <c r="D72" t="n">
-        <v>14.0787</v>
+        <v>13.3375</v>
       </c>
       <c r="E72" t="n">
-        <v>2.70316</v>
+        <v>3.04063</v>
       </c>
       <c r="F72" t="n">
-        <v>3.14449</v>
+        <v>3.23665</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>3.90719</v>
+        <v>3.89135</v>
       </c>
       <c r="C73" t="n">
-        <v>4.36165</v>
+        <v>4.29625</v>
       </c>
       <c r="D73" t="n">
-        <v>14.7305</v>
+        <v>14.2467</v>
       </c>
       <c r="E73" t="n">
-        <v>2.76348</v>
+        <v>3.10436</v>
       </c>
       <c r="F73" t="n">
-        <v>3.26397</v>
+        <v>3.32249</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.11785</v>
+        <v>4.12027</v>
       </c>
       <c r="C74" t="n">
-        <v>4.53364</v>
+        <v>4.52992</v>
       </c>
       <c r="D74" t="n">
-        <v>13.8758</v>
+        <v>14.7673</v>
       </c>
       <c r="E74" t="n">
-        <v>2.87922</v>
+        <v>3.17013</v>
       </c>
       <c r="F74" t="n">
-        <v>3.40523</v>
+        <v>3.46558</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.49149</v>
+        <v>4.47035</v>
       </c>
       <c r="C75" t="n">
-        <v>4.8524</v>
+        <v>4.84606</v>
       </c>
       <c r="D75" t="n">
-        <v>14.8334</v>
+        <v>15.5161</v>
       </c>
       <c r="E75" t="n">
-        <v>3.0105</v>
+        <v>3.3089</v>
       </c>
       <c r="F75" t="n">
-        <v>3.54418</v>
+        <v>3.61192</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.00681</v>
+        <v>4.95332</v>
       </c>
       <c r="C76" t="n">
-        <v>5.30395</v>
+        <v>5.26464</v>
       </c>
       <c r="D76" t="n">
-        <v>16.15</v>
+        <v>16.601</v>
       </c>
       <c r="E76" t="n">
-        <v>3.20246</v>
+        <v>3.49614</v>
       </c>
       <c r="F76" t="n">
-        <v>3.79614</v>
+        <v>3.84623</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.74025</v>
+        <v>5.6503</v>
       </c>
       <c r="C77" t="n">
-        <v>5.98711</v>
+        <v>5.95015</v>
       </c>
       <c r="D77" t="n">
-        <v>17.2436</v>
+        <v>17.5947</v>
       </c>
       <c r="E77" t="n">
-        <v>2.66037</v>
+        <v>2.9912</v>
       </c>
       <c r="F77" t="n">
-        <v>3.11043</v>
+        <v>3.12858</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.78903</v>
+        <v>6.79264</v>
       </c>
       <c r="C78" t="n">
-        <v>7.04449</v>
+        <v>7.01726</v>
       </c>
       <c r="D78" t="n">
-        <v>15.5922</v>
+        <v>15.3306</v>
       </c>
       <c r="E78" t="n">
-        <v>2.70173</v>
+        <v>3.01186</v>
       </c>
       <c r="F78" t="n">
-        <v>3.15359</v>
+        <v>3.17888</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>8.51735</v>
+        <v>8.47824</v>
       </c>
       <c r="C79" t="n">
-        <v>4.20084</v>
+        <v>4.15818</v>
       </c>
       <c r="D79" t="n">
-        <v>16.5554</v>
+        <v>16.3994</v>
       </c>
       <c r="E79" t="n">
-        <v>2.72292</v>
+        <v>3.03117</v>
       </c>
       <c r="F79" t="n">
-        <v>3.21694</v>
+        <v>3.22335</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>11.2561</v>
+        <v>11.1732</v>
       </c>
       <c r="C80" t="n">
-        <v>4.22409</v>
+        <v>4.19234</v>
       </c>
       <c r="D80" t="n">
-        <v>17.75</v>
+        <v>17.4981</v>
       </c>
       <c r="E80" t="n">
-        <v>2.73733</v>
+        <v>3.04845</v>
       </c>
       <c r="F80" t="n">
-        <v>3.26174</v>
+        <v>3.2752</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>3.8825</v>
+        <v>3.91506</v>
       </c>
       <c r="C81" t="n">
-        <v>4.22399</v>
+        <v>4.26363</v>
       </c>
       <c r="D81" t="n">
-        <v>18.6915</v>
+        <v>18.5556</v>
       </c>
       <c r="E81" t="n">
-        <v>2.76534</v>
+        <v>3.07424</v>
       </c>
       <c r="F81" t="n">
-        <v>3.31471</v>
+        <v>3.32015</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>3.93845</v>
+        <v>3.97888</v>
       </c>
       <c r="C82" t="n">
-        <v>4.25989</v>
+        <v>4.25857</v>
       </c>
       <c r="D82" t="n">
-        <v>19.7274</v>
+        <v>19.6141</v>
       </c>
       <c r="E82" t="n">
-        <v>2.79035</v>
+        <v>3.09726</v>
       </c>
       <c r="F82" t="n">
-        <v>3.3559</v>
+        <v>3.38307</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>3.99904</v>
+        <v>4.05558</v>
       </c>
       <c r="C83" t="n">
-        <v>4.30429</v>
+        <v>4.3164</v>
       </c>
       <c r="D83" t="n">
-        <v>20.9787</v>
+        <v>20.7704</v>
       </c>
       <c r="E83" t="n">
-        <v>2.81052</v>
+        <v>3.1272</v>
       </c>
       <c r="F83" t="n">
-        <v>3.39993</v>
+        <v>3.43975</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.08742</v>
+        <v>4.12296</v>
       </c>
       <c r="C84" t="n">
-        <v>4.36905</v>
+        <v>4.38324</v>
       </c>
       <c r="D84" t="n">
-        <v>22.0089</v>
+        <v>21.8796</v>
       </c>
       <c r="E84" t="n">
-        <v>2.85542</v>
+        <v>3.16823</v>
       </c>
       <c r="F84" t="n">
-        <v>3.47587</v>
+        <v>3.50416</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.17972</v>
+        <v>4.22732</v>
       </c>
       <c r="C85" t="n">
-        <v>4.45039</v>
+        <v>4.43392</v>
       </c>
       <c r="D85" t="n">
-        <v>23.2048</v>
+        <v>22.9662</v>
       </c>
       <c r="E85" t="n">
-        <v>2.89542</v>
+        <v>3.21082</v>
       </c>
       <c r="F85" t="n">
-        <v>3.54528</v>
+        <v>3.56979</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>4.31632</v>
+        <v>4.33243</v>
       </c>
       <c r="C86" t="n">
-        <v>4.56241</v>
+        <v>4.54408</v>
       </c>
       <c r="D86" t="n">
-        <v>24.1968</v>
+        <v>24.0632</v>
       </c>
       <c r="E86" t="n">
-        <v>2.94596</v>
+        <v>3.25371</v>
       </c>
       <c r="F86" t="n">
-        <v>3.6495</v>
+        <v>3.67755</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>4.46734</v>
+        <v>4.49623</v>
       </c>
       <c r="C87" t="n">
-        <v>4.7107</v>
+        <v>4.67717</v>
       </c>
       <c r="D87" t="n">
-        <v>25.4819</v>
+        <v>25.3273</v>
       </c>
       <c r="E87" t="n">
-        <v>3.02536</v>
+        <v>3.32614</v>
       </c>
       <c r="F87" t="n">
-        <v>3.79263</v>
+        <v>3.80586</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>4.71724</v>
+        <v>4.72816</v>
       </c>
       <c r="C88" t="n">
-        <v>4.96693</v>
+        <v>4.90146</v>
       </c>
       <c r="D88" t="n">
-        <v>26.6944</v>
+        <v>26.4845</v>
       </c>
       <c r="E88" t="n">
-        <v>3.12814</v>
+        <v>3.41094</v>
       </c>
       <c r="F88" t="n">
-        <v>3.98984</v>
+        <v>4.00458</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>5.06107</v>
+        <v>5.0458</v>
       </c>
       <c r="C89" t="n">
-        <v>5.3715</v>
+        <v>5.32428</v>
       </c>
       <c r="D89" t="n">
-        <v>27.9183</v>
+        <v>27.8292</v>
       </c>
       <c r="E89" t="n">
-        <v>3.3069</v>
+        <v>3.5168</v>
       </c>
       <c r="F89" t="n">
-        <v>4.30037</v>
+        <v>4.35115</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>5.55962</v>
+        <v>5.53914</v>
       </c>
       <c r="C90" t="n">
-        <v>5.95211</v>
+        <v>5.85518</v>
       </c>
       <c r="D90" t="n">
-        <v>29.2467</v>
+        <v>29.041</v>
       </c>
       <c r="E90" t="n">
-        <v>3.55436</v>
+        <v>3.73528</v>
       </c>
       <c r="F90" t="n">
-        <v>4.89013</v>
+        <v>4.85884</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>6.37316</v>
+        <v>6.34779</v>
       </c>
       <c r="C91" t="n">
-        <v>6.76504</v>
+        <v>6.721</v>
       </c>
       <c r="D91" t="n">
-        <v>30.5853</v>
+        <v>30.4228</v>
       </c>
       <c r="E91" t="n">
-        <v>2.87479</v>
+        <v>3.15276</v>
       </c>
       <c r="F91" t="n">
-        <v>3.48623</v>
+        <v>3.5103</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>7.53128</v>
+        <v>7.64335</v>
       </c>
       <c r="C92" t="n">
-        <v>7.98293</v>
+        <v>7.9791</v>
       </c>
       <c r="D92" t="n">
-        <v>24.7561</v>
+        <v>24.7097</v>
       </c>
       <c r="E92" t="n">
-        <v>2.89513</v>
+        <v>3.19581</v>
       </c>
       <c r="F92" t="n">
-        <v>3.60591</v>
+        <v>3.62544</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>9.59765</v>
+        <v>9.597379999999999</v>
       </c>
       <c r="C93" t="n">
-        <v>9.64263</v>
+        <v>9.60046</v>
       </c>
       <c r="D93" t="n">
-        <v>25.6289</v>
+        <v>25.6238</v>
       </c>
       <c r="E93" t="n">
-        <v>2.95913</v>
+        <v>3.23952</v>
       </c>
       <c r="F93" t="n">
-        <v>3.84398</v>
+        <v>3.79376</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>12.629</v>
+        <v>12.5521</v>
       </c>
       <c r="C94" t="n">
-        <v>4.81087</v>
+        <v>4.84149</v>
       </c>
       <c r="D94" t="n">
-        <v>26.4668</v>
+        <v>26.4303</v>
       </c>
       <c r="E94" t="n">
-        <v>3.02563</v>
+        <v>3.28714</v>
       </c>
       <c r="F94" t="n">
-        <v>4.06818</v>
+        <v>4.07048</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>4.58597</v>
+        <v>4.62102</v>
       </c>
       <c r="C95" t="n">
-        <v>5.06145</v>
+        <v>5.04083</v>
       </c>
       <c r="D95" t="n">
-        <v>27.4085</v>
+        <v>27.4059</v>
       </c>
       <c r="E95" t="n">
-        <v>3.14995</v>
+        <v>3.39464</v>
       </c>
       <c r="F95" t="n">
-        <v>4.46749</v>
+        <v>4.40381</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>4.92915</v>
+        <v>4.91128</v>
       </c>
       <c r="C96" t="n">
-        <v>5.30305</v>
+        <v>5.30806</v>
       </c>
       <c r="D96" t="n">
-        <v>28.308</v>
+        <v>28.3012</v>
       </c>
       <c r="E96" t="n">
-        <v>3.29391</v>
+        <v>3.51476</v>
       </c>
       <c r="F96" t="n">
-        <v>4.85517</v>
+        <v>4.86086</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>5.27134</v>
+        <v>5.33069</v>
       </c>
       <c r="C97" t="n">
-        <v>5.54148</v>
+        <v>5.51378</v>
       </c>
       <c r="D97" t="n">
-        <v>29.4264</v>
+        <v>29.184</v>
       </c>
       <c r="E97" t="n">
-        <v>3.52758</v>
+        <v>3.63382</v>
       </c>
       <c r="F97" t="n">
-        <v>5.3355</v>
+        <v>5.30882</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>5.75425</v>
+        <v>5.78405</v>
       </c>
       <c r="C98" t="n">
-        <v>5.80625</v>
+        <v>5.81449</v>
       </c>
       <c r="D98" t="n">
-        <v>30.3887</v>
+        <v>30.1519</v>
       </c>
       <c r="E98" t="n">
-        <v>3.8112</v>
+        <v>3.89976</v>
       </c>
       <c r="F98" t="n">
-        <v>5.86072</v>
+        <v>5.92424</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>6.23174</v>
+        <v>6.29387</v>
       </c>
       <c r="C99" t="n">
-        <v>6.04604</v>
+        <v>6.04171</v>
       </c>
       <c r="D99" t="n">
-        <v>31.406</v>
+        <v>31.3823</v>
       </c>
       <c r="E99" t="n">
-        <v>4.10552</v>
+        <v>4.14579</v>
       </c>
       <c r="F99" t="n">
-        <v>6.43867</v>
+        <v>6.57817</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>6.83958</v>
+        <v>6.78251</v>
       </c>
       <c r="C100" t="n">
-        <v>6.36192</v>
+        <v>6.33298</v>
       </c>
       <c r="D100" t="n">
-        <v>32.5084</v>
+        <v>32.4394</v>
       </c>
       <c r="E100" t="n">
-        <v>4.40664</v>
+        <v>4.44277</v>
       </c>
       <c r="F100" t="n">
-        <v>7.01211</v>
+        <v>7.10146</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.37195</v>
+        <v>7.34994</v>
       </c>
       <c r="C101" t="n">
-        <v>6.65117</v>
+        <v>6.63788</v>
       </c>
       <c r="D101" t="n">
-        <v>33.544</v>
+        <v>33.5492</v>
       </c>
       <c r="E101" t="n">
-        <v>4.69779</v>
+        <v>4.80784</v>
       </c>
       <c r="F101" t="n">
-        <v>7.49502</v>
+        <v>7.60214</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.91305</v>
+        <v>7.8519</v>
       </c>
       <c r="C102" t="n">
-        <v>6.97878</v>
+        <v>6.97643</v>
       </c>
       <c r="D102" t="n">
-        <v>34.6916</v>
+        <v>34.7467</v>
       </c>
       <c r="E102" t="n">
-        <v>4.99403</v>
+        <v>5.09264</v>
       </c>
       <c r="F102" t="n">
-        <v>7.98215</v>
+        <v>8.073040000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.52891</v>
+        <v>8.47748</v>
       </c>
       <c r="C103" t="n">
-        <v>7.46325</v>
+        <v>7.39541</v>
       </c>
       <c r="D103" t="n">
-        <v>35.9439</v>
+        <v>36.0094</v>
       </c>
       <c r="E103" t="n">
-        <v>5.2433</v>
+        <v>5.43095</v>
       </c>
       <c r="F103" t="n">
-        <v>8.49367</v>
+        <v>8.494429999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.2273</v>
+        <v>9.19272</v>
       </c>
       <c r="C104" t="n">
-        <v>8.00116</v>
+        <v>7.94729</v>
       </c>
       <c r="D104" t="n">
-        <v>37.2424</v>
+        <v>37.2821</v>
       </c>
       <c r="E104" t="n">
-        <v>5.57596</v>
+        <v>5.79704</v>
       </c>
       <c r="F104" t="n">
-        <v>8.94514</v>
+        <v>9.05542</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>9.99959</v>
+        <v>9.963710000000001</v>
       </c>
       <c r="C105" t="n">
-        <v>8.82761</v>
+        <v>8.7356</v>
       </c>
       <c r="D105" t="n">
-        <v>38.5409</v>
+        <v>38.5699</v>
       </c>
       <c r="E105" t="n">
-        <v>4.3059</v>
+        <v>4.56444</v>
       </c>
       <c r="F105" t="n">
-        <v>6.33493</v>
+        <v>6.34252</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>11.1124</v>
+        <v>11.0445</v>
       </c>
       <c r="C106" t="n">
-        <v>9.914</v>
+        <v>9.86088</v>
       </c>
       <c r="D106" t="n">
-        <v>39.8892</v>
+        <v>39.9193</v>
       </c>
       <c r="E106" t="n">
-        <v>4.44065</v>
+        <v>4.71295</v>
       </c>
       <c r="F106" t="n">
-        <v>6.55256</v>
+        <v>6.57793</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>12.685</v>
+        <v>12.6315</v>
       </c>
       <c r="C107" t="n">
-        <v>11.4501</v>
+        <v>11.4267</v>
       </c>
       <c r="D107" t="n">
-        <v>30.3104</v>
+        <v>30.4124</v>
       </c>
       <c r="E107" t="n">
-        <v>4.59464</v>
+        <v>4.85487</v>
       </c>
       <c r="F107" t="n">
-        <v>6.824</v>
+        <v>6.81079</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>15.094</v>
+        <v>15.0032</v>
       </c>
       <c r="C108" t="n">
-        <v>6.40378</v>
+        <v>6.35112</v>
       </c>
       <c r="D108" t="n">
-        <v>31.3238</v>
+        <v>31.3332</v>
       </c>
       <c r="E108" t="n">
-        <v>4.72713</v>
+        <v>5.01046</v>
       </c>
       <c r="F108" t="n">
-        <v>7.02658</v>
+        <v>7.02608</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>19.0003</v>
+        <v>18.6775</v>
       </c>
       <c r="C109" t="n">
-        <v>6.52988</v>
+        <v>6.48047</v>
       </c>
       <c r="D109" t="n">
-        <v>32.2632</v>
+        <v>32.0528</v>
       </c>
       <c r="E109" t="n">
-        <v>4.84421</v>
+        <v>5.12585</v>
       </c>
       <c r="F109" t="n">
-        <v>7.25439</v>
+        <v>7.25639</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.5947</v>
+        <v>7.58873</v>
       </c>
       <c r="C110" t="n">
-        <v>6.66606</v>
+        <v>6.62307</v>
       </c>
       <c r="D110" t="n">
-        <v>33.1053</v>
+        <v>33.1818</v>
       </c>
       <c r="E110" t="n">
-        <v>4.96464</v>
+        <v>5.2558</v>
       </c>
       <c r="F110" t="n">
-        <v>7.49672</v>
+        <v>7.49522</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.8351</v>
+        <v>7.84687</v>
       </c>
       <c r="C111" t="n">
-        <v>6.80621</v>
+        <v>6.77766</v>
       </c>
       <c r="D111" t="n">
-        <v>34.0429</v>
+        <v>33.9625</v>
       </c>
       <c r="E111" t="n">
-        <v>5.11097</v>
+        <v>5.38411</v>
       </c>
       <c r="F111" t="n">
-        <v>7.71566</v>
+        <v>7.7475</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.091419999999999</v>
+        <v>8.069089999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>6.98013</v>
+        <v>6.94162</v>
       </c>
       <c r="D112" t="n">
-        <v>34.9559</v>
+        <v>34.884</v>
       </c>
       <c r="E112" t="n">
-        <v>5.25843</v>
+        <v>5.54261</v>
       </c>
       <c r="F112" t="n">
-        <v>7.98296</v>
+        <v>7.98971</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.295030000000001</v>
+        <v>8.345050000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>7.16943</v>
+        <v>7.13089</v>
       </c>
       <c r="D113" t="n">
-        <v>36.0448</v>
+        <v>35.868</v>
       </c>
       <c r="E113" t="n">
-        <v>5.39259</v>
+        <v>5.69261</v>
       </c>
       <c r="F113" t="n">
-        <v>8.20889</v>
+        <v>8.279719999999999</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.559850000000001</v>
+        <v>8.593360000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>7.38639</v>
+        <v>7.3539</v>
       </c>
       <c r="D114" t="n">
-        <v>37.0958</v>
+        <v>37.0931</v>
       </c>
       <c r="E114" t="n">
-        <v>5.55727</v>
+        <v>5.8674</v>
       </c>
       <c r="F114" t="n">
-        <v>8.490360000000001</v>
+        <v>8.55256</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>8.89514</v>
+        <v>8.881769999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>7.6262</v>
+        <v>7.59728</v>
       </c>
       <c r="D115" t="n">
-        <v>38.0822</v>
+        <v>37.9615</v>
       </c>
       <c r="E115" t="n">
-        <v>5.74835</v>
+        <v>6.03645</v>
       </c>
       <c r="F115" t="n">
-        <v>8.83399</v>
+        <v>8.88396</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>9.22743</v>
+        <v>9.280559999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>7.95349</v>
+        <v>7.93126</v>
       </c>
       <c r="D116" t="n">
-        <v>39.4234</v>
+        <v>39.2403</v>
       </c>
       <c r="E116" t="n">
-        <v>5.94755</v>
+        <v>6.23048</v>
       </c>
       <c r="F116" t="n">
-        <v>9.158659999999999</v>
+        <v>9.1967</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>9.69478</v>
+        <v>9.69007</v>
       </c>
       <c r="C117" t="n">
-        <v>8.382389999999999</v>
+        <v>8.37228</v>
       </c>
       <c r="D117" t="n">
-        <v>40.458</v>
+        <v>40.3808</v>
       </c>
       <c r="E117" t="n">
-        <v>6.1886</v>
+        <v>6.45765</v>
       </c>
       <c r="F117" t="n">
-        <v>9.566229999999999</v>
+        <v>9.57132</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>10.2797</v>
+        <v>10.2573</v>
       </c>
       <c r="C118" t="n">
-        <v>8.953440000000001</v>
+        <v>8.91804</v>
       </c>
       <c r="D118" t="n">
-        <v>41.619</v>
+        <v>41.5556</v>
       </c>
       <c r="E118" t="n">
-        <v>6.48375</v>
+        <v>6.76051</v>
       </c>
       <c r="F118" t="n">
-        <v>10.0552</v>
+        <v>10.0753</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>11.0263</v>
+        <v>11.0011</v>
       </c>
       <c r="C119" t="n">
-        <v>9.75116</v>
+        <v>9.66394</v>
       </c>
       <c r="D119" t="n">
-        <v>43.0049</v>
+        <v>42.7728</v>
       </c>
       <c r="E119" t="n">
-        <v>4.83238</v>
+        <v>5.09914</v>
       </c>
       <c r="F119" t="n">
-        <v>6.93798</v>
+        <v>6.95569</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>12.0605</v>
+        <v>12.014</v>
       </c>
       <c r="C120" t="n">
-        <v>10.8053</v>
+        <v>10.7692</v>
       </c>
       <c r="D120" t="n">
-        <v>44.3832</v>
+        <v>44.3908</v>
       </c>
       <c r="E120" t="n">
-        <v>4.91665</v>
+        <v>5.18242</v>
       </c>
       <c r="F120" t="n">
-        <v>7.12532</v>
+        <v>7.15597</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.5344</v>
+        <v>13.4742</v>
       </c>
       <c r="C121" t="n">
-        <v>12.3743</v>
+        <v>12.2998</v>
       </c>
       <c r="D121" t="n">
-        <v>33.0554</v>
+        <v>33.2699</v>
       </c>
       <c r="E121" t="n">
-        <v>5.05389</v>
+        <v>5.30083</v>
       </c>
       <c r="F121" t="n">
-        <v>7.34034</v>
+        <v>7.34474</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>15.7318</v>
+        <v>15.6619</v>
       </c>
       <c r="C122" t="n">
-        <v>6.76183</v>
+        <v>6.73309</v>
       </c>
       <c r="D122" t="n">
-        <v>34.1191</v>
+        <v>33.9639</v>
       </c>
       <c r="E122" t="n">
-        <v>5.13184</v>
+        <v>5.40453</v>
       </c>
       <c r="F122" t="n">
-        <v>7.54121</v>
+        <v>7.56018</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>19.226</v>
+        <v>18.9913</v>
       </c>
       <c r="C123" t="n">
-        <v>6.88571</v>
+        <v>6.86919</v>
       </c>
       <c r="D123" t="n">
-        <v>34.9589</v>
+        <v>34.9704</v>
       </c>
       <c r="E123" t="n">
-        <v>5.26706</v>
+        <v>5.50672</v>
       </c>
       <c r="F123" t="n">
-        <v>7.77684</v>
+        <v>7.78167</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>8.00475</v>
+        <v>8.034979999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>7.0461</v>
+        <v>7.01839</v>
       </c>
       <c r="D124" t="n">
-        <v>35.8943</v>
+        <v>35.8276</v>
       </c>
       <c r="E124" t="n">
-        <v>5.3751</v>
+        <v>5.6495</v>
       </c>
       <c r="F124" t="n">
-        <v>7.98209</v>
+        <v>8.019869999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>8.22695</v>
+        <v>8.23747</v>
       </c>
       <c r="C125" t="n">
-        <v>7.18943</v>
+        <v>7.20127</v>
       </c>
       <c r="D125" t="n">
-        <v>36.7308</v>
+        <v>36.787</v>
       </c>
       <c r="E125" t="n">
-        <v>5.52157</v>
+        <v>5.7689</v>
       </c>
       <c r="F125" t="n">
-        <v>8.2685</v>
+        <v>8.28036</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>8.45064</v>
+        <v>8.42</v>
       </c>
       <c r="C126" t="n">
-        <v>7.35226</v>
+        <v>7.32743</v>
       </c>
       <c r="D126" t="n">
-        <v>37.7276</v>
+        <v>37.8395</v>
       </c>
       <c r="E126" t="n">
-        <v>5.64962</v>
+        <v>5.90881</v>
       </c>
       <c r="F126" t="n">
-        <v>8.53829</v>
+        <v>8.530939999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>8.69848</v>
+        <v>8.66446</v>
       </c>
       <c r="C127" t="n">
-        <v>7.5314</v>
+        <v>7.51151</v>
       </c>
       <c r="D127" t="n">
-        <v>38.6511</v>
+        <v>38.6264</v>
       </c>
       <c r="E127" t="n">
-        <v>5.81717</v>
+        <v>6.05699</v>
       </c>
       <c r="F127" t="n">
-        <v>8.82799</v>
+        <v>8.87327</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>8.96771</v>
+        <v>8.94928</v>
       </c>
       <c r="C128" t="n">
-        <v>7.77064</v>
+        <v>7.73437</v>
       </c>
       <c r="D128" t="n">
-        <v>39.7265</v>
+        <v>39.6775</v>
       </c>
       <c r="E128" t="n">
-        <v>5.98118</v>
+        <v>6.2014</v>
       </c>
       <c r="F128" t="n">
-        <v>9.13317</v>
+        <v>9.152010000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>9.237130000000001</v>
+        <v>9.25381</v>
       </c>
       <c r="C129" t="n">
-        <v>8.02505</v>
+        <v>8.00029</v>
       </c>
       <c r="D129" t="n">
-        <v>40.9186</v>
+        <v>40.7565</v>
       </c>
       <c r="E129" t="n">
-        <v>6.16535</v>
+        <v>6.36763</v>
       </c>
       <c r="F129" t="n">
-        <v>9.45049</v>
+        <v>9.471030000000001</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>9.629099999999999</v>
+        <v>9.626989999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>8.386279999999999</v>
+        <v>8.329140000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>41.9882</v>
+        <v>41.9053</v>
       </c>
       <c r="E130" t="n">
-        <v>6.37796</v>
+        <v>6.59088</v>
       </c>
       <c r="F130" t="n">
-        <v>9.815060000000001</v>
+        <v>9.832940000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>10.062</v>
+        <v>10.0405</v>
       </c>
       <c r="C131" t="n">
-        <v>8.800610000000001</v>
+        <v>8.766859999999999</v>
       </c>
       <c r="D131" t="n">
-        <v>43.076</v>
+        <v>43.1657</v>
       </c>
       <c r="E131" t="n">
-        <v>6.62936</v>
+        <v>6.85134</v>
       </c>
       <c r="F131" t="n">
-        <v>10.2374</v>
+        <v>10.3048</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>10.623</v>
+        <v>10.6242</v>
       </c>
       <c r="C132" t="n">
-        <v>9.38036</v>
+        <v>9.3133</v>
       </c>
       <c r="D132" t="n">
-        <v>44.4168</v>
+        <v>44.297</v>
       </c>
       <c r="E132" t="n">
-        <v>6.91138</v>
+        <v>7.14263</v>
       </c>
       <c r="F132" t="n">
-        <v>10.7545</v>
+        <v>10.7811</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>11.3633</v>
+        <v>11.3526</v>
       </c>
       <c r="C133" t="n">
-        <v>10.1287</v>
+        <v>10.0678</v>
       </c>
       <c r="D133" t="n">
-        <v>45.6242</v>
+        <v>45.4382</v>
       </c>
       <c r="E133" t="n">
-        <v>7.35687</v>
+        <v>7.55055</v>
       </c>
       <c r="F133" t="n">
-        <v>11.3387</v>
+        <v>11.3867</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>12.3751</v>
+        <v>12.337</v>
       </c>
       <c r="C134" t="n">
-        <v>11.192</v>
+        <v>11.116</v>
       </c>
       <c r="D134" t="n">
-        <v>46.823</v>
+        <v>46.7865</v>
       </c>
       <c r="E134" t="n">
-        <v>10.8444</v>
+        <v>10.9642</v>
       </c>
       <c r="F134" t="n">
-        <v>13.2837</v>
+        <v>13.3372</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.7743</v>
+        <v>13.7257</v>
       </c>
       <c r="C135" t="n">
-        <v>12.7197</v>
+        <v>12.6046</v>
       </c>
       <c r="D135" t="n">
-        <v>34.5495</v>
+        <v>34.6361</v>
       </c>
       <c r="E135" t="n">
-        <v>10.9665</v>
+        <v>11.1212</v>
       </c>
       <c r="F135" t="n">
-        <v>13.5463</v>
+        <v>13.5908</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>15.8241</v>
+        <v>15.7986</v>
       </c>
       <c r="C136" t="n">
-        <v>15.4222</v>
+        <v>15.3319</v>
       </c>
       <c r="D136" t="n">
-        <v>35.4016</v>
+        <v>35.6059</v>
       </c>
       <c r="E136" t="n">
-        <v>11.0212</v>
+        <v>11.2332</v>
       </c>
       <c r="F136" t="n">
-        <v>13.703</v>
+        <v>13.7146</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>19.0738</v>
+        <v>18.932</v>
       </c>
       <c r="C137" t="n">
-        <v>15.5221</v>
+        <v>15.4717</v>
       </c>
       <c r="D137" t="n">
-        <v>36.3756</v>
+        <v>36.4284</v>
       </c>
       <c r="E137" t="n">
-        <v>11.1663</v>
+        <v>11.2998</v>
       </c>
       <c r="F137" t="n">
-        <v>13.9511</v>
+        <v>13.9978</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>13.8239</v>
+        <v>13.7689</v>
       </c>
       <c r="C138" t="n">
-        <v>15.6343</v>
+        <v>15.6435</v>
       </c>
       <c r="D138" t="n">
-        <v>37.2189</v>
+        <v>37.3606</v>
       </c>
       <c r="E138" t="n">
-        <v>11.2485</v>
+        <v>11.3908</v>
       </c>
       <c r="F138" t="n">
-        <v>14.2385</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>14.001</v>
+        <v>13.9998</v>
       </c>
       <c r="C139" t="n">
-        <v>15.8202</v>
+        <v>15.9364</v>
       </c>
       <c r="D139" t="n">
-        <v>38.1623</v>
+        <v>38.1724</v>
       </c>
       <c r="E139" t="n">
-        <v>11.4464</v>
+        <v>11.5124</v>
       </c>
       <c r="F139" t="n">
-        <v>14.4468</v>
+        <v>14.4715</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.9778</v>
+        <v>14.1214</v>
       </c>
       <c r="C140" t="n">
-        <v>16.0193</v>
+        <v>15.9985</v>
       </c>
       <c r="D140" t="n">
-        <v>39.1382</v>
+        <v>39.1718</v>
       </c>
       <c r="E140" t="n">
-        <v>11.5655</v>
+        <v>11.6391</v>
       </c>
       <c r="F140" t="n">
-        <v>14.6997</v>
+        <v>14.7088</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>14.2843</v>
+        <v>14.2719</v>
       </c>
       <c r="C141" t="n">
-        <v>16.1068</v>
+        <v>16.2943</v>
       </c>
       <c r="D141" t="n">
-        <v>40.24</v>
+        <v>40.3107</v>
       </c>
       <c r="E141" t="n">
-        <v>11.6437</v>
+        <v>11.7174</v>
       </c>
       <c r="F141" t="n">
-        <v>14.9925</v>
+        <v>14.9588</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>14.5938</v>
+        <v>14.5765</v>
       </c>
       <c r="C142" t="n">
-        <v>16.3318</v>
+        <v>16.3907</v>
       </c>
       <c r="D142" t="n">
-        <v>41.2368</v>
+        <v>41.2893</v>
       </c>
       <c r="E142" t="n">
-        <v>11.8013</v>
+        <v>11.8468</v>
       </c>
       <c r="F142" t="n">
-        <v>15.2833</v>
+        <v>15.2803</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>14.6579</v>
+        <v>14.7121</v>
       </c>
       <c r="C143" t="n">
-        <v>16.6356</v>
+        <v>16.6179</v>
       </c>
       <c r="D143" t="n">
-        <v>42.3033</v>
+        <v>42.171</v>
       </c>
       <c r="E143" t="n">
-        <v>11.9953</v>
+        <v>12.0176</v>
       </c>
       <c r="F143" t="n">
-        <v>15.6626</v>
+        <v>15.6109</v>
       </c>
     </row>
   </sheetData>
